--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -12,14 +12,14 @@
     <sheet name="changes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="summary" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="comparison" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Vivo" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Claro" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TIM" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Ranking" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Vivo" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Claro" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TIM" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$T$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$T$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'changes'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -58,11 +58,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00808080"/>
       <sz val="9"/>
@@ -70,10 +65,15 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="001F3864"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -85,8 +85,23 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F5FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -94,28 +109,73 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -186,6 +246,887 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Control — cheapest R$ over time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!B36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="0033A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$B$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!C36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="660099"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$C$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!D36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="DA291C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$D$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>R$</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Post — cheapest R$ over time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!E36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="0033A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$E$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!F36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="660099"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$F$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!G36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="DA291C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$G$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>R$</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Pre — cheapest R$ over time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!H36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="0033A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$H$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!I36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="660099"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$I$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!J36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="DA291C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$J$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>R$</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Digital — cheapest R$ over time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!K36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="0033A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$K$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!L36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="660099"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$L$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!M36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="DA291C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$M$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>R$</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4140000" cy="2592000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4140000" cy="2592000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4140000" cy="2592000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4140000" cy="2592000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -474,6 +1415,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008A8A8A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -612,7 +1554,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -681,70 +1623,70 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Controle 30GB</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>claro:plano-controle-30gb</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="4" t="n">
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/controle</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_control_SP.json</t>
         </is>
@@ -758,7 +1700,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -821,70 +1763,70 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>flex</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Flex 15GB</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>claro:plano-flex-15gb</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="6" t="n">
         <v>44.9</v>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="4" t="n">
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="S5" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/flex</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="T5" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_flex_SP.json</t>
         </is>
@@ -898,7 +1840,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -961,70 +1903,70 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>flex</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Flex 30GB</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>claro:plano-flex-30gb</t>
         </is>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="4" t="n">
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/flex</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_flex_SP.json</t>
         </is>
@@ -1038,7 +1980,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1101,70 +2043,70 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Pós 100GB</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>claro:plano-pos-100gb</t>
         </is>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="6" t="n">
         <v>179.9</v>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="4" t="n">
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S9" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/pos</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="T9" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_postpaid_SP.json</t>
         </is>
@@ -1178,7 +2120,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1241,70 +2183,70 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Pós 200GB</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>claro:plano-pos-200gb</t>
         </is>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="6" t="n">
         <v>339.9</v>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="4" t="n">
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="S11" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/pos</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T11" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_postpaid_SP.json</t>
         </is>
@@ -1318,7 +2260,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1381,70 +2323,70 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Pós 60GB</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>claro:plano-pos-60gb</t>
         </is>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="6" t="n">
         <v>124.9</v>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="4" t="n">
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="S13" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/pos</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="T13" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_postpaid_SP.json</t>
         </is>
@@ -1458,7 +2400,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1517,62 +2459,62 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>TIM Controle 41GB</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>tim:162901</t>
         </is>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="6" t="n">
         <v>58.99</v>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="n">
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="T15" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_control_SP.html</t>
         </is>
@@ -1586,7 +2528,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1641,62 +2583,62 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Plus 45GB</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>tim:155891</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" s="6" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="4" t="n">
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="T17" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_control_SP.html</t>
         </is>
@@ -1710,7 +2652,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1765,60 +2707,60 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Pro Express</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>tim:143576</t>
         </is>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="6" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="T19" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_control_SP.html</t>
         </is>
@@ -1832,7 +2774,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1887,62 +2829,62 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>TIM Black A Express 67GB</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>tim:55121</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" s="6" t="n">
         <v>119.99</v>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="4" t="n">
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_postpaid_SP.html</t>
         </is>
@@ -1956,7 +2898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2011,62 +2953,62 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>TIM Black C Express 107GB</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>tim:52151</t>
         </is>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" s="6" t="n">
         <v>164.99</v>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="4" t="n">
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="T23" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_postpaid_SP.html</t>
         </is>
@@ -2080,7 +3022,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2135,62 +3077,62 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>TIM Black Plus 80GB</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>tim:54256</t>
         </is>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" s="6" t="n">
         <v>149.99</v>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="4" t="n">
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr"/>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
         </is>
       </c>
-      <c r="T25" s="2" t="inlineStr">
+      <c r="T25" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_postpaid_SP.html</t>
         </is>
@@ -2204,7 +3146,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2259,62 +3201,62 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 16GB</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>tim:106306</t>
         </is>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="4" t="n">
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
-      <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
-      <c r="S27" s="2" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
+      <c r="T27" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_prepaid_SP.html</t>
         </is>
@@ -2328,7 +3270,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2383,62 +3325,62 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 8GB</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>tim:59901</t>
         </is>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="4" t="n">
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="T29" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_prepaid_SP.html</t>
         </is>
@@ -2452,7 +3394,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2515,70 +3457,70 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029300-51gb</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 31 GB de bônus</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr">
         <is>
           <t>6 meses grátis de Gemini com AI Plus</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="S31" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="T31" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_control_SP.html</t>
         </is>
@@ -2592,7 +3534,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2617,16 +3559,16 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029273-51gb</t>
+          <t>vivo:VIV202600029273-61gb</t>
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
@@ -2655,70 +3597,70 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle Entretenimento</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029307-51gb</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 31 GB de bônus</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr"/>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+      <c r="R33" s="5" t="inlineStr">
         <is>
           <t>Assinatura Vivo TV Inicial inclusa</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="S33" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="T33" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_control_SP.html</t>
         </is>
@@ -2732,7 +3674,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2757,16 +3699,16 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029313-51gb</t>
+          <t>vivo:VIV202600029313-61gb</t>
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
@@ -2795,70 +3737,70 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle Netflix</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029308-51gb</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 31 GB de bônus</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" s="2" t="inlineStr"/>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+      <c r="R35" s="5" t="inlineStr">
         <is>
           <t>Assinatura Netflix Padrão com anúncios</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="S35" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="T35" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_control_SP.html</t>
         </is>
@@ -2872,7 +3814,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2897,16 +3839,16 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029301-51gb</t>
+          <t>vivo:VIV202600029301-61gb</t>
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
@@ -2935,66 +3877,66 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>lite</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600005312-30gb</t>
         </is>
       </c>
-      <c r="H37" s="3" t="n">
+      <c r="H37" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="4" t="n">
+      <c r="I37" s="6" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>30 GB de franquia 2 Meses de YouTube ilimitado</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr"/>
+      <c r="O37" s="5" t="inlineStr"/>
+      <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr"/>
+      <c r="R37" s="5" t="inlineStr"/>
+      <c r="S37" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
         </is>
       </c>
-      <c r="T37" s="2" t="inlineStr">
+      <c r="T37" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_lite_SP.html</t>
         </is>
@@ -3008,7 +3950,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3067,66 +4009,66 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>lite</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600019132-20gb</t>
         </is>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="H39" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="4" t="n">
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 2 Meses de YouTube ilimitado</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr"/>
+      <c r="O39" s="5" t="inlineStr"/>
+      <c r="P39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr"/>
+      <c r="R39" s="5" t="inlineStr"/>
+      <c r="S39" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
         </is>
       </c>
-      <c r="T39" s="2" t="inlineStr">
+      <c r="T39" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_lite_SP.html</t>
         </is>
@@ -3140,7 +4082,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3195,62 +4137,62 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>lite</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600019129-40gb</t>
         </is>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="H41" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="4" t="n">
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" s="2" t="inlineStr"/>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr"/>
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr"/>
+      <c r="O41" s="5" t="inlineStr"/>
+      <c r="P41" s="5" t="inlineStr"/>
+      <c r="Q41" s="5" t="inlineStr"/>
+      <c r="R41" s="5" t="inlineStr"/>
+      <c r="S41" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
         </is>
       </c>
-      <c r="T41" s="2" t="inlineStr">
+      <c r="T41" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_lite_SP.html</t>
         </is>
@@ -3264,7 +4206,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3327,74 +4269,74 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Disney+</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600022115-60gb</t>
         </is>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="4" t="n">
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>50 GB de franquia 10 GB de bônus</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="5" t="inlineStr"/>
+      <c r="P43" s="5" t="inlineStr">
         <is>
           <t>Disney+</t>
         </is>
       </c>
-      <c r="Q43" s="2" t="inlineStr"/>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="Q43" s="5" t="inlineStr"/>
+      <c r="R43" s="5" t="inlineStr">
         <is>
           <t>Assinatura Disney+ Padrão inclusa</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr">
+      <c r="S43" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
-      <c r="T43" s="2" t="inlineStr">
+      <c r="T43" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
@@ -3408,7 +4350,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3475,74 +4417,74 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Netflix</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600029234-60gb</t>
         </is>
       </c>
-      <c r="H45" s="3" t="n">
+      <c r="H45" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="4" t="n">
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="5" t="inlineStr"/>
+      <c r="K45" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>50 GB de franquia 10 GB de bônus</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr"/>
-      <c r="P45" s="2" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr"/>
+      <c r="O45" s="5" t="inlineStr"/>
+      <c r="P45" s="5" t="inlineStr">
         <is>
           <t>Netflix</t>
         </is>
       </c>
-      <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr">
+      <c r="Q45" s="5" t="inlineStr"/>
+      <c r="R45" s="5" t="inlineStr">
         <is>
           <t>Assinatura Netflix Padrão inclusa</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr">
+      <c r="S45" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
-      <c r="T45" s="2" t="inlineStr">
+      <c r="T45" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
@@ -3556,7 +4498,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3623,74 +4565,74 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Spotify</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600029229-60gb</t>
         </is>
       </c>
-      <c r="H47" s="3" t="n">
+      <c r="H47" s="6" t="n">
         <v>165</v>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="4" t="n">
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>50 GB de franquia 10 GB de bônus</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" s="2" t="inlineStr">
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="5" t="inlineStr"/>
+      <c r="P47" s="5" t="inlineStr">
         <is>
           <t>Spotify</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="inlineStr"/>
-      <c r="R47" s="2" t="inlineStr">
+      <c r="Q47" s="5" t="inlineStr"/>
+      <c r="R47" s="5" t="inlineStr">
         <is>
           <t>Assinatura Spotify Premium inclusa</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr">
+      <c r="S47" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
-      <c r="T47" s="2" t="inlineStr">
+      <c r="T47" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
@@ -3704,7 +4646,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3767,66 +4709,66 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600022379-25gb</t>
         </is>
       </c>
-      <c r="H49" s="3" t="n">
+      <c r="H49" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="4" t="n">
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr"/>
+      <c r="K49" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
-      <c r="O49" s="2" t="inlineStr"/>
-      <c r="P49" s="2" t="inlineStr"/>
-      <c r="Q49" s="2" t="inlineStr"/>
-      <c r="R49" s="2" t="inlineStr"/>
-      <c r="S49" s="2" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr"/>
+      <c r="O49" s="5" t="inlineStr"/>
+      <c r="P49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr"/>
+      <c r="R49" s="5" t="inlineStr"/>
+      <c r="S49" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
         </is>
       </c>
-      <c r="T49" s="2" t="inlineStr">
+      <c r="T49" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_prepaid_SP.html</t>
         </is>
@@ -3840,7 +4782,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3899,66 +4841,66 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600022379-5gb</t>
         </is>
       </c>
-      <c r="H51" s="3" t="n">
+      <c r="H51" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="4" t="n">
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr"/>
+      <c r="K51" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>5 GB para navegar como quiser</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr"/>
-      <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" s="2" t="inlineStr"/>
-      <c r="Q51" s="2" t="inlineStr"/>
-      <c r="R51" s="2" t="inlineStr"/>
-      <c r="S51" s="2" t="inlineStr">
+      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr"/>
+      <c r="O51" s="5" t="inlineStr"/>
+      <c r="P51" s="5" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr"/>
+      <c r="R51" s="5" t="inlineStr"/>
+      <c r="S51" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
         </is>
       </c>
-      <c r="T51" s="2" t="inlineStr">
+      <c r="T51" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_prepaid_SP.html</t>
         </is>
@@ -3972,7 +4914,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4039,6 +4981,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008A8A8A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4177,7 +5120,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -4246,70 +5189,70 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Controle 30GB</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>claro:plano-controle-30gb</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="4" t="n">
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/controle</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_control_SP.json</t>
         </is>
@@ -4323,7 +5266,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -4386,70 +5329,70 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>flex</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Flex 15GB</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>claro:plano-flex-15gb</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="6" t="n">
         <v>44.9</v>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="4" t="n">
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="S5" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/flex</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="T5" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_flex_SP.json</t>
         </is>
@@ -4463,7 +5406,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -4526,70 +5469,70 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>flex</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Flex 30GB</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>claro:plano-flex-30gb</t>
         </is>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="4" t="n">
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/flex</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_flex_SP.json</t>
         </is>
@@ -4603,7 +5546,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -4666,70 +5609,70 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Pós 100GB</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>claro:plano-pos-100gb</t>
         </is>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="6" t="n">
         <v>179.9</v>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="4" t="n">
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S9" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/pos</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="T9" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_postpaid_SP.json</t>
         </is>
@@ -4743,7 +5686,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4806,70 +5749,70 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Pós 200GB</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>claro:plano-pos-200gb</t>
         </is>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="6" t="n">
         <v>339.9</v>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="4" t="n">
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="S11" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/pos</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T11" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_postpaid_SP.json</t>
         </is>
@@ -4883,7 +5826,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -4946,70 +5889,70 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Pós 60GB</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>claro:plano-pos-60gb</t>
         </is>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="6" t="n">
         <v>124.9</v>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="4" t="n">
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="S13" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/pos</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="T13" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_postpaid_SP.json</t>
         </is>
@@ -5023,7 +5966,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -5082,62 +6025,62 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>TIM Controle 41GB</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>tim:162901</t>
         </is>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="6" t="n">
         <v>58.99</v>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="n">
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="T15" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_control_SP.html</t>
         </is>
@@ -5151,7 +6094,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5206,62 +6149,62 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Plus 45GB</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>tim:155891</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" s="6" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="4" t="n">
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="T17" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_control_SP.html</t>
         </is>
@@ -5275,7 +6218,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -5330,60 +6273,60 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Pro Express</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>tim:143576</t>
         </is>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="6" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="T19" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_control_SP.html</t>
         </is>
@@ -5397,7 +6340,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -5452,62 +6395,62 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>TIM Black A Express 67GB</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>tim:55121</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" s="6" t="n">
         <v>119.99</v>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="4" t="n">
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_postpaid_SP.html</t>
         </is>
@@ -5521,7 +6464,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -5576,62 +6519,62 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>TIM Black C Express 107GB</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>tim:52151</t>
         </is>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" s="6" t="n">
         <v>164.99</v>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="4" t="n">
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="T23" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_postpaid_SP.html</t>
         </is>
@@ -5645,7 +6588,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -5700,62 +6643,62 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>TIM Black Plus 80GB</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>tim:54256</t>
         </is>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" s="6" t="n">
         <v>149.99</v>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="4" t="n">
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr"/>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
         </is>
       </c>
-      <c r="T25" s="2" t="inlineStr">
+      <c r="T25" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_postpaid_SP.html</t>
         </is>
@@ -5769,7 +6712,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -5824,62 +6767,62 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 16GB</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>tim:106306</t>
         </is>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="4" t="n">
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
-      <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
-      <c r="S27" s="2" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
+      <c r="T27" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_prepaid_SP.html</t>
         </is>
@@ -5893,7 +6836,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -5948,62 +6891,62 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 8GB</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>tim:59901</t>
         </is>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="4" t="n">
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="T29" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_prepaid_SP.html</t>
         </is>
@@ -6017,7 +6960,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -6080,70 +7023,70 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029300-51gb</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 31 GB de bônus</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr">
         <is>
           <t>6 meses grátis de Gemini com AI Plus</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="S31" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="T31" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_control_SP.html</t>
         </is>
@@ -6157,7 +7100,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -6182,16 +7125,16 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029273-51gb</t>
+          <t>vivo:VIV202600029273-61gb</t>
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
@@ -6220,70 +7163,70 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle Entretenimento</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029307-51gb</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 31 GB de bônus</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr"/>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+      <c r="R33" s="5" t="inlineStr">
         <is>
           <t>Assinatura Vivo TV Inicial inclusa</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="S33" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="T33" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_control_SP.html</t>
         </is>
@@ -6297,7 +7240,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -6322,16 +7265,16 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029313-51gb</t>
+          <t>vivo:VIV202600029313-61gb</t>
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
@@ -6360,70 +7303,70 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle Netflix</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029308-51gb</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 31 GB de bônus</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" s="2" t="inlineStr"/>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+      <c r="R35" s="5" t="inlineStr">
         <is>
           <t>Assinatura Netflix Padrão com anúncios</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="S35" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="T35" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_control_SP.html</t>
         </is>
@@ -6437,7 +7380,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -6462,16 +7405,16 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029301-51gb</t>
+          <t>vivo:VIV202600029301-61gb</t>
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
@@ -6500,66 +7443,66 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>lite</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600005312-30gb</t>
         </is>
       </c>
-      <c r="H37" s="3" t="n">
+      <c r="H37" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="4" t="n">
+      <c r="I37" s="6" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>30 GB de franquia 2 Meses de YouTube ilimitado</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr"/>
+      <c r="O37" s="5" t="inlineStr"/>
+      <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr"/>
+      <c r="R37" s="5" t="inlineStr"/>
+      <c r="S37" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
         </is>
       </c>
-      <c r="T37" s="2" t="inlineStr">
+      <c r="T37" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_lite_SP.html</t>
         </is>
@@ -6573,7 +7516,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -6632,66 +7575,66 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>lite</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600019132-20gb</t>
         </is>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="H39" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="4" t="n">
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 2 Meses de YouTube ilimitado</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr"/>
+      <c r="O39" s="5" t="inlineStr"/>
+      <c r="P39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr"/>
+      <c r="R39" s="5" t="inlineStr"/>
+      <c r="S39" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
         </is>
       </c>
-      <c r="T39" s="2" t="inlineStr">
+      <c r="T39" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_lite_SP.html</t>
         </is>
@@ -6705,7 +7648,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -6760,62 +7703,62 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>lite</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600019129-40gb</t>
         </is>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="H41" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="4" t="n">
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" s="2" t="inlineStr"/>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr"/>
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr"/>
+      <c r="O41" s="5" t="inlineStr"/>
+      <c r="P41" s="5" t="inlineStr"/>
+      <c r="Q41" s="5" t="inlineStr"/>
+      <c r="R41" s="5" t="inlineStr"/>
+      <c r="S41" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
         </is>
       </c>
-      <c r="T41" s="2" t="inlineStr">
+      <c r="T41" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_lite_SP.html</t>
         </is>
@@ -6829,7 +7772,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -6892,74 +7835,74 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Disney+</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600022115-60gb</t>
         </is>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="4" t="n">
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>50 GB de franquia 10 GB de bônus</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="5" t="inlineStr"/>
+      <c r="P43" s="5" t="inlineStr">
         <is>
           <t>Disney+</t>
         </is>
       </c>
-      <c r="Q43" s="2" t="inlineStr"/>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="Q43" s="5" t="inlineStr"/>
+      <c r="R43" s="5" t="inlineStr">
         <is>
           <t>Assinatura Disney+ Padrão inclusa</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr">
+      <c r="S43" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
-      <c r="T43" s="2" t="inlineStr">
+      <c r="T43" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
@@ -6973,7 +7916,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -7040,74 +7983,74 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Netflix</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600029234-60gb</t>
         </is>
       </c>
-      <c r="H45" s="3" t="n">
+      <c r="H45" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="4" t="n">
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="5" t="inlineStr"/>
+      <c r="K45" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>50 GB de franquia 10 GB de bônus</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr"/>
-      <c r="P45" s="2" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr"/>
+      <c r="O45" s="5" t="inlineStr"/>
+      <c r="P45" s="5" t="inlineStr">
         <is>
           <t>Netflix</t>
         </is>
       </c>
-      <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr">
+      <c r="Q45" s="5" t="inlineStr"/>
+      <c r="R45" s="5" t="inlineStr">
         <is>
           <t>Assinatura Netflix Padrão inclusa</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr">
+      <c r="S45" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
-      <c r="T45" s="2" t="inlineStr">
+      <c r="T45" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
@@ -7121,7 +8064,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -7188,74 +8131,74 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Spotify</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600029229-60gb</t>
         </is>
       </c>
-      <c r="H47" s="3" t="n">
+      <c r="H47" s="6" t="n">
         <v>165</v>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="4" t="n">
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>50 GB de franquia 10 GB de bônus</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" s="2" t="inlineStr">
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="5" t="inlineStr"/>
+      <c r="P47" s="5" t="inlineStr">
         <is>
           <t>Spotify</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="inlineStr"/>
-      <c r="R47" s="2" t="inlineStr">
+      <c r="Q47" s="5" t="inlineStr"/>
+      <c r="R47" s="5" t="inlineStr">
         <is>
           <t>Assinatura Spotify Premium inclusa</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr">
+      <c r="S47" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
-      <c r="T47" s="2" t="inlineStr">
+      <c r="T47" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
@@ -7269,7 +8212,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -7332,66 +8275,66 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600022379-25gb</t>
         </is>
       </c>
-      <c r="H49" s="3" t="n">
+      <c r="H49" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="4" t="n">
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr"/>
+      <c r="K49" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
-      <c r="O49" s="2" t="inlineStr"/>
-      <c r="P49" s="2" t="inlineStr"/>
-      <c r="Q49" s="2" t="inlineStr"/>
-      <c r="R49" s="2" t="inlineStr"/>
-      <c r="S49" s="2" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr"/>
+      <c r="O49" s="5" t="inlineStr"/>
+      <c r="P49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr"/>
+      <c r="R49" s="5" t="inlineStr"/>
+      <c r="S49" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
         </is>
       </c>
-      <c r="T49" s="2" t="inlineStr">
+      <c r="T49" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_prepaid_SP.html</t>
         </is>
@@ -7405,7 +8348,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -7464,66 +8407,66 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600022379-5gb</t>
         </is>
       </c>
-      <c r="H51" s="3" t="n">
+      <c r="H51" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="4" t="n">
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr"/>
+      <c r="K51" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>5 GB para navegar como quiser</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr"/>
-      <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" s="2" t="inlineStr"/>
-      <c r="Q51" s="2" t="inlineStr"/>
-      <c r="R51" s="2" t="inlineStr"/>
-      <c r="S51" s="2" t="inlineStr">
+      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr"/>
+      <c r="O51" s="5" t="inlineStr"/>
+      <c r="P51" s="5" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr"/>
+      <c r="R51" s="5" t="inlineStr"/>
+      <c r="S51" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
         </is>
       </c>
-      <c r="T51" s="2" t="inlineStr">
+      <c r="T51" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_prepaid_SP.html</t>
         </is>
@@ -7537,7 +8480,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -7597,6 +8540,23 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:T52"/>
+  <conditionalFormatting sqref="H2:H52">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I52">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>NOT(ISBLANK(I2))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7604,6 +8564,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008A8A8A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7669,7 +8630,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7677,6 +8637,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00102A43"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7691,26 +8652,26 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Mobile Price Tracker — Summary</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Run timestamp</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Latest snapshot</t>
         </is>
@@ -7722,7 +8683,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Plans in latest</t>
         </is>
@@ -7732,7 +8693,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Snapshots in history</t>
         </is>
@@ -7742,27 +8703,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>carrier</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t># plans</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>min price</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>avg price</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>max price</t>
         </is>
@@ -7778,15 +8739,15 @@
         <f>COUNTIF(latest!$C$2:$C$2000,$A$9)</f>
         <v/>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="10">
         <f>IFERROR(_xlfn.MINIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
         <v/>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="10">
         <f>IFERROR(AVERAGEIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
         <v/>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="10">
         <f>IFERROR(_xlfn.MAXIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
         <v/>
       </c>
@@ -7801,15 +8762,15 @@
         <f>COUNTIF(latest!$C$2:$C$2000,$A$10)</f>
         <v/>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="10">
         <f>IFERROR(_xlfn.MINIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$10),"-")</f>
         <v/>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="10">
         <f>IFERROR(AVERAGEIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$10),"-")</f>
         <v/>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="10">
         <f>IFERROR(_xlfn.MAXIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$10),"-")</f>
         <v/>
       </c>
@@ -7824,15 +8785,15 @@
         <f>COUNTIF(latest!$C$2:$C$2000,$A$11)</f>
         <v/>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="10">
         <f>IFERROR(_xlfn.MINIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$11),"-")</f>
         <v/>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="10">
         <f>IFERROR(AVERAGEIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$11),"-")</f>
         <v/>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="10">
         <f>IFERROR(_xlfn.MAXIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$11),"-")</f>
         <v/>
       </c>
@@ -7845,6 +8806,260 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002E7D32"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Price evolution — cheapest R$ per carrier × category, by date</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Control (R$/mo)</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Post (R$/mo)</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Pre (R$, recarga)</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="n"/>
+      <c r="J35" s="11" t="n"/>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>Digital (R$/mo)</t>
+        </is>
+      </c>
+      <c r="L35" s="11" t="n"/>
+      <c r="M35" s="11" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="M36" s="11" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="C37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="D37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="E37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="F37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="G37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="H37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="I37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="J37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="K37" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,$A37),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,$A37),0)),"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,$A37),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,$A37),0)),"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,$A37),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,$A37),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Pre = cheapest recharge amount captured (true R$/day needs validity-days we don't yet capture — CONTEXT §8). Digital = min of Vivo Lite / Claro Flex. Daily rows now; monthly roll-up is the planned next step.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="H35:J35"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B37:D37">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E37:G37">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H37:J37">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K37:M37">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7861,51 +9076,51 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Cross-operator comparison — within category, aligned by price rank</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Ranking (today) — within category, aligned by price rank</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Pure Postpaid</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Vivo R$</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Claro R$</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>TIM R$</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Vivo plan</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Claro plan</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>TIM plan</t>
         </is>
@@ -7941,29 +9156,29 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="6" t="n">
         <v>165</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="6" t="n">
         <v>164.9</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="6" t="n">
         <v>129.99</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Globoplay (60GB)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Pós 50GB com GeForce NOW (50GB)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>TIM Black 70GB (70GB)</t>
         </is>
@@ -7999,29 +9214,29 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="6" t="n">
         <v>239.9</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="6" t="n">
         <v>149.99</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Disney+ (60GB)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Pós 150GB (150GB)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>TIM Black Plus 80GB (80GB)</t>
         </is>
@@ -8057,21 +9272,23 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="6" t="n">
         <v>159.99</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Premiere (60GB)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>TIM Black Premium 110GB (110GB)</t>
         </is>
@@ -8099,44 +9316,44 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Control / Hybrid</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>Vivo R$</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>Claro R$</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>TIM R$</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>Vivo plan</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>Claro plan</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>TIM plan</t>
         </is>
@@ -8172,29 +9389,29 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="C16" s="3" t="n">
+      <c r="B16" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C16" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="6" t="n">
         <v>60.99</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle (51GB)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle (61GB)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Controle 30GB (30GB)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Light Express 31GB (31GB)</t>
         </is>
@@ -8205,7 +9422,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>99.90000000000001</v>
@@ -8215,7 +9432,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Educação (51GB)</t>
+          <t>Vivo Controle Educação (61GB)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8230,21 +9447,23 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="D18" s="3" t="n">
+      <c r="B18" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="6" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Saúde (51GB)</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Saúde (61GB)</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Pro Express</t>
         </is>
@@ -8255,14 +9474,14 @@
         <v>5</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>84.98999999999999</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Música (51GB)</t>
+          <t>Vivo Controle Música (61GB)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8272,77 +9491,81 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Netflix (51GB)</t>
-        </is>
-      </c>
+      <c r="B20" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix (61GB)</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Entretenimento (51GB)</t>
+          <t>Vivo Controle Entretenimento (61GB)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Note: prepaid is not a clean unit — Claro Prezão is a daily fee (R$1/dia) vs Vivo/TIM recharge amounts.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>Vivo R$</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>Claro R$</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>TIM R$</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="1" t="inlineStr">
         <is>
           <t>Vivo plan</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>Claro plan</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>TIM plan</t>
         </is>
@@ -8378,21 +9601,23 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré (5GB)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 8GB (8GB)</t>
         </is>
@@ -8420,64 +9645,68 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré (25GB)</t>
         </is>
       </c>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Digital</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Digital = Vivo Lite + Claro Flex (TIM has no digital line).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>Vivo R$</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>Claro R$</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="1" t="inlineStr">
         <is>
           <t>TIM R$</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="1" t="inlineStr">
         <is>
           <t>Vivo plan</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="1" t="inlineStr">
         <is>
           <t>Claro plan</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>TIM plan</t>
         </is>
@@ -8505,25 +9734,27 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="6" t="n">
         <v>59.9</v>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Easy Lite (20GB)</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Flex 20GB (20GB)</t>
         </is>
       </c>
+      <c r="G35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -8547,25 +9778,27 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="6" t="n">
         <v>119.9</v>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Easy Lite (30GB)</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Flex 40GB (40GB)</t>
         </is>
       </c>
+      <c r="G37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -8581,13 +9814,74 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B5:D11">
+    <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
+      <formula>AND(B5&lt;&gt;"",B5=MIN($B5:$D5))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15:D21">
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>AND(B15&lt;&gt;"",B15=MIN($B15:$D15))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26:D29">
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
+      <formula>AND(B26&lt;&gt;"",B26=MIN($B26:$D26))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34:D38">
+    <cfRule type="expression" priority="7" dxfId="1" stopIfTrue="1">
+      <formula>AND(B34&lt;&gt;"",B34=MIN($B34:$D34))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00660099"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -8605,53 +9899,60 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Price R$</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Promo R$</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Voice</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unlimited apps</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Streaming</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Postpaid</t>
         </is>
       </c>
+      <c r="B2" s="16" t="n"/>
+      <c r="C2" s="16" t="n"/>
+      <c r="D2" s="16" t="n"/>
+      <c r="E2" s="16" t="n"/>
+      <c r="F2" s="16" t="n"/>
+      <c r="G2" s="16" t="n"/>
+      <c r="H2" s="16" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -8678,28 +9979,28 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Globoplay</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="6" t="n">
         <v>165</v>
       </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>60 GB (50 GB de franquia 10 GB de bônus)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Globoplay</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Assinatura Globoplay inclusa</t>
         </is>
@@ -8734,28 +10035,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Disney+</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>60 GB (50 GB de franquia 10 GB de bônus)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Disney+</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Assinatura Disney+ Padrão inclusa</t>
         </is>
@@ -8790,28 +10091,28 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Premiere</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>60 GB (50 GB de franquia 10 GB de bônus)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Premiere</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Assinatura Premiere inclusa</t>
         </is>
@@ -8842,11 +10143,18 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -8873,24 +10181,24 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="B12" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>6 meses grátis de Gemini com AI Plus</t>
         </is>
@@ -8903,12 +10211,12 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -8921,24 +10229,24 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle Saúde</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="B14" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Assinatura Vale Saúde Sempre inclusa</t>
         </is>
@@ -8951,12 +10259,12 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -8969,24 +10277,24 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle Netflix</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="B16" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Assinatura Netflix Padrão com anúncios</t>
         </is>
@@ -8999,12 +10307,12 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
@@ -9017,11 +10325,18 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Digital</t>
         </is>
       </c>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="16" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -9044,24 +10359,24 @@
       <c r="H19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>20 GB (20 GB de franquia 2 Meses de YouTube ilimitado)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -9084,24 +10399,24 @@
       <c r="H21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>30 GB</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -9124,11 +10439,18 @@
       <c r="H23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -9151,24 +10473,24 @@
       <c r="H25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>5 GB (5 GB para navegar como quiser)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -9191,33 +10513,82 @@
       <c r="H27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>25 GB (15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B3:B9">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B17">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B23">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25:B28">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00DA291C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -9235,53 +10606,60 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Price R$</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Promo R$</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Voice</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unlimited apps</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Streaming</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Postpaid</t>
         </is>
       </c>
+      <c r="B2" s="16" t="n"/>
+      <c r="C2" s="16" t="n"/>
+      <c r="D2" s="16" t="n"/>
+      <c r="E2" s="16" t="n"/>
+      <c r="F2" s="16" t="n"/>
+      <c r="G2" s="16" t="n"/>
+      <c r="H2" s="16" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -9312,28 +10690,28 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Pós 50GB com GeForce NOW</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="6" t="n">
         <v>164.9</v>
       </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>50 GB</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado; Inclusa assinatura GeForce NOW</t>
         </is>
@@ -9368,28 +10746,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Pós 150GB</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="6" t="n">
         <v>239.9</v>
       </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>150 GB</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas e Europa; Claro Sync: Smartwatch conectado</t>
         </is>
@@ -9424,11 +10802,18 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -9439,7 +10824,7 @@
       <c r="B9" s="3" t="n">
         <v>59.9</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="17" t="n">
         <v>54.9</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -9461,28 +10846,28 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Controle 30GB</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>30 GB</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
         </is>
@@ -9517,11 +10902,18 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Digital</t>
         </is>
       </c>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9552,28 +10944,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Flex 20GB</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="6" t="n">
         <v>59.9</v>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>20 GB</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
         </is>
@@ -9608,39 +11000,46 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Flex 40GB</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="6" t="n">
         <v>119.9</v>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>40 GB</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Para redes sociais e apps; Bônus uso livre; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -9667,13 +11066,62 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B3:B7">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9:B11">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:B16">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000033A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -9691,53 +11139,60 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Price R$</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Promo R$</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Voice</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unlimited apps</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Streaming</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Postpaid</t>
         </is>
       </c>
+      <c r="B2" s="16" t="n"/>
+      <c r="C2" s="16" t="n"/>
+      <c r="D2" s="16" t="n"/>
+      <c r="E2" s="16" t="n"/>
+      <c r="F2" s="16" t="n"/>
+      <c r="G2" s="16" t="n"/>
+      <c r="H2" s="16" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -9760,24 +11215,24 @@
       <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>TIM Black 70GB</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="6" t="n">
         <v>129.99</v>
       </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>70 GB</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -9800,24 +11255,24 @@
       <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>TIM Black Plus 80GB</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="6" t="n">
         <v>149.99</v>
       </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>80 GB</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -9840,24 +11295,24 @@
       <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>TIM Black Premium 110GB</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="6" t="n">
         <v>159.99</v>
       </c>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>110 GB</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -9880,11 +11335,18 @@
       <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -9907,24 +11369,24 @@
       <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Light Express 31GB</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="6" t="n">
         <v>60.99</v>
       </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>31 GB</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9947,20 +11409,20 @@
       <c r="H13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Pro Express</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="6" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -9983,11 +11445,18 @@
       <c r="H15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -10010,24 +11479,24 @@
       <c r="H17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 8GB</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>8 GB</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -10050,6 +11519,42 @@
       <c r="H19" s="2" t="n"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B3:B9">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B15">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17:B19">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
     </row>

--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -18,8 +18,8 @@
     <sheet name="TIM" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$T$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$T$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$T$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$T$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -296,12 +296,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37</f>
+              <f>'comparison'!$A$37:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$B$37</f>
+              <f>'comparison'!$B$37:$B$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -333,12 +333,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37</f>
+              <f>'comparison'!$A$37:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$C$37</f>
+              <f>'comparison'!$C$37:$C$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -370,12 +370,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37</f>
+              <f>'comparison'!$A$37:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$D$37</f>
+              <f>'comparison'!$D$37:$D$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -493,12 +493,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37</f>
+              <f>'comparison'!$A$37:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$E$37</f>
+              <f>'comparison'!$E$37:$E$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -530,12 +530,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37</f>
+              <f>'comparison'!$A$37:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$F$37</f>
+              <f>'comparison'!$F$37:$F$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -567,12 +567,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37</f>
+              <f>'comparison'!$A$37:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$G$37</f>
+              <f>'comparison'!$G$37:$G$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -690,12 +690,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37</f>
+              <f>'comparison'!$A$37:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$H$37</f>
+              <f>'comparison'!$H$37:$H$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -727,12 +727,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37</f>
+              <f>'comparison'!$A$37:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$I$37</f>
+              <f>'comparison'!$I$37:$I$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -764,12 +764,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37</f>
+              <f>'comparison'!$A$37:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$J$37</f>
+              <f>'comparison'!$J$37:$J$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -887,12 +887,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37</f>
+              <f>'comparison'!$A$37:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$K$37</f>
+              <f>'comparison'!$K$37:$K$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -924,12 +924,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37</f>
+              <f>'comparison'!$A$37:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$L$37</f>
+              <f>'comparison'!$L$37:$L$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -961,12 +961,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37</f>
+              <f>'comparison'!$A$37:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$M$37</f>
+              <f>'comparison'!$M$37:$M$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1419,7 +1419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T52"/>
+  <dimension ref="A1:T101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4972,8 +4972,3322 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Controle 25GB</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-25gb</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>De R$ 59,90 Por:</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="L53" s="5" t="inlineStr"/>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N53" s="5" t="inlineStr"/>
+      <c r="O53" s="5" t="inlineStr"/>
+      <c r="P53" s="5" t="inlineStr"/>
+      <c r="Q53" s="5" t="inlineStr"/>
+      <c r="R53" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e vídeos; Bônus exclusivo; Aproveite na sua franquia; WhatsApp e ligações ilimitadas</t>
+        </is>
+      </c>
+      <c r="S53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="T53" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb-gaming</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr"/>
+      <c r="J55" s="5" t="inlineStr"/>
+      <c r="K55" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N55" s="5" t="inlineStr"/>
+      <c r="O55" s="5" t="inlineStr"/>
+      <c r="P55" s="5" t="inlineStr"/>
+      <c r="Q55" s="5" t="inlineStr"/>
+      <c r="R55" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus para redes sociais e apps; Bônus uso livre; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="S55" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="T55" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Flex 15GB</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-15gb</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I56" s="3" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Flex 20GB</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-20gb</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr"/>
+      <c r="K57" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L57" s="5" t="inlineStr"/>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N57" s="5" t="inlineStr"/>
+      <c r="O57" s="5" t="inlineStr"/>
+      <c r="P57" s="5" t="inlineStr"/>
+      <c r="Q57" s="5" t="inlineStr"/>
+      <c r="R57" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="S57" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="T57" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Flex 30GB</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-30gb</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Flex 40GB</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-40gb</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr"/>
+      <c r="J59" s="5" t="inlineStr"/>
+      <c r="K59" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L59" s="5" t="inlineStr"/>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N59" s="5" t="inlineStr"/>
+      <c r="O59" s="5" t="inlineStr"/>
+      <c r="P59" s="5" t="inlineStr"/>
+      <c r="Q59" s="5" t="inlineStr"/>
+      <c r="R59" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e apps; Bônus uso livre; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="S59" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="T59" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Pós 100GB</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-100gb</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Pós 150GB</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-150gb</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr"/>
+      <c r="J61" s="5" t="inlineStr"/>
+      <c r="K61" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="L61" s="5" t="inlineStr"/>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N61" s="5" t="inlineStr"/>
+      <c r="O61" s="5" t="inlineStr"/>
+      <c r="P61" s="5" t="inlineStr"/>
+      <c r="Q61" s="5" t="inlineStr"/>
+      <c r="R61" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas e Europa; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="S61" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T61" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Pós 200GB</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-200gb</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="I62" s="3" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Pós 50GB com GeForce NOW</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb-geforce</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr"/>
+      <c r="J63" s="5" t="inlineStr"/>
+      <c r="K63" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="L63" s="5" t="inlineStr"/>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N63" s="5" t="inlineStr"/>
+      <c r="O63" s="5" t="inlineStr"/>
+      <c r="P63" s="5" t="inlineStr"/>
+      <c r="Q63" s="5" t="inlineStr"/>
+      <c r="R63" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado; Inclusa assinatura GeForce NOW</t>
+        </is>
+      </c>
+      <c r="S63" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T63" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Pós 60GB</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Prezão R$1 por dia</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>claro:prez-o-r-1-por-dia</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr"/>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>prepaid Prezão — preço por dia; recargas a partir de R$15</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L65" s="5" t="inlineStr"/>
+      <c r="M65" s="5" t="inlineStr"/>
+      <c r="N65" s="5" t="inlineStr"/>
+      <c r="O65" s="5" t="inlineStr"/>
+      <c r="P65" s="5" t="inlineStr"/>
+      <c r="Q65" s="5" t="inlineStr"/>
+      <c r="R65" s="5" t="inlineStr"/>
+      <c r="S65" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="T65" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle 41GB</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>tim:162901</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Light Express 31GB</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>tim:143536</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>60.99</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr"/>
+      <c r="J67" s="5" t="inlineStr"/>
+      <c r="K67" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="L67" s="5" t="inlineStr"/>
+      <c r="M67" s="5" t="inlineStr"/>
+      <c r="N67" s="5" t="inlineStr"/>
+      <c r="O67" s="5" t="inlineStr"/>
+      <c r="P67" s="5" t="inlineStr"/>
+      <c r="Q67" s="5" t="inlineStr"/>
+      <c r="R67" s="5" t="inlineStr"/>
+      <c r="S67" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T67" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Plus 45GB</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>tim:155891</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Premium 53GB</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>tim:162896</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr"/>
+      <c r="J69" s="5" t="inlineStr"/>
+      <c r="K69" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="L69" s="5" t="inlineStr"/>
+      <c r="M69" s="5" t="inlineStr"/>
+      <c r="N69" s="5" t="inlineStr"/>
+      <c r="O69" s="5" t="inlineStr"/>
+      <c r="P69" s="5" t="inlineStr"/>
+      <c r="Q69" s="5" t="inlineStr"/>
+      <c r="R69" s="5" t="inlineStr"/>
+      <c r="S69" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T69" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Pro Express</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>tim:143576</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I70" s="3" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black 70GB</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>tim:54206</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr"/>
+      <c r="J71" s="5" t="inlineStr"/>
+      <c r="K71" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="L71" s="5" t="inlineStr"/>
+      <c r="M71" s="5" t="inlineStr"/>
+      <c r="N71" s="5" t="inlineStr"/>
+      <c r="O71" s="5" t="inlineStr"/>
+      <c r="P71" s="5" t="inlineStr"/>
+      <c r="Q71" s="5" t="inlineStr"/>
+      <c r="R71" s="5" t="inlineStr"/>
+      <c r="S71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T71" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black A Express 67GB</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>tim:55121</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>119.99</v>
+      </c>
+      <c r="I72" s="3" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black B Express 82GB</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>tim:52146</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr"/>
+      <c r="J73" s="5" t="inlineStr"/>
+      <c r="K73" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="L73" s="5" t="inlineStr"/>
+      <c r="M73" s="5" t="inlineStr"/>
+      <c r="N73" s="5" t="inlineStr"/>
+      <c r="O73" s="5" t="inlineStr"/>
+      <c r="P73" s="5" t="inlineStr"/>
+      <c r="Q73" s="5" t="inlineStr"/>
+      <c r="R73" s="5" t="inlineStr"/>
+      <c r="S73" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T73" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black C Express 107GB</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>tim:52151</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black C Ultra 95GB</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>tim:100581</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr"/>
+      <c r="J75" s="5" t="inlineStr"/>
+      <c r="K75" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="L75" s="5" t="inlineStr"/>
+      <c r="M75" s="5" t="inlineStr"/>
+      <c r="N75" s="5" t="inlineStr"/>
+      <c r="O75" s="5" t="inlineStr"/>
+      <c r="P75" s="5" t="inlineStr"/>
+      <c r="Q75" s="5" t="inlineStr"/>
+      <c r="R75" s="5" t="inlineStr"/>
+      <c r="S75" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T75" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black Plus 80GB</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>tim:54256</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black Premium 110GB</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>tim:54261</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr"/>
+      <c r="J77" s="5" t="inlineStr"/>
+      <c r="K77" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="L77" s="5" t="inlineStr"/>
+      <c r="M77" s="5" t="inlineStr"/>
+      <c r="N77" s="5" t="inlineStr"/>
+      <c r="O77" s="5" t="inlineStr"/>
+      <c r="P77" s="5" t="inlineStr"/>
+      <c r="Q77" s="5" t="inlineStr"/>
+      <c r="R77" s="5" t="inlineStr"/>
+      <c r="S77" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T77" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 16GB</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>tim:106306</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 6GB</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>tim:59906</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr"/>
+      <c r="J79" s="5" t="inlineStr"/>
+      <c r="K79" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L79" s="5" t="inlineStr"/>
+      <c r="M79" s="5" t="inlineStr"/>
+      <c r="N79" s="5" t="inlineStr"/>
+      <c r="O79" s="5" t="inlineStr"/>
+      <c r="P79" s="5" t="inlineStr"/>
+      <c r="Q79" s="5" t="inlineStr"/>
+      <c r="R79" s="5" t="inlineStr"/>
+      <c r="S79" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="T79" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 8GB</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>tim:59901</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029270-46gb</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr"/>
+      <c r="J81" s="5" t="inlineStr"/>
+      <c r="K81" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>15 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr"/>
+      <c r="N81" s="5" t="inlineStr"/>
+      <c r="O81" s="5" t="inlineStr"/>
+      <c r="P81" s="5" t="inlineStr"/>
+      <c r="Q81" s="5" t="inlineStr"/>
+      <c r="R81" s="5" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="S81" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T81" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Educação</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029273-61gb</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr"/>
+      <c r="J83" s="5" t="inlineStr"/>
+      <c r="K83" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr"/>
+      <c r="N83" s="5" t="inlineStr"/>
+      <c r="O83" s="5" t="inlineStr"/>
+      <c r="P83" s="5" t="inlineStr"/>
+      <c r="Q83" s="5" t="inlineStr"/>
+      <c r="R83" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vivae inclusa</t>
+        </is>
+      </c>
+      <c r="S83" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T83" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Entretenimento</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="I84" s="3" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Vivo TV Inicial inclusa</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Música</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029313-61gb</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr"/>
+      <c r="J85" s="5" t="inlineStr"/>
+      <c r="K85" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M85" s="5" t="inlineStr"/>
+      <c r="N85" s="5" t="inlineStr"/>
+      <c r="O85" s="5" t="inlineStr"/>
+      <c r="P85" s="5" t="inlineStr"/>
+      <c r="Q85" s="5" t="inlineStr"/>
+      <c r="R85" s="5" t="inlineStr">
+        <is>
+          <t>Apple Music Individual</t>
+        </is>
+      </c>
+      <c r="S85" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T85" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="I86" s="3" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão com anúncios</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Saúde</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029301-61gb</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr"/>
+      <c r="J87" s="5" t="inlineStr"/>
+      <c r="K87" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M87" s="5" t="inlineStr"/>
+      <c r="N87" s="5" t="inlineStr"/>
+      <c r="O87" s="5" t="inlineStr"/>
+      <c r="P87" s="5" t="inlineStr"/>
+      <c r="Q87" s="5" t="inlineStr"/>
+      <c r="R87" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vale Saúde Sempre inclusa</t>
+        </is>
+      </c>
+      <c r="S87" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T87" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600005312-30gb</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I88" s="3" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>30 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>Youtube Ilimitado</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600019134-40gb</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr"/>
+      <c r="J89" s="5" t="inlineStr"/>
+      <c r="K89" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>40 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M89" s="5" t="inlineStr"/>
+      <c r="N89" s="5" t="inlineStr"/>
+      <c r="O89" s="5" t="inlineStr"/>
+      <c r="P89" s="5" t="inlineStr"/>
+      <c r="Q89" s="5" t="inlineStr"/>
+      <c r="R89" s="5" t="inlineStr">
+        <is>
+          <t>Youtube Ilimitado</t>
+        </is>
+      </c>
+      <c r="S89" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="T89" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600019132-20gb</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="I90" s="3" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>Youtube Ilimitado</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Amazon</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029255-60gb</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr"/>
+      <c r="J91" s="5" t="inlineStr"/>
+      <c r="K91" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M91" s="5" t="inlineStr"/>
+      <c r="N91" s="5" t="inlineStr"/>
+      <c r="O91" s="5" t="inlineStr"/>
+      <c r="P91" s="5" t="inlineStr"/>
+      <c r="Q91" s="5" t="inlineStr"/>
+      <c r="R91" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Amazon Prime inclusa</t>
+        </is>
+      </c>
+      <c r="S91" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T91" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Disney+</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022115-60gb</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>Disney+</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Disney+ Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Globoplay</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029246-60gb</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr"/>
+      <c r="J93" s="5" t="inlineStr"/>
+      <c r="K93" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M93" s="5" t="inlineStr"/>
+      <c r="N93" s="5" t="inlineStr"/>
+      <c r="O93" s="5" t="inlineStr"/>
+      <c r="P93" s="5" t="inlineStr">
+        <is>
+          <t>Globoplay</t>
+        </is>
+      </c>
+      <c r="Q93" s="5" t="inlineStr"/>
+      <c r="R93" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Globoplay inclusa</t>
+        </is>
+      </c>
+      <c r="S93" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T93" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Netflix</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029234-60gb</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I94" s="3" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Premiere</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029249-60gb</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr"/>
+      <c r="J95" s="5" t="inlineStr"/>
+      <c r="K95" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M95" s="5" t="inlineStr"/>
+      <c r="N95" s="5" t="inlineStr"/>
+      <c r="O95" s="5" t="inlineStr"/>
+      <c r="P95" s="5" t="inlineStr">
+        <is>
+          <t>Premiere</t>
+        </is>
+      </c>
+      <c r="Q95" s="5" t="inlineStr"/>
+      <c r="R95" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Premiere inclusa</t>
+        </is>
+      </c>
+      <c r="S95" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T95" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Spotify</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029229-60gb</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="I96" s="3" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Spotify Premium inclusa</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Travel</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029244-70gb</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr"/>
+      <c r="J97" s="5" t="inlineStr"/>
+      <c r="K97" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>60 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M97" s="5" t="inlineStr"/>
+      <c r="N97" s="5" t="inlineStr"/>
+      <c r="O97" s="5" t="inlineStr"/>
+      <c r="P97" s="5" t="inlineStr"/>
+      <c r="Q97" s="5" t="inlineStr"/>
+      <c r="R97" s="5" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="S97" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T97" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022379-25gb</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I98" s="3" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022379-9gb</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr"/>
+      <c r="J99" s="5" t="inlineStr"/>
+      <c r="K99" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>6 GB para navegar como quiser 3 GB para navegar no YouTube</t>
+        </is>
+      </c>
+      <c r="M99" s="5" t="inlineStr"/>
+      <c r="N99" s="5" t="inlineStr"/>
+      <c r="O99" s="5" t="inlineStr"/>
+      <c r="P99" s="5" t="inlineStr"/>
+      <c r="Q99" s="5" t="inlineStr"/>
+      <c r="R99" s="5" t="inlineStr"/>
+      <c r="S99" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="T99" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022379-5gb</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I100" s="3" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>5 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:10:23</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022379-4gb</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr"/>
+      <c r="J101" s="5" t="inlineStr"/>
+      <c r="K101" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>4 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M101" s="5" t="inlineStr"/>
+      <c r="N101" s="5" t="inlineStr"/>
+      <c r="O101" s="5" t="inlineStr"/>
+      <c r="P101" s="5" t="inlineStr"/>
+      <c r="Q101" s="5" t="inlineStr"/>
+      <c r="R101" s="5" t="inlineStr"/>
+      <c r="S101" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="T101" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T52"/>
+  <autoFilter ref="A1:T101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4985,7 +8299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T52"/>
+  <dimension ref="A1:T50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5115,12 +8429,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5191,12 +8505,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -5261,12 +8575,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5331,12 +8645,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -5401,12 +8715,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -5471,12 +8785,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5541,12 +8855,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -5611,12 +8925,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5681,12 +8995,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -5751,12 +9065,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -5821,12 +9135,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -5891,12 +9205,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -5961,12 +9275,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -6027,12 +9341,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6089,12 +9403,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -6151,12 +9465,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6213,12 +9527,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -6275,12 +9589,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -6335,12 +9649,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -6397,12 +9711,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -6459,12 +9773,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -6521,12 +9835,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -6583,12 +9897,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -6645,12 +9959,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -6707,12 +10021,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -6769,12 +10083,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -6831,12 +10145,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -6893,12 +10207,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -6955,12 +10269,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -7025,12 +10339,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -7095,12 +10409,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -7165,12 +10479,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -7235,12 +10549,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -7305,12 +10619,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -7375,12 +10689,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -7445,12 +10759,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -7488,7 +10802,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>30 GB de franquia 2 Meses de YouTube ilimitado</t>
+          <t>30 GB de franquia</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr"/>
@@ -7496,7 +10810,11 @@
       <c r="O37" s="5" t="inlineStr"/>
       <c r="P37" s="5" t="inlineStr"/>
       <c r="Q37" s="5" t="inlineStr"/>
-      <c r="R37" s="5" t="inlineStr"/>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>Youtube Ilimitado</t>
+        </is>
+      </c>
       <c r="S37" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
@@ -7511,12 +10829,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -7554,7 +10872,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>40 GB de franquia 2 Meses de YouTube ilimitado</t>
+          <t>40 GB de franquia</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
@@ -7562,7 +10880,11 @@
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Youtube Ilimitado</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
@@ -7577,12 +10899,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -7620,7 +10942,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>20 GB de franquia 2 Meses de YouTube ilimitado</t>
+          <t>20 GB de franquia</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr"/>
@@ -7628,7 +10950,11 @@
       <c r="O39" s="5" t="inlineStr"/>
       <c r="P39" s="5" t="inlineStr"/>
       <c r="Q39" s="5" t="inlineStr"/>
-      <c r="R39" s="5" t="inlineStr"/>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>Youtube Ilimitado</t>
+        </is>
+      </c>
       <c r="S39" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
@@ -7643,12 +10969,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -7658,7 +10984,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>lite</t>
+          <t>postpaid</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -7668,49 +10994,57 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Easy Lite</t>
+          <t>Vivo Pós com Amazon</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600019127-30gb</t>
+          <t>vivo:VIV202600029255-60gb</t>
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="I40" s="3" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Amazon Prime inclusa</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>data/raw/vivo_lite_SP.html</t>
+          <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -7720,7 +11054,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>lite</t>
+          <t>postpaid</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -7730,49 +11064,61 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Easy Lite</t>
+          <t>Vivo Pós com Disney+</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600019129-40gb</t>
+          <t>vivo:VIV202600022115-60gb</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="I41" s="6" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
       <c r="K41" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="L41" s="5" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="inlineStr"/>
       <c r="O41" s="5" t="inlineStr"/>
-      <c r="P41" s="5" t="inlineStr"/>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
+          <t>Disney+</t>
+        </is>
+      </c>
       <c r="Q41" s="5" t="inlineStr"/>
-      <c r="R41" s="5" t="inlineStr"/>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Disney+ Padrão inclusa</t>
+        </is>
+      </c>
       <c r="S41" s="5" t="inlineStr">
         <is>
-          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
       <c r="T41" s="5" t="inlineStr">
         <is>
-          <t>data/raw/vivo_lite_SP.html</t>
+          <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -7792,16 +11138,16 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Vivo Pós com Amazon</t>
+          <t>Vivo Pós com Globoplay</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029255-60gb</t>
+          <t>vivo:VIV202600029246-60gb</t>
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
@@ -7816,11 +11162,15 @@
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr"/>
-      <c r="P42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Globoplay</t>
+        </is>
+      </c>
       <c r="Q42" s="2" t="inlineStr"/>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Assinatura Amazon Prime inclusa</t>
+          <t>Assinatura Globoplay inclusa</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -7837,12 +11187,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -7862,12 +11212,12 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Vivo Pós com Disney+</t>
+          <t>Vivo Pós com Netflix</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600022115-60gb</t>
+          <t>vivo:VIV202600029234-60gb</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
@@ -7888,13 +11238,13 @@
       <c r="O43" s="5" t="inlineStr"/>
       <c r="P43" s="5" t="inlineStr">
         <is>
-          <t>Disney+</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="Q43" s="5" t="inlineStr"/>
       <c r="R43" s="5" t="inlineStr">
         <is>
-          <t>Assinatura Disney+ Padrão inclusa</t>
+          <t>Assinatura Netflix Padrão inclusa</t>
         </is>
       </c>
       <c r="S43" s="5" t="inlineStr">
@@ -7911,12 +11261,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -7936,16 +11286,16 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Vivo Pós com Globoplay</t>
+          <t>Vivo Pós com Premiere</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029246-60gb</t>
+          <t>vivo:VIV202600029249-60gb</t>
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
@@ -7962,13 +11312,13 @@
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Globoplay</t>
+          <t>Premiere</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Assinatura Globoplay inclusa</t>
+          <t>Assinatura Premiere inclusa</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -7985,12 +11335,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -8010,16 +11360,16 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Vivo Pós com Netflix</t>
+          <t>Vivo Pós com Spotify</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029234-60gb</t>
+          <t>vivo:VIV202600029229-60gb</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I45" s="6" t="inlineStr"/>
       <c r="J45" s="5" t="inlineStr"/>
@@ -8036,13 +11386,13 @@
       <c r="O45" s="5" t="inlineStr"/>
       <c r="P45" s="5" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="Q45" s="5" t="inlineStr"/>
       <c r="R45" s="5" t="inlineStr">
         <is>
-          <t>Assinatura Netflix Padrão inclusa</t>
+          <t>Assinatura Spotify Premium inclusa</t>
         </is>
       </c>
       <c r="S45" s="5" t="inlineStr">
@@ -8059,12 +11409,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -8084,39 +11434,35 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Vivo Pós com Premiere</t>
+          <t>Vivo Pós com Travel</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029249-60gb</t>
+          <t>vivo:VIV202600029244-70gb</t>
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="I46" s="3" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="4" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>50 GB de franquia 10 GB de bônus</t>
+          <t>60 GB de franquia 10 GB de bônus</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>Premiere</t>
-        </is>
-      </c>
+      <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Assinatura Premiere inclusa</t>
+          <t>6 meses grátis de Gemini com AI Plus</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -8133,12 +11479,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -8148,7 +11494,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>postpaid</t>
+          <t>prepaid</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -8158,61 +11504,53 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Vivo Pós com Spotify</t>
+          <t>Vivo Pré</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029229-60gb</t>
+          <t>vivo:VIV202600022379-25gb</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>165</v>
+        <v>30</v>
       </c>
       <c r="I47" s="6" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
       <c r="K47" s="7" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>50 GB de franquia 10 GB de bônus</t>
+          <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="inlineStr"/>
       <c r="O47" s="5" t="inlineStr"/>
-      <c r="P47" s="5" t="inlineStr">
-        <is>
-          <t>Spotify</t>
-        </is>
-      </c>
+      <c r="P47" s="5" t="inlineStr"/>
       <c r="Q47" s="5" t="inlineStr"/>
-      <c r="R47" s="5" t="inlineStr">
-        <is>
-          <t>Assinatura Spotify Premium inclusa</t>
-        </is>
-      </c>
+      <c r="R47" s="5" t="inlineStr"/>
       <c r="S47" s="5" t="inlineStr">
         <is>
-          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
         </is>
       </c>
       <c r="T47" s="5" t="inlineStr">
         <is>
-          <t>data/raw/vivo_postpaid_SP.html</t>
+          <t>data/raw/vivo_prepaid_SP.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -8222,7 +11560,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>postpaid</t>
+          <t>prepaid</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -8232,25 +11570,25 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Vivo Pós com Travel</t>
+          <t>Vivo Pré</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029244-70gb</t>
+          <t>vivo:VIV202600022379-9gb</t>
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>215</v>
+        <v>25</v>
       </c>
       <c r="I48" s="3" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="4" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>60 GB de franquia 10 GB de bônus</t>
+          <t>6 GB para navegar como quiser 3 GB para navegar no YouTube</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
@@ -8258,31 +11596,27 @@
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr"/>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>6 meses grátis de Gemini com AI Plus</t>
-        </is>
-      </c>
+      <c r="R48" s="2" t="inlineStr"/>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>data/raw/vivo_postpaid_SP.html</t>
+          <t>data/raw/vivo_prepaid_SP.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -8307,20 +11641,20 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600022379-25gb</t>
+          <t>vivo:VIV202600022379-5gb</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I49" s="6" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr"/>
       <c r="K49" s="7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
+          <t>5 GB para navegar como quiser</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr"/>
@@ -8343,12 +11677,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -8373,20 +11707,20 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600022379-9gb</t>
+          <t>vivo:VIV202600022379-4gb</t>
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I50" s="3" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>6 GB para navegar como quiser 3 GB para navegar no YouTube</t>
+          <t>4 GB para navegar como quiser</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
@@ -8406,141 +11740,9 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-22T22:45:24</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>prepaid</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Vivo Pré</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600022379-5gb</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="I51" s="6" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
-      <c r="K51" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>5 GB para navegar como quiser</t>
-        </is>
-      </c>
-      <c r="M51" s="5" t="inlineStr"/>
-      <c r="N51" s="5" t="inlineStr"/>
-      <c r="O51" s="5" t="inlineStr"/>
-      <c r="P51" s="5" t="inlineStr"/>
-      <c r="Q51" s="5" t="inlineStr"/>
-      <c r="R51" s="5" t="inlineStr"/>
-      <c r="S51" s="5" t="inlineStr">
-        <is>
-          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
-        </is>
-      </c>
-      <c r="T51" s="5" t="inlineStr">
-        <is>
-          <t>data/raw/vivo_prepaid_SP.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T22:45:24</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>prepaid</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Pré</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600022379-4gb</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="I52" s="3" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>4 GB para navegar como quiser</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr"/>
-      <c r="P52" s="2" t="inlineStr"/>
-      <c r="Q52" s="2" t="inlineStr"/>
-      <c r="R52" s="2" t="inlineStr"/>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>data/raw/vivo_prepaid_SP.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T52"/>
-  <conditionalFormatting sqref="H2:H52">
+  <autoFilter ref="A1:T50"/>
+  <conditionalFormatting sqref="H2:H50">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -8552,7 +11754,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I52">
+  <conditionalFormatting sqref="I2:I50">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>NOT(ISBLANK(I2))</formula>
     </cfRule>
@@ -8568,7 +11770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8628,6 +11830,80 @@
           <t>delta_brl</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600019127-30gb</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600019129-40gb</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8666,7 +11942,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:24</t>
+          <t>2026-06-23T22:10:23</t>
         </is>
       </c>
     </row>
@@ -8678,7 +11954,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
@@ -8689,7 +11965,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -8699,7 +11975,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -8810,7 +12086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8988,8 +12264,63 @@
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B38" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,$A38)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,$A38))</f>
+        <v/>
+      </c>
+      <c r="C38" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,$A38)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,$A38))</f>
+        <v/>
+      </c>
+      <c r="D38" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,$A38)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,$A38))</f>
+        <v/>
+      </c>
+      <c r="E38" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,$A38)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,$A38))</f>
+        <v/>
+      </c>
+      <c r="F38" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,$A38)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,$A38))</f>
+        <v/>
+      </c>
+      <c r="G38" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,$A38)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,$A38))</f>
+        <v/>
+      </c>
+      <c r="H38" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,$A38)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,$A38))</f>
+        <v/>
+      </c>
+      <c r="I38" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,$A38)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,$A38))</f>
+        <v/>
+      </c>
+      <c r="J38" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,$A38)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,$A38))</f>
+        <v/>
+      </c>
+      <c r="K38" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,$A38),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,$A38),0)),"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,$A38),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,$A38),0)),"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,$A38),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,$A38),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>Pre = cheapest recharge amount captured (true R$/day needs validity-days we don't yet capture — CONTEXT §8). Digital = min of Vivo Lite / Claro Flex. Daily rows now; monthly roll-up is the planned next step.</t>
         </is>
@@ -9003,7 +12334,7 @@
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="H35:J35"/>
   </mergeCells>
-  <conditionalFormatting sqref="B37:D37">
+  <conditionalFormatting sqref="B37:D38">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -9015,7 +12346,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E37:G37">
+  <conditionalFormatting sqref="E37:G38">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -9027,7 +12358,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H37:J37">
+  <conditionalFormatting sqref="H37:J38">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -9039,7 +12370,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K37:M37">
+  <conditionalFormatting sqref="K37:M38">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -9063,7 +12394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9781,37 +13112,18 @@
       <c r="A37" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B37" s="6" t="n">
-        <v>40</v>
-      </c>
+      <c r="B37" s="14" t="n"/>
       <c r="C37" s="6" t="n">
         <v>119.9</v>
       </c>
       <c r="D37" s="14" t="n"/>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Easy Lite (30GB)</t>
-        </is>
-      </c>
+      <c r="E37" s="14" t="n"/>
       <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Flex 40GB (40GB)</t>
         </is>
       </c>
       <c r="G37" s="14" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Easy Lite (40GB)</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:D11">
@@ -9859,7 +13171,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B34:D38">
+  <conditionalFormatting sqref="B34:D37">
     <cfRule type="expression" priority="7" dxfId="1" stopIfTrue="1">
       <formula>AND(B34&lt;&gt;"",B34=MIN($B34:$D34))</formula>
     </cfRule>
@@ -9885,7 +13197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10350,13 +13662,17 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30 GB (30 GB de franquia 2 Meses de YouTube ilimitado)</t>
+          <t>30 GB (30 GB de franquia)</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Youtube Ilimitado</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -10370,13 +13686,17 @@
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>20 GB (20 GB de franquia 2 Meses de YouTube ilimitado)</t>
+          <t>20 GB (20 GB de franquia)</t>
         </is>
       </c>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Youtube Ilimitado</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -10390,47 +13710,45 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40 GB (40 GB de franquia 2 Meses de YouTube ilimitado)</t>
+          <t>40 GB (40 GB de franquia)</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Youtube Ilimitado</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Easy Lite</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>30 GB</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Prepaid</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="16" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Easy Lite</t>
+          <t>Vivo Pré</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>40 GB</t>
+          <t>4 GB (4 GB para navegar como quiser)</t>
         </is>
       </c>
       <c r="E23" s="2" t="n"/>
@@ -10439,18 +13757,24 @@
       <c r="H23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Prepaid</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
-      <c r="G24" s="16" t="n"/>
-      <c r="H24" s="16" t="n"/>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>5 GB (5 GB para navegar como quiser)</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -10459,12 +13783,12 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4 GB (4 GB para navegar como quiser)</t>
+          <t>9 GB (6 GB para navegar como quiser 3 GB para navegar no YouTube)</t>
         </is>
       </c>
       <c r="E25" s="2" t="n"/>
@@ -10479,58 +13803,18 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>5 GB (5 GB para navegar como quiser)</t>
+          <t>25 GB (15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube)</t>
         </is>
       </c>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Pré</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>9 GB (6 GB para navegar como quiser 3 GB para navegar no YouTube)</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Vivo Pré</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>25 GB (15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube)</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3:B9">
@@ -10557,7 +13841,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B23">
+  <conditionalFormatting sqref="B19:B21">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10569,7 +13853,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B25:B28">
+  <conditionalFormatting sqref="B23:B26">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -18,7 +18,7 @@
     <sheet name="TIM" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$T$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$T$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$T$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -296,12 +296,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$38</f>
+              <f>'comparison'!$A$37:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$B$37:$B$38</f>
+              <f>'comparison'!$B$37:$B$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -333,12 +333,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$38</f>
+              <f>'comparison'!$A$37:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$C$37:$C$38</f>
+              <f>'comparison'!$C$37:$C$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -370,12 +370,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$38</f>
+              <f>'comparison'!$A$37:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$D$37:$D$38</f>
+              <f>'comparison'!$D$37:$D$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -493,12 +493,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$38</f>
+              <f>'comparison'!$A$37:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$E$37:$E$38</f>
+              <f>'comparison'!$E$37:$E$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -530,12 +530,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$38</f>
+              <f>'comparison'!$A$37:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$F$37:$F$38</f>
+              <f>'comparison'!$F$37:$F$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -567,12 +567,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$38</f>
+              <f>'comparison'!$A$37:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$G$37:$G$38</f>
+              <f>'comparison'!$G$37:$G$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -690,12 +690,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$38</f>
+              <f>'comparison'!$A$37:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$H$37:$H$38</f>
+              <f>'comparison'!$H$37:$H$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -727,12 +727,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$38</f>
+              <f>'comparison'!$A$37:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$I$37:$I$38</f>
+              <f>'comparison'!$I$37:$I$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -764,12 +764,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$38</f>
+              <f>'comparison'!$A$37:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$J$37:$J$38</f>
+              <f>'comparison'!$J$37:$J$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -887,12 +887,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$38</f>
+              <f>'comparison'!$A$37:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$K$37:$K$38</f>
+              <f>'comparison'!$K$37:$K$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -924,12 +924,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$38</f>
+              <f>'comparison'!$A$37:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$L$37:$L$38</f>
+              <f>'comparison'!$L$37:$L$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -961,12 +961,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$38</f>
+              <f>'comparison'!$A$37:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$M$37:$M$38</f>
+              <f>'comparison'!$M$37:$M$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1419,7 +1419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T101"/>
+  <dimension ref="A1:T150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8286,8 +8286,3322 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Controle 25GB</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-25gb</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>De R$ 59,90 Por:</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e vídeos; Bônus exclusivo; Aproveite na sua franquia; WhatsApp e ligações ilimitadas</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr"/>
+      <c r="J103" s="5" t="inlineStr"/>
+      <c r="K103" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L103" s="5" t="inlineStr"/>
+      <c r="M103" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N103" s="5" t="inlineStr"/>
+      <c r="O103" s="5" t="inlineStr"/>
+      <c r="P103" s="5" t="inlineStr"/>
+      <c r="Q103" s="5" t="inlineStr"/>
+      <c r="R103" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="S103" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="T103" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb-gaming</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I104" s="3" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr"/>
+      <c r="P104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus para redes sociais e apps; Bônus uso livre; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>Flex 15GB</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-15gb</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr"/>
+      <c r="J105" s="5" t="inlineStr"/>
+      <c r="K105" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="L105" s="5" t="inlineStr"/>
+      <c r="M105" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N105" s="5" t="inlineStr"/>
+      <c r="O105" s="5" t="inlineStr"/>
+      <c r="P105" s="5" t="inlineStr"/>
+      <c r="Q105" s="5" t="inlineStr"/>
+      <c r="R105" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="S105" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="T105" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Flex 20GB</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-20gb</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I106" s="3" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr"/>
+      <c r="P106" s="2" t="inlineStr"/>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Flex 30GB</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-30gb</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr"/>
+      <c r="J107" s="5" t="inlineStr"/>
+      <c r="K107" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L107" s="5" t="inlineStr"/>
+      <c r="M107" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N107" s="5" t="inlineStr"/>
+      <c r="O107" s="5" t="inlineStr"/>
+      <c r="P107" s="5" t="inlineStr"/>
+      <c r="Q107" s="5" t="inlineStr"/>
+      <c r="R107" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="S107" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="T107" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Flex 40GB</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-40gb</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I108" s="3" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="inlineStr"/>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e apps; Bônus uso livre; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>Pós 100GB</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-100gb</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr"/>
+      <c r="J109" s="5" t="inlineStr"/>
+      <c r="K109" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="L109" s="5" t="inlineStr"/>
+      <c r="M109" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N109" s="5" t="inlineStr"/>
+      <c r="O109" s="5" t="inlineStr"/>
+      <c r="P109" s="5" t="inlineStr"/>
+      <c r="Q109" s="5" t="inlineStr"/>
+      <c r="R109" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="S109" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T109" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Pós 150GB</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-150gb</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="I110" s="3" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="inlineStr"/>
+      <c r="Q110" s="2" t="inlineStr"/>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas e Europa; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>Pós 200GB</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-200gb</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr"/>
+      <c r="J111" s="5" t="inlineStr"/>
+      <c r="K111" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="L111" s="5" t="inlineStr"/>
+      <c r="M111" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N111" s="5" t="inlineStr"/>
+      <c r="O111" s="5" t="inlineStr"/>
+      <c r="P111" s="5" t="inlineStr"/>
+      <c r="Q111" s="5" t="inlineStr"/>
+      <c r="R111" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="S111" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T111" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Pós 50GB com GeForce NOW</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb-geforce</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="I112" s="3" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="inlineStr"/>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado; Inclusa assinatura GeForce NOW</t>
+        </is>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>Pós 60GB</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr"/>
+      <c r="J113" s="5" t="inlineStr"/>
+      <c r="K113" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L113" s="5" t="inlineStr"/>
+      <c r="M113" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N113" s="5" t="inlineStr"/>
+      <c r="O113" s="5" t="inlineStr"/>
+      <c r="P113" s="5" t="inlineStr"/>
+      <c r="Q113" s="5" t="inlineStr"/>
+      <c r="R113" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="S113" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T113" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Prezão R$1 por dia</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>claro:prez-o-r-1-por-dia</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" s="3" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>prepaid Prezão — preço por dia; recargas a partir de R$15</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr"/>
+      <c r="P114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr"/>
+      <c r="R114" s="2" t="inlineStr"/>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle 41GB</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>tim:162901</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr"/>
+      <c r="J115" s="5" t="inlineStr"/>
+      <c r="K115" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="L115" s="5" t="inlineStr"/>
+      <c r="M115" s="5" t="inlineStr"/>
+      <c r="N115" s="5" t="inlineStr"/>
+      <c r="O115" s="5" t="inlineStr"/>
+      <c r="P115" s="5" t="inlineStr"/>
+      <c r="Q115" s="5" t="inlineStr"/>
+      <c r="R115" s="5" t="inlineStr"/>
+      <c r="S115" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T115" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Light Express 31GB</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>tim:143536</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>60.99</v>
+      </c>
+      <c r="I116" s="3" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr"/>
+      <c r="P116" s="2" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr"/>
+      <c r="R116" s="2" t="inlineStr"/>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Plus 45GB</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>tim:155891</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr"/>
+      <c r="J117" s="5" t="inlineStr"/>
+      <c r="K117" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="L117" s="5" t="inlineStr"/>
+      <c r="M117" s="5" t="inlineStr"/>
+      <c r="N117" s="5" t="inlineStr"/>
+      <c r="O117" s="5" t="inlineStr"/>
+      <c r="P117" s="5" t="inlineStr"/>
+      <c r="Q117" s="5" t="inlineStr"/>
+      <c r="R117" s="5" t="inlineStr"/>
+      <c r="S117" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T117" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Premium 53GB</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>tim:162896</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="I118" s="3" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr"/>
+      <c r="P118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="inlineStr"/>
+      <c r="R118" s="2" t="inlineStr"/>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Pro Express</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>tim:143576</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr"/>
+      <c r="J119" s="5" t="inlineStr"/>
+      <c r="K119" s="7" t="inlineStr"/>
+      <c r="L119" s="5" t="inlineStr"/>
+      <c r="M119" s="5" t="inlineStr"/>
+      <c r="N119" s="5" t="inlineStr"/>
+      <c r="O119" s="5" t="inlineStr"/>
+      <c r="P119" s="5" t="inlineStr"/>
+      <c r="Q119" s="5" t="inlineStr"/>
+      <c r="R119" s="5" t="inlineStr"/>
+      <c r="S119" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T119" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black 70GB</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>tim:54206</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="I120" s="3" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr"/>
+      <c r="P120" s="2" t="inlineStr"/>
+      <c r="Q120" s="2" t="inlineStr"/>
+      <c r="R120" s="2" t="inlineStr"/>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black A Express 67GB</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>tim:55121</t>
+        </is>
+      </c>
+      <c r="H121" s="6" t="n">
+        <v>119.99</v>
+      </c>
+      <c r="I121" s="6" t="inlineStr"/>
+      <c r="J121" s="5" t="inlineStr"/>
+      <c r="K121" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="L121" s="5" t="inlineStr"/>
+      <c r="M121" s="5" t="inlineStr"/>
+      <c r="N121" s="5" t="inlineStr"/>
+      <c r="O121" s="5" t="inlineStr"/>
+      <c r="P121" s="5" t="inlineStr"/>
+      <c r="Q121" s="5" t="inlineStr"/>
+      <c r="R121" s="5" t="inlineStr"/>
+      <c r="S121" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T121" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black B Express 82GB</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>tim:52146</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="I122" s="3" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr"/>
+      <c r="P122" s="2" t="inlineStr"/>
+      <c r="Q122" s="2" t="inlineStr"/>
+      <c r="R122" s="2" t="inlineStr"/>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black C Express 107GB</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>tim:52151</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr"/>
+      <c r="J123" s="5" t="inlineStr"/>
+      <c r="K123" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="L123" s="5" t="inlineStr"/>
+      <c r="M123" s="5" t="inlineStr"/>
+      <c r="N123" s="5" t="inlineStr"/>
+      <c r="O123" s="5" t="inlineStr"/>
+      <c r="P123" s="5" t="inlineStr"/>
+      <c r="Q123" s="5" t="inlineStr"/>
+      <c r="R123" s="5" t="inlineStr"/>
+      <c r="S123" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T123" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black C Ultra 95GB</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>tim:100581</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I124" s="3" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr"/>
+      <c r="R124" s="2" t="inlineStr"/>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black Plus 80GB</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>tim:54256</t>
+        </is>
+      </c>
+      <c r="H125" s="6" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="I125" s="6" t="inlineStr"/>
+      <c r="J125" s="5" t="inlineStr"/>
+      <c r="K125" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="L125" s="5" t="inlineStr"/>
+      <c r="M125" s="5" t="inlineStr"/>
+      <c r="N125" s="5" t="inlineStr"/>
+      <c r="O125" s="5" t="inlineStr"/>
+      <c r="P125" s="5" t="inlineStr"/>
+      <c r="Q125" s="5" t="inlineStr"/>
+      <c r="R125" s="5" t="inlineStr"/>
+      <c r="S125" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T125" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black Premium 110GB</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>tim:54261</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I126" s="3" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr"/>
+      <c r="P126" s="2" t="inlineStr"/>
+      <c r="Q126" s="2" t="inlineStr"/>
+      <c r="R126" s="2" t="inlineStr"/>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 16GB</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>tim:106306</t>
+        </is>
+      </c>
+      <c r="H127" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr"/>
+      <c r="J127" s="5" t="inlineStr"/>
+      <c r="K127" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="L127" s="5" t="inlineStr"/>
+      <c r="M127" s="5" t="inlineStr"/>
+      <c r="N127" s="5" t="inlineStr"/>
+      <c r="O127" s="5" t="inlineStr"/>
+      <c r="P127" s="5" t="inlineStr"/>
+      <c r="Q127" s="5" t="inlineStr"/>
+      <c r="R127" s="5" t="inlineStr"/>
+      <c r="S127" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="T127" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 6GB</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>tim:59906</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I128" s="3" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr"/>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr"/>
+      <c r="R128" s="2" t="inlineStr"/>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 8GB</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>tim:59901</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr"/>
+      <c r="J129" s="5" t="inlineStr"/>
+      <c r="K129" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L129" s="5" t="inlineStr"/>
+      <c r="M129" s="5" t="inlineStr"/>
+      <c r="N129" s="5" t="inlineStr"/>
+      <c r="O129" s="5" t="inlineStr"/>
+      <c r="P129" s="5" t="inlineStr"/>
+      <c r="Q129" s="5" t="inlineStr"/>
+      <c r="R129" s="5" t="inlineStr"/>
+      <c r="S129" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="T129" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029270-46gb</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="I130" s="3" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>15 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr"/>
+      <c r="P130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="inlineStr"/>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr"/>
+      <c r="J131" s="5" t="inlineStr"/>
+      <c r="K131" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M131" s="5" t="inlineStr"/>
+      <c r="N131" s="5" t="inlineStr"/>
+      <c r="O131" s="5" t="inlineStr"/>
+      <c r="P131" s="5" t="inlineStr"/>
+      <c r="Q131" s="5" t="inlineStr"/>
+      <c r="R131" s="5" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="S131" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T131" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Educação</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029273-61gb</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I132" s="3" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr"/>
+      <c r="O132" s="2" t="inlineStr"/>
+      <c r="P132" s="2" t="inlineStr"/>
+      <c r="Q132" s="2" t="inlineStr"/>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Vivae inclusa</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Entretenimento</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="I133" s="6" t="inlineStr"/>
+      <c r="J133" s="5" t="inlineStr"/>
+      <c r="K133" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M133" s="5" t="inlineStr"/>
+      <c r="N133" s="5" t="inlineStr"/>
+      <c r="O133" s="5" t="inlineStr"/>
+      <c r="P133" s="5" t="inlineStr"/>
+      <c r="Q133" s="5" t="inlineStr"/>
+      <c r="R133" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vivo TV Inicial inclusa</t>
+        </is>
+      </c>
+      <c r="S133" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T133" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Música</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029313-61gb</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="I134" s="3" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr"/>
+      <c r="O134" s="2" t="inlineStr"/>
+      <c r="P134" s="2" t="inlineStr"/>
+      <c r="Q134" s="2" t="inlineStr"/>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>Apple Music Individual</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="I135" s="6" t="inlineStr"/>
+      <c r="J135" s="5" t="inlineStr"/>
+      <c r="K135" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L135" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M135" s="5" t="inlineStr"/>
+      <c r="N135" s="5" t="inlineStr"/>
+      <c r="O135" s="5" t="inlineStr"/>
+      <c r="P135" s="5" t="inlineStr"/>
+      <c r="Q135" s="5" t="inlineStr"/>
+      <c r="R135" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão com anúncios</t>
+        </is>
+      </c>
+      <c r="S135" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T135" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Saúde</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029301-61gb</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I136" s="3" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr"/>
+      <c r="O136" s="2" t="inlineStr"/>
+      <c r="P136" s="2" t="inlineStr"/>
+      <c r="Q136" s="2" t="inlineStr"/>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Vale Saúde Sempre inclusa</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025883-30gb</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr"/>
+      <c r="J137" s="5" t="inlineStr"/>
+      <c r="K137" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L137" s="5" t="inlineStr">
+        <is>
+          <t>30 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M137" s="5" t="inlineStr"/>
+      <c r="N137" s="5" t="inlineStr"/>
+      <c r="O137" s="5" t="inlineStr"/>
+      <c r="P137" s="5" t="inlineStr"/>
+      <c r="Q137" s="5" t="inlineStr"/>
+      <c r="R137" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem desconto no plano</t>
+        </is>
+      </c>
+      <c r="S137" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="T137" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025885-40gb</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I138" s="3" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>40 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr"/>
+      <c r="O138" s="2" t="inlineStr"/>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr"/>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem desconto no plano</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025888-20gb</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="I139" s="6" t="inlineStr"/>
+      <c r="J139" s="5" t="inlineStr"/>
+      <c r="K139" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L139" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M139" s="5" t="inlineStr"/>
+      <c r="N139" s="5" t="inlineStr"/>
+      <c r="O139" s="5" t="inlineStr"/>
+      <c r="P139" s="5" t="inlineStr"/>
+      <c r="Q139" s="5" t="inlineStr"/>
+      <c r="R139" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem desconto no plano</t>
+        </is>
+      </c>
+      <c r="S139" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="T139" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Amazon</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029255-60gb</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="I140" s="3" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr"/>
+      <c r="O140" s="2" t="inlineStr"/>
+      <c r="P140" s="2" t="inlineStr"/>
+      <c r="Q140" s="2" t="inlineStr"/>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Amazon Prime inclusa</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Disney+</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022115-60gb</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I141" s="6" t="inlineStr"/>
+      <c r="J141" s="5" t="inlineStr"/>
+      <c r="K141" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L141" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M141" s="5" t="inlineStr"/>
+      <c r="N141" s="5" t="inlineStr"/>
+      <c r="O141" s="5" t="inlineStr"/>
+      <c r="P141" s="5" t="inlineStr">
+        <is>
+          <t>Disney+</t>
+        </is>
+      </c>
+      <c r="Q141" s="5" t="inlineStr"/>
+      <c r="R141" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Disney+ Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="S141" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T141" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Globoplay</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029246-60gb</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="I142" s="3" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr"/>
+      <c r="O142" s="2" t="inlineStr"/>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>Globoplay</t>
+        </is>
+      </c>
+      <c r="Q142" s="2" t="inlineStr"/>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Globoplay inclusa</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Netflix</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029234-60gb</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I143" s="6" t="inlineStr"/>
+      <c r="J143" s="5" t="inlineStr"/>
+      <c r="K143" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L143" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M143" s="5" t="inlineStr"/>
+      <c r="N143" s="5" t="inlineStr"/>
+      <c r="O143" s="5" t="inlineStr"/>
+      <c r="P143" s="5" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="Q143" s="5" t="inlineStr"/>
+      <c r="R143" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="S143" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T143" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Premiere</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029249-60gb</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I144" s="3" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr"/>
+      <c r="O144" s="2" t="inlineStr"/>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>Premiere</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr"/>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Premiere inclusa</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Spotify</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029229-60gb</t>
+        </is>
+      </c>
+      <c r="H145" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="I145" s="6" t="inlineStr"/>
+      <c r="J145" s="5" t="inlineStr"/>
+      <c r="K145" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L145" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M145" s="5" t="inlineStr"/>
+      <c r="N145" s="5" t="inlineStr"/>
+      <c r="O145" s="5" t="inlineStr"/>
+      <c r="P145" s="5" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="Q145" s="5" t="inlineStr"/>
+      <c r="R145" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Spotify Premium inclusa</t>
+        </is>
+      </c>
+      <c r="S145" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T145" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Travel</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029244-70gb</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="I146" s="3" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>60 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr"/>
+      <c r="O146" s="2" t="inlineStr"/>
+      <c r="P146" s="2" t="inlineStr"/>
+      <c r="Q146" s="2" t="inlineStr"/>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022379-25gb</t>
+        </is>
+      </c>
+      <c r="H147" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I147" s="6" t="inlineStr"/>
+      <c r="J147" s="5" t="inlineStr"/>
+      <c r="K147" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="L147" s="5" t="inlineStr">
+        <is>
+          <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
+        </is>
+      </c>
+      <c r="M147" s="5" t="inlineStr"/>
+      <c r="N147" s="5" t="inlineStr"/>
+      <c r="O147" s="5" t="inlineStr"/>
+      <c r="P147" s="5" t="inlineStr"/>
+      <c r="Q147" s="5" t="inlineStr"/>
+      <c r="R147" s="5" t="inlineStr"/>
+      <c r="S147" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="T147" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022379-9gb</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I148" s="3" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>6 GB para navegar como quiser 3 GB para navegar no YouTube</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr"/>
+      <c r="O148" s="2" t="inlineStr"/>
+      <c r="P148" s="2" t="inlineStr"/>
+      <c r="Q148" s="2" t="inlineStr"/>
+      <c r="R148" s="2" t="inlineStr"/>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022379-5gb</t>
+        </is>
+      </c>
+      <c r="H149" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I149" s="6" t="inlineStr"/>
+      <c r="J149" s="5" t="inlineStr"/>
+      <c r="K149" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L149" s="5" t="inlineStr">
+        <is>
+          <t>5 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M149" s="5" t="inlineStr"/>
+      <c r="N149" s="5" t="inlineStr"/>
+      <c r="O149" s="5" t="inlineStr"/>
+      <c r="P149" s="5" t="inlineStr"/>
+      <c r="Q149" s="5" t="inlineStr"/>
+      <c r="R149" s="5" t="inlineStr"/>
+      <c r="S149" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="T149" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:14:36</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022379-4gb</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I150" s="3" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>4 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr"/>
+      <c r="O150" s="2" t="inlineStr"/>
+      <c r="P150" s="2" t="inlineStr"/>
+      <c r="Q150" s="2" t="inlineStr"/>
+      <c r="R150" s="2" t="inlineStr"/>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T101"/>
+  <autoFilter ref="A1:T150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8429,12 +11743,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -8505,12 +11819,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -8575,12 +11889,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -8645,12 +11959,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -8715,12 +12029,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -8785,12 +12099,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -8855,12 +12169,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -8925,12 +12239,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -8995,12 +12309,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -9065,12 +12379,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -9135,12 +12449,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -9205,12 +12519,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -9275,12 +12589,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -9341,12 +12655,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -9403,12 +12717,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -9465,12 +12779,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -9527,12 +12841,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -9589,12 +12903,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -9649,12 +12963,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -9711,12 +13025,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -9773,12 +13087,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -9835,12 +13149,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -9897,12 +13211,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -9959,12 +13273,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -10021,12 +13335,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10083,12 +13397,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -10145,12 +13459,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -10207,12 +13521,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -10269,12 +13583,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -10339,12 +13653,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -10409,12 +13723,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -10479,12 +13793,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -10549,12 +13863,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -10619,12 +13933,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -10689,12 +14003,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -10759,12 +14073,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -10789,7 +14103,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600005312-30gb</t>
+          <t>vivo:VIV202600025883-30gb</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
@@ -10812,7 +14126,7 @@
       <c r="Q37" s="5" t="inlineStr"/>
       <c r="R37" s="5" t="inlineStr">
         <is>
-          <t>Youtube Ilimitado</t>
+          <t>2 meses de YouTube sem desconto no plano</t>
         </is>
       </c>
       <c r="S37" s="5" t="inlineStr">
@@ -10829,12 +14143,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -10859,7 +14173,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600019134-40gb</t>
+          <t>vivo:VIV202600025885-40gb</t>
         </is>
       </c>
       <c r="H38" s="3" t="n">
@@ -10882,7 +14196,7 @@
       <c r="Q38" s="2" t="inlineStr"/>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>Youtube Ilimitado</t>
+          <t>2 meses de YouTube sem desconto no plano</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -10899,12 +14213,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -10929,7 +14243,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600019132-20gb</t>
+          <t>vivo:VIV202600025888-20gb</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
@@ -10952,7 +14266,7 @@
       <c r="Q39" s="5" t="inlineStr"/>
       <c r="R39" s="5" t="inlineStr">
         <is>
-          <t>Youtube Ilimitado</t>
+          <t>2 meses de YouTube sem desconto no plano</t>
         </is>
       </c>
       <c r="S39" s="5" t="inlineStr">
@@ -10969,12 +14283,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -11039,12 +14353,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -11113,12 +14427,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -11187,12 +14501,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -11261,12 +14575,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -11335,12 +14649,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -11409,12 +14723,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -11479,12 +14793,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -11545,12 +14859,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -11611,12 +14925,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -11677,12 +14991,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -11770,7 +15084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11834,7 +15148,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>new</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -11854,7 +15168,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600019127-30gb</t>
+          <t>vivo:VIV202600025883-30gb</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -11862,48 +15176,196 @@
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="n">
+        <v>30</v>
+      </c>
       <c r="I2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025885-40gb</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025888-20gb</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
           <t>removed</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>lite</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600019129-40gb</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600005312-30gb</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="G3" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600019132-20gb</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600019134-40gb</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11942,7 +15404,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T22:10:23</t>
+          <t>2026-06-24T22:14:36</t>
         </is>
       </c>
     </row>
@@ -11954,7 +15416,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
@@ -11975,7 +15437,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -12086,7 +15548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12319,8 +15781,63 @@
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B39" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,$A39)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,$A39))</f>
+        <v/>
+      </c>
+      <c r="C39" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,$A39)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,$A39))</f>
+        <v/>
+      </c>
+      <c r="D39" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,$A39)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,$A39))</f>
+        <v/>
+      </c>
+      <c r="E39" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,$A39)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,$A39))</f>
+        <v/>
+      </c>
+      <c r="F39" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,$A39)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,$A39))</f>
+        <v/>
+      </c>
+      <c r="G39" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,$A39)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,$A39))</f>
+        <v/>
+      </c>
+      <c r="H39" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,$A39)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,$A39))</f>
+        <v/>
+      </c>
+      <c r="I39" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,$A39)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,$A39))</f>
+        <v/>
+      </c>
+      <c r="J39" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,$A39)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,$A39))</f>
+        <v/>
+      </c>
+      <c r="K39" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,$A39),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,$A39),0)),"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,$A39),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,$A39),0)),"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,$A39),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,$A39),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Pre = cheapest recharge amount captured (true R$/day needs validity-days we don't yet capture — CONTEXT §8). Digital = min of Vivo Lite / Claro Flex. Daily rows now; monthly roll-up is the planned next step.</t>
         </is>
@@ -12334,7 +15851,7 @@
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="H35:J35"/>
   </mergeCells>
-  <conditionalFormatting sqref="B37:D38">
+  <conditionalFormatting sqref="B37:D39">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -12346,7 +15863,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E37:G38">
+  <conditionalFormatting sqref="E37:G39">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -12358,7 +15875,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H37:J38">
+  <conditionalFormatting sqref="H37:J39">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -12370,7 +15887,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K37:M38">
+  <conditionalFormatting sqref="K37:M39">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -13670,7 +17187,7 @@
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Youtube Ilimitado</t>
+          <t>2 meses de YouTube sem desconto no plano</t>
         </is>
       </c>
     </row>
@@ -13694,7 +17211,7 @@
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Youtube Ilimitado</t>
+          <t>2 meses de YouTube sem desconto no plano</t>
         </is>
       </c>
     </row>
@@ -13718,7 +17235,7 @@
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Youtube Ilimitado</t>
+          <t>2 meses de YouTube sem desconto no plano</t>
         </is>
       </c>
     </row>

--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -18,7 +18,7 @@
     <sheet name="TIM" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$T$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$T$199</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$T$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -296,12 +296,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$39</f>
+              <f>'comparison'!$A$37:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$B$37:$B$39</f>
+              <f>'comparison'!$B$37:$B$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -333,12 +333,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$39</f>
+              <f>'comparison'!$A$37:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$C$37:$C$39</f>
+              <f>'comparison'!$C$37:$C$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -370,12 +370,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$39</f>
+              <f>'comparison'!$A$37:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$D$37:$D$39</f>
+              <f>'comparison'!$D$37:$D$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -493,12 +493,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$39</f>
+              <f>'comparison'!$A$37:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$E$37:$E$39</f>
+              <f>'comparison'!$E$37:$E$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -530,12 +530,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$39</f>
+              <f>'comparison'!$A$37:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$F$37:$F$39</f>
+              <f>'comparison'!$F$37:$F$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -567,12 +567,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$39</f>
+              <f>'comparison'!$A$37:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$G$37:$G$39</f>
+              <f>'comparison'!$G$37:$G$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -690,12 +690,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$39</f>
+              <f>'comparison'!$A$37:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$H$37:$H$39</f>
+              <f>'comparison'!$H$37:$H$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -727,12 +727,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$39</f>
+              <f>'comparison'!$A$37:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$I$37:$I$39</f>
+              <f>'comparison'!$I$37:$I$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -764,12 +764,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$39</f>
+              <f>'comparison'!$A$37:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$J$37:$J$39</f>
+              <f>'comparison'!$J$37:$J$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -887,12 +887,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$39</f>
+              <f>'comparison'!$A$37:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$K$37:$K$39</f>
+              <f>'comparison'!$K$37:$K$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -924,12 +924,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$39</f>
+              <f>'comparison'!$A$37:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$L$37:$L$39</f>
+              <f>'comparison'!$L$37:$L$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -961,12 +961,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$37:$A$39</f>
+              <f>'comparison'!$A$37:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$M$37:$M$39</f>
+              <f>'comparison'!$M$37:$M$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1419,7 +1419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T150"/>
+  <dimension ref="A1:T199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11600,8 +11600,3322 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>Controle 25GB</t>
+        </is>
+      </c>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-25gb</t>
+        </is>
+      </c>
+      <c r="H151" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I151" s="6" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>De R$ 59,90 Por:</t>
+        </is>
+      </c>
+      <c r="K151" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="L151" s="5" t="inlineStr"/>
+      <c r="M151" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N151" s="5" t="inlineStr"/>
+      <c r="O151" s="5" t="inlineStr"/>
+      <c r="P151" s="5" t="inlineStr"/>
+      <c r="Q151" s="5" t="inlineStr"/>
+      <c r="R151" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e vídeos; Bônus exclusivo; Aproveite na sua franquia; WhatsApp e ligações ilimitadas</t>
+        </is>
+      </c>
+      <c r="S151" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="T151" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I152" s="3" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr"/>
+      <c r="O152" s="2" t="inlineStr"/>
+      <c r="P152" s="2" t="inlineStr"/>
+      <c r="Q152" s="2" t="inlineStr"/>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb-gaming</t>
+        </is>
+      </c>
+      <c r="H153" s="6" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I153" s="6" t="inlineStr"/>
+      <c r="J153" s="5" t="inlineStr"/>
+      <c r="K153" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L153" s="5" t="inlineStr"/>
+      <c r="M153" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N153" s="5" t="inlineStr"/>
+      <c r="O153" s="5" t="inlineStr"/>
+      <c r="P153" s="5" t="inlineStr"/>
+      <c r="Q153" s="5" t="inlineStr"/>
+      <c r="R153" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus para redes sociais e apps; Bônus uso livre; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="S153" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="T153" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Flex 15GB</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-15gb</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I154" s="3" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr"/>
+      <c r="O154" s="2" t="inlineStr"/>
+      <c r="P154" s="2" t="inlineStr"/>
+      <c r="Q154" s="2" t="inlineStr"/>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>Flex 20GB</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-20gb</t>
+        </is>
+      </c>
+      <c r="H155" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I155" s="6" t="inlineStr"/>
+      <c r="J155" s="5" t="inlineStr"/>
+      <c r="K155" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L155" s="5" t="inlineStr"/>
+      <c r="M155" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N155" s="5" t="inlineStr"/>
+      <c r="O155" s="5" t="inlineStr"/>
+      <c r="P155" s="5" t="inlineStr"/>
+      <c r="Q155" s="5" t="inlineStr"/>
+      <c r="R155" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="S155" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="T155" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Flex 30GB</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-30gb</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I156" s="3" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L156" s="2" t="inlineStr"/>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr"/>
+      <c r="O156" s="2" t="inlineStr"/>
+      <c r="P156" s="2" t="inlineStr"/>
+      <c r="Q156" s="2" t="inlineStr"/>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>Flex 40GB</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-40gb</t>
+        </is>
+      </c>
+      <c r="H157" s="6" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I157" s="6" t="inlineStr"/>
+      <c r="J157" s="5" t="inlineStr"/>
+      <c r="K157" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L157" s="5" t="inlineStr"/>
+      <c r="M157" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N157" s="5" t="inlineStr"/>
+      <c r="O157" s="5" t="inlineStr"/>
+      <c r="P157" s="5" t="inlineStr"/>
+      <c r="Q157" s="5" t="inlineStr"/>
+      <c r="R157" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e apps; Bônus uso livre; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="S157" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="T157" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Pós 100GB</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-100gb</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="I158" s="3" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr"/>
+      <c r="O158" s="2" t="inlineStr"/>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr"/>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Pós 150GB</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-150gb</t>
+        </is>
+      </c>
+      <c r="H159" s="6" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr"/>
+      <c r="J159" s="5" t="inlineStr"/>
+      <c r="K159" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="L159" s="5" t="inlineStr"/>
+      <c r="M159" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N159" s="5" t="inlineStr"/>
+      <c r="O159" s="5" t="inlineStr"/>
+      <c r="P159" s="5" t="inlineStr"/>
+      <c r="Q159" s="5" t="inlineStr"/>
+      <c r="R159" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas e Europa; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="S159" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T159" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Pós 200GB</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-200gb</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="I160" s="3" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr"/>
+      <c r="O160" s="2" t="inlineStr"/>
+      <c r="P160" s="2" t="inlineStr"/>
+      <c r="Q160" s="2" t="inlineStr"/>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>Pós 50GB com GeForce NOW</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb-geforce</t>
+        </is>
+      </c>
+      <c r="H161" s="6" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="I161" s="6" t="inlineStr"/>
+      <c r="J161" s="5" t="inlineStr"/>
+      <c r="K161" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="L161" s="5" t="inlineStr"/>
+      <c r="M161" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N161" s="5" t="inlineStr"/>
+      <c r="O161" s="5" t="inlineStr"/>
+      <c r="P161" s="5" t="inlineStr"/>
+      <c r="Q161" s="5" t="inlineStr"/>
+      <c r="R161" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado; Inclusa assinatura GeForce NOW</t>
+        </is>
+      </c>
+      <c r="S161" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T161" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Pós 60GB</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="I162" s="3" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L162" s="2" t="inlineStr"/>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr"/>
+      <c r="O162" s="2" t="inlineStr"/>
+      <c r="P162" s="2" t="inlineStr"/>
+      <c r="Q162" s="2" t="inlineStr"/>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>Prezão R$1 por dia</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>claro:prez-o-r-1-por-dia</t>
+        </is>
+      </c>
+      <c r="H163" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I163" s="6" t="inlineStr"/>
+      <c r="J163" s="5" t="inlineStr">
+        <is>
+          <t>prepaid Prezão — preço por dia; recargas a partir de R$15</t>
+        </is>
+      </c>
+      <c r="K163" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L163" s="5" t="inlineStr"/>
+      <c r="M163" s="5" t="inlineStr"/>
+      <c r="N163" s="5" t="inlineStr"/>
+      <c r="O163" s="5" t="inlineStr"/>
+      <c r="P163" s="5" t="inlineStr"/>
+      <c r="Q163" s="5" t="inlineStr"/>
+      <c r="R163" s="5" t="inlineStr"/>
+      <c r="S163" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="T163" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle 41GB</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>tim:162901</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="I164" s="3" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr"/>
+      <c r="O164" s="2" t="inlineStr"/>
+      <c r="P164" s="2" t="inlineStr"/>
+      <c r="Q164" s="2" t="inlineStr"/>
+      <c r="R164" s="2" t="inlineStr"/>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Light Express 31GB</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>tim:143536</t>
+        </is>
+      </c>
+      <c r="H165" s="6" t="n">
+        <v>60.99</v>
+      </c>
+      <c r="I165" s="6" t="inlineStr"/>
+      <c r="J165" s="5" t="inlineStr"/>
+      <c r="K165" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="L165" s="5" t="inlineStr"/>
+      <c r="M165" s="5" t="inlineStr"/>
+      <c r="N165" s="5" t="inlineStr"/>
+      <c r="O165" s="5" t="inlineStr"/>
+      <c r="P165" s="5" t="inlineStr"/>
+      <c r="Q165" s="5" t="inlineStr"/>
+      <c r="R165" s="5" t="inlineStr"/>
+      <c r="S165" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T165" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Plus 45GB</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>tim:155891</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I166" s="3" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="L166" s="2" t="inlineStr"/>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr"/>
+      <c r="O166" s="2" t="inlineStr"/>
+      <c r="P166" s="2" t="inlineStr"/>
+      <c r="Q166" s="2" t="inlineStr"/>
+      <c r="R166" s="2" t="inlineStr"/>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Premium 53GB</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
+          <t>tim:162896</t>
+        </is>
+      </c>
+      <c r="H167" s="6" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="I167" s="6" t="inlineStr"/>
+      <c r="J167" s="5" t="inlineStr"/>
+      <c r="K167" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="L167" s="5" t="inlineStr"/>
+      <c r="M167" s="5" t="inlineStr"/>
+      <c r="N167" s="5" t="inlineStr"/>
+      <c r="O167" s="5" t="inlineStr"/>
+      <c r="P167" s="5" t="inlineStr"/>
+      <c r="Q167" s="5" t="inlineStr"/>
+      <c r="R167" s="5" t="inlineStr"/>
+      <c r="S167" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T167" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Pro Express</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>tim:143576</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I168" s="3" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="4" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr"/>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr"/>
+      <c r="O168" s="2" t="inlineStr"/>
+      <c r="P168" s="2" t="inlineStr"/>
+      <c r="Q168" s="2" t="inlineStr"/>
+      <c r="R168" s="2" t="inlineStr"/>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black 70GB</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr">
+        <is>
+          <t>tim:54206</t>
+        </is>
+      </c>
+      <c r="H169" s="6" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="I169" s="6" t="inlineStr"/>
+      <c r="J169" s="5" t="inlineStr"/>
+      <c r="K169" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="L169" s="5" t="inlineStr"/>
+      <c r="M169" s="5" t="inlineStr"/>
+      <c r="N169" s="5" t="inlineStr"/>
+      <c r="O169" s="5" t="inlineStr"/>
+      <c r="P169" s="5" t="inlineStr"/>
+      <c r="Q169" s="5" t="inlineStr"/>
+      <c r="R169" s="5" t="inlineStr"/>
+      <c r="S169" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T169" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black A Express 67GB</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>tim:55121</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="n">
+        <v>119.99</v>
+      </c>
+      <c r="I170" s="3" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr"/>
+      <c r="O170" s="2" t="inlineStr"/>
+      <c r="P170" s="2" t="inlineStr"/>
+      <c r="Q170" s="2" t="inlineStr"/>
+      <c r="R170" s="2" t="inlineStr"/>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black B Express 82GB</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>tim:52146</t>
+        </is>
+      </c>
+      <c r="H171" s="6" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="I171" s="6" t="inlineStr"/>
+      <c r="J171" s="5" t="inlineStr"/>
+      <c r="K171" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="L171" s="5" t="inlineStr"/>
+      <c r="M171" s="5" t="inlineStr"/>
+      <c r="N171" s="5" t="inlineStr"/>
+      <c r="O171" s="5" t="inlineStr"/>
+      <c r="P171" s="5" t="inlineStr"/>
+      <c r="Q171" s="5" t="inlineStr"/>
+      <c r="R171" s="5" t="inlineStr"/>
+      <c r="S171" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T171" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black C Express 107GB</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>tim:52151</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="I172" s="3" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="L172" s="2" t="inlineStr"/>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr"/>
+      <c r="O172" s="2" t="inlineStr"/>
+      <c r="P172" s="2" t="inlineStr"/>
+      <c r="Q172" s="2" t="inlineStr"/>
+      <c r="R172" s="2" t="inlineStr"/>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black C Ultra 95GB</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>tim:100581</t>
+        </is>
+      </c>
+      <c r="H173" s="6" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I173" s="6" t="inlineStr"/>
+      <c r="J173" s="5" t="inlineStr"/>
+      <c r="K173" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="L173" s="5" t="inlineStr"/>
+      <c r="M173" s="5" t="inlineStr"/>
+      <c r="N173" s="5" t="inlineStr"/>
+      <c r="O173" s="5" t="inlineStr"/>
+      <c r="P173" s="5" t="inlineStr"/>
+      <c r="Q173" s="5" t="inlineStr"/>
+      <c r="R173" s="5" t="inlineStr"/>
+      <c r="S173" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T173" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black Plus 80GB</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>tim:54256</t>
+        </is>
+      </c>
+      <c r="H174" s="3" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="I174" s="3" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="L174" s="2" t="inlineStr"/>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr"/>
+      <c r="O174" s="2" t="inlineStr"/>
+      <c r="P174" s="2" t="inlineStr"/>
+      <c r="Q174" s="2" t="inlineStr"/>
+      <c r="R174" s="2" t="inlineStr"/>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black Premium 110GB</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>tim:54261</t>
+        </is>
+      </c>
+      <c r="H175" s="6" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I175" s="6" t="inlineStr"/>
+      <c r="J175" s="5" t="inlineStr"/>
+      <c r="K175" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="L175" s="5" t="inlineStr"/>
+      <c r="M175" s="5" t="inlineStr"/>
+      <c r="N175" s="5" t="inlineStr"/>
+      <c r="O175" s="5" t="inlineStr"/>
+      <c r="P175" s="5" t="inlineStr"/>
+      <c r="Q175" s="5" t="inlineStr"/>
+      <c r="R175" s="5" t="inlineStr"/>
+      <c r="S175" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="T175" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 16GB</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>tim:106306</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I176" s="3" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="L176" s="2" t="inlineStr"/>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr"/>
+      <c r="O176" s="2" t="inlineStr"/>
+      <c r="P176" s="2" t="inlineStr"/>
+      <c r="Q176" s="2" t="inlineStr"/>
+      <c r="R176" s="2" t="inlineStr"/>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 6GB</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="inlineStr">
+        <is>
+          <t>tim:59906</t>
+        </is>
+      </c>
+      <c r="H177" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I177" s="6" t="inlineStr"/>
+      <c r="J177" s="5" t="inlineStr"/>
+      <c r="K177" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L177" s="5" t="inlineStr"/>
+      <c r="M177" s="5" t="inlineStr"/>
+      <c r="N177" s="5" t="inlineStr"/>
+      <c r="O177" s="5" t="inlineStr"/>
+      <c r="P177" s="5" t="inlineStr"/>
+      <c r="Q177" s="5" t="inlineStr"/>
+      <c r="R177" s="5" t="inlineStr"/>
+      <c r="S177" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="T177" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 8GB</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>tim:59901</t>
+        </is>
+      </c>
+      <c r="H178" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I178" s="3" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L178" s="2" t="inlineStr"/>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr"/>
+      <c r="O178" s="2" t="inlineStr"/>
+      <c r="P178" s="2" t="inlineStr"/>
+      <c r="Q178" s="2" t="inlineStr"/>
+      <c r="R178" s="2" t="inlineStr"/>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029270-46gb</t>
+        </is>
+      </c>
+      <c r="H179" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I179" s="6" t="inlineStr"/>
+      <c r="J179" s="5" t="inlineStr"/>
+      <c r="K179" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="L179" s="5" t="inlineStr">
+        <is>
+          <t>15 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M179" s="5" t="inlineStr"/>
+      <c r="N179" s="5" t="inlineStr"/>
+      <c r="O179" s="5" t="inlineStr"/>
+      <c r="P179" s="5" t="inlineStr"/>
+      <c r="Q179" s="5" t="inlineStr"/>
+      <c r="R179" s="5" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="S179" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T179" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="H180" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I180" s="3" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr"/>
+      <c r="O180" s="2" t="inlineStr"/>
+      <c r="P180" s="2" t="inlineStr"/>
+      <c r="Q180" s="2" t="inlineStr"/>
+      <c r="R180" s="2" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Educação</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029273-61gb</t>
+        </is>
+      </c>
+      <c r="H181" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I181" s="6" t="inlineStr"/>
+      <c r="J181" s="5" t="inlineStr"/>
+      <c r="K181" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L181" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M181" s="5" t="inlineStr"/>
+      <c r="N181" s="5" t="inlineStr"/>
+      <c r="O181" s="5" t="inlineStr"/>
+      <c r="P181" s="5" t="inlineStr"/>
+      <c r="Q181" s="5" t="inlineStr"/>
+      <c r="R181" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vivae inclusa</t>
+        </is>
+      </c>
+      <c r="S181" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T181" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Entretenimento</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="H182" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="I182" s="3" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr"/>
+      <c r="N182" s="2" t="inlineStr"/>
+      <c r="O182" s="2" t="inlineStr"/>
+      <c r="P182" s="2" t="inlineStr"/>
+      <c r="Q182" s="2" t="inlineStr"/>
+      <c r="R182" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Vivo TV Inicial inclusa</t>
+        </is>
+      </c>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Música</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029313-61gb</t>
+        </is>
+      </c>
+      <c r="H183" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="I183" s="6" t="inlineStr"/>
+      <c r="J183" s="5" t="inlineStr"/>
+      <c r="K183" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L183" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M183" s="5" t="inlineStr"/>
+      <c r="N183" s="5" t="inlineStr"/>
+      <c r="O183" s="5" t="inlineStr"/>
+      <c r="P183" s="5" t="inlineStr"/>
+      <c r="Q183" s="5" t="inlineStr"/>
+      <c r="R183" s="5" t="inlineStr">
+        <is>
+          <t>Apple Music Individual</t>
+        </is>
+      </c>
+      <c r="S183" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T183" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="H184" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="I184" s="3" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr"/>
+      <c r="O184" s="2" t="inlineStr"/>
+      <c r="P184" s="2" t="inlineStr"/>
+      <c r="Q184" s="2" t="inlineStr"/>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão com anúncios</t>
+        </is>
+      </c>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Saúde</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029301-61gb</t>
+        </is>
+      </c>
+      <c r="H185" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I185" s="6" t="inlineStr"/>
+      <c r="J185" s="5" t="inlineStr"/>
+      <c r="K185" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L185" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M185" s="5" t="inlineStr"/>
+      <c r="N185" s="5" t="inlineStr"/>
+      <c r="O185" s="5" t="inlineStr"/>
+      <c r="P185" s="5" t="inlineStr"/>
+      <c r="Q185" s="5" t="inlineStr"/>
+      <c r="R185" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vale Saúde Sempre inclusa</t>
+        </is>
+      </c>
+      <c r="S185" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="T185" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025883-30gb</t>
+        </is>
+      </c>
+      <c r="H186" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I186" s="3" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>30 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr"/>
+      <c r="O186" s="2" t="inlineStr"/>
+      <c r="P186" s="2" t="inlineStr"/>
+      <c r="Q186" s="2" t="inlineStr"/>
+      <c r="R186" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="S186" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025885-40gb</t>
+        </is>
+      </c>
+      <c r="H187" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="I187" s="6" t="inlineStr"/>
+      <c r="J187" s="5" t="inlineStr"/>
+      <c r="K187" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L187" s="5" t="inlineStr">
+        <is>
+          <t>40 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M187" s="5" t="inlineStr"/>
+      <c r="N187" s="5" t="inlineStr"/>
+      <c r="O187" s="5" t="inlineStr"/>
+      <c r="P187" s="5" t="inlineStr"/>
+      <c r="Q187" s="5" t="inlineStr"/>
+      <c r="R187" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="S187" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="T187" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025888-20gb</t>
+        </is>
+      </c>
+      <c r="H188" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="I188" s="3" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr"/>
+      <c r="N188" s="2" t="inlineStr"/>
+      <c r="O188" s="2" t="inlineStr"/>
+      <c r="P188" s="2" t="inlineStr"/>
+      <c r="Q188" s="2" t="inlineStr"/>
+      <c r="R188" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Amazon</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029255-60gb</t>
+        </is>
+      </c>
+      <c r="H189" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="I189" s="6" t="inlineStr"/>
+      <c r="J189" s="5" t="inlineStr"/>
+      <c r="K189" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L189" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M189" s="5" t="inlineStr"/>
+      <c r="N189" s="5" t="inlineStr"/>
+      <c r="O189" s="5" t="inlineStr"/>
+      <c r="P189" s="5" t="inlineStr"/>
+      <c r="Q189" s="5" t="inlineStr"/>
+      <c r="R189" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Amazon Prime inclusa</t>
+        </is>
+      </c>
+      <c r="S189" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T189" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Disney+</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022115-60gb</t>
+        </is>
+      </c>
+      <c r="H190" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I190" s="3" t="inlineStr"/>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr"/>
+      <c r="N190" s="2" t="inlineStr"/>
+      <c r="O190" s="2" t="inlineStr"/>
+      <c r="P190" s="2" t="inlineStr">
+        <is>
+          <t>Disney+</t>
+        </is>
+      </c>
+      <c r="Q190" s="2" t="inlineStr"/>
+      <c r="R190" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Disney+ Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="S190" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T190" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Globoplay</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029246-60gb</t>
+        </is>
+      </c>
+      <c r="H191" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="I191" s="6" t="inlineStr"/>
+      <c r="J191" s="5" t="inlineStr"/>
+      <c r="K191" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L191" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M191" s="5" t="inlineStr"/>
+      <c r="N191" s="5" t="inlineStr"/>
+      <c r="O191" s="5" t="inlineStr"/>
+      <c r="P191" s="5" t="inlineStr">
+        <is>
+          <t>Globoplay</t>
+        </is>
+      </c>
+      <c r="Q191" s="5" t="inlineStr"/>
+      <c r="R191" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Globoplay inclusa</t>
+        </is>
+      </c>
+      <c r="S191" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T191" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Netflix</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029234-60gb</t>
+        </is>
+      </c>
+      <c r="H192" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I192" s="3" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr"/>
+      <c r="O192" s="2" t="inlineStr"/>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="Q192" s="2" t="inlineStr"/>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Premiere</t>
+        </is>
+      </c>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029249-60gb</t>
+        </is>
+      </c>
+      <c r="H193" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I193" s="6" t="inlineStr"/>
+      <c r="J193" s="5" t="inlineStr"/>
+      <c r="K193" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L193" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M193" s="5" t="inlineStr"/>
+      <c r="N193" s="5" t="inlineStr"/>
+      <c r="O193" s="5" t="inlineStr"/>
+      <c r="P193" s="5" t="inlineStr">
+        <is>
+          <t>Premiere</t>
+        </is>
+      </c>
+      <c r="Q193" s="5" t="inlineStr"/>
+      <c r="R193" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Premiere inclusa</t>
+        </is>
+      </c>
+      <c r="S193" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T193" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Spotify</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029229-60gb</t>
+        </is>
+      </c>
+      <c r="H194" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="I194" s="3" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr"/>
+      <c r="O194" s="2" t="inlineStr"/>
+      <c r="P194" s="2" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="Q194" s="2" t="inlineStr"/>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Spotify Premium inclusa</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Travel</t>
+        </is>
+      </c>
+      <c r="G195" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029244-70gb</t>
+        </is>
+      </c>
+      <c r="H195" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="I195" s="6" t="inlineStr"/>
+      <c r="J195" s="5" t="inlineStr"/>
+      <c r="K195" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="L195" s="5" t="inlineStr">
+        <is>
+          <t>60 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M195" s="5" t="inlineStr"/>
+      <c r="N195" s="5" t="inlineStr"/>
+      <c r="O195" s="5" t="inlineStr"/>
+      <c r="P195" s="5" t="inlineStr"/>
+      <c r="Q195" s="5" t="inlineStr"/>
+      <c r="R195" s="5" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="S195" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="T195" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-25gb</t>
+        </is>
+      </c>
+      <c r="H196" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I196" s="3" t="inlineStr"/>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr"/>
+      <c r="O196" s="2" t="inlineStr"/>
+      <c r="P196" s="2" t="inlineStr"/>
+      <c r="Q196" s="2" t="inlineStr"/>
+      <c r="R196" s="2" t="inlineStr"/>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G197" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-9gb</t>
+        </is>
+      </c>
+      <c r="H197" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I197" s="6" t="inlineStr"/>
+      <c r="J197" s="5" t="inlineStr"/>
+      <c r="K197" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L197" s="5" t="inlineStr">
+        <is>
+          <t>6 GB para navegar como quiser 3 GB para navegar no YouTube</t>
+        </is>
+      </c>
+      <c r="M197" s="5" t="inlineStr"/>
+      <c r="N197" s="5" t="inlineStr"/>
+      <c r="O197" s="5" t="inlineStr"/>
+      <c r="P197" s="5" t="inlineStr"/>
+      <c r="Q197" s="5" t="inlineStr"/>
+      <c r="R197" s="5" t="inlineStr"/>
+      <c r="S197" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="T197" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-5gb</t>
+        </is>
+      </c>
+      <c r="H198" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I198" s="3" t="inlineStr"/>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>5 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="2" t="inlineStr"/>
+      <c r="O198" s="2" t="inlineStr"/>
+      <c r="P198" s="2" t="inlineStr"/>
+      <c r="Q198" s="2" t="inlineStr"/>
+      <c r="R198" s="2" t="inlineStr"/>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:19:40</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-4gb</t>
+        </is>
+      </c>
+      <c r="H199" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="I199" s="6" t="inlineStr"/>
+      <c r="J199" s="5" t="inlineStr"/>
+      <c r="K199" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L199" s="5" t="inlineStr">
+        <is>
+          <t>4 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M199" s="5" t="inlineStr"/>
+      <c r="N199" s="5" t="inlineStr"/>
+      <c r="O199" s="5" t="inlineStr"/>
+      <c r="P199" s="5" t="inlineStr"/>
+      <c r="Q199" s="5" t="inlineStr"/>
+      <c r="R199" s="5" t="inlineStr"/>
+      <c r="S199" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="T199" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T150"/>
+  <autoFilter ref="A1:T199"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11743,12 +15057,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -11819,12 +15133,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -11889,12 +15203,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -11959,12 +15273,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -12029,12 +15343,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -12099,12 +15413,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -12169,12 +15483,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -12239,12 +15553,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -12309,12 +15623,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -12379,12 +15693,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -12449,12 +15763,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -12519,12 +15833,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -12589,12 +15903,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -12655,12 +15969,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -12717,12 +16031,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -12779,12 +16093,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -12841,12 +16155,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -12903,12 +16217,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -12963,12 +16277,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -13025,12 +16339,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -13087,12 +16401,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -13149,12 +16463,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -13211,12 +16525,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -13273,12 +16587,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -13335,12 +16649,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -13397,12 +16711,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -13459,12 +16773,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -13521,12 +16835,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -13583,12 +16897,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -13653,12 +16967,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -13723,12 +17037,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -13793,12 +17107,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -13863,12 +17177,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -13933,12 +17247,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -14003,12 +17317,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -14073,12 +17387,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -14126,7 +17440,7 @@
       <c r="Q37" s="5" t="inlineStr"/>
       <c r="R37" s="5" t="inlineStr">
         <is>
-          <t>2 meses de YouTube sem desconto no plano</t>
+          <t>2 meses de YouTube sem consumo no plano</t>
         </is>
       </c>
       <c r="S37" s="5" t="inlineStr">
@@ -14143,12 +17457,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -14196,7 +17510,7 @@
       <c r="Q38" s="2" t="inlineStr"/>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>2 meses de YouTube sem desconto no plano</t>
+          <t>2 meses de YouTube sem consumo no plano</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -14213,12 +17527,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -14266,7 +17580,7 @@
       <c r="Q39" s="5" t="inlineStr"/>
       <c r="R39" s="5" t="inlineStr">
         <is>
-          <t>2 meses de YouTube sem desconto no plano</t>
+          <t>2 meses de YouTube sem consumo no plano</t>
         </is>
       </c>
       <c r="S39" s="5" t="inlineStr">
@@ -14283,12 +17597,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -14353,12 +17667,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -14427,12 +17741,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -14501,12 +17815,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -14575,12 +17889,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -14649,12 +17963,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -14723,12 +18037,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -14793,12 +18107,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -14823,7 +18137,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600022379-25gb</t>
+          <t>vivo:VIV202600029370-25gb</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
@@ -14859,12 +18173,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -14889,7 +18203,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600022379-9gb</t>
+          <t>vivo:VIV202600029370-9gb</t>
         </is>
       </c>
       <c r="H48" s="3" t="n">
@@ -14925,12 +18239,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -14955,7 +18269,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600022379-5gb</t>
+          <t>vivo:VIV202600029370-5gb</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
@@ -14991,12 +18305,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -15021,7 +18335,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600022379-4gb</t>
+          <t>vivo:VIV202600029370-4gb</t>
         </is>
       </c>
       <c r="H50" s="3" t="n">
@@ -15084,7 +18398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15158,7 +18472,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>lite</t>
+          <t>prepaid</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -15168,12 +18482,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600025883-30gb</t>
+          <t>vivo:VIV202600029370-25gb</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Easy Lite</t>
+          <t>Vivo Pré</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -15195,7 +18509,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>lite</t>
+          <t>prepaid</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -15205,17 +18519,17 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600025885-40gb</t>
+          <t>vivo:VIV202600029370-4gb</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Easy Lite</t>
+          <t>Vivo Pré</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr"/>
       <c r="H3" s="6" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I3" s="6" t="inlineStr"/>
     </row>
@@ -15232,7 +18546,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>lite</t>
+          <t>prepaid</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -15242,24 +18556,24 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600025888-20gb</t>
+          <t>vivo:VIV202600029370-5gb</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Easy Lite</t>
+          <t>Vivo Pré</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>new</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -15269,7 +18583,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>lite</t>
+          <t>prepaid</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -15279,18 +18593,18 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600005312-30gb</t>
+          <t>vivo:VIV202600029370-9gb</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Easy Lite</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H5" s="6" t="inlineStr"/>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>25</v>
+      </c>
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
@@ -15306,7 +18620,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>lite</t>
+          <t>prepaid</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -15316,16 +18630,16 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600019132-20gb</t>
+          <t>vivo:VIV202600022379-25gb</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Easy Lite</t>
+          <t>Vivo Pré</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
@@ -15343,7 +18657,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>lite</t>
+          <t>prepaid</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -15353,19 +18667,93 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600019134-40gb</t>
+          <t>vivo:VIV202600022379-4gb</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Easy Lite</t>
+          <t>Vivo Pré</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022379-5gb</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022379-9gb</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15404,7 +18792,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:14:36</t>
+          <t>2026-06-25T22:19:40</t>
         </is>
       </c>
     </row>
@@ -15416,7 +18804,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -15437,7 +18825,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -15548,7 +18936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15836,8 +19224,63 @@
         <v/>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B40" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,$A40)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,$A40))</f>
+        <v/>
+      </c>
+      <c r="C40" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,$A40)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,$A40))</f>
+        <v/>
+      </c>
+      <c r="D40" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,$A40)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,$A40))</f>
+        <v/>
+      </c>
+      <c r="E40" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,$A40)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,$A40))</f>
+        <v/>
+      </c>
+      <c r="F40" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,$A40)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,$A40))</f>
+        <v/>
+      </c>
+      <c r="G40" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,$A40)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,$A40))</f>
+        <v/>
+      </c>
+      <c r="H40" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,$A40)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,$A40))</f>
+        <v/>
+      </c>
+      <c r="I40" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,$A40)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,$A40))</f>
+        <v/>
+      </c>
+      <c r="J40" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,$A40)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,$A40))</f>
+        <v/>
+      </c>
+      <c r="K40" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,$A40),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,$A40),0)),"")</f>
+        <v/>
+      </c>
+      <c r="L40" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,$A40),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,$A40),0)),"")</f>
+        <v/>
+      </c>
+      <c r="M40" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,$A40),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,$A40),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>Pre = cheapest recharge amount captured (true R$/day needs validity-days we don't yet capture — CONTEXT §8). Digital = min of Vivo Lite / Claro Flex. Daily rows now; monthly roll-up is the planned next step.</t>
         </is>
@@ -15851,7 +19294,7 @@
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="H35:J35"/>
   </mergeCells>
-  <conditionalFormatting sqref="B37:D39">
+  <conditionalFormatting sqref="B37:D40">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -15863,7 +19306,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E37:G39">
+  <conditionalFormatting sqref="E37:G40">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -15875,7 +19318,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H37:J39">
+  <conditionalFormatting sqref="H37:J40">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -15887,7 +19330,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K37:M39">
+  <conditionalFormatting sqref="K37:M40">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -17187,7 +20630,7 @@
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2 meses de YouTube sem desconto no plano</t>
+          <t>2 meses de YouTube sem consumo no plano</t>
         </is>
       </c>
     </row>
@@ -17211,7 +20654,7 @@
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>2 meses de YouTube sem desconto no plano</t>
+          <t>2 meses de YouTube sem consumo no plano</t>
         </is>
       </c>
     </row>
@@ -17235,7 +20678,7 @@
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2 meses de YouTube sem desconto no plano</t>
+          <t>2 meses de YouTube sem consumo no plano</t>
         </is>
       </c>
     </row>

--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -19,7 +19,7 @@
     <sheet name="TIM" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$U$254</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$U$309</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$U$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -300,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$7</f>
+              <f>'comparison'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$B$3:$B$7</f>
+              <f>'comparison'!$B$3:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -337,12 +337,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$7</f>
+              <f>'comparison'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$C$3:$C$7</f>
+              <f>'comparison'!$C$3:$C$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -374,12 +374,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$7</f>
+              <f>'comparison'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$D$3:$D$7</f>
+              <f>'comparison'!$D$3:$D$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$7</f>
+              <f>'comparison'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$E$3:$E$7</f>
+              <f>'comparison'!$E$3:$E$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -534,12 +534,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$7</f>
+              <f>'comparison'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$F$3:$F$7</f>
+              <f>'comparison'!$F$3:$F$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -571,12 +571,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$7</f>
+              <f>'comparison'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$G$3:$G$7</f>
+              <f>'comparison'!$G$3:$G$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,12 +694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$7</f>
+              <f>'comparison'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$H$3:$H$7</f>
+              <f>'comparison'!$H$3:$H$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -731,12 +731,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$7</f>
+              <f>'comparison'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$I$3:$I$7</f>
+              <f>'comparison'!$I$3:$I$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -768,12 +768,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$7</f>
+              <f>'comparison'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$J$3:$J$7</f>
+              <f>'comparison'!$J$3:$J$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -891,12 +891,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$7</f>
+              <f>'comparison'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$K$3:$K$7</f>
+              <f>'comparison'!$K$3:$K$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -928,12 +928,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$7</f>
+              <f>'comparison'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$L$3:$L$7</f>
+              <f>'comparison'!$L$3:$L$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -965,12 +965,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$7</f>
+              <f>'comparison'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$M$3:$M$7</f>
+              <f>'comparison'!$M$3:$M$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1602,7 +1602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U254"/>
+  <dimension ref="A1:U309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -19094,8 +19094,3801 @@
         </is>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B255" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C255" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D255" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F255" s="5" t="inlineStr">
+        <is>
+          <t>Controle 25GB</t>
+        </is>
+      </c>
+      <c r="G255" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-25gb</t>
+        </is>
+      </c>
+      <c r="H255" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I255" s="6" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="J255" s="5" t="inlineStr">
+        <is>
+          <t>De R$ 59,90 Por:</t>
+        </is>
+      </c>
+      <c r="K255" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="L255" s="5" t="inlineStr"/>
+      <c r="M255" s="5" t="inlineStr"/>
+      <c r="N255" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O255" s="5" t="inlineStr"/>
+      <c r="P255" s="5" t="inlineStr"/>
+      <c r="Q255" s="5" t="inlineStr"/>
+      <c r="R255" s="5" t="inlineStr"/>
+      <c r="S255" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e vídeos; Bônus exclusivo; Aproveite na sua franquia; WhatsApp e ligações ilimitadas</t>
+        </is>
+      </c>
+      <c r="T255" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U255" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb</t>
+        </is>
+      </c>
+      <c r="H256" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I256" s="3" t="inlineStr"/>
+      <c r="J256" s="2" t="inlineStr"/>
+      <c r="K256" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L256" s="2" t="inlineStr"/>
+      <c r="M256" s="2" t="inlineStr"/>
+      <c r="N256" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O256" s="2" t="inlineStr"/>
+      <c r="P256" s="2" t="inlineStr"/>
+      <c r="Q256" s="2" t="inlineStr"/>
+      <c r="R256" s="2" t="inlineStr"/>
+      <c r="S256" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U256" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B257" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C257" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D257" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E257" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F257" s="5" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G257" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb-gaming</t>
+        </is>
+      </c>
+      <c r="H257" s="6" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I257" s="6" t="inlineStr"/>
+      <c r="J257" s="5" t="inlineStr"/>
+      <c r="K257" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L257" s="5" t="inlineStr"/>
+      <c r="M257" s="5" t="inlineStr"/>
+      <c r="N257" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O257" s="5" t="inlineStr"/>
+      <c r="P257" s="5" t="inlineStr"/>
+      <c r="Q257" s="5" t="inlineStr"/>
+      <c r="R257" s="5" t="inlineStr"/>
+      <c r="S257" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus para redes sociais e apps; Bônus uso livre; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T257" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U257" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Flex 15GB</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-15gb</t>
+        </is>
+      </c>
+      <c r="H258" s="3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I258" s="3" t="inlineStr"/>
+      <c r="J258" s="2" t="inlineStr"/>
+      <c r="K258" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L258" s="2" t="inlineStr"/>
+      <c r="M258" s="2" t="inlineStr"/>
+      <c r="N258" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O258" s="2" t="inlineStr"/>
+      <c r="P258" s="2" t="inlineStr"/>
+      <c r="Q258" s="2" t="inlineStr"/>
+      <c r="R258" s="2" t="inlineStr"/>
+      <c r="S258" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U258" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B259" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D259" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E259" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F259" s="5" t="inlineStr">
+        <is>
+          <t>Flex 20GB</t>
+        </is>
+      </c>
+      <c r="G259" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-20gb</t>
+        </is>
+      </c>
+      <c r="H259" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I259" s="6" t="inlineStr"/>
+      <c r="J259" s="5" t="inlineStr"/>
+      <c r="K259" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L259" s="5" t="inlineStr"/>
+      <c r="M259" s="5" t="inlineStr"/>
+      <c r="N259" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O259" s="5" t="inlineStr"/>
+      <c r="P259" s="5" t="inlineStr"/>
+      <c r="Q259" s="5" t="inlineStr"/>
+      <c r="R259" s="5" t="inlineStr"/>
+      <c r="S259" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T259" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U259" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Flex 30GB</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-30gb</t>
+        </is>
+      </c>
+      <c r="H260" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I260" s="3" t="inlineStr"/>
+      <c r="J260" s="2" t="inlineStr"/>
+      <c r="K260" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L260" s="2" t="inlineStr"/>
+      <c r="M260" s="2" t="inlineStr"/>
+      <c r="N260" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O260" s="2" t="inlineStr"/>
+      <c r="P260" s="2" t="inlineStr"/>
+      <c r="Q260" s="2" t="inlineStr"/>
+      <c r="R260" s="2" t="inlineStr"/>
+      <c r="S260" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="T260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U260" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B261" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F261" s="5" t="inlineStr">
+        <is>
+          <t>Flex 40GB</t>
+        </is>
+      </c>
+      <c r="G261" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-40gb</t>
+        </is>
+      </c>
+      <c r="H261" s="6" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I261" s="6" t="inlineStr"/>
+      <c r="J261" s="5" t="inlineStr"/>
+      <c r="K261" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L261" s="5" t="inlineStr"/>
+      <c r="M261" s="5" t="inlineStr"/>
+      <c r="N261" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O261" s="5" t="inlineStr"/>
+      <c r="P261" s="5" t="inlineStr"/>
+      <c r="Q261" s="5" t="inlineStr"/>
+      <c r="R261" s="5" t="inlineStr"/>
+      <c r="S261" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e apps; Bônus uso livre; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="T261" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U261" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Pós 100GB</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-100gb</t>
+        </is>
+      </c>
+      <c r="H262" s="3" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="I262" s="3" t="inlineStr"/>
+      <c r="J262" s="2" t="inlineStr"/>
+      <c r="K262" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L262" s="2" t="inlineStr"/>
+      <c r="M262" s="2" t="inlineStr"/>
+      <c r="N262" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O262" s="2" t="inlineStr"/>
+      <c r="P262" s="2" t="inlineStr"/>
+      <c r="Q262" s="2" t="inlineStr"/>
+      <c r="R262" s="2" t="inlineStr"/>
+      <c r="S262" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U262" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B263" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>Pós 150GB</t>
+        </is>
+      </c>
+      <c r="G263" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-150gb</t>
+        </is>
+      </c>
+      <c r="H263" s="6" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="I263" s="6" t="inlineStr"/>
+      <c r="J263" s="5" t="inlineStr"/>
+      <c r="K263" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="L263" s="5" t="inlineStr"/>
+      <c r="M263" s="5" t="inlineStr"/>
+      <c r="N263" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O263" s="5" t="inlineStr"/>
+      <c r="P263" s="5" t="inlineStr"/>
+      <c r="Q263" s="5" t="inlineStr"/>
+      <c r="R263" s="5" t="inlineStr"/>
+      <c r="S263" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas e Europa; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T263" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U263" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Pós 200GB</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-200gb</t>
+        </is>
+      </c>
+      <c r="H264" s="3" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="I264" s="3" t="inlineStr"/>
+      <c r="J264" s="2" t="inlineStr"/>
+      <c r="K264" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="L264" s="2" t="inlineStr"/>
+      <c r="M264" s="2" t="inlineStr"/>
+      <c r="N264" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O264" s="2" t="inlineStr"/>
+      <c r="P264" s="2" t="inlineStr"/>
+      <c r="Q264" s="2" t="inlineStr"/>
+      <c r="R264" s="2" t="inlineStr"/>
+      <c r="S264" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U264" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>Pós 50GB com GeForce NOW</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb-geforce</t>
+        </is>
+      </c>
+      <c r="H265" s="6" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="I265" s="6" t="inlineStr"/>
+      <c r="J265" s="5" t="inlineStr"/>
+      <c r="K265" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="L265" s="5" t="inlineStr"/>
+      <c r="M265" s="5" t="inlineStr"/>
+      <c r="N265" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O265" s="5" t="inlineStr"/>
+      <c r="P265" s="5" t="inlineStr"/>
+      <c r="Q265" s="5" t="inlineStr"/>
+      <c r="R265" s="5" t="inlineStr"/>
+      <c r="S265" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado; Inclusa assinatura GeForce NOW</t>
+        </is>
+      </c>
+      <c r="T265" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U265" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Pós 60GB</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb</t>
+        </is>
+      </c>
+      <c r="H266" s="3" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="I266" s="3" t="inlineStr"/>
+      <c r="J266" s="2" t="inlineStr"/>
+      <c r="K266" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L266" s="2" t="inlineStr"/>
+      <c r="M266" s="2" t="inlineStr"/>
+      <c r="N266" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O266" s="2" t="inlineStr"/>
+      <c r="P266" s="2" t="inlineStr"/>
+      <c r="Q266" s="2" t="inlineStr"/>
+      <c r="R266" s="2" t="inlineStr"/>
+      <c r="S266" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U266" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 10GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G267" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-10gb</t>
+        </is>
+      </c>
+      <c r="H267" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I267" s="6" t="inlineStr"/>
+      <c r="J267" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K267" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L267" s="5" t="inlineStr"/>
+      <c r="M267" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="N267" s="5" t="inlineStr"/>
+      <c r="O267" s="5" t="inlineStr"/>
+      <c r="P267" s="5" t="inlineStr"/>
+      <c r="Q267" s="5" t="inlineStr"/>
+      <c r="R267" s="5" t="inlineStr"/>
+      <c r="S267" s="5" t="inlineStr"/>
+      <c r="T267" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U267" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 12GB (30 dias)</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-30d-12gb</t>
+        </is>
+      </c>
+      <c r="H268" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I268" s="3" t="inlineStr"/>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$30 — validade 30 dias</t>
+        </is>
+      </c>
+      <c r="K268" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L268" s="2" t="inlineStr"/>
+      <c r="M268" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N268" s="2" t="inlineStr"/>
+      <c r="O268" s="2" t="inlineStr"/>
+      <c r="P268" s="2" t="inlineStr"/>
+      <c r="Q268" s="2" t="inlineStr"/>
+      <c r="R268" s="2" t="inlineStr"/>
+      <c r="S268" s="2" t="inlineStr"/>
+      <c r="T268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U268" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 4GB (12 dias)</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-12d-4gb</t>
+        </is>
+      </c>
+      <c r="H269" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I269" s="6" t="inlineStr"/>
+      <c r="J269" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$15 — validade 12 dias</t>
+        </is>
+      </c>
+      <c r="K269" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L269" s="5" t="inlineStr"/>
+      <c r="M269" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N269" s="5" t="inlineStr"/>
+      <c r="O269" s="5" t="inlineStr"/>
+      <c r="P269" s="5" t="inlineStr"/>
+      <c r="Q269" s="5" t="inlineStr"/>
+      <c r="R269" s="5" t="inlineStr"/>
+      <c r="S269" s="5" t="inlineStr"/>
+      <c r="T269" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U269" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 5GB (15 dias)</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-15d-5gb</t>
+        </is>
+      </c>
+      <c r="H270" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I270" s="3" t="inlineStr"/>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$15 — validade 15 dias</t>
+        </is>
+      </c>
+      <c r="K270" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L270" s="2" t="inlineStr"/>
+      <c r="M270" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N270" s="2" t="inlineStr"/>
+      <c r="O270" s="2" t="inlineStr"/>
+      <c r="P270" s="2" t="inlineStr"/>
+      <c r="Q270" s="2" t="inlineStr"/>
+      <c r="R270" s="2" t="inlineStr"/>
+      <c r="S270" s="2" t="inlineStr"/>
+      <c r="T270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U270" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 6GB (20 dias)</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-20d-6gb</t>
+        </is>
+      </c>
+      <c r="H271" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I271" s="6" t="inlineStr"/>
+      <c r="J271" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$20 — validade 20 dias</t>
+        </is>
+      </c>
+      <c r="K271" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L271" s="5" t="inlineStr"/>
+      <c r="M271" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="N271" s="5" t="inlineStr"/>
+      <c r="O271" s="5" t="inlineStr"/>
+      <c r="P271" s="5" t="inlineStr"/>
+      <c r="Q271" s="5" t="inlineStr"/>
+      <c r="R271" s="5" t="inlineStr"/>
+      <c r="S271" s="5" t="inlineStr"/>
+      <c r="T271" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U271" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 8GB (20 dias)</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-20d-8gb</t>
+        </is>
+      </c>
+      <c r="H272" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I272" s="3" t="inlineStr"/>
+      <c r="J272" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$20 — validade 20 dias</t>
+        </is>
+      </c>
+      <c r="K272" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L272" s="2" t="inlineStr"/>
+      <c r="M272" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="N272" s="2" t="inlineStr"/>
+      <c r="O272" s="2" t="inlineStr"/>
+      <c r="P272" s="2" t="inlineStr"/>
+      <c r="Q272" s="2" t="inlineStr"/>
+      <c r="R272" s="2" t="inlineStr"/>
+      <c r="S272" s="2" t="inlineStr"/>
+      <c r="T272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U272" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B273" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F273" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 9GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G273" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-9gb</t>
+        </is>
+      </c>
+      <c r="H273" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I273" s="6" t="inlineStr"/>
+      <c r="J273" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K273" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L273" s="5" t="inlineStr"/>
+      <c r="M273" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="N273" s="5" t="inlineStr"/>
+      <c r="O273" s="5" t="inlineStr"/>
+      <c r="P273" s="5" t="inlineStr"/>
+      <c r="Q273" s="5" t="inlineStr"/>
+      <c r="R273" s="5" t="inlineStr"/>
+      <c r="S273" s="5" t="inlineStr"/>
+      <c r="T273" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U273" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle 41GB</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>tim:162901</t>
+        </is>
+      </c>
+      <c r="H274" s="3" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="I274" s="3" t="inlineStr"/>
+      <c r="J274" s="2" t="inlineStr"/>
+      <c r="K274" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="L274" s="2" t="inlineStr"/>
+      <c r="M274" s="2" t="inlineStr"/>
+      <c r="N274" s="2" t="inlineStr"/>
+      <c r="O274" s="2" t="inlineStr"/>
+      <c r="P274" s="2" t="inlineStr"/>
+      <c r="Q274" s="2" t="inlineStr"/>
+      <c r="R274" s="2" t="inlineStr"/>
+      <c r="S274" s="2" t="inlineStr"/>
+      <c r="T274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U274" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F275" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Light Express 31GB</t>
+        </is>
+      </c>
+      <c r="G275" s="5" t="inlineStr">
+        <is>
+          <t>tim:143536</t>
+        </is>
+      </c>
+      <c r="H275" s="6" t="n">
+        <v>60.99</v>
+      </c>
+      <c r="I275" s="6" t="inlineStr"/>
+      <c r="J275" s="5" t="inlineStr"/>
+      <c r="K275" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="L275" s="5" t="inlineStr"/>
+      <c r="M275" s="5" t="inlineStr"/>
+      <c r="N275" s="5" t="inlineStr"/>
+      <c r="O275" s="5" t="inlineStr"/>
+      <c r="P275" s="5" t="inlineStr"/>
+      <c r="Q275" s="5" t="inlineStr"/>
+      <c r="R275" s="5" t="inlineStr"/>
+      <c r="S275" s="5" t="inlineStr"/>
+      <c r="T275" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U275" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Plus 45GB</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>tim:155891</t>
+        </is>
+      </c>
+      <c r="H276" s="3" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I276" s="3" t="inlineStr"/>
+      <c r="J276" s="2" t="inlineStr"/>
+      <c r="K276" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="L276" s="2" t="inlineStr"/>
+      <c r="M276" s="2" t="inlineStr"/>
+      <c r="N276" s="2" t="inlineStr"/>
+      <c r="O276" s="2" t="inlineStr"/>
+      <c r="P276" s="2" t="inlineStr"/>
+      <c r="Q276" s="2" t="inlineStr"/>
+      <c r="R276" s="2" t="inlineStr"/>
+      <c r="S276" s="2" t="inlineStr"/>
+      <c r="T276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U276" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E277" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Premium 53GB</t>
+        </is>
+      </c>
+      <c r="G277" s="5" t="inlineStr">
+        <is>
+          <t>tim:162896</t>
+        </is>
+      </c>
+      <c r="H277" s="6" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="I277" s="6" t="inlineStr"/>
+      <c r="J277" s="5" t="inlineStr"/>
+      <c r="K277" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="L277" s="5" t="inlineStr"/>
+      <c r="M277" s="5" t="inlineStr"/>
+      <c r="N277" s="5" t="inlineStr"/>
+      <c r="O277" s="5" t="inlineStr"/>
+      <c r="P277" s="5" t="inlineStr"/>
+      <c r="Q277" s="5" t="inlineStr"/>
+      <c r="R277" s="5" t="inlineStr"/>
+      <c r="S277" s="5" t="inlineStr"/>
+      <c r="T277" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U277" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Pro Express</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>tim:143576</t>
+        </is>
+      </c>
+      <c r="H278" s="3" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I278" s="3" t="inlineStr"/>
+      <c r="J278" s="2" t="inlineStr"/>
+      <c r="K278" s="4" t="inlineStr"/>
+      <c r="L278" s="2" t="inlineStr"/>
+      <c r="M278" s="2" t="inlineStr"/>
+      <c r="N278" s="2" t="inlineStr"/>
+      <c r="O278" s="2" t="inlineStr"/>
+      <c r="P278" s="2" t="inlineStr"/>
+      <c r="Q278" s="2" t="inlineStr"/>
+      <c r="R278" s="2" t="inlineStr"/>
+      <c r="S278" s="2" t="inlineStr"/>
+      <c r="T278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U278" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D279" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F279" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black 70GB</t>
+        </is>
+      </c>
+      <c r="G279" s="5" t="inlineStr">
+        <is>
+          <t>tim:54206</t>
+        </is>
+      </c>
+      <c r="H279" s="6" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="I279" s="6" t="inlineStr"/>
+      <c r="J279" s="5" t="inlineStr"/>
+      <c r="K279" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="L279" s="5" t="inlineStr"/>
+      <c r="M279" s="5" t="inlineStr"/>
+      <c r="N279" s="5" t="inlineStr"/>
+      <c r="O279" s="5" t="inlineStr"/>
+      <c r="P279" s="5" t="inlineStr"/>
+      <c r="Q279" s="5" t="inlineStr"/>
+      <c r="R279" s="5" t="inlineStr"/>
+      <c r="S279" s="5" t="inlineStr"/>
+      <c r="T279" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U279" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black A Express 67GB</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>tim:55121</t>
+        </is>
+      </c>
+      <c r="H280" s="3" t="n">
+        <v>119.99</v>
+      </c>
+      <c r="I280" s="3" t="inlineStr"/>
+      <c r="J280" s="2" t="inlineStr"/>
+      <c r="K280" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="L280" s="2" t="inlineStr"/>
+      <c r="M280" s="2" t="inlineStr"/>
+      <c r="N280" s="2" t="inlineStr"/>
+      <c r="O280" s="2" t="inlineStr"/>
+      <c r="P280" s="2" t="inlineStr"/>
+      <c r="Q280" s="2" t="inlineStr"/>
+      <c r="R280" s="2" t="inlineStr"/>
+      <c r="S280" s="2" t="inlineStr"/>
+      <c r="T280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U280" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B281" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F281" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black B Express 82GB</t>
+        </is>
+      </c>
+      <c r="G281" s="5" t="inlineStr">
+        <is>
+          <t>tim:52146</t>
+        </is>
+      </c>
+      <c r="H281" s="6" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="I281" s="6" t="inlineStr"/>
+      <c r="J281" s="5" t="inlineStr"/>
+      <c r="K281" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="L281" s="5" t="inlineStr"/>
+      <c r="M281" s="5" t="inlineStr"/>
+      <c r="N281" s="5" t="inlineStr"/>
+      <c r="O281" s="5" t="inlineStr"/>
+      <c r="P281" s="5" t="inlineStr"/>
+      <c r="Q281" s="5" t="inlineStr"/>
+      <c r="R281" s="5" t="inlineStr"/>
+      <c r="S281" s="5" t="inlineStr"/>
+      <c r="T281" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U281" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black C Express 107GB</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>tim:52151</t>
+        </is>
+      </c>
+      <c r="H282" s="3" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="I282" s="3" t="inlineStr"/>
+      <c r="J282" s="2" t="inlineStr"/>
+      <c r="K282" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="L282" s="2" t="inlineStr"/>
+      <c r="M282" s="2" t="inlineStr"/>
+      <c r="N282" s="2" t="inlineStr"/>
+      <c r="O282" s="2" t="inlineStr"/>
+      <c r="P282" s="2" t="inlineStr"/>
+      <c r="Q282" s="2" t="inlineStr"/>
+      <c r="R282" s="2" t="inlineStr"/>
+      <c r="S282" s="2" t="inlineStr"/>
+      <c r="T282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U282" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B283" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F283" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black C Ultra 95GB</t>
+        </is>
+      </c>
+      <c r="G283" s="5" t="inlineStr">
+        <is>
+          <t>tim:100581</t>
+        </is>
+      </c>
+      <c r="H283" s="6" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I283" s="6" t="inlineStr"/>
+      <c r="J283" s="5" t="inlineStr"/>
+      <c r="K283" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="L283" s="5" t="inlineStr"/>
+      <c r="M283" s="5" t="inlineStr"/>
+      <c r="N283" s="5" t="inlineStr"/>
+      <c r="O283" s="5" t="inlineStr"/>
+      <c r="P283" s="5" t="inlineStr"/>
+      <c r="Q283" s="5" t="inlineStr"/>
+      <c r="R283" s="5" t="inlineStr"/>
+      <c r="S283" s="5" t="inlineStr"/>
+      <c r="T283" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U283" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black Plus 80GB</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>tim:54256</t>
+        </is>
+      </c>
+      <c r="H284" s="3" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="I284" s="3" t="inlineStr"/>
+      <c r="J284" s="2" t="inlineStr"/>
+      <c r="K284" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="L284" s="2" t="inlineStr"/>
+      <c r="M284" s="2" t="inlineStr"/>
+      <c r="N284" s="2" t="inlineStr"/>
+      <c r="O284" s="2" t="inlineStr"/>
+      <c r="P284" s="2" t="inlineStr"/>
+      <c r="Q284" s="2" t="inlineStr"/>
+      <c r="R284" s="2" t="inlineStr"/>
+      <c r="S284" s="2" t="inlineStr"/>
+      <c r="T284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U284" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B285" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C285" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D285" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F285" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black Premium 110GB</t>
+        </is>
+      </c>
+      <c r="G285" s="5" t="inlineStr">
+        <is>
+          <t>tim:54261</t>
+        </is>
+      </c>
+      <c r="H285" s="6" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I285" s="6" t="inlineStr"/>
+      <c r="J285" s="5" t="inlineStr"/>
+      <c r="K285" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="L285" s="5" t="inlineStr"/>
+      <c r="M285" s="5" t="inlineStr"/>
+      <c r="N285" s="5" t="inlineStr"/>
+      <c r="O285" s="5" t="inlineStr"/>
+      <c r="P285" s="5" t="inlineStr"/>
+      <c r="Q285" s="5" t="inlineStr"/>
+      <c r="R285" s="5" t="inlineStr"/>
+      <c r="S285" s="5" t="inlineStr"/>
+      <c r="T285" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U285" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 16GB</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>tim:106306</t>
+        </is>
+      </c>
+      <c r="H286" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I286" s="3" t="inlineStr"/>
+      <c r="J286" s="2" t="inlineStr"/>
+      <c r="K286" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="L286" s="2" t="inlineStr"/>
+      <c r="M286" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N286" s="2" t="inlineStr"/>
+      <c r="O286" s="2" t="inlineStr"/>
+      <c r="P286" s="2" t="inlineStr"/>
+      <c r="Q286" s="2" t="inlineStr"/>
+      <c r="R286" s="2" t="inlineStr"/>
+      <c r="S286" s="2" t="inlineStr"/>
+      <c r="T286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U286" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B287" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D287" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F287" s="5" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 6GB</t>
+        </is>
+      </c>
+      <c r="G287" s="5" t="inlineStr">
+        <is>
+          <t>tim:59906</t>
+        </is>
+      </c>
+      <c r="H287" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I287" s="6" t="inlineStr"/>
+      <c r="J287" s="5" t="inlineStr"/>
+      <c r="K287" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L287" s="5" t="inlineStr"/>
+      <c r="M287" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N287" s="5" t="inlineStr"/>
+      <c r="O287" s="5" t="inlineStr"/>
+      <c r="P287" s="5" t="inlineStr"/>
+      <c r="Q287" s="5" t="inlineStr"/>
+      <c r="R287" s="5" t="inlineStr"/>
+      <c r="S287" s="5" t="inlineStr"/>
+      <c r="T287" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U287" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 8GB</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>tim:59901</t>
+        </is>
+      </c>
+      <c r="H288" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I288" s="3" t="inlineStr"/>
+      <c r="J288" s="2" t="inlineStr"/>
+      <c r="K288" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L288" s="2" t="inlineStr"/>
+      <c r="M288" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N288" s="2" t="inlineStr"/>
+      <c r="O288" s="2" t="inlineStr"/>
+      <c r="P288" s="2" t="inlineStr"/>
+      <c r="Q288" s="2" t="inlineStr"/>
+      <c r="R288" s="2" t="inlineStr"/>
+      <c r="S288" s="2" t="inlineStr"/>
+      <c r="T288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U288" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B289" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D289" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F289" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G289" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029270-46gb</t>
+        </is>
+      </c>
+      <c r="H289" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I289" s="6" t="inlineStr"/>
+      <c r="J289" s="5" t="inlineStr"/>
+      <c r="K289" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="L289" s="5" t="inlineStr">
+        <is>
+          <t>15 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M289" s="5" t="inlineStr"/>
+      <c r="N289" s="5" t="inlineStr"/>
+      <c r="O289" s="5" t="inlineStr"/>
+      <c r="P289" s="5" t="inlineStr"/>
+      <c r="Q289" s="5" t="inlineStr"/>
+      <c r="R289" s="5" t="inlineStr"/>
+      <c r="S289" s="5" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="T289" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U289" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="H290" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I290" s="3" t="inlineStr"/>
+      <c r="J290" s="2" t="inlineStr"/>
+      <c r="K290" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M290" s="2" t="inlineStr"/>
+      <c r="N290" s="2" t="inlineStr"/>
+      <c r="O290" s="2" t="inlineStr"/>
+      <c r="P290" s="2" t="inlineStr"/>
+      <c r="Q290" s="2" t="inlineStr"/>
+      <c r="R290" s="2" t="inlineStr"/>
+      <c r="S290" s="2" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="T290" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U290" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B291" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C291" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D291" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E291" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F291" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Educação</t>
+        </is>
+      </c>
+      <c r="G291" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029273-61gb</t>
+        </is>
+      </c>
+      <c r="H291" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I291" s="6" t="inlineStr"/>
+      <c r="J291" s="5" t="inlineStr"/>
+      <c r="K291" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L291" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M291" s="5" t="inlineStr"/>
+      <c r="N291" s="5" t="inlineStr"/>
+      <c r="O291" s="5" t="inlineStr"/>
+      <c r="P291" s="5" t="inlineStr"/>
+      <c r="Q291" s="5" t="inlineStr"/>
+      <c r="R291" s="5" t="inlineStr"/>
+      <c r="S291" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vivae inclusa</t>
+        </is>
+      </c>
+      <c r="T291" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U291" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Entretenimento</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="H292" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="I292" s="3" t="inlineStr"/>
+      <c r="J292" s="2" t="inlineStr"/>
+      <c r="K292" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="inlineStr"/>
+      <c r="N292" s="2" t="inlineStr"/>
+      <c r="O292" s="2" t="inlineStr"/>
+      <c r="P292" s="2" t="inlineStr"/>
+      <c r="Q292" s="2" t="inlineStr"/>
+      <c r="R292" s="2" t="inlineStr"/>
+      <c r="S292" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Vivo TV Inicial inclusa</t>
+        </is>
+      </c>
+      <c r="T292" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U292" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B293" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E293" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F293" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Música</t>
+        </is>
+      </c>
+      <c r="G293" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029313-61gb</t>
+        </is>
+      </c>
+      <c r="H293" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="I293" s="6" t="inlineStr"/>
+      <c r="J293" s="5" t="inlineStr"/>
+      <c r="K293" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L293" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M293" s="5" t="inlineStr"/>
+      <c r="N293" s="5" t="inlineStr"/>
+      <c r="O293" s="5" t="inlineStr"/>
+      <c r="P293" s="5" t="inlineStr"/>
+      <c r="Q293" s="5" t="inlineStr"/>
+      <c r="R293" s="5" t="inlineStr"/>
+      <c r="S293" s="5" t="inlineStr">
+        <is>
+          <t>Apple Music Individual</t>
+        </is>
+      </c>
+      <c r="T293" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U293" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="H294" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="I294" s="3" t="inlineStr"/>
+      <c r="J294" s="2" t="inlineStr"/>
+      <c r="K294" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="inlineStr"/>
+      <c r="N294" s="2" t="inlineStr"/>
+      <c r="O294" s="2" t="inlineStr"/>
+      <c r="P294" s="2" t="inlineStr"/>
+      <c r="Q294" s="2" t="inlineStr"/>
+      <c r="R294" s="2" t="inlineStr"/>
+      <c r="S294" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão com anúncios</t>
+        </is>
+      </c>
+      <c r="T294" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U294" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B295" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E295" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Saúde</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029301-61gb</t>
+        </is>
+      </c>
+      <c r="H295" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I295" s="6" t="inlineStr"/>
+      <c r="J295" s="5" t="inlineStr"/>
+      <c r="K295" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L295" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M295" s="5" t="inlineStr"/>
+      <c r="N295" s="5" t="inlineStr"/>
+      <c r="O295" s="5" t="inlineStr"/>
+      <c r="P295" s="5" t="inlineStr"/>
+      <c r="Q295" s="5" t="inlineStr"/>
+      <c r="R295" s="5" t="inlineStr"/>
+      <c r="S295" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vale Saúde Sempre inclusa</t>
+        </is>
+      </c>
+      <c r="T295" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U295" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025883-30gb</t>
+        </is>
+      </c>
+      <c r="H296" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I296" s="3" t="inlineStr"/>
+      <c r="J296" s="2" t="inlineStr"/>
+      <c r="K296" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>30 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="inlineStr"/>
+      <c r="N296" s="2" t="inlineStr"/>
+      <c r="O296" s="2" t="inlineStr"/>
+      <c r="P296" s="2" t="inlineStr"/>
+      <c r="Q296" s="2" t="inlineStr"/>
+      <c r="R296" s="2" t="inlineStr"/>
+      <c r="S296" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T296" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U296" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E297" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025885-40gb</t>
+        </is>
+      </c>
+      <c r="H297" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="I297" s="6" t="inlineStr"/>
+      <c r="J297" s="5" t="inlineStr"/>
+      <c r="K297" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L297" s="5" t="inlineStr">
+        <is>
+          <t>40 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M297" s="5" t="inlineStr"/>
+      <c r="N297" s="5" t="inlineStr"/>
+      <c r="O297" s="5" t="inlineStr"/>
+      <c r="P297" s="5" t="inlineStr"/>
+      <c r="Q297" s="5" t="inlineStr"/>
+      <c r="R297" s="5" t="inlineStr"/>
+      <c r="S297" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T297" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U297" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025888-20gb</t>
+        </is>
+      </c>
+      <c r="H298" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="I298" s="3" t="inlineStr"/>
+      <c r="J298" s="2" t="inlineStr"/>
+      <c r="K298" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="inlineStr"/>
+      <c r="N298" s="2" t="inlineStr"/>
+      <c r="O298" s="2" t="inlineStr"/>
+      <c r="P298" s="2" t="inlineStr"/>
+      <c r="Q298" s="2" t="inlineStr"/>
+      <c r="R298" s="2" t="inlineStr"/>
+      <c r="S298" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T298" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U298" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B299" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C299" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D299" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E299" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F299" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Amazon</t>
+        </is>
+      </c>
+      <c r="G299" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029255-60gb</t>
+        </is>
+      </c>
+      <c r="H299" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="I299" s="6" t="inlineStr"/>
+      <c r="J299" s="5" t="inlineStr"/>
+      <c r="K299" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L299" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M299" s="5" t="inlineStr"/>
+      <c r="N299" s="5" t="inlineStr"/>
+      <c r="O299" s="5" t="inlineStr"/>
+      <c r="P299" s="5" t="inlineStr"/>
+      <c r="Q299" s="5" t="inlineStr"/>
+      <c r="R299" s="5" t="inlineStr"/>
+      <c r="S299" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Amazon Prime inclusa</t>
+        </is>
+      </c>
+      <c r="T299" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U299" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Disney+</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022115-60gb</t>
+        </is>
+      </c>
+      <c r="H300" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I300" s="3" t="inlineStr"/>
+      <c r="J300" s="2" t="inlineStr"/>
+      <c r="K300" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L300" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M300" s="2" t="inlineStr"/>
+      <c r="N300" s="2" t="inlineStr"/>
+      <c r="O300" s="2" t="inlineStr"/>
+      <c r="P300" s="2" t="inlineStr"/>
+      <c r="Q300" s="2" t="inlineStr">
+        <is>
+          <t>Disney+</t>
+        </is>
+      </c>
+      <c r="R300" s="2" t="inlineStr"/>
+      <c r="S300" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Disney+ Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="T300" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U300" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B301" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C301" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D301" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E301" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F301" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Globoplay</t>
+        </is>
+      </c>
+      <c r="G301" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029246-60gb</t>
+        </is>
+      </c>
+      <c r="H301" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="I301" s="6" t="inlineStr"/>
+      <c r="J301" s="5" t="inlineStr"/>
+      <c r="K301" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L301" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M301" s="5" t="inlineStr"/>
+      <c r="N301" s="5" t="inlineStr"/>
+      <c r="O301" s="5" t="inlineStr"/>
+      <c r="P301" s="5" t="inlineStr"/>
+      <c r="Q301" s="5" t="inlineStr">
+        <is>
+          <t>Globoplay</t>
+        </is>
+      </c>
+      <c r="R301" s="5" t="inlineStr"/>
+      <c r="S301" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Globoplay inclusa</t>
+        </is>
+      </c>
+      <c r="T301" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U301" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Netflix</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029234-60gb</t>
+        </is>
+      </c>
+      <c r="H302" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I302" s="3" t="inlineStr"/>
+      <c r="J302" s="2" t="inlineStr"/>
+      <c r="K302" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L302" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="inlineStr"/>
+      <c r="N302" s="2" t="inlineStr"/>
+      <c r="O302" s="2" t="inlineStr"/>
+      <c r="P302" s="2" t="inlineStr"/>
+      <c r="Q302" s="2" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="R302" s="2" t="inlineStr"/>
+      <c r="S302" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="T302" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U302" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B303" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D303" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F303" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Premiere</t>
+        </is>
+      </c>
+      <c r="G303" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029249-60gb</t>
+        </is>
+      </c>
+      <c r="H303" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I303" s="6" t="inlineStr"/>
+      <c r="J303" s="5" t="inlineStr"/>
+      <c r="K303" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L303" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M303" s="5" t="inlineStr"/>
+      <c r="N303" s="5" t="inlineStr"/>
+      <c r="O303" s="5" t="inlineStr"/>
+      <c r="P303" s="5" t="inlineStr"/>
+      <c r="Q303" s="5" t="inlineStr">
+        <is>
+          <t>Premiere</t>
+        </is>
+      </c>
+      <c r="R303" s="5" t="inlineStr"/>
+      <c r="S303" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Premiere inclusa</t>
+        </is>
+      </c>
+      <c r="T303" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U303" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Spotify</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029229-60gb</t>
+        </is>
+      </c>
+      <c r="H304" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="I304" s="3" t="inlineStr"/>
+      <c r="J304" s="2" t="inlineStr"/>
+      <c r="K304" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L304" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="inlineStr"/>
+      <c r="N304" s="2" t="inlineStr"/>
+      <c r="O304" s="2" t="inlineStr"/>
+      <c r="P304" s="2" t="inlineStr"/>
+      <c r="Q304" s="2" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="R304" s="2" t="inlineStr"/>
+      <c r="S304" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Spotify Premium inclusa</t>
+        </is>
+      </c>
+      <c r="T304" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U304" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B305" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C305" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D305" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E305" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F305" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Travel</t>
+        </is>
+      </c>
+      <c r="G305" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029244-70gb</t>
+        </is>
+      </c>
+      <c r="H305" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="I305" s="6" t="inlineStr"/>
+      <c r="J305" s="5" t="inlineStr"/>
+      <c r="K305" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="L305" s="5" t="inlineStr">
+        <is>
+          <t>60 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M305" s="5" t="inlineStr"/>
+      <c r="N305" s="5" t="inlineStr"/>
+      <c r="O305" s="5" t="inlineStr"/>
+      <c r="P305" s="5" t="inlineStr"/>
+      <c r="Q305" s="5" t="inlineStr"/>
+      <c r="R305" s="5" t="inlineStr"/>
+      <c r="S305" s="5" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="T305" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U305" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-25gb</t>
+        </is>
+      </c>
+      <c r="H306" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I306" s="3" t="inlineStr"/>
+      <c r="J306" s="2" t="inlineStr"/>
+      <c r="K306" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L306" s="2" t="inlineStr">
+        <is>
+          <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N306" s="2" t="inlineStr"/>
+      <c r="O306" s="2" t="inlineStr"/>
+      <c r="P306" s="2" t="inlineStr"/>
+      <c r="Q306" s="2" t="inlineStr"/>
+      <c r="R306" s="2" t="inlineStr"/>
+      <c r="S306" s="2" t="inlineStr"/>
+      <c r="T306" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U306" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B307" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D307" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F307" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G307" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-9gb</t>
+        </is>
+      </c>
+      <c r="H307" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I307" s="6" t="inlineStr"/>
+      <c r="J307" s="5" t="inlineStr"/>
+      <c r="K307" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L307" s="5" t="inlineStr">
+        <is>
+          <t>6 GB para navegar como quiser 3 GB para navegar no YouTube</t>
+        </is>
+      </c>
+      <c r="M307" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="N307" s="5" t="inlineStr"/>
+      <c r="O307" s="5" t="inlineStr"/>
+      <c r="P307" s="5" t="inlineStr"/>
+      <c r="Q307" s="5" t="inlineStr"/>
+      <c r="R307" s="5" t="inlineStr"/>
+      <c r="S307" s="5" t="inlineStr"/>
+      <c r="T307" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U307" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-5gb</t>
+        </is>
+      </c>
+      <c r="H308" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I308" s="3" t="inlineStr"/>
+      <c r="J308" s="2" t="inlineStr"/>
+      <c r="K308" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L308" s="2" t="inlineStr">
+        <is>
+          <t>5 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N308" s="2" t="inlineStr"/>
+      <c r="O308" s="2" t="inlineStr"/>
+      <c r="P308" s="2" t="inlineStr"/>
+      <c r="Q308" s="2" t="inlineStr"/>
+      <c r="R308" s="2" t="inlineStr"/>
+      <c r="S308" s="2" t="inlineStr"/>
+      <c r="T308" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U308" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B309" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T22:00:50</t>
+        </is>
+      </c>
+      <c r="C309" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D309" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F309" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G309" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-4gb</t>
+        </is>
+      </c>
+      <c r="H309" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="I309" s="6" t="inlineStr"/>
+      <c r="J309" s="5" t="inlineStr"/>
+      <c r="K309" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L309" s="5" t="inlineStr">
+        <is>
+          <t>4 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M309" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N309" s="5" t="inlineStr"/>
+      <c r="O309" s="5" t="inlineStr"/>
+      <c r="P309" s="5" t="inlineStr"/>
+      <c r="Q309" s="5" t="inlineStr"/>
+      <c r="R309" s="5" t="inlineStr"/>
+      <c r="S309" s="5" t="inlineStr"/>
+      <c r="T309" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U309" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U254"/>
+  <autoFilter ref="A1:U309"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19684,12 +23477,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -19761,12 +23554,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -19832,12 +23625,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -19903,12 +23696,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -19974,12 +23767,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -20045,12 +23838,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -20116,12 +23909,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -20187,12 +23980,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -20258,12 +24051,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -20329,12 +24122,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -20400,12 +24193,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -20471,12 +24264,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -20542,12 +24335,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -20611,12 +24404,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -20680,12 +24473,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -20749,12 +24542,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -20818,12 +24611,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -20887,12 +24680,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -20956,12 +24749,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -21025,12 +24818,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -21088,12 +24881,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -21151,12 +24944,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -21214,12 +25007,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -21277,12 +25070,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -21338,12 +25131,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -21401,12 +25194,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -21464,12 +25257,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -21527,12 +25320,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -21590,12 +25383,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -21653,12 +25446,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -21716,12 +25509,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -21779,12 +25572,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -21844,12 +25637,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -21909,12 +25702,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -21974,12 +25767,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -22045,12 +25838,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -22075,16 +25868,16 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029300-51gb</t>
+          <t>vivo:VIV202600029300-61gb</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I37" s="6" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr"/>
       <c r="K37" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
@@ -22116,12 +25909,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -22146,16 +25939,16 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029273-51gb</t>
+          <t>vivo:VIV202600029273-61gb</t>
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
@@ -22187,12 +25980,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -22217,16 +26010,16 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029307-51gb</t>
+          <t>vivo:VIV202600029307-61gb</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I39" s="6" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
       <c r="K39" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
@@ -22258,12 +26051,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -22288,16 +26081,16 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029313-51gb</t>
+          <t>vivo:VIV202600029313-61gb</t>
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I40" s="3" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -22329,12 +26122,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -22359,16 +26152,16 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029308-51gb</t>
+          <t>vivo:VIV202600029308-61gb</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I41" s="6" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
       <c r="K41" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
@@ -22400,12 +26193,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -22430,16 +26223,16 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029301-51gb</t>
+          <t>vivo:VIV202600029301-61gb</t>
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
@@ -22471,12 +26264,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -22542,12 +26335,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -22613,12 +26406,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -22684,12 +26477,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -22755,12 +26548,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -22830,12 +26623,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -22905,12 +26698,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -22980,12 +26773,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -23055,12 +26848,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -23130,12 +26923,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -23201,12 +26994,12 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -23270,12 +27063,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -23339,12 +27132,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -23408,12 +27201,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -23504,7 +27297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23573,12 +27366,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>claro</t>
+          <t>vivo</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>prepaid</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -23588,17 +27381,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>claro:prezao-12d-4gb</t>
+          <t>vivo:VIV202600029273-61gb</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Prezão 4GB (12 dias)</t>
+          <t>Vivo Controle Educação</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="I2" s="3" t="inlineStr"/>
     </row>
@@ -23610,12 +27403,12 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>claro</t>
+          <t>vivo</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>prepaid</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -23625,17 +27418,17 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>claro:prezao-15d-5gb</t>
+          <t>vivo:VIV202600029300-61gb</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Prezão 5GB (15 dias)</t>
+          <t>Vivo Controle</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr"/>
       <c r="H3" s="6" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="I3" s="6" t="inlineStr"/>
     </row>
@@ -23647,12 +27440,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>claro</t>
+          <t>vivo</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>prepaid</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -23662,17 +27455,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>claro:prezao-20d-6gb</t>
+          <t>vivo:VIV202600029301-61gb</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Prezão 6GB (20 dias)</t>
+          <t>Vivo Controle Saúde</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
@@ -23684,12 +27477,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>claro</t>
+          <t>vivo</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>prepaid</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -23699,17 +27492,17 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>claro:prezao-20d-8gb</t>
+          <t>vivo:VIV202600029307-61gb</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Prezão 8GB (20 dias)</t>
+          <t>Vivo Controle Entretenimento</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr"/>
       <c r="H5" s="6" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="I5" s="6" t="inlineStr"/>
     </row>
@@ -23721,12 +27514,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>claro</t>
+          <t>vivo</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>prepaid</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -23736,17 +27529,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>claro:prezao-25d-10gb</t>
+          <t>vivo:VIV202600029308-61gb</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Prezão 10GB (25 dias)</t>
+          <t>Vivo Controle Netflix</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="n">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
@@ -23758,12 +27551,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>claro</t>
+          <t>vivo</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>prepaid</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -23773,34 +27566,34 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>claro:prezao-25d-9gb</t>
+          <t>vivo:VIV202600029313-61gb</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Prezão 9GB (25 dias)</t>
+          <t>Vivo Controle Música</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="6" t="n">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>claro</t>
+          <t>vivo</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>prepaid</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -23810,24 +27603,24 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>claro:prezao-30d-12gb</t>
+          <t>vivo:VIV202600029273-51gb</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Prezão 12GB (30 dias)</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="n">
-        <v>30</v>
-      </c>
+          <t>Vivo Controle Educação</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -23847,24 +27640,24 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029273-51gb</t>
+          <t>vivo:VIV202600029300-51gb</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Educação</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="n">
-        <v>85</v>
-      </c>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -23884,24 +27677,24 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029300-51gb</t>
+          <t>vivo:VIV202600029301-51gb</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>Vivo Controle Saúde</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -23921,24 +27714,24 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029301-51gb</t>
+          <t>vivo:VIV202600029307-51gb</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Saúde</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr"/>
-      <c r="H11" s="6" t="n">
-        <v>85</v>
-      </c>
+          <t>Vivo Controle Entretenimento</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
       <c r="I11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -23958,24 +27751,24 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029307-51gb</t>
+          <t>vivo:VIV202600029308-51gb</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Entretenimento</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="n">
-        <v>105</v>
-      </c>
+          <t>Vivo Controle Netflix</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -23995,315 +27788,19 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029308-51gb</t>
+          <t>vivo:VIV202600029313-51gb</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Netflix</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="n">
+          <t>Vivo Controle Música</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
         <v>90</v>
       </c>
+      <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029313-51gb</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Música</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>claro</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>prepaid</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>claro:prez-o-r-1-por-dia</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Prezão R$1 por dia</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029273-61gb</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Educação</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029300-61gb</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Vivo Controle</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="H17" s="6" t="inlineStr"/>
-      <c r="I17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029301-61gb</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Saúde</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029307-61gb</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Vivo Controle Entretenimento</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>110</v>
-      </c>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029308-61gb</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Netflix</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029313-61gb</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Vivo Controle Música</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24342,7 +27839,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T22:10:02</t>
+          <t>2026-06-27T22:00:50</t>
         </is>
       </c>
     </row>
@@ -24354,7 +27851,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -24375,7 +27872,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -24486,7 +27983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24867,8 +28364,61 @@
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="12" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B8" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0)),"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0)),"")</f>
+        <v/>
+      </c>
+      <c r="M8" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Rows = day: each cell = cheapest R$ that carrier offered in the category on that snapshot_date — a live MINIFS over `history` matching the EXACT date (a locale-safe text date built from the row's date, since history stores dates as TEXT — CONTEXT §7). Pre = cheapest 30-day prepaid plan (validity_days &gt;= 28; pre-#18 dates have no validity → blank, fills from 26-Jun on). Digital = min of Vivo Lite / Claro Flex. Heatmap = per-category-block green→yellow (each cell vs all carriers in its category; subtle while prices are near-flat, differentiates as they move). Grows one row per day; charts on the `Charts` sheet.</t>
         </is>
@@ -24882,7 +28432,7 @@
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="K1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:D7">
+  <conditionalFormatting sqref="B3:D8">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -24892,7 +28442,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:G7">
+  <conditionalFormatting sqref="E3:G8">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -24902,7 +28452,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:J7">
+  <conditionalFormatting sqref="H3:J8">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -24912,7 +28462,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:M7">
+  <conditionalFormatting sqref="K3:M8">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -24978,15 +28528,15 @@
         </is>
       </c>
       <c r="Q38" s="10">
-        <f>IF('comparison'!B7="",NA(),'comparison'!B7)</f>
+        <f>IF('comparison'!B8="",NA(),'comparison'!B8)</f>
         <v/>
       </c>
       <c r="R38" s="10">
-        <f>IF('comparison'!C7="",NA(),'comparison'!C7)</f>
+        <f>IF('comparison'!C8="",NA(),'comparison'!C8)</f>
         <v/>
       </c>
       <c r="S38" s="10">
-        <f>IF('comparison'!D7="",NA(),'comparison'!D7)</f>
+        <f>IF('comparison'!D8="",NA(),'comparison'!D8)</f>
         <v/>
       </c>
     </row>
@@ -24997,15 +28547,15 @@
         </is>
       </c>
       <c r="Q39" s="10">
-        <f>IF('comparison'!E7="",NA(),'comparison'!E7)</f>
+        <f>IF('comparison'!E8="",NA(),'comparison'!E8)</f>
         <v/>
       </c>
       <c r="R39" s="10">
-        <f>IF('comparison'!F7="",NA(),'comparison'!F7)</f>
+        <f>IF('comparison'!F8="",NA(),'comparison'!F8)</f>
         <v/>
       </c>
       <c r="S39" s="10">
-        <f>IF('comparison'!G7="",NA(),'comparison'!G7)</f>
+        <f>IF('comparison'!G8="",NA(),'comparison'!G8)</f>
         <v/>
       </c>
     </row>
@@ -25016,15 +28566,15 @@
         </is>
       </c>
       <c r="Q40" s="10">
-        <f>IF('comparison'!H7="",NA(),'comparison'!H7)</f>
+        <f>IF('comparison'!H8="",NA(),'comparison'!H8)</f>
         <v/>
       </c>
       <c r="R40" s="10">
-        <f>IF('comparison'!I7="",NA(),'comparison'!I7)</f>
+        <f>IF('comparison'!I8="",NA(),'comparison'!I8)</f>
         <v/>
       </c>
       <c r="S40" s="10">
-        <f>IF('comparison'!J7="",NA(),'comparison'!J7)</f>
+        <f>IF('comparison'!J8="",NA(),'comparison'!J8)</f>
         <v/>
       </c>
     </row>
@@ -25035,15 +28585,15 @@
         </is>
       </c>
       <c r="Q41" s="10">
-        <f>IF('comparison'!K7="",NA(),'comparison'!K7)</f>
+        <f>IF('comparison'!K8="",NA(),'comparison'!K8)</f>
         <v/>
       </c>
       <c r="R41" s="10">
-        <f>IF('comparison'!L7="",NA(),'comparison'!L7)</f>
+        <f>IF('comparison'!L8="",NA(),'comparison'!L8)</f>
         <v/>
       </c>
       <c r="S41" s="10">
-        <f>IF('comparison'!M7="",NA(),'comparison'!M7)</f>
+        <f>IF('comparison'!M8="",NA(),'comparison'!M8)</f>
         <v/>
       </c>
     </row>
@@ -25390,7 +28940,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>69.90000000000001</v>
@@ -25400,7 +28950,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle (51GB)</t>
+          <t>Vivo Controle (61GB)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -25419,7 +28969,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>99.90000000000001</v>
@@ -25429,7 +28979,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Educação (51GB)</t>
+          <t>Vivo Controle Educação (61GB)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -25448,7 +28998,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C18" s="15" t="n"/>
       <c r="D18" s="6" t="n">
@@ -25456,7 +29006,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Saúde (51GB)</t>
+          <t>Vivo Controle Saúde (61GB)</t>
         </is>
       </c>
       <c r="F18" s="15" t="n"/>
@@ -25471,14 +29021,14 @@
         <v>5</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>84.98999999999999</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Música (51GB)</t>
+          <t>Vivo Controle Música (61GB)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -25492,13 +29042,13 @@
         <v>6</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C20" s="15" t="n"/>
       <c r="D20" s="15" t="n"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Netflix (51GB)</t>
+          <t>Vivo Controle Netflix (61GB)</t>
         </is>
       </c>
       <c r="F20" s="15" t="n"/>
@@ -25509,11 +29059,11 @@
         <v>7</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Entretenimento (51GB)</t>
+          <t>Vivo Controle Entretenimento (61GB)</t>
         </is>
       </c>
     </row>
@@ -26228,12 +29778,12 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E12" s="5" t="n"/>
@@ -26252,12 +29802,12 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -26276,12 +29826,12 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E14" s="5" t="n"/>
@@ -26300,12 +29850,12 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -26324,12 +29874,12 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E16" s="5" t="n"/>
@@ -26348,12 +29898,12 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>

--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -19,7 +19,7 @@
     <sheet name="TIM" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$U$309</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$U$364</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$U$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -300,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$8</f>
+              <f>'comparison'!$A$3:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$B$3:$B$8</f>
+              <f>'comparison'!$B$3:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -337,12 +337,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$8</f>
+              <f>'comparison'!$A$3:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$C$3:$C$8</f>
+              <f>'comparison'!$C$3:$C$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -374,12 +374,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$8</f>
+              <f>'comparison'!$A$3:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$D$3:$D$8</f>
+              <f>'comparison'!$D$3:$D$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$8</f>
+              <f>'comparison'!$A$3:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$E$3:$E$8</f>
+              <f>'comparison'!$E$3:$E$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -534,12 +534,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$8</f>
+              <f>'comparison'!$A$3:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$F$3:$F$8</f>
+              <f>'comparison'!$F$3:$F$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -571,12 +571,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$8</f>
+              <f>'comparison'!$A$3:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$G$3:$G$8</f>
+              <f>'comparison'!$G$3:$G$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,12 +694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$8</f>
+              <f>'comparison'!$A$3:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$H$3:$H$8</f>
+              <f>'comparison'!$H$3:$H$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -731,12 +731,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$8</f>
+              <f>'comparison'!$A$3:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$I$3:$I$8</f>
+              <f>'comparison'!$I$3:$I$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -768,12 +768,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$8</f>
+              <f>'comparison'!$A$3:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$J$3:$J$8</f>
+              <f>'comparison'!$J$3:$J$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -891,12 +891,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$8</f>
+              <f>'comparison'!$A$3:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$K$3:$K$8</f>
+              <f>'comparison'!$K$3:$K$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -928,12 +928,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$8</f>
+              <f>'comparison'!$A$3:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$L$3:$L$8</f>
+              <f>'comparison'!$L$3:$L$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -965,12 +965,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$8</f>
+              <f>'comparison'!$A$3:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$M$3:$M$8</f>
+              <f>'comparison'!$M$3:$M$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1602,7 +1602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U309"/>
+  <dimension ref="A1:U364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -22887,8 +22887,3801 @@
         </is>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>Controle 25GB</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-25gb</t>
+        </is>
+      </c>
+      <c r="H310" s="3" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I310" s="3" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="J310" s="2" t="inlineStr">
+        <is>
+          <t>De R$ 59,90 Por:</t>
+        </is>
+      </c>
+      <c r="K310" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L310" s="2" t="inlineStr"/>
+      <c r="M310" s="2" t="inlineStr"/>
+      <c r="N310" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O310" s="2" t="inlineStr"/>
+      <c r="P310" s="2" t="inlineStr"/>
+      <c r="Q310" s="2" t="inlineStr"/>
+      <c r="R310" s="2" t="inlineStr"/>
+      <c r="S310" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e vídeos; Bônus exclusivo; Aproveite na sua franquia; WhatsApp e ligações ilimitadas</t>
+        </is>
+      </c>
+      <c r="T310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U310" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B311" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C311" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D311" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F311" s="5" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G311" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb</t>
+        </is>
+      </c>
+      <c r="H311" s="6" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I311" s="6" t="inlineStr"/>
+      <c r="J311" s="5" t="inlineStr"/>
+      <c r="K311" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L311" s="5" t="inlineStr"/>
+      <c r="M311" s="5" t="inlineStr"/>
+      <c r="N311" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O311" s="5" t="inlineStr"/>
+      <c r="P311" s="5" t="inlineStr"/>
+      <c r="Q311" s="5" t="inlineStr"/>
+      <c r="R311" s="5" t="inlineStr"/>
+      <c r="S311" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T311" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U311" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb-gaming</t>
+        </is>
+      </c>
+      <c r="H312" s="3" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I312" s="3" t="inlineStr"/>
+      <c r="J312" s="2" t="inlineStr"/>
+      <c r="K312" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L312" s="2" t="inlineStr"/>
+      <c r="M312" s="2" t="inlineStr"/>
+      <c r="N312" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O312" s="2" t="inlineStr"/>
+      <c r="P312" s="2" t="inlineStr"/>
+      <c r="Q312" s="2" t="inlineStr"/>
+      <c r="R312" s="2" t="inlineStr"/>
+      <c r="S312" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus para redes sociais e apps; Bônus uso livre; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U312" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B313" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D313" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F313" s="5" t="inlineStr">
+        <is>
+          <t>Flex 15GB</t>
+        </is>
+      </c>
+      <c r="G313" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-15gb</t>
+        </is>
+      </c>
+      <c r="H313" s="6" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I313" s="6" t="inlineStr"/>
+      <c r="J313" s="5" t="inlineStr"/>
+      <c r="K313" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="L313" s="5" t="inlineStr"/>
+      <c r="M313" s="5" t="inlineStr"/>
+      <c r="N313" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O313" s="5" t="inlineStr"/>
+      <c r="P313" s="5" t="inlineStr"/>
+      <c r="Q313" s="5" t="inlineStr"/>
+      <c r="R313" s="5" t="inlineStr"/>
+      <c r="S313" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T313" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U313" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>Flex 20GB</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-20gb</t>
+        </is>
+      </c>
+      <c r="H314" s="3" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I314" s="3" t="inlineStr"/>
+      <c r="J314" s="2" t="inlineStr"/>
+      <c r="K314" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L314" s="2" t="inlineStr"/>
+      <c r="M314" s="2" t="inlineStr"/>
+      <c r="N314" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O314" s="2" t="inlineStr"/>
+      <c r="P314" s="2" t="inlineStr"/>
+      <c r="Q314" s="2" t="inlineStr"/>
+      <c r="R314" s="2" t="inlineStr"/>
+      <c r="S314" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U314" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B315" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C315" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D315" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E315" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F315" s="5" t="inlineStr">
+        <is>
+          <t>Flex 30GB</t>
+        </is>
+      </c>
+      <c r="G315" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-30gb</t>
+        </is>
+      </c>
+      <c r="H315" s="6" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I315" s="6" t="inlineStr"/>
+      <c r="J315" s="5" t="inlineStr"/>
+      <c r="K315" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L315" s="5" t="inlineStr"/>
+      <c r="M315" s="5" t="inlineStr"/>
+      <c r="N315" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O315" s="5" t="inlineStr"/>
+      <c r="P315" s="5" t="inlineStr"/>
+      <c r="Q315" s="5" t="inlineStr"/>
+      <c r="R315" s="5" t="inlineStr"/>
+      <c r="S315" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="T315" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U315" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>Flex 40GB</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-40gb</t>
+        </is>
+      </c>
+      <c r="H316" s="3" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I316" s="3" t="inlineStr"/>
+      <c r="J316" s="2" t="inlineStr"/>
+      <c r="K316" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L316" s="2" t="inlineStr"/>
+      <c r="M316" s="2" t="inlineStr"/>
+      <c r="N316" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O316" s="2" t="inlineStr"/>
+      <c r="P316" s="2" t="inlineStr"/>
+      <c r="Q316" s="2" t="inlineStr"/>
+      <c r="R316" s="2" t="inlineStr"/>
+      <c r="S316" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e apps; Bônus uso livre; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="T316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U316" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E317" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>Pós 100GB</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-100gb</t>
+        </is>
+      </c>
+      <c r="H317" s="6" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="I317" s="6" t="inlineStr"/>
+      <c r="J317" s="5" t="inlineStr"/>
+      <c r="K317" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="L317" s="5" t="inlineStr"/>
+      <c r="M317" s="5" t="inlineStr"/>
+      <c r="N317" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O317" s="5" t="inlineStr"/>
+      <c r="P317" s="5" t="inlineStr"/>
+      <c r="Q317" s="5" t="inlineStr"/>
+      <c r="R317" s="5" t="inlineStr"/>
+      <c r="S317" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T317" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U317" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>Pós 150GB</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-150gb</t>
+        </is>
+      </c>
+      <c r="H318" s="3" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="I318" s="3" t="inlineStr"/>
+      <c r="J318" s="2" t="inlineStr"/>
+      <c r="K318" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="L318" s="2" t="inlineStr"/>
+      <c r="M318" s="2" t="inlineStr"/>
+      <c r="N318" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O318" s="2" t="inlineStr"/>
+      <c r="P318" s="2" t="inlineStr"/>
+      <c r="Q318" s="2" t="inlineStr"/>
+      <c r="R318" s="2" t="inlineStr"/>
+      <c r="S318" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas e Europa; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U318" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B319" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C319" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D319" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E319" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F319" s="5" t="inlineStr">
+        <is>
+          <t>Pós 200GB</t>
+        </is>
+      </c>
+      <c r="G319" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-200gb</t>
+        </is>
+      </c>
+      <c r="H319" s="6" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="I319" s="6" t="inlineStr"/>
+      <c r="J319" s="5" t="inlineStr"/>
+      <c r="K319" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="L319" s="5" t="inlineStr"/>
+      <c r="M319" s="5" t="inlineStr"/>
+      <c r="N319" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O319" s="5" t="inlineStr"/>
+      <c r="P319" s="5" t="inlineStr"/>
+      <c r="Q319" s="5" t="inlineStr"/>
+      <c r="R319" s="5" t="inlineStr"/>
+      <c r="S319" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T319" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U319" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>Pós 50GB com GeForce NOW</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb-geforce</t>
+        </is>
+      </c>
+      <c r="H320" s="3" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="I320" s="3" t="inlineStr"/>
+      <c r="J320" s="2" t="inlineStr"/>
+      <c r="K320" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="L320" s="2" t="inlineStr"/>
+      <c r="M320" s="2" t="inlineStr"/>
+      <c r="N320" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O320" s="2" t="inlineStr"/>
+      <c r="P320" s="2" t="inlineStr"/>
+      <c r="Q320" s="2" t="inlineStr"/>
+      <c r="R320" s="2" t="inlineStr"/>
+      <c r="S320" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado; Inclusa assinatura GeForce NOW</t>
+        </is>
+      </c>
+      <c r="T320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U320" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E321" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F321" s="5" t="inlineStr">
+        <is>
+          <t>Pós 60GB</t>
+        </is>
+      </c>
+      <c r="G321" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb</t>
+        </is>
+      </c>
+      <c r="H321" s="6" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="I321" s="6" t="inlineStr"/>
+      <c r="J321" s="5" t="inlineStr"/>
+      <c r="K321" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L321" s="5" t="inlineStr"/>
+      <c r="M321" s="5" t="inlineStr"/>
+      <c r="N321" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O321" s="5" t="inlineStr"/>
+      <c r="P321" s="5" t="inlineStr"/>
+      <c r="Q321" s="5" t="inlineStr"/>
+      <c r="R321" s="5" t="inlineStr"/>
+      <c r="S321" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T321" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U321" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 10GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-10gb</t>
+        </is>
+      </c>
+      <c r="H322" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I322" s="3" t="inlineStr"/>
+      <c r="J322" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K322" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L322" s="2" t="inlineStr"/>
+      <c r="M322" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="N322" s="2" t="inlineStr"/>
+      <c r="O322" s="2" t="inlineStr"/>
+      <c r="P322" s="2" t="inlineStr"/>
+      <c r="Q322" s="2" t="inlineStr"/>
+      <c r="R322" s="2" t="inlineStr"/>
+      <c r="S322" s="2" t="inlineStr"/>
+      <c r="T322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U322" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E323" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F323" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 12GB (30 dias)</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-30d-12gb</t>
+        </is>
+      </c>
+      <c r="H323" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I323" s="6" t="inlineStr"/>
+      <c r="J323" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$30 — validade 30 dias</t>
+        </is>
+      </c>
+      <c r="K323" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L323" s="5" t="inlineStr"/>
+      <c r="M323" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N323" s="5" t="inlineStr"/>
+      <c r="O323" s="5" t="inlineStr"/>
+      <c r="P323" s="5" t="inlineStr"/>
+      <c r="Q323" s="5" t="inlineStr"/>
+      <c r="R323" s="5" t="inlineStr"/>
+      <c r="S323" s="5" t="inlineStr"/>
+      <c r="T323" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U323" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 4GB (12 dias)</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-12d-4gb</t>
+        </is>
+      </c>
+      <c r="H324" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I324" s="3" t="inlineStr"/>
+      <c r="J324" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$15 — validade 12 dias</t>
+        </is>
+      </c>
+      <c r="K324" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L324" s="2" t="inlineStr"/>
+      <c r="M324" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N324" s="2" t="inlineStr"/>
+      <c r="O324" s="2" t="inlineStr"/>
+      <c r="P324" s="2" t="inlineStr"/>
+      <c r="Q324" s="2" t="inlineStr"/>
+      <c r="R324" s="2" t="inlineStr"/>
+      <c r="S324" s="2" t="inlineStr"/>
+      <c r="T324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U324" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E325" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F325" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 5GB (15 dias)</t>
+        </is>
+      </c>
+      <c r="G325" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-15d-5gb</t>
+        </is>
+      </c>
+      <c r="H325" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I325" s="6" t="inlineStr"/>
+      <c r="J325" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$15 — validade 15 dias</t>
+        </is>
+      </c>
+      <c r="K325" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L325" s="5" t="inlineStr"/>
+      <c r="M325" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N325" s="5" t="inlineStr"/>
+      <c r="O325" s="5" t="inlineStr"/>
+      <c r="P325" s="5" t="inlineStr"/>
+      <c r="Q325" s="5" t="inlineStr"/>
+      <c r="R325" s="5" t="inlineStr"/>
+      <c r="S325" s="5" t="inlineStr"/>
+      <c r="T325" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U325" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 6GB (20 dias)</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-20d-6gb</t>
+        </is>
+      </c>
+      <c r="H326" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I326" s="3" t="inlineStr"/>
+      <c r="J326" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$20 — validade 20 dias</t>
+        </is>
+      </c>
+      <c r="K326" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L326" s="2" t="inlineStr"/>
+      <c r="M326" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="N326" s="2" t="inlineStr"/>
+      <c r="O326" s="2" t="inlineStr"/>
+      <c r="P326" s="2" t="inlineStr"/>
+      <c r="Q326" s="2" t="inlineStr"/>
+      <c r="R326" s="2" t="inlineStr"/>
+      <c r="S326" s="2" t="inlineStr"/>
+      <c r="T326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U326" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B327" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C327" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D327" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E327" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F327" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 8GB (20 dias)</t>
+        </is>
+      </c>
+      <c r="G327" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-20d-8gb</t>
+        </is>
+      </c>
+      <c r="H327" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I327" s="6" t="inlineStr"/>
+      <c r="J327" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$20 — validade 20 dias</t>
+        </is>
+      </c>
+      <c r="K327" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L327" s="5" t="inlineStr"/>
+      <c r="M327" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="N327" s="5" t="inlineStr"/>
+      <c r="O327" s="5" t="inlineStr"/>
+      <c r="P327" s="5" t="inlineStr"/>
+      <c r="Q327" s="5" t="inlineStr"/>
+      <c r="R327" s="5" t="inlineStr"/>
+      <c r="S327" s="5" t="inlineStr"/>
+      <c r="T327" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U327" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 9GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-9gb</t>
+        </is>
+      </c>
+      <c r="H328" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I328" s="3" t="inlineStr"/>
+      <c r="J328" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K328" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L328" s="2" t="inlineStr"/>
+      <c r="M328" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="N328" s="2" t="inlineStr"/>
+      <c r="O328" s="2" t="inlineStr"/>
+      <c r="P328" s="2" t="inlineStr"/>
+      <c r="Q328" s="2" t="inlineStr"/>
+      <c r="R328" s="2" t="inlineStr"/>
+      <c r="S328" s="2" t="inlineStr"/>
+      <c r="T328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U328" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B329" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C329" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D329" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E329" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F329" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle 41GB</t>
+        </is>
+      </c>
+      <c r="G329" s="5" t="inlineStr">
+        <is>
+          <t>tim:162901</t>
+        </is>
+      </c>
+      <c r="H329" s="6" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="I329" s="6" t="inlineStr"/>
+      <c r="J329" s="5" t="inlineStr"/>
+      <c r="K329" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="L329" s="5" t="inlineStr"/>
+      <c r="M329" s="5" t="inlineStr"/>
+      <c r="N329" s="5" t="inlineStr"/>
+      <c r="O329" s="5" t="inlineStr"/>
+      <c r="P329" s="5" t="inlineStr"/>
+      <c r="Q329" s="5" t="inlineStr"/>
+      <c r="R329" s="5" t="inlineStr"/>
+      <c r="S329" s="5" t="inlineStr"/>
+      <c r="T329" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U329" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Light Express 31GB</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>tim:143536</t>
+        </is>
+      </c>
+      <c r="H330" s="3" t="n">
+        <v>60.99</v>
+      </c>
+      <c r="I330" s="3" t="inlineStr"/>
+      <c r="J330" s="2" t="inlineStr"/>
+      <c r="K330" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="L330" s="2" t="inlineStr"/>
+      <c r="M330" s="2" t="inlineStr"/>
+      <c r="N330" s="2" t="inlineStr"/>
+      <c r="O330" s="2" t="inlineStr"/>
+      <c r="P330" s="2" t="inlineStr"/>
+      <c r="Q330" s="2" t="inlineStr"/>
+      <c r="R330" s="2" t="inlineStr"/>
+      <c r="S330" s="2" t="inlineStr"/>
+      <c r="T330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U330" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B331" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C331" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D331" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E331" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F331" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Plus 45GB</t>
+        </is>
+      </c>
+      <c r="G331" s="5" t="inlineStr">
+        <is>
+          <t>tim:155891</t>
+        </is>
+      </c>
+      <c r="H331" s="6" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I331" s="6" t="inlineStr"/>
+      <c r="J331" s="5" t="inlineStr"/>
+      <c r="K331" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="L331" s="5" t="inlineStr"/>
+      <c r="M331" s="5" t="inlineStr"/>
+      <c r="N331" s="5" t="inlineStr"/>
+      <c r="O331" s="5" t="inlineStr"/>
+      <c r="P331" s="5" t="inlineStr"/>
+      <c r="Q331" s="5" t="inlineStr"/>
+      <c r="R331" s="5" t="inlineStr"/>
+      <c r="S331" s="5" t="inlineStr"/>
+      <c r="T331" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U331" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Premium 53GB</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>tim:162896</t>
+        </is>
+      </c>
+      <c r="H332" s="3" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="I332" s="3" t="inlineStr"/>
+      <c r="J332" s="2" t="inlineStr"/>
+      <c r="K332" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="L332" s="2" t="inlineStr"/>
+      <c r="M332" s="2" t="inlineStr"/>
+      <c r="N332" s="2" t="inlineStr"/>
+      <c r="O332" s="2" t="inlineStr"/>
+      <c r="P332" s="2" t="inlineStr"/>
+      <c r="Q332" s="2" t="inlineStr"/>
+      <c r="R332" s="2" t="inlineStr"/>
+      <c r="S332" s="2" t="inlineStr"/>
+      <c r="T332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U332" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B333" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C333" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D333" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E333" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F333" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Pro Express</t>
+        </is>
+      </c>
+      <c r="G333" s="5" t="inlineStr">
+        <is>
+          <t>tim:143576</t>
+        </is>
+      </c>
+      <c r="H333" s="6" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I333" s="6" t="inlineStr"/>
+      <c r="J333" s="5" t="inlineStr"/>
+      <c r="K333" s="7" t="inlineStr"/>
+      <c r="L333" s="5" t="inlineStr"/>
+      <c r="M333" s="5" t="inlineStr"/>
+      <c r="N333" s="5" t="inlineStr"/>
+      <c r="O333" s="5" t="inlineStr"/>
+      <c r="P333" s="5" t="inlineStr"/>
+      <c r="Q333" s="5" t="inlineStr"/>
+      <c r="R333" s="5" t="inlineStr"/>
+      <c r="S333" s="5" t="inlineStr"/>
+      <c r="T333" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U333" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black 70GB</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>tim:54206</t>
+        </is>
+      </c>
+      <c r="H334" s="3" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="I334" s="3" t="inlineStr"/>
+      <c r="J334" s="2" t="inlineStr"/>
+      <c r="K334" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="L334" s="2" t="inlineStr"/>
+      <c r="M334" s="2" t="inlineStr"/>
+      <c r="N334" s="2" t="inlineStr"/>
+      <c r="O334" s="2" t="inlineStr"/>
+      <c r="P334" s="2" t="inlineStr"/>
+      <c r="Q334" s="2" t="inlineStr"/>
+      <c r="R334" s="2" t="inlineStr"/>
+      <c r="S334" s="2" t="inlineStr"/>
+      <c r="T334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U334" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B335" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C335" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D335" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E335" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F335" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black A Express 67GB</t>
+        </is>
+      </c>
+      <c r="G335" s="5" t="inlineStr">
+        <is>
+          <t>tim:55121</t>
+        </is>
+      </c>
+      <c r="H335" s="6" t="n">
+        <v>119.99</v>
+      </c>
+      <c r="I335" s="6" t="inlineStr"/>
+      <c r="J335" s="5" t="inlineStr"/>
+      <c r="K335" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="L335" s="5" t="inlineStr"/>
+      <c r="M335" s="5" t="inlineStr"/>
+      <c r="N335" s="5" t="inlineStr"/>
+      <c r="O335" s="5" t="inlineStr"/>
+      <c r="P335" s="5" t="inlineStr"/>
+      <c r="Q335" s="5" t="inlineStr"/>
+      <c r="R335" s="5" t="inlineStr"/>
+      <c r="S335" s="5" t="inlineStr"/>
+      <c r="T335" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U335" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black B Express 82GB</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>tim:52146</t>
+        </is>
+      </c>
+      <c r="H336" s="3" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="I336" s="3" t="inlineStr"/>
+      <c r="J336" s="2" t="inlineStr"/>
+      <c r="K336" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="L336" s="2" t="inlineStr"/>
+      <c r="M336" s="2" t="inlineStr"/>
+      <c r="N336" s="2" t="inlineStr"/>
+      <c r="O336" s="2" t="inlineStr"/>
+      <c r="P336" s="2" t="inlineStr"/>
+      <c r="Q336" s="2" t="inlineStr"/>
+      <c r="R336" s="2" t="inlineStr"/>
+      <c r="S336" s="2" t="inlineStr"/>
+      <c r="T336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U336" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B337" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C337" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D337" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E337" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F337" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black C Express 107GB</t>
+        </is>
+      </c>
+      <c r="G337" s="5" t="inlineStr">
+        <is>
+          <t>tim:52151</t>
+        </is>
+      </c>
+      <c r="H337" s="6" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="I337" s="6" t="inlineStr"/>
+      <c r="J337" s="5" t="inlineStr"/>
+      <c r="K337" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="L337" s="5" t="inlineStr"/>
+      <c r="M337" s="5" t="inlineStr"/>
+      <c r="N337" s="5" t="inlineStr"/>
+      <c r="O337" s="5" t="inlineStr"/>
+      <c r="P337" s="5" t="inlineStr"/>
+      <c r="Q337" s="5" t="inlineStr"/>
+      <c r="R337" s="5" t="inlineStr"/>
+      <c r="S337" s="5" t="inlineStr"/>
+      <c r="T337" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U337" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black C Ultra 95GB</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>tim:100581</t>
+        </is>
+      </c>
+      <c r="H338" s="3" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I338" s="3" t="inlineStr"/>
+      <c r="J338" s="2" t="inlineStr"/>
+      <c r="K338" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L338" s="2" t="inlineStr"/>
+      <c r="M338" s="2" t="inlineStr"/>
+      <c r="N338" s="2" t="inlineStr"/>
+      <c r="O338" s="2" t="inlineStr"/>
+      <c r="P338" s="2" t="inlineStr"/>
+      <c r="Q338" s="2" t="inlineStr"/>
+      <c r="R338" s="2" t="inlineStr"/>
+      <c r="S338" s="2" t="inlineStr"/>
+      <c r="T338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U338" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B339" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C339" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D339" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E339" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F339" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black Plus 80GB</t>
+        </is>
+      </c>
+      <c r="G339" s="5" t="inlineStr">
+        <is>
+          <t>tim:54256</t>
+        </is>
+      </c>
+      <c r="H339" s="6" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="I339" s="6" t="inlineStr"/>
+      <c r="J339" s="5" t="inlineStr"/>
+      <c r="K339" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="L339" s="5" t="inlineStr"/>
+      <c r="M339" s="5" t="inlineStr"/>
+      <c r="N339" s="5" t="inlineStr"/>
+      <c r="O339" s="5" t="inlineStr"/>
+      <c r="P339" s="5" t="inlineStr"/>
+      <c r="Q339" s="5" t="inlineStr"/>
+      <c r="R339" s="5" t="inlineStr"/>
+      <c r="S339" s="5" t="inlineStr"/>
+      <c r="T339" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U339" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black Premium 110GB</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>tim:54261</t>
+        </is>
+      </c>
+      <c r="H340" s="3" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I340" s="3" t="inlineStr"/>
+      <c r="J340" s="2" t="inlineStr"/>
+      <c r="K340" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="L340" s="2" t="inlineStr"/>
+      <c r="M340" s="2" t="inlineStr"/>
+      <c r="N340" s="2" t="inlineStr"/>
+      <c r="O340" s="2" t="inlineStr"/>
+      <c r="P340" s="2" t="inlineStr"/>
+      <c r="Q340" s="2" t="inlineStr"/>
+      <c r="R340" s="2" t="inlineStr"/>
+      <c r="S340" s="2" t="inlineStr"/>
+      <c r="T340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U340" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B341" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C341" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D341" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E341" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F341" s="5" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 16GB</t>
+        </is>
+      </c>
+      <c r="G341" s="5" t="inlineStr">
+        <is>
+          <t>tim:106306</t>
+        </is>
+      </c>
+      <c r="H341" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I341" s="6" t="inlineStr"/>
+      <c r="J341" s="5" t="inlineStr"/>
+      <c r="K341" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="L341" s="5" t="inlineStr"/>
+      <c r="M341" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N341" s="5" t="inlineStr"/>
+      <c r="O341" s="5" t="inlineStr"/>
+      <c r="P341" s="5" t="inlineStr"/>
+      <c r="Q341" s="5" t="inlineStr"/>
+      <c r="R341" s="5" t="inlineStr"/>
+      <c r="S341" s="5" t="inlineStr"/>
+      <c r="T341" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U341" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 6GB</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>tim:59906</t>
+        </is>
+      </c>
+      <c r="H342" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I342" s="3" t="inlineStr"/>
+      <c r="J342" s="2" t="inlineStr"/>
+      <c r="K342" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L342" s="2" t="inlineStr"/>
+      <c r="M342" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N342" s="2" t="inlineStr"/>
+      <c r="O342" s="2" t="inlineStr"/>
+      <c r="P342" s="2" t="inlineStr"/>
+      <c r="Q342" s="2" t="inlineStr"/>
+      <c r="R342" s="2" t="inlineStr"/>
+      <c r="S342" s="2" t="inlineStr"/>
+      <c r="T342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U342" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B343" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C343" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D343" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E343" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F343" s="5" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 8GB</t>
+        </is>
+      </c>
+      <c r="G343" s="5" t="inlineStr">
+        <is>
+          <t>tim:59901</t>
+        </is>
+      </c>
+      <c r="H343" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I343" s="6" t="inlineStr"/>
+      <c r="J343" s="5" t="inlineStr"/>
+      <c r="K343" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L343" s="5" t="inlineStr"/>
+      <c r="M343" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N343" s="5" t="inlineStr"/>
+      <c r="O343" s="5" t="inlineStr"/>
+      <c r="P343" s="5" t="inlineStr"/>
+      <c r="Q343" s="5" t="inlineStr"/>
+      <c r="R343" s="5" t="inlineStr"/>
+      <c r="S343" s="5" t="inlineStr"/>
+      <c r="T343" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U343" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029270-46gb</t>
+        </is>
+      </c>
+      <c r="H344" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="I344" s="3" t="inlineStr"/>
+      <c r="J344" s="2" t="inlineStr"/>
+      <c r="K344" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="L344" s="2" t="inlineStr">
+        <is>
+          <t>15 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="inlineStr"/>
+      <c r="N344" s="2" t="inlineStr"/>
+      <c r="O344" s="2" t="inlineStr"/>
+      <c r="P344" s="2" t="inlineStr"/>
+      <c r="Q344" s="2" t="inlineStr"/>
+      <c r="R344" s="2" t="inlineStr"/>
+      <c r="S344" s="2" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="T344" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U344" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B345" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C345" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D345" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E345" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F345" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G345" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="H345" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="I345" s="6" t="inlineStr"/>
+      <c r="J345" s="5" t="inlineStr"/>
+      <c r="K345" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L345" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M345" s="5" t="inlineStr"/>
+      <c r="N345" s="5" t="inlineStr"/>
+      <c r="O345" s="5" t="inlineStr"/>
+      <c r="P345" s="5" t="inlineStr"/>
+      <c r="Q345" s="5" t="inlineStr"/>
+      <c r="R345" s="5" t="inlineStr"/>
+      <c r="S345" s="5" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="T345" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U345" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Educação</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029273-61gb</t>
+        </is>
+      </c>
+      <c r="H346" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I346" s="3" t="inlineStr"/>
+      <c r="J346" s="2" t="inlineStr"/>
+      <c r="K346" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L346" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="inlineStr"/>
+      <c r="N346" s="2" t="inlineStr"/>
+      <c r="O346" s="2" t="inlineStr"/>
+      <c r="P346" s="2" t="inlineStr"/>
+      <c r="Q346" s="2" t="inlineStr"/>
+      <c r="R346" s="2" t="inlineStr"/>
+      <c r="S346" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Vivae inclusa</t>
+        </is>
+      </c>
+      <c r="T346" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U346" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B347" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C347" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D347" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F347" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Entretenimento</t>
+        </is>
+      </c>
+      <c r="G347" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="H347" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="I347" s="6" t="inlineStr"/>
+      <c r="J347" s="5" t="inlineStr"/>
+      <c r="K347" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L347" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M347" s="5" t="inlineStr"/>
+      <c r="N347" s="5" t="inlineStr"/>
+      <c r="O347" s="5" t="inlineStr"/>
+      <c r="P347" s="5" t="inlineStr"/>
+      <c r="Q347" s="5" t="inlineStr"/>
+      <c r="R347" s="5" t="inlineStr"/>
+      <c r="S347" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vivo TV Inicial inclusa</t>
+        </is>
+      </c>
+      <c r="T347" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U347" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Música</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029313-61gb</t>
+        </is>
+      </c>
+      <c r="H348" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="I348" s="3" t="inlineStr"/>
+      <c r="J348" s="2" t="inlineStr"/>
+      <c r="K348" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L348" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M348" s="2" t="inlineStr"/>
+      <c r="N348" s="2" t="inlineStr"/>
+      <c r="O348" s="2" t="inlineStr"/>
+      <c r="P348" s="2" t="inlineStr"/>
+      <c r="Q348" s="2" t="inlineStr"/>
+      <c r="R348" s="2" t="inlineStr"/>
+      <c r="S348" s="2" t="inlineStr">
+        <is>
+          <t>Apple Music Individual</t>
+        </is>
+      </c>
+      <c r="T348" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U348" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B349" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C349" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D349" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E349" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F349" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix</t>
+        </is>
+      </c>
+      <c r="G349" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="H349" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="I349" s="6" t="inlineStr"/>
+      <c r="J349" s="5" t="inlineStr"/>
+      <c r="K349" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L349" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M349" s="5" t="inlineStr"/>
+      <c r="N349" s="5" t="inlineStr"/>
+      <c r="O349" s="5" t="inlineStr"/>
+      <c r="P349" s="5" t="inlineStr"/>
+      <c r="Q349" s="5" t="inlineStr"/>
+      <c r="R349" s="5" t="inlineStr"/>
+      <c r="S349" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão com anúncios</t>
+        </is>
+      </c>
+      <c r="T349" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U349" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Saúde</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029301-61gb</t>
+        </is>
+      </c>
+      <c r="H350" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I350" s="3" t="inlineStr"/>
+      <c r="J350" s="2" t="inlineStr"/>
+      <c r="K350" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L350" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="inlineStr"/>
+      <c r="N350" s="2" t="inlineStr"/>
+      <c r="O350" s="2" t="inlineStr"/>
+      <c r="P350" s="2" t="inlineStr"/>
+      <c r="Q350" s="2" t="inlineStr"/>
+      <c r="R350" s="2" t="inlineStr"/>
+      <c r="S350" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Vale Saúde Sempre inclusa</t>
+        </is>
+      </c>
+      <c r="T350" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U350" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B351" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C351" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D351" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E351" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F351" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G351" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025883-30gb</t>
+        </is>
+      </c>
+      <c r="H351" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I351" s="6" t="inlineStr"/>
+      <c r="J351" s="5" t="inlineStr"/>
+      <c r="K351" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L351" s="5" t="inlineStr">
+        <is>
+          <t>30 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M351" s="5" t="inlineStr"/>
+      <c r="N351" s="5" t="inlineStr"/>
+      <c r="O351" s="5" t="inlineStr"/>
+      <c r="P351" s="5" t="inlineStr"/>
+      <c r="Q351" s="5" t="inlineStr"/>
+      <c r="R351" s="5" t="inlineStr"/>
+      <c r="S351" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T351" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U351" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025885-40gb</t>
+        </is>
+      </c>
+      <c r="H352" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I352" s="3" t="inlineStr"/>
+      <c r="J352" s="2" t="inlineStr"/>
+      <c r="K352" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L352" s="2" t="inlineStr">
+        <is>
+          <t>40 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M352" s="2" t="inlineStr"/>
+      <c r="N352" s="2" t="inlineStr"/>
+      <c r="O352" s="2" t="inlineStr"/>
+      <c r="P352" s="2" t="inlineStr"/>
+      <c r="Q352" s="2" t="inlineStr"/>
+      <c r="R352" s="2" t="inlineStr"/>
+      <c r="S352" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T352" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U352" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B353" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C353" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D353" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E353" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F353" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G353" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025888-20gb</t>
+        </is>
+      </c>
+      <c r="H353" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="I353" s="6" t="inlineStr"/>
+      <c r="J353" s="5" t="inlineStr"/>
+      <c r="K353" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L353" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M353" s="5" t="inlineStr"/>
+      <c r="N353" s="5" t="inlineStr"/>
+      <c r="O353" s="5" t="inlineStr"/>
+      <c r="P353" s="5" t="inlineStr"/>
+      <c r="Q353" s="5" t="inlineStr"/>
+      <c r="R353" s="5" t="inlineStr"/>
+      <c r="S353" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T353" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U353" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Amazon</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029255-60gb</t>
+        </is>
+      </c>
+      <c r="H354" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="I354" s="3" t="inlineStr"/>
+      <c r="J354" s="2" t="inlineStr"/>
+      <c r="K354" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L354" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="inlineStr"/>
+      <c r="N354" s="2" t="inlineStr"/>
+      <c r="O354" s="2" t="inlineStr"/>
+      <c r="P354" s="2" t="inlineStr"/>
+      <c r="Q354" s="2" t="inlineStr"/>
+      <c r="R354" s="2" t="inlineStr"/>
+      <c r="S354" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Amazon Prime inclusa</t>
+        </is>
+      </c>
+      <c r="T354" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U354" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B355" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C355" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D355" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E355" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F355" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Disney+</t>
+        </is>
+      </c>
+      <c r="G355" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022115-60gb</t>
+        </is>
+      </c>
+      <c r="H355" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I355" s="6" t="inlineStr"/>
+      <c r="J355" s="5" t="inlineStr"/>
+      <c r="K355" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L355" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M355" s="5" t="inlineStr"/>
+      <c r="N355" s="5" t="inlineStr"/>
+      <c r="O355" s="5" t="inlineStr"/>
+      <c r="P355" s="5" t="inlineStr"/>
+      <c r="Q355" s="5" t="inlineStr">
+        <is>
+          <t>Disney+</t>
+        </is>
+      </c>
+      <c r="R355" s="5" t="inlineStr"/>
+      <c r="S355" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Disney+ Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="T355" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U355" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Globoplay</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029246-60gb</t>
+        </is>
+      </c>
+      <c r="H356" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="I356" s="3" t="inlineStr"/>
+      <c r="J356" s="2" t="inlineStr"/>
+      <c r="K356" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L356" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M356" s="2" t="inlineStr"/>
+      <c r="N356" s="2" t="inlineStr"/>
+      <c r="O356" s="2" t="inlineStr"/>
+      <c r="P356" s="2" t="inlineStr"/>
+      <c r="Q356" s="2" t="inlineStr">
+        <is>
+          <t>Globoplay</t>
+        </is>
+      </c>
+      <c r="R356" s="2" t="inlineStr"/>
+      <c r="S356" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Globoplay inclusa</t>
+        </is>
+      </c>
+      <c r="T356" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U356" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B357" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C357" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D357" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E357" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F357" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Netflix</t>
+        </is>
+      </c>
+      <c r="G357" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029234-60gb</t>
+        </is>
+      </c>
+      <c r="H357" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I357" s="6" t="inlineStr"/>
+      <c r="J357" s="5" t="inlineStr"/>
+      <c r="K357" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L357" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M357" s="5" t="inlineStr"/>
+      <c r="N357" s="5" t="inlineStr"/>
+      <c r="O357" s="5" t="inlineStr"/>
+      <c r="P357" s="5" t="inlineStr"/>
+      <c r="Q357" s="5" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="R357" s="5" t="inlineStr"/>
+      <c r="S357" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="T357" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U357" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Premiere</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029249-60gb</t>
+        </is>
+      </c>
+      <c r="H358" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I358" s="3" t="inlineStr"/>
+      <c r="J358" s="2" t="inlineStr"/>
+      <c r="K358" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L358" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M358" s="2" t="inlineStr"/>
+      <c r="N358" s="2" t="inlineStr"/>
+      <c r="O358" s="2" t="inlineStr"/>
+      <c r="P358" s="2" t="inlineStr"/>
+      <c r="Q358" s="2" t="inlineStr">
+        <is>
+          <t>Premiere</t>
+        </is>
+      </c>
+      <c r="R358" s="2" t="inlineStr"/>
+      <c r="S358" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Premiere inclusa</t>
+        </is>
+      </c>
+      <c r="T358" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U358" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B359" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C359" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D359" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E359" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F359" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Spotify</t>
+        </is>
+      </c>
+      <c r="G359" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029229-60gb</t>
+        </is>
+      </c>
+      <c r="H359" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="I359" s="6" t="inlineStr"/>
+      <c r="J359" s="5" t="inlineStr"/>
+      <c r="K359" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L359" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M359" s="5" t="inlineStr"/>
+      <c r="N359" s="5" t="inlineStr"/>
+      <c r="O359" s="5" t="inlineStr"/>
+      <c r="P359" s="5" t="inlineStr"/>
+      <c r="Q359" s="5" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="R359" s="5" t="inlineStr"/>
+      <c r="S359" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Spotify Premium inclusa</t>
+        </is>
+      </c>
+      <c r="T359" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U359" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Travel</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029244-70gb</t>
+        </is>
+      </c>
+      <c r="H360" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="I360" s="3" t="inlineStr"/>
+      <c r="J360" s="2" t="inlineStr"/>
+      <c r="K360" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="L360" s="2" t="inlineStr">
+        <is>
+          <t>60 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M360" s="2" t="inlineStr"/>
+      <c r="N360" s="2" t="inlineStr"/>
+      <c r="O360" s="2" t="inlineStr"/>
+      <c r="P360" s="2" t="inlineStr"/>
+      <c r="Q360" s="2" t="inlineStr"/>
+      <c r="R360" s="2" t="inlineStr"/>
+      <c r="S360" s="2" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="T360" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U360" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B361" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C361" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D361" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E361" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F361" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G361" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-25gb</t>
+        </is>
+      </c>
+      <c r="H361" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I361" s="6" t="inlineStr"/>
+      <c r="J361" s="5" t="inlineStr"/>
+      <c r="K361" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="L361" s="5" t="inlineStr">
+        <is>
+          <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
+        </is>
+      </c>
+      <c r="M361" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N361" s="5" t="inlineStr"/>
+      <c r="O361" s="5" t="inlineStr"/>
+      <c r="P361" s="5" t="inlineStr"/>
+      <c r="Q361" s="5" t="inlineStr"/>
+      <c r="R361" s="5" t="inlineStr"/>
+      <c r="S361" s="5" t="inlineStr"/>
+      <c r="T361" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U361" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-9gb</t>
+        </is>
+      </c>
+      <c r="H362" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I362" s="3" t="inlineStr"/>
+      <c r="J362" s="2" t="inlineStr"/>
+      <c r="K362" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L362" s="2" t="inlineStr">
+        <is>
+          <t>6 GB para navegar como quiser 3 GB para navegar no YouTube</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="N362" s="2" t="inlineStr"/>
+      <c r="O362" s="2" t="inlineStr"/>
+      <c r="P362" s="2" t="inlineStr"/>
+      <c r="Q362" s="2" t="inlineStr"/>
+      <c r="R362" s="2" t="inlineStr"/>
+      <c r="S362" s="2" t="inlineStr"/>
+      <c r="T362" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U362" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B363" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C363" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D363" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E363" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F363" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G363" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-5gb</t>
+        </is>
+      </c>
+      <c r="H363" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I363" s="6" t="inlineStr"/>
+      <c r="J363" s="5" t="inlineStr"/>
+      <c r="K363" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L363" s="5" t="inlineStr">
+        <is>
+          <t>5 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M363" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="N363" s="5" t="inlineStr"/>
+      <c r="O363" s="5" t="inlineStr"/>
+      <c r="P363" s="5" t="inlineStr"/>
+      <c r="Q363" s="5" t="inlineStr"/>
+      <c r="R363" s="5" t="inlineStr"/>
+      <c r="S363" s="5" t="inlineStr"/>
+      <c r="T363" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U363" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T22:00:27</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-4gb</t>
+        </is>
+      </c>
+      <c r="H364" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I364" s="3" t="inlineStr"/>
+      <c r="J364" s="2" t="inlineStr"/>
+      <c r="K364" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L364" s="2" t="inlineStr">
+        <is>
+          <t>4 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N364" s="2" t="inlineStr"/>
+      <c r="O364" s="2" t="inlineStr"/>
+      <c r="P364" s="2" t="inlineStr"/>
+      <c r="Q364" s="2" t="inlineStr"/>
+      <c r="R364" s="2" t="inlineStr"/>
+      <c r="S364" s="2" t="inlineStr"/>
+      <c r="T364" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U364" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U309"/>
+  <autoFilter ref="A1:U364"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23477,12 +27270,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -23554,12 +27347,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -23625,12 +27418,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -23696,12 +27489,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -23767,12 +27560,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -23838,12 +27631,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -23909,12 +27702,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -23980,12 +27773,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -24051,12 +27844,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -24122,12 +27915,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -24193,12 +27986,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -24264,12 +28057,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -24335,12 +28128,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -24404,12 +28197,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -24473,12 +28266,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -24542,12 +28335,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -24611,12 +28404,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -24680,12 +28473,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -24749,12 +28542,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -24818,12 +28611,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -24881,12 +28674,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -24944,12 +28737,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -25007,12 +28800,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -25070,12 +28863,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -25131,12 +28924,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -25194,12 +28987,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -25257,12 +29050,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -25320,12 +29113,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -25383,12 +29176,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -25446,12 +29239,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -25509,12 +29302,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -25572,12 +29365,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -25637,12 +29430,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -25702,12 +29495,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -25767,12 +29560,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -25838,12 +29631,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -25909,12 +29702,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -25980,12 +29773,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -26051,12 +29844,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -26122,12 +29915,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -26193,12 +29986,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -26264,12 +30057,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -26335,12 +30128,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -26406,12 +30199,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -26477,12 +30270,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -26548,12 +30341,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -26623,12 +30416,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -26698,12 +30491,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -26773,12 +30566,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -26848,12 +30641,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -26923,12 +30716,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -26994,12 +30787,12 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -27063,12 +30856,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -27132,12 +30925,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -27201,12 +30994,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -27297,7 +31090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -27357,450 +31150,6 @@
           <t>delta_brl</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029273-61gb</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Educação</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029300-61gb</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Vivo Controle</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029301-61gb</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Saúde</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029307-61gb</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Vivo Controle Entretenimento</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6" t="n">
-        <v>110</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029308-61gb</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Netflix</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029313-61gb</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Vivo Controle Música</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029273-51gb</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Educação</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029300-51gb</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Vivo Controle</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029301-51gb</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Saúde</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029307-51gb</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Vivo Controle Entretenimento</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>105</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029308-51gb</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Netflix</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029313-51gb</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Vivo Controle Música</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27839,7 +31188,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T22:00:50</t>
+          <t>2026-06-28T22:00:27</t>
         </is>
       </c>
     </row>
@@ -27851,7 +31200,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -27872,7 +31221,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -27983,7 +31332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28417,8 +31766,61 @@
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B9" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0)),"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0)),"")</f>
+        <v/>
+      </c>
+      <c r="M9" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Rows = day: each cell = cheapest R$ that carrier offered in the category on that snapshot_date — a live MINIFS over `history` matching the EXACT date (a locale-safe text date built from the row's date, since history stores dates as TEXT — CONTEXT §7). Pre = cheapest 30-day prepaid plan (validity_days &gt;= 28; pre-#18 dates have no validity → blank, fills from 26-Jun on). Digital = min of Vivo Lite / Claro Flex. Heatmap = per-category-block green→yellow (each cell vs all carriers in its category; subtle while prices are near-flat, differentiates as they move). Grows one row per day; charts on the `Charts` sheet.</t>
         </is>
@@ -28432,7 +31834,7 @@
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="K1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:D8">
+  <conditionalFormatting sqref="B3:D9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -28442,7 +31844,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:G8">
+  <conditionalFormatting sqref="E3:G9">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -28452,7 +31854,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:J8">
+  <conditionalFormatting sqref="H3:J9">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -28462,7 +31864,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:M8">
+  <conditionalFormatting sqref="K3:M9">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -28528,15 +31930,15 @@
         </is>
       </c>
       <c r="Q38" s="10">
-        <f>IF('comparison'!B8="",NA(),'comparison'!B8)</f>
+        <f>IF('comparison'!B9="",NA(),'comparison'!B9)</f>
         <v/>
       </c>
       <c r="R38" s="10">
-        <f>IF('comparison'!C8="",NA(),'comparison'!C8)</f>
+        <f>IF('comparison'!C9="",NA(),'comparison'!C9)</f>
         <v/>
       </c>
       <c r="S38" s="10">
-        <f>IF('comparison'!D8="",NA(),'comparison'!D8)</f>
+        <f>IF('comparison'!D9="",NA(),'comparison'!D9)</f>
         <v/>
       </c>
     </row>
@@ -28547,15 +31949,15 @@
         </is>
       </c>
       <c r="Q39" s="10">
-        <f>IF('comparison'!E8="",NA(),'comparison'!E8)</f>
+        <f>IF('comparison'!E9="",NA(),'comparison'!E9)</f>
         <v/>
       </c>
       <c r="R39" s="10">
-        <f>IF('comparison'!F8="",NA(),'comparison'!F8)</f>
+        <f>IF('comparison'!F9="",NA(),'comparison'!F9)</f>
         <v/>
       </c>
       <c r="S39" s="10">
-        <f>IF('comparison'!G8="",NA(),'comparison'!G8)</f>
+        <f>IF('comparison'!G9="",NA(),'comparison'!G9)</f>
         <v/>
       </c>
     </row>
@@ -28566,15 +31968,15 @@
         </is>
       </c>
       <c r="Q40" s="10">
-        <f>IF('comparison'!H8="",NA(),'comparison'!H8)</f>
+        <f>IF('comparison'!H9="",NA(),'comparison'!H9)</f>
         <v/>
       </c>
       <c r="R40" s="10">
-        <f>IF('comparison'!I8="",NA(),'comparison'!I8)</f>
+        <f>IF('comparison'!I9="",NA(),'comparison'!I9)</f>
         <v/>
       </c>
       <c r="S40" s="10">
-        <f>IF('comparison'!J8="",NA(),'comparison'!J8)</f>
+        <f>IF('comparison'!J9="",NA(),'comparison'!J9)</f>
         <v/>
       </c>
     </row>
@@ -28585,15 +31987,15 @@
         </is>
       </c>
       <c r="Q41" s="10">
-        <f>IF('comparison'!K8="",NA(),'comparison'!K8)</f>
+        <f>IF('comparison'!K9="",NA(),'comparison'!K9)</f>
         <v/>
       </c>
       <c r="R41" s="10">
-        <f>IF('comparison'!L8="",NA(),'comparison'!L8)</f>
+        <f>IF('comparison'!L9="",NA(),'comparison'!L9)</f>
         <v/>
       </c>
       <c r="S41" s="10">
-        <f>IF('comparison'!M8="",NA(),'comparison'!M8)</f>
+        <f>IF('comparison'!M9="",NA(),'comparison'!M9)</f>
         <v/>
       </c>
     </row>

--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -19,7 +19,7 @@
     <sheet name="TIM" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$U$364</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$U$419</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$U$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -300,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$9</f>
+              <f>'comparison'!$A$3:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$B$3:$B$9</f>
+              <f>'comparison'!$B$3:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -337,12 +337,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$9</f>
+              <f>'comparison'!$A$3:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$C$3:$C$9</f>
+              <f>'comparison'!$C$3:$C$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -374,12 +374,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$9</f>
+              <f>'comparison'!$A$3:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$D$3:$D$9</f>
+              <f>'comparison'!$D$3:$D$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$9</f>
+              <f>'comparison'!$A$3:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$E$3:$E$9</f>
+              <f>'comparison'!$E$3:$E$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -534,12 +534,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$9</f>
+              <f>'comparison'!$A$3:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$F$3:$F$9</f>
+              <f>'comparison'!$F$3:$F$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -571,12 +571,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$9</f>
+              <f>'comparison'!$A$3:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$G$3:$G$9</f>
+              <f>'comparison'!$G$3:$G$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,12 +694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$9</f>
+              <f>'comparison'!$A$3:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$H$3:$H$9</f>
+              <f>'comparison'!$H$3:$H$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -731,12 +731,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$9</f>
+              <f>'comparison'!$A$3:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$I$3:$I$9</f>
+              <f>'comparison'!$I$3:$I$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -768,12 +768,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$9</f>
+              <f>'comparison'!$A$3:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$J$3:$J$9</f>
+              <f>'comparison'!$J$3:$J$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -891,12 +891,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$9</f>
+              <f>'comparison'!$A$3:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$K$3:$K$9</f>
+              <f>'comparison'!$K$3:$K$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -928,12 +928,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$9</f>
+              <f>'comparison'!$A$3:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$L$3:$L$9</f>
+              <f>'comparison'!$L$3:$L$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -965,12 +965,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$9</f>
+              <f>'comparison'!$A$3:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$M$3:$M$9</f>
+              <f>'comparison'!$M$3:$M$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1602,7 +1602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U364"/>
+  <dimension ref="A1:U419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -26680,8 +26680,3801 @@
         </is>
       </c>
     </row>
+    <row r="365">
+      <c r="A365" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B365" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C365" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D365" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E365" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F365" s="5" t="inlineStr">
+        <is>
+          <t>Controle 25GB</t>
+        </is>
+      </c>
+      <c r="G365" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-25gb</t>
+        </is>
+      </c>
+      <c r="H365" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I365" s="6" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="J365" s="5" t="inlineStr">
+        <is>
+          <t>De R$ 59,90 Por:</t>
+        </is>
+      </c>
+      <c r="K365" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="L365" s="5" t="inlineStr"/>
+      <c r="M365" s="5" t="inlineStr"/>
+      <c r="N365" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O365" s="5" t="inlineStr"/>
+      <c r="P365" s="5" t="inlineStr"/>
+      <c r="Q365" s="5" t="inlineStr"/>
+      <c r="R365" s="5" t="inlineStr"/>
+      <c r="S365" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e vídeos; Bônus exclusivo; Aproveite na sua franquia; WhatsApp e ligações ilimitadas</t>
+        </is>
+      </c>
+      <c r="T365" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U365" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb</t>
+        </is>
+      </c>
+      <c r="H366" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I366" s="3" t="inlineStr"/>
+      <c r="J366" s="2" t="inlineStr"/>
+      <c r="K366" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L366" s="2" t="inlineStr"/>
+      <c r="M366" s="2" t="inlineStr"/>
+      <c r="N366" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O366" s="2" t="inlineStr"/>
+      <c r="P366" s="2" t="inlineStr"/>
+      <c r="Q366" s="2" t="inlineStr"/>
+      <c r="R366" s="2" t="inlineStr"/>
+      <c r="S366" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U366" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B367" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C367" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D367" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E367" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F367" s="5" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G367" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb-gaming</t>
+        </is>
+      </c>
+      <c r="H367" s="6" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I367" s="6" t="inlineStr"/>
+      <c r="J367" s="5" t="inlineStr"/>
+      <c r="K367" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L367" s="5" t="inlineStr"/>
+      <c r="M367" s="5" t="inlineStr"/>
+      <c r="N367" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O367" s="5" t="inlineStr"/>
+      <c r="P367" s="5" t="inlineStr"/>
+      <c r="Q367" s="5" t="inlineStr"/>
+      <c r="R367" s="5" t="inlineStr"/>
+      <c r="S367" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus para redes sociais e apps; Bônus uso livre; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T367" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U367" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>Flex 15GB</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-15gb</t>
+        </is>
+      </c>
+      <c r="H368" s="3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I368" s="3" t="inlineStr"/>
+      <c r="J368" s="2" t="inlineStr"/>
+      <c r="K368" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L368" s="2" t="inlineStr"/>
+      <c r="M368" s="2" t="inlineStr"/>
+      <c r="N368" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O368" s="2" t="inlineStr"/>
+      <c r="P368" s="2" t="inlineStr"/>
+      <c r="Q368" s="2" t="inlineStr"/>
+      <c r="R368" s="2" t="inlineStr"/>
+      <c r="S368" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U368" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B369" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C369" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D369" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E369" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F369" s="5" t="inlineStr">
+        <is>
+          <t>Flex 20GB</t>
+        </is>
+      </c>
+      <c r="G369" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-20gb</t>
+        </is>
+      </c>
+      <c r="H369" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I369" s="6" t="inlineStr"/>
+      <c r="J369" s="5" t="inlineStr"/>
+      <c r="K369" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L369" s="5" t="inlineStr"/>
+      <c r="M369" s="5" t="inlineStr"/>
+      <c r="N369" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O369" s="5" t="inlineStr"/>
+      <c r="P369" s="5" t="inlineStr"/>
+      <c r="Q369" s="5" t="inlineStr"/>
+      <c r="R369" s="5" t="inlineStr"/>
+      <c r="S369" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T369" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U369" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>Flex 30GB</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-30gb</t>
+        </is>
+      </c>
+      <c r="H370" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I370" s="3" t="inlineStr"/>
+      <c r="J370" s="2" t="inlineStr"/>
+      <c r="K370" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L370" s="2" t="inlineStr"/>
+      <c r="M370" s="2" t="inlineStr"/>
+      <c r="N370" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O370" s="2" t="inlineStr"/>
+      <c r="P370" s="2" t="inlineStr"/>
+      <c r="Q370" s="2" t="inlineStr"/>
+      <c r="R370" s="2" t="inlineStr"/>
+      <c r="S370" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="T370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U370" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B371" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C371" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D371" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E371" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F371" s="5" t="inlineStr">
+        <is>
+          <t>Flex 40GB</t>
+        </is>
+      </c>
+      <c r="G371" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-40gb</t>
+        </is>
+      </c>
+      <c r="H371" s="6" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I371" s="6" t="inlineStr"/>
+      <c r="J371" s="5" t="inlineStr"/>
+      <c r="K371" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L371" s="5" t="inlineStr"/>
+      <c r="M371" s="5" t="inlineStr"/>
+      <c r="N371" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O371" s="5" t="inlineStr"/>
+      <c r="P371" s="5" t="inlineStr"/>
+      <c r="Q371" s="5" t="inlineStr"/>
+      <c r="R371" s="5" t="inlineStr"/>
+      <c r="S371" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e apps; Bônus uso livre; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="T371" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U371" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>Pós 100GB</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-100gb</t>
+        </is>
+      </c>
+      <c r="H372" s="3" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="I372" s="3" t="inlineStr"/>
+      <c r="J372" s="2" t="inlineStr"/>
+      <c r="K372" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L372" s="2" t="inlineStr"/>
+      <c r="M372" s="2" t="inlineStr"/>
+      <c r="N372" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O372" s="2" t="inlineStr"/>
+      <c r="P372" s="2" t="inlineStr"/>
+      <c r="Q372" s="2" t="inlineStr"/>
+      <c r="R372" s="2" t="inlineStr"/>
+      <c r="S372" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U372" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B373" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C373" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D373" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E373" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F373" s="5" t="inlineStr">
+        <is>
+          <t>Pós 150GB</t>
+        </is>
+      </c>
+      <c r="G373" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-150gb</t>
+        </is>
+      </c>
+      <c r="H373" s="6" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="I373" s="6" t="inlineStr"/>
+      <c r="J373" s="5" t="inlineStr"/>
+      <c r="K373" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="L373" s="5" t="inlineStr"/>
+      <c r="M373" s="5" t="inlineStr"/>
+      <c r="N373" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O373" s="5" t="inlineStr"/>
+      <c r="P373" s="5" t="inlineStr"/>
+      <c r="Q373" s="5" t="inlineStr"/>
+      <c r="R373" s="5" t="inlineStr"/>
+      <c r="S373" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas e Europa; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T373" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U373" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>Pós 200GB</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-200gb</t>
+        </is>
+      </c>
+      <c r="H374" s="3" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="I374" s="3" t="inlineStr"/>
+      <c r="J374" s="2" t="inlineStr"/>
+      <c r="K374" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="L374" s="2" t="inlineStr"/>
+      <c r="M374" s="2" t="inlineStr"/>
+      <c r="N374" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O374" s="2" t="inlineStr"/>
+      <c r="P374" s="2" t="inlineStr"/>
+      <c r="Q374" s="2" t="inlineStr"/>
+      <c r="R374" s="2" t="inlineStr"/>
+      <c r="S374" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U374" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B375" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C375" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D375" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E375" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F375" s="5" t="inlineStr">
+        <is>
+          <t>Pós 50GB com GeForce NOW</t>
+        </is>
+      </c>
+      <c r="G375" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb-geforce</t>
+        </is>
+      </c>
+      <c r="H375" s="6" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="I375" s="6" t="inlineStr"/>
+      <c r="J375" s="5" t="inlineStr"/>
+      <c r="K375" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="L375" s="5" t="inlineStr"/>
+      <c r="M375" s="5" t="inlineStr"/>
+      <c r="N375" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O375" s="5" t="inlineStr"/>
+      <c r="P375" s="5" t="inlineStr"/>
+      <c r="Q375" s="5" t="inlineStr"/>
+      <c r="R375" s="5" t="inlineStr"/>
+      <c r="S375" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado; Inclusa assinatura GeForce NOW</t>
+        </is>
+      </c>
+      <c r="T375" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U375" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>Pós 60GB</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb</t>
+        </is>
+      </c>
+      <c r="H376" s="3" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="I376" s="3" t="inlineStr"/>
+      <c r="J376" s="2" t="inlineStr"/>
+      <c r="K376" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L376" s="2" t="inlineStr"/>
+      <c r="M376" s="2" t="inlineStr"/>
+      <c r="N376" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O376" s="2" t="inlineStr"/>
+      <c r="P376" s="2" t="inlineStr"/>
+      <c r="Q376" s="2" t="inlineStr"/>
+      <c r="R376" s="2" t="inlineStr"/>
+      <c r="S376" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U376" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B377" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C377" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D377" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E377" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F377" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 10GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G377" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-10gb</t>
+        </is>
+      </c>
+      <c r="H377" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I377" s="6" t="inlineStr"/>
+      <c r="J377" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K377" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L377" s="5" t="inlineStr"/>
+      <c r="M377" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="N377" s="5" t="inlineStr"/>
+      <c r="O377" s="5" t="inlineStr"/>
+      <c r="P377" s="5" t="inlineStr"/>
+      <c r="Q377" s="5" t="inlineStr"/>
+      <c r="R377" s="5" t="inlineStr"/>
+      <c r="S377" s="5" t="inlineStr"/>
+      <c r="T377" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U377" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 12GB (30 dias)</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-30d-12gb</t>
+        </is>
+      </c>
+      <c r="H378" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I378" s="3" t="inlineStr"/>
+      <c r="J378" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$30 — validade 30 dias</t>
+        </is>
+      </c>
+      <c r="K378" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L378" s="2" t="inlineStr"/>
+      <c r="M378" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N378" s="2" t="inlineStr"/>
+      <c r="O378" s="2" t="inlineStr"/>
+      <c r="P378" s="2" t="inlineStr"/>
+      <c r="Q378" s="2" t="inlineStr"/>
+      <c r="R378" s="2" t="inlineStr"/>
+      <c r="S378" s="2" t="inlineStr"/>
+      <c r="T378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U378" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B379" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C379" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D379" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E379" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F379" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 4GB (12 dias)</t>
+        </is>
+      </c>
+      <c r="G379" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-12d-4gb</t>
+        </is>
+      </c>
+      <c r="H379" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I379" s="6" t="inlineStr"/>
+      <c r="J379" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$15 — validade 12 dias</t>
+        </is>
+      </c>
+      <c r="K379" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L379" s="5" t="inlineStr"/>
+      <c r="M379" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N379" s="5" t="inlineStr"/>
+      <c r="O379" s="5" t="inlineStr"/>
+      <c r="P379" s="5" t="inlineStr"/>
+      <c r="Q379" s="5" t="inlineStr"/>
+      <c r="R379" s="5" t="inlineStr"/>
+      <c r="S379" s="5" t="inlineStr"/>
+      <c r="T379" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U379" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 5GB (15 dias)</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-15d-5gb</t>
+        </is>
+      </c>
+      <c r="H380" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I380" s="3" t="inlineStr"/>
+      <c r="J380" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$15 — validade 15 dias</t>
+        </is>
+      </c>
+      <c r="K380" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L380" s="2" t="inlineStr"/>
+      <c r="M380" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N380" s="2" t="inlineStr"/>
+      <c r="O380" s="2" t="inlineStr"/>
+      <c r="P380" s="2" t="inlineStr"/>
+      <c r="Q380" s="2" t="inlineStr"/>
+      <c r="R380" s="2" t="inlineStr"/>
+      <c r="S380" s="2" t="inlineStr"/>
+      <c r="T380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U380" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B381" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C381" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D381" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E381" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F381" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 6GB (20 dias)</t>
+        </is>
+      </c>
+      <c r="G381" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-20d-6gb</t>
+        </is>
+      </c>
+      <c r="H381" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I381" s="6" t="inlineStr"/>
+      <c r="J381" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$20 — validade 20 dias</t>
+        </is>
+      </c>
+      <c r="K381" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L381" s="5" t="inlineStr"/>
+      <c r="M381" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="N381" s="5" t="inlineStr"/>
+      <c r="O381" s="5" t="inlineStr"/>
+      <c r="P381" s="5" t="inlineStr"/>
+      <c r="Q381" s="5" t="inlineStr"/>
+      <c r="R381" s="5" t="inlineStr"/>
+      <c r="S381" s="5" t="inlineStr"/>
+      <c r="T381" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U381" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 8GB (20 dias)</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-20d-8gb</t>
+        </is>
+      </c>
+      <c r="H382" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I382" s="3" t="inlineStr"/>
+      <c r="J382" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$20 — validade 20 dias</t>
+        </is>
+      </c>
+      <c r="K382" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L382" s="2" t="inlineStr"/>
+      <c r="M382" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="N382" s="2" t="inlineStr"/>
+      <c r="O382" s="2" t="inlineStr"/>
+      <c r="P382" s="2" t="inlineStr"/>
+      <c r="Q382" s="2" t="inlineStr"/>
+      <c r="R382" s="2" t="inlineStr"/>
+      <c r="S382" s="2" t="inlineStr"/>
+      <c r="T382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U382" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B383" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C383" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D383" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E383" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F383" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 9GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G383" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-9gb</t>
+        </is>
+      </c>
+      <c r="H383" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I383" s="6" t="inlineStr"/>
+      <c r="J383" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K383" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L383" s="5" t="inlineStr"/>
+      <c r="M383" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="N383" s="5" t="inlineStr"/>
+      <c r="O383" s="5" t="inlineStr"/>
+      <c r="P383" s="5" t="inlineStr"/>
+      <c r="Q383" s="5" t="inlineStr"/>
+      <c r="R383" s="5" t="inlineStr"/>
+      <c r="S383" s="5" t="inlineStr"/>
+      <c r="T383" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U383" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle 41GB</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>tim:162901</t>
+        </is>
+      </c>
+      <c r="H384" s="3" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="I384" s="3" t="inlineStr"/>
+      <c r="J384" s="2" t="inlineStr"/>
+      <c r="K384" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="L384" s="2" t="inlineStr"/>
+      <c r="M384" s="2" t="inlineStr"/>
+      <c r="N384" s="2" t="inlineStr"/>
+      <c r="O384" s="2" t="inlineStr"/>
+      <c r="P384" s="2" t="inlineStr"/>
+      <c r="Q384" s="2" t="inlineStr"/>
+      <c r="R384" s="2" t="inlineStr"/>
+      <c r="S384" s="2" t="inlineStr"/>
+      <c r="T384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U384" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B385" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C385" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D385" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E385" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F385" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Light Express 31GB</t>
+        </is>
+      </c>
+      <c r="G385" s="5" t="inlineStr">
+        <is>
+          <t>tim:143536</t>
+        </is>
+      </c>
+      <c r="H385" s="6" t="n">
+        <v>60.99</v>
+      </c>
+      <c r="I385" s="6" t="inlineStr"/>
+      <c r="J385" s="5" t="inlineStr"/>
+      <c r="K385" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="L385" s="5" t="inlineStr"/>
+      <c r="M385" s="5" t="inlineStr"/>
+      <c r="N385" s="5" t="inlineStr"/>
+      <c r="O385" s="5" t="inlineStr"/>
+      <c r="P385" s="5" t="inlineStr"/>
+      <c r="Q385" s="5" t="inlineStr"/>
+      <c r="R385" s="5" t="inlineStr"/>
+      <c r="S385" s="5" t="inlineStr"/>
+      <c r="T385" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U385" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Plus 45GB</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>tim:155891</t>
+        </is>
+      </c>
+      <c r="H386" s="3" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I386" s="3" t="inlineStr"/>
+      <c r="J386" s="2" t="inlineStr"/>
+      <c r="K386" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="L386" s="2" t="inlineStr"/>
+      <c r="M386" s="2" t="inlineStr"/>
+      <c r="N386" s="2" t="inlineStr"/>
+      <c r="O386" s="2" t="inlineStr"/>
+      <c r="P386" s="2" t="inlineStr"/>
+      <c r="Q386" s="2" t="inlineStr"/>
+      <c r="R386" s="2" t="inlineStr"/>
+      <c r="S386" s="2" t="inlineStr"/>
+      <c r="T386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U386" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B387" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C387" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D387" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E387" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F387" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Premium 53GB</t>
+        </is>
+      </c>
+      <c r="G387" s="5" t="inlineStr">
+        <is>
+          <t>tim:162896</t>
+        </is>
+      </c>
+      <c r="H387" s="6" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="I387" s="6" t="inlineStr"/>
+      <c r="J387" s="5" t="inlineStr"/>
+      <c r="K387" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="L387" s="5" t="inlineStr"/>
+      <c r="M387" s="5" t="inlineStr"/>
+      <c r="N387" s="5" t="inlineStr"/>
+      <c r="O387" s="5" t="inlineStr"/>
+      <c r="P387" s="5" t="inlineStr"/>
+      <c r="Q387" s="5" t="inlineStr"/>
+      <c r="R387" s="5" t="inlineStr"/>
+      <c r="S387" s="5" t="inlineStr"/>
+      <c r="T387" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U387" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Pro Express</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>tim:143576</t>
+        </is>
+      </c>
+      <c r="H388" s="3" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I388" s="3" t="inlineStr"/>
+      <c r="J388" s="2" t="inlineStr"/>
+      <c r="K388" s="4" t="inlineStr"/>
+      <c r="L388" s="2" t="inlineStr"/>
+      <c r="M388" s="2" t="inlineStr"/>
+      <c r="N388" s="2" t="inlineStr"/>
+      <c r="O388" s="2" t="inlineStr"/>
+      <c r="P388" s="2" t="inlineStr"/>
+      <c r="Q388" s="2" t="inlineStr"/>
+      <c r="R388" s="2" t="inlineStr"/>
+      <c r="S388" s="2" t="inlineStr"/>
+      <c r="T388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U388" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B389" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C389" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D389" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E389" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F389" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black 70GB</t>
+        </is>
+      </c>
+      <c r="G389" s="5" t="inlineStr">
+        <is>
+          <t>tim:54206</t>
+        </is>
+      </c>
+      <c r="H389" s="6" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="I389" s="6" t="inlineStr"/>
+      <c r="J389" s="5" t="inlineStr"/>
+      <c r="K389" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="L389" s="5" t="inlineStr"/>
+      <c r="M389" s="5" t="inlineStr"/>
+      <c r="N389" s="5" t="inlineStr"/>
+      <c r="O389" s="5" t="inlineStr"/>
+      <c r="P389" s="5" t="inlineStr"/>
+      <c r="Q389" s="5" t="inlineStr"/>
+      <c r="R389" s="5" t="inlineStr"/>
+      <c r="S389" s="5" t="inlineStr"/>
+      <c r="T389" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U389" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black A Express 67GB</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>tim:55121</t>
+        </is>
+      </c>
+      <c r="H390" s="3" t="n">
+        <v>119.99</v>
+      </c>
+      <c r="I390" s="3" t="inlineStr"/>
+      <c r="J390" s="2" t="inlineStr"/>
+      <c r="K390" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="L390" s="2" t="inlineStr"/>
+      <c r="M390" s="2" t="inlineStr"/>
+      <c r="N390" s="2" t="inlineStr"/>
+      <c r="O390" s="2" t="inlineStr"/>
+      <c r="P390" s="2" t="inlineStr"/>
+      <c r="Q390" s="2" t="inlineStr"/>
+      <c r="R390" s="2" t="inlineStr"/>
+      <c r="S390" s="2" t="inlineStr"/>
+      <c r="T390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U390" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B391" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C391" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D391" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E391" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F391" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black B Express 82GB</t>
+        </is>
+      </c>
+      <c r="G391" s="5" t="inlineStr">
+        <is>
+          <t>tim:52146</t>
+        </is>
+      </c>
+      <c r="H391" s="6" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="I391" s="6" t="inlineStr"/>
+      <c r="J391" s="5" t="inlineStr"/>
+      <c r="K391" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="L391" s="5" t="inlineStr"/>
+      <c r="M391" s="5" t="inlineStr"/>
+      <c r="N391" s="5" t="inlineStr"/>
+      <c r="O391" s="5" t="inlineStr"/>
+      <c r="P391" s="5" t="inlineStr"/>
+      <c r="Q391" s="5" t="inlineStr"/>
+      <c r="R391" s="5" t="inlineStr"/>
+      <c r="S391" s="5" t="inlineStr"/>
+      <c r="T391" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U391" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black C Express 107GB</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>tim:52151</t>
+        </is>
+      </c>
+      <c r="H392" s="3" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="I392" s="3" t="inlineStr"/>
+      <c r="J392" s="2" t="inlineStr"/>
+      <c r="K392" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="L392" s="2" t="inlineStr"/>
+      <c r="M392" s="2" t="inlineStr"/>
+      <c r="N392" s="2" t="inlineStr"/>
+      <c r="O392" s="2" t="inlineStr"/>
+      <c r="P392" s="2" t="inlineStr"/>
+      <c r="Q392" s="2" t="inlineStr"/>
+      <c r="R392" s="2" t="inlineStr"/>
+      <c r="S392" s="2" t="inlineStr"/>
+      <c r="T392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U392" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B393" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C393" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D393" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E393" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F393" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black C Ultra 95GB</t>
+        </is>
+      </c>
+      <c r="G393" s="5" t="inlineStr">
+        <is>
+          <t>tim:100581</t>
+        </is>
+      </c>
+      <c r="H393" s="6" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I393" s="6" t="inlineStr"/>
+      <c r="J393" s="5" t="inlineStr"/>
+      <c r="K393" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="L393" s="5" t="inlineStr"/>
+      <c r="M393" s="5" t="inlineStr"/>
+      <c r="N393" s="5" t="inlineStr"/>
+      <c r="O393" s="5" t="inlineStr"/>
+      <c r="P393" s="5" t="inlineStr"/>
+      <c r="Q393" s="5" t="inlineStr"/>
+      <c r="R393" s="5" t="inlineStr"/>
+      <c r="S393" s="5" t="inlineStr"/>
+      <c r="T393" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U393" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black Plus 80GB</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>tim:54256</t>
+        </is>
+      </c>
+      <c r="H394" s="3" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="I394" s="3" t="inlineStr"/>
+      <c r="J394" s="2" t="inlineStr"/>
+      <c r="K394" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="L394" s="2" t="inlineStr"/>
+      <c r="M394" s="2" t="inlineStr"/>
+      <c r="N394" s="2" t="inlineStr"/>
+      <c r="O394" s="2" t="inlineStr"/>
+      <c r="P394" s="2" t="inlineStr"/>
+      <c r="Q394" s="2" t="inlineStr"/>
+      <c r="R394" s="2" t="inlineStr"/>
+      <c r="S394" s="2" t="inlineStr"/>
+      <c r="T394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U394" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B395" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C395" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D395" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E395" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F395" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black Premium 110GB</t>
+        </is>
+      </c>
+      <c r="G395" s="5" t="inlineStr">
+        <is>
+          <t>tim:54261</t>
+        </is>
+      </c>
+      <c r="H395" s="6" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I395" s="6" t="inlineStr"/>
+      <c r="J395" s="5" t="inlineStr"/>
+      <c r="K395" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="L395" s="5" t="inlineStr"/>
+      <c r="M395" s="5" t="inlineStr"/>
+      <c r="N395" s="5" t="inlineStr"/>
+      <c r="O395" s="5" t="inlineStr"/>
+      <c r="P395" s="5" t="inlineStr"/>
+      <c r="Q395" s="5" t="inlineStr"/>
+      <c r="R395" s="5" t="inlineStr"/>
+      <c r="S395" s="5" t="inlineStr"/>
+      <c r="T395" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U395" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 16GB</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>tim:106306</t>
+        </is>
+      </c>
+      <c r="H396" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I396" s="3" t="inlineStr"/>
+      <c r="J396" s="2" t="inlineStr"/>
+      <c r="K396" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="L396" s="2" t="inlineStr"/>
+      <c r="M396" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N396" s="2" t="inlineStr"/>
+      <c r="O396" s="2" t="inlineStr"/>
+      <c r="P396" s="2" t="inlineStr"/>
+      <c r="Q396" s="2" t="inlineStr"/>
+      <c r="R396" s="2" t="inlineStr"/>
+      <c r="S396" s="2" t="inlineStr"/>
+      <c r="T396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U396" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B397" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C397" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D397" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E397" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F397" s="5" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 6GB</t>
+        </is>
+      </c>
+      <c r="G397" s="5" t="inlineStr">
+        <is>
+          <t>tim:59906</t>
+        </is>
+      </c>
+      <c r="H397" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I397" s="6" t="inlineStr"/>
+      <c r="J397" s="5" t="inlineStr"/>
+      <c r="K397" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L397" s="5" t="inlineStr"/>
+      <c r="M397" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N397" s="5" t="inlineStr"/>
+      <c r="O397" s="5" t="inlineStr"/>
+      <c r="P397" s="5" t="inlineStr"/>
+      <c r="Q397" s="5" t="inlineStr"/>
+      <c r="R397" s="5" t="inlineStr"/>
+      <c r="S397" s="5" t="inlineStr"/>
+      <c r="T397" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U397" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 8GB</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>tim:59901</t>
+        </is>
+      </c>
+      <c r="H398" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I398" s="3" t="inlineStr"/>
+      <c r="J398" s="2" t="inlineStr"/>
+      <c r="K398" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L398" s="2" t="inlineStr"/>
+      <c r="M398" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N398" s="2" t="inlineStr"/>
+      <c r="O398" s="2" t="inlineStr"/>
+      <c r="P398" s="2" t="inlineStr"/>
+      <c r="Q398" s="2" t="inlineStr"/>
+      <c r="R398" s="2" t="inlineStr"/>
+      <c r="S398" s="2" t="inlineStr"/>
+      <c r="T398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U398" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B399" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C399" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D399" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E399" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F399" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G399" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029270-46gb</t>
+        </is>
+      </c>
+      <c r="H399" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I399" s="6" t="inlineStr"/>
+      <c r="J399" s="5" t="inlineStr"/>
+      <c r="K399" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="L399" s="5" t="inlineStr">
+        <is>
+          <t>15 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M399" s="5" t="inlineStr"/>
+      <c r="N399" s="5" t="inlineStr"/>
+      <c r="O399" s="5" t="inlineStr"/>
+      <c r="P399" s="5" t="inlineStr"/>
+      <c r="Q399" s="5" t="inlineStr"/>
+      <c r="R399" s="5" t="inlineStr"/>
+      <c r="S399" s="5" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="T399" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U399" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="H400" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I400" s="3" t="inlineStr"/>
+      <c r="J400" s="2" t="inlineStr"/>
+      <c r="K400" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L400" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M400" s="2" t="inlineStr"/>
+      <c r="N400" s="2" t="inlineStr"/>
+      <c r="O400" s="2" t="inlineStr"/>
+      <c r="P400" s="2" t="inlineStr"/>
+      <c r="Q400" s="2" t="inlineStr"/>
+      <c r="R400" s="2" t="inlineStr"/>
+      <c r="S400" s="2" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="T400" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U400" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B401" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C401" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D401" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E401" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F401" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Educação</t>
+        </is>
+      </c>
+      <c r="G401" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029273-61gb</t>
+        </is>
+      </c>
+      <c r="H401" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I401" s="6" t="inlineStr"/>
+      <c r="J401" s="5" t="inlineStr"/>
+      <c r="K401" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L401" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M401" s="5" t="inlineStr"/>
+      <c r="N401" s="5" t="inlineStr"/>
+      <c r="O401" s="5" t="inlineStr"/>
+      <c r="P401" s="5" t="inlineStr"/>
+      <c r="Q401" s="5" t="inlineStr"/>
+      <c r="R401" s="5" t="inlineStr"/>
+      <c r="S401" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vivae inclusa</t>
+        </is>
+      </c>
+      <c r="T401" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U401" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Entretenimento</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="H402" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="I402" s="3" t="inlineStr"/>
+      <c r="J402" s="2" t="inlineStr"/>
+      <c r="K402" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L402" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M402" s="2" t="inlineStr"/>
+      <c r="N402" s="2" t="inlineStr"/>
+      <c r="O402" s="2" t="inlineStr"/>
+      <c r="P402" s="2" t="inlineStr"/>
+      <c r="Q402" s="2" t="inlineStr"/>
+      <c r="R402" s="2" t="inlineStr"/>
+      <c r="S402" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Vivo TV Inicial inclusa</t>
+        </is>
+      </c>
+      <c r="T402" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U402" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B403" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C403" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D403" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E403" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F403" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Música</t>
+        </is>
+      </c>
+      <c r="G403" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029313-61gb</t>
+        </is>
+      </c>
+      <c r="H403" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="I403" s="6" t="inlineStr"/>
+      <c r="J403" s="5" t="inlineStr"/>
+      <c r="K403" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L403" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M403" s="5" t="inlineStr"/>
+      <c r="N403" s="5" t="inlineStr"/>
+      <c r="O403" s="5" t="inlineStr"/>
+      <c r="P403" s="5" t="inlineStr"/>
+      <c r="Q403" s="5" t="inlineStr"/>
+      <c r="R403" s="5" t="inlineStr"/>
+      <c r="S403" s="5" t="inlineStr">
+        <is>
+          <t>Apple Music Individual</t>
+        </is>
+      </c>
+      <c r="T403" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U403" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="H404" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="I404" s="3" t="inlineStr"/>
+      <c r="J404" s="2" t="inlineStr"/>
+      <c r="K404" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L404" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M404" s="2" t="inlineStr"/>
+      <c r="N404" s="2" t="inlineStr"/>
+      <c r="O404" s="2" t="inlineStr"/>
+      <c r="P404" s="2" t="inlineStr"/>
+      <c r="Q404" s="2" t="inlineStr"/>
+      <c r="R404" s="2" t="inlineStr"/>
+      <c r="S404" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão com anúncios</t>
+        </is>
+      </c>
+      <c r="T404" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U404" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B405" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C405" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D405" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E405" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F405" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Saúde</t>
+        </is>
+      </c>
+      <c r="G405" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029301-61gb</t>
+        </is>
+      </c>
+      <c r="H405" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I405" s="6" t="inlineStr"/>
+      <c r="J405" s="5" t="inlineStr"/>
+      <c r="K405" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L405" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M405" s="5" t="inlineStr"/>
+      <c r="N405" s="5" t="inlineStr"/>
+      <c r="O405" s="5" t="inlineStr"/>
+      <c r="P405" s="5" t="inlineStr"/>
+      <c r="Q405" s="5" t="inlineStr"/>
+      <c r="R405" s="5" t="inlineStr"/>
+      <c r="S405" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vale Saúde Sempre inclusa</t>
+        </is>
+      </c>
+      <c r="T405" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U405" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025883-30gb</t>
+        </is>
+      </c>
+      <c r="H406" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I406" s="3" t="inlineStr"/>
+      <c r="J406" s="2" t="inlineStr"/>
+      <c r="K406" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L406" s="2" t="inlineStr">
+        <is>
+          <t>30 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M406" s="2" t="inlineStr"/>
+      <c r="N406" s="2" t="inlineStr"/>
+      <c r="O406" s="2" t="inlineStr"/>
+      <c r="P406" s="2" t="inlineStr"/>
+      <c r="Q406" s="2" t="inlineStr"/>
+      <c r="R406" s="2" t="inlineStr"/>
+      <c r="S406" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T406" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U406" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B407" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C407" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D407" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E407" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F407" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G407" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025885-40gb</t>
+        </is>
+      </c>
+      <c r="H407" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="I407" s="6" t="inlineStr"/>
+      <c r="J407" s="5" t="inlineStr"/>
+      <c r="K407" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L407" s="5" t="inlineStr">
+        <is>
+          <t>40 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M407" s="5" t="inlineStr"/>
+      <c r="N407" s="5" t="inlineStr"/>
+      <c r="O407" s="5" t="inlineStr"/>
+      <c r="P407" s="5" t="inlineStr"/>
+      <c r="Q407" s="5" t="inlineStr"/>
+      <c r="R407" s="5" t="inlineStr"/>
+      <c r="S407" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T407" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U407" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025888-20gb</t>
+        </is>
+      </c>
+      <c r="H408" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="I408" s="3" t="inlineStr"/>
+      <c r="J408" s="2" t="inlineStr"/>
+      <c r="K408" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L408" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M408" s="2" t="inlineStr"/>
+      <c r="N408" s="2" t="inlineStr"/>
+      <c r="O408" s="2" t="inlineStr"/>
+      <c r="P408" s="2" t="inlineStr"/>
+      <c r="Q408" s="2" t="inlineStr"/>
+      <c r="R408" s="2" t="inlineStr"/>
+      <c r="S408" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T408" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U408" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B409" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C409" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D409" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E409" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F409" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Amazon</t>
+        </is>
+      </c>
+      <c r="G409" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029255-60gb</t>
+        </is>
+      </c>
+      <c r="H409" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="I409" s="6" t="inlineStr"/>
+      <c r="J409" s="5" t="inlineStr"/>
+      <c r="K409" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L409" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M409" s="5" t="inlineStr"/>
+      <c r="N409" s="5" t="inlineStr"/>
+      <c r="O409" s="5" t="inlineStr"/>
+      <c r="P409" s="5" t="inlineStr"/>
+      <c r="Q409" s="5" t="inlineStr"/>
+      <c r="R409" s="5" t="inlineStr"/>
+      <c r="S409" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Amazon Prime inclusa</t>
+        </is>
+      </c>
+      <c r="T409" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U409" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Disney+</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022115-60gb</t>
+        </is>
+      </c>
+      <c r="H410" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I410" s="3" t="inlineStr"/>
+      <c r="J410" s="2" t="inlineStr"/>
+      <c r="K410" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L410" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M410" s="2" t="inlineStr"/>
+      <c r="N410" s="2" t="inlineStr"/>
+      <c r="O410" s="2" t="inlineStr"/>
+      <c r="P410" s="2" t="inlineStr"/>
+      <c r="Q410" s="2" t="inlineStr">
+        <is>
+          <t>Disney+</t>
+        </is>
+      </c>
+      <c r="R410" s="2" t="inlineStr"/>
+      <c r="S410" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Disney+ Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="T410" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U410" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B411" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C411" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D411" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E411" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F411" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Globoplay</t>
+        </is>
+      </c>
+      <c r="G411" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029246-60gb</t>
+        </is>
+      </c>
+      <c r="H411" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="I411" s="6" t="inlineStr"/>
+      <c r="J411" s="5" t="inlineStr"/>
+      <c r="K411" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L411" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M411" s="5" t="inlineStr"/>
+      <c r="N411" s="5" t="inlineStr"/>
+      <c r="O411" s="5" t="inlineStr"/>
+      <c r="P411" s="5" t="inlineStr"/>
+      <c r="Q411" s="5" t="inlineStr">
+        <is>
+          <t>Globoplay</t>
+        </is>
+      </c>
+      <c r="R411" s="5" t="inlineStr"/>
+      <c r="S411" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Globoplay inclusa</t>
+        </is>
+      </c>
+      <c r="T411" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U411" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Netflix</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029234-60gb</t>
+        </is>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I412" s="3" t="inlineStr"/>
+      <c r="J412" s="2" t="inlineStr"/>
+      <c r="K412" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L412" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M412" s="2" t="inlineStr"/>
+      <c r="N412" s="2" t="inlineStr"/>
+      <c r="O412" s="2" t="inlineStr"/>
+      <c r="P412" s="2" t="inlineStr"/>
+      <c r="Q412" s="2" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="R412" s="2" t="inlineStr"/>
+      <c r="S412" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="T412" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U412" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B413" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C413" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D413" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E413" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F413" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Premiere</t>
+        </is>
+      </c>
+      <c r="G413" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029249-60gb</t>
+        </is>
+      </c>
+      <c r="H413" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I413" s="6" t="inlineStr"/>
+      <c r="J413" s="5" t="inlineStr"/>
+      <c r="K413" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L413" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M413" s="5" t="inlineStr"/>
+      <c r="N413" s="5" t="inlineStr"/>
+      <c r="O413" s="5" t="inlineStr"/>
+      <c r="P413" s="5" t="inlineStr"/>
+      <c r="Q413" s="5" t="inlineStr">
+        <is>
+          <t>Premiere</t>
+        </is>
+      </c>
+      <c r="R413" s="5" t="inlineStr"/>
+      <c r="S413" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Premiere inclusa</t>
+        </is>
+      </c>
+      <c r="T413" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U413" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Spotify</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029229-60gb</t>
+        </is>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="I414" s="3" t="inlineStr"/>
+      <c r="J414" s="2" t="inlineStr"/>
+      <c r="K414" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L414" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M414" s="2" t="inlineStr"/>
+      <c r="N414" s="2" t="inlineStr"/>
+      <c r="O414" s="2" t="inlineStr"/>
+      <c r="P414" s="2" t="inlineStr"/>
+      <c r="Q414" s="2" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="R414" s="2" t="inlineStr"/>
+      <c r="S414" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Spotify Premium inclusa</t>
+        </is>
+      </c>
+      <c r="T414" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U414" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B415" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C415" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D415" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E415" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F415" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Travel</t>
+        </is>
+      </c>
+      <c r="G415" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029244-70gb</t>
+        </is>
+      </c>
+      <c r="H415" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="I415" s="6" t="inlineStr"/>
+      <c r="J415" s="5" t="inlineStr"/>
+      <c r="K415" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="L415" s="5" t="inlineStr">
+        <is>
+          <t>60 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M415" s="5" t="inlineStr"/>
+      <c r="N415" s="5" t="inlineStr"/>
+      <c r="O415" s="5" t="inlineStr"/>
+      <c r="P415" s="5" t="inlineStr"/>
+      <c r="Q415" s="5" t="inlineStr"/>
+      <c r="R415" s="5" t="inlineStr"/>
+      <c r="S415" s="5" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="T415" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U415" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-25gb</t>
+        </is>
+      </c>
+      <c r="H416" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I416" s="3" t="inlineStr"/>
+      <c r="J416" s="2" t="inlineStr"/>
+      <c r="K416" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L416" s="2" t="inlineStr">
+        <is>
+          <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
+        </is>
+      </c>
+      <c r="M416" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N416" s="2" t="inlineStr"/>
+      <c r="O416" s="2" t="inlineStr"/>
+      <c r="P416" s="2" t="inlineStr"/>
+      <c r="Q416" s="2" t="inlineStr"/>
+      <c r="R416" s="2" t="inlineStr"/>
+      <c r="S416" s="2" t="inlineStr"/>
+      <c r="T416" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U416" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B417" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C417" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D417" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E417" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F417" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G417" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-9gb</t>
+        </is>
+      </c>
+      <c r="H417" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I417" s="6" t="inlineStr"/>
+      <c r="J417" s="5" t="inlineStr"/>
+      <c r="K417" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L417" s="5" t="inlineStr">
+        <is>
+          <t>6 GB para navegar como quiser 3 GB para navegar no YouTube</t>
+        </is>
+      </c>
+      <c r="M417" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="N417" s="5" t="inlineStr"/>
+      <c r="O417" s="5" t="inlineStr"/>
+      <c r="P417" s="5" t="inlineStr"/>
+      <c r="Q417" s="5" t="inlineStr"/>
+      <c r="R417" s="5" t="inlineStr"/>
+      <c r="S417" s="5" t="inlineStr"/>
+      <c r="T417" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U417" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-5gb</t>
+        </is>
+      </c>
+      <c r="H418" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I418" s="3" t="inlineStr"/>
+      <c r="J418" s="2" t="inlineStr"/>
+      <c r="K418" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L418" s="2" t="inlineStr">
+        <is>
+          <t>5 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M418" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N418" s="2" t="inlineStr"/>
+      <c r="O418" s="2" t="inlineStr"/>
+      <c r="P418" s="2" t="inlineStr"/>
+      <c r="Q418" s="2" t="inlineStr"/>
+      <c r="R418" s="2" t="inlineStr"/>
+      <c r="S418" s="2" t="inlineStr"/>
+      <c r="T418" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U418" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B419" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29T22:07:51</t>
+        </is>
+      </c>
+      <c r="C419" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D419" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E419" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F419" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G419" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-4gb</t>
+        </is>
+      </c>
+      <c r="H419" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="I419" s="6" t="inlineStr"/>
+      <c r="J419" s="5" t="inlineStr"/>
+      <c r="K419" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L419" s="5" t="inlineStr">
+        <is>
+          <t>4 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M419" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N419" s="5" t="inlineStr"/>
+      <c r="O419" s="5" t="inlineStr"/>
+      <c r="P419" s="5" t="inlineStr"/>
+      <c r="Q419" s="5" t="inlineStr"/>
+      <c r="R419" s="5" t="inlineStr"/>
+      <c r="S419" s="5" t="inlineStr"/>
+      <c r="T419" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U419" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U364"/>
+  <autoFilter ref="A1:U419"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27270,12 +31063,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -27347,12 +31140,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -27418,12 +31211,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -27489,12 +31282,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -27560,12 +31353,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -27631,12 +31424,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -27702,12 +31495,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -27773,12 +31566,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -27844,12 +31637,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -27915,12 +31708,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -27986,12 +31779,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -28057,12 +31850,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -28128,12 +31921,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -28197,12 +31990,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -28266,12 +32059,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -28335,12 +32128,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -28404,12 +32197,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -28473,12 +32266,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -28542,12 +32335,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -28611,12 +32404,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -28674,12 +32467,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -28737,12 +32530,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -28800,12 +32593,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -28863,12 +32656,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -28924,12 +32717,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -28987,12 +32780,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -29050,12 +32843,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -29113,12 +32906,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -29176,12 +32969,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -29239,12 +33032,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -29302,12 +33095,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -29365,12 +33158,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -29430,12 +33223,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -29495,12 +33288,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -29560,12 +33353,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -29631,12 +33424,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -29702,12 +33495,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -29773,12 +33566,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -29844,12 +33637,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -29915,12 +33708,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -29986,12 +33779,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -30057,12 +33850,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -30128,12 +33921,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -30199,12 +33992,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -30270,12 +34063,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -30341,12 +34134,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -30416,12 +34209,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -30491,12 +34284,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -30566,12 +34359,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -30641,12 +34434,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -30716,12 +34509,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -30787,12 +34580,12 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -30856,12 +34649,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -30925,12 +34718,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -30994,12 +34787,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -31188,7 +34981,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28T22:00:27</t>
+          <t>2026-06-29T22:07:51</t>
         </is>
       </c>
     </row>
@@ -31200,7 +34993,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -31221,7 +35014,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -31332,7 +35125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -31819,8 +35612,61 @@
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="12" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B10" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0)),"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0)),"")</f>
+        <v/>
+      </c>
+      <c r="M10" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Rows = day: each cell = cheapest R$ that carrier offered in the category on that snapshot_date — a live MINIFS over `history` matching the EXACT date (a locale-safe text date built from the row's date, since history stores dates as TEXT — CONTEXT §7). Pre = cheapest 30-day prepaid plan (validity_days &gt;= 28; pre-#18 dates have no validity → blank, fills from 26-Jun on). Digital = min of Vivo Lite / Claro Flex. Heatmap = per-category-block green→yellow (each cell vs all carriers in its category; subtle while prices are near-flat, differentiates as they move). Grows one row per day; charts on the `Charts` sheet.</t>
         </is>
@@ -31834,7 +35680,7 @@
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="K1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:D9">
+  <conditionalFormatting sqref="B3:D10">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -31844,7 +35690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:G9">
+  <conditionalFormatting sqref="E3:G10">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -31854,7 +35700,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:J9">
+  <conditionalFormatting sqref="H3:J10">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -31864,7 +35710,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:M9">
+  <conditionalFormatting sqref="K3:M10">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -31930,15 +35776,15 @@
         </is>
       </c>
       <c r="Q38" s="10">
-        <f>IF('comparison'!B9="",NA(),'comparison'!B9)</f>
+        <f>IF('comparison'!B10="",NA(),'comparison'!B10)</f>
         <v/>
       </c>
       <c r="R38" s="10">
-        <f>IF('comparison'!C9="",NA(),'comparison'!C9)</f>
+        <f>IF('comparison'!C10="",NA(),'comparison'!C10)</f>
         <v/>
       </c>
       <c r="S38" s="10">
-        <f>IF('comparison'!D9="",NA(),'comparison'!D9)</f>
+        <f>IF('comparison'!D10="",NA(),'comparison'!D10)</f>
         <v/>
       </c>
     </row>
@@ -31949,15 +35795,15 @@
         </is>
       </c>
       <c r="Q39" s="10">
-        <f>IF('comparison'!E9="",NA(),'comparison'!E9)</f>
+        <f>IF('comparison'!E10="",NA(),'comparison'!E10)</f>
         <v/>
       </c>
       <c r="R39" s="10">
-        <f>IF('comparison'!F9="",NA(),'comparison'!F9)</f>
+        <f>IF('comparison'!F10="",NA(),'comparison'!F10)</f>
         <v/>
       </c>
       <c r="S39" s="10">
-        <f>IF('comparison'!G9="",NA(),'comparison'!G9)</f>
+        <f>IF('comparison'!G10="",NA(),'comparison'!G10)</f>
         <v/>
       </c>
     </row>
@@ -31968,15 +35814,15 @@
         </is>
       </c>
       <c r="Q40" s="10">
-        <f>IF('comparison'!H9="",NA(),'comparison'!H9)</f>
+        <f>IF('comparison'!H10="",NA(),'comparison'!H10)</f>
         <v/>
       </c>
       <c r="R40" s="10">
-        <f>IF('comparison'!I9="",NA(),'comparison'!I9)</f>
+        <f>IF('comparison'!I10="",NA(),'comparison'!I10)</f>
         <v/>
       </c>
       <c r="S40" s="10">
-        <f>IF('comparison'!J9="",NA(),'comparison'!J9)</f>
+        <f>IF('comparison'!J10="",NA(),'comparison'!J10)</f>
         <v/>
       </c>
     </row>
@@ -31987,15 +35833,15 @@
         </is>
       </c>
       <c r="Q41" s="10">
-        <f>IF('comparison'!K9="",NA(),'comparison'!K9)</f>
+        <f>IF('comparison'!K10="",NA(),'comparison'!K10)</f>
         <v/>
       </c>
       <c r="R41" s="10">
-        <f>IF('comparison'!L9="",NA(),'comparison'!L9)</f>
+        <f>IF('comparison'!L10="",NA(),'comparison'!L10)</f>
         <v/>
       </c>
       <c r="S41" s="10">
-        <f>IF('comparison'!M9="",NA(),'comparison'!M9)</f>
+        <f>IF('comparison'!M10="",NA(),'comparison'!M10)</f>
         <v/>
       </c>
     </row>

--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -19,7 +19,7 @@
     <sheet name="TIM" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$U$419</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$U$474</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$U$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -300,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$10</f>
+              <f>'comparison'!$A$3:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$B$3:$B$10</f>
+              <f>'comparison'!$B$3:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -337,12 +337,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$10</f>
+              <f>'comparison'!$A$3:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$C$3:$C$10</f>
+              <f>'comparison'!$C$3:$C$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -374,12 +374,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$10</f>
+              <f>'comparison'!$A$3:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$D$3:$D$10</f>
+              <f>'comparison'!$D$3:$D$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$10</f>
+              <f>'comparison'!$A$3:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$E$3:$E$10</f>
+              <f>'comparison'!$E$3:$E$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -534,12 +534,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$10</f>
+              <f>'comparison'!$A$3:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$F$3:$F$10</f>
+              <f>'comparison'!$F$3:$F$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -571,12 +571,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$10</f>
+              <f>'comparison'!$A$3:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$G$3:$G$10</f>
+              <f>'comparison'!$G$3:$G$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,12 +694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$10</f>
+              <f>'comparison'!$A$3:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$H$3:$H$10</f>
+              <f>'comparison'!$H$3:$H$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -731,12 +731,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$10</f>
+              <f>'comparison'!$A$3:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$I$3:$I$10</f>
+              <f>'comparison'!$I$3:$I$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -768,12 +768,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$10</f>
+              <f>'comparison'!$A$3:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$J$3:$J$10</f>
+              <f>'comparison'!$J$3:$J$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -891,12 +891,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$10</f>
+              <f>'comparison'!$A$3:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$K$3:$K$10</f>
+              <f>'comparison'!$K$3:$K$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -928,12 +928,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$10</f>
+              <f>'comparison'!$A$3:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$L$3:$L$10</f>
+              <f>'comparison'!$L$3:$L$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -965,12 +965,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$10</f>
+              <f>'comparison'!$A$3:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$M$3:$M$10</f>
+              <f>'comparison'!$M$3:$M$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1602,7 +1602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U419"/>
+  <dimension ref="A1:U474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -30473,8 +30473,3801 @@
         </is>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>Controle 25GB</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-25gb</t>
+        </is>
+      </c>
+      <c r="H420" s="3" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I420" s="3" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="J420" s="2" t="inlineStr">
+        <is>
+          <t>De R$ 59,90 Por:</t>
+        </is>
+      </c>
+      <c r="K420" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L420" s="2" t="inlineStr"/>
+      <c r="M420" s="2" t="inlineStr"/>
+      <c r="N420" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O420" s="2" t="inlineStr"/>
+      <c r="P420" s="2" t="inlineStr"/>
+      <c r="Q420" s="2" t="inlineStr"/>
+      <c r="R420" s="2" t="inlineStr"/>
+      <c r="S420" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e vídeos; Bônus exclusivo; Aproveite na sua franquia; WhatsApp e ligações ilimitadas</t>
+        </is>
+      </c>
+      <c r="T420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U420" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B421" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C421" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D421" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E421" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F421" s="5" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G421" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb</t>
+        </is>
+      </c>
+      <c r="H421" s="6" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I421" s="6" t="inlineStr"/>
+      <c r="J421" s="5" t="inlineStr"/>
+      <c r="K421" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L421" s="5" t="inlineStr"/>
+      <c r="M421" s="5" t="inlineStr"/>
+      <c r="N421" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O421" s="5" t="inlineStr"/>
+      <c r="P421" s="5" t="inlineStr"/>
+      <c r="Q421" s="5" t="inlineStr"/>
+      <c r="R421" s="5" t="inlineStr"/>
+      <c r="S421" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T421" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U421" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb-gaming</t>
+        </is>
+      </c>
+      <c r="H422" s="3" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I422" s="3" t="inlineStr"/>
+      <c r="J422" s="2" t="inlineStr"/>
+      <c r="K422" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L422" s="2" t="inlineStr"/>
+      <c r="M422" s="2" t="inlineStr"/>
+      <c r="N422" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O422" s="2" t="inlineStr"/>
+      <c r="P422" s="2" t="inlineStr"/>
+      <c r="Q422" s="2" t="inlineStr"/>
+      <c r="R422" s="2" t="inlineStr"/>
+      <c r="S422" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus para redes sociais e apps; Bônus uso livre; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U422" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B423" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C423" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D423" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E423" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F423" s="5" t="inlineStr">
+        <is>
+          <t>Flex 15GB</t>
+        </is>
+      </c>
+      <c r="G423" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-15gb</t>
+        </is>
+      </c>
+      <c r="H423" s="6" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I423" s="6" t="inlineStr"/>
+      <c r="J423" s="5" t="inlineStr"/>
+      <c r="K423" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="L423" s="5" t="inlineStr"/>
+      <c r="M423" s="5" t="inlineStr"/>
+      <c r="N423" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O423" s="5" t="inlineStr"/>
+      <c r="P423" s="5" t="inlineStr"/>
+      <c r="Q423" s="5" t="inlineStr"/>
+      <c r="R423" s="5" t="inlineStr"/>
+      <c r="S423" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T423" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U423" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>Flex 20GB</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-20gb</t>
+        </is>
+      </c>
+      <c r="H424" s="3" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I424" s="3" t="inlineStr"/>
+      <c r="J424" s="2" t="inlineStr"/>
+      <c r="K424" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L424" s="2" t="inlineStr"/>
+      <c r="M424" s="2" t="inlineStr"/>
+      <c r="N424" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O424" s="2" t="inlineStr"/>
+      <c r="P424" s="2" t="inlineStr"/>
+      <c r="Q424" s="2" t="inlineStr"/>
+      <c r="R424" s="2" t="inlineStr"/>
+      <c r="S424" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U424" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B425" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C425" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D425" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E425" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F425" s="5" t="inlineStr">
+        <is>
+          <t>Flex 30GB</t>
+        </is>
+      </c>
+      <c r="G425" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-30gb</t>
+        </is>
+      </c>
+      <c r="H425" s="6" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I425" s="6" t="inlineStr"/>
+      <c r="J425" s="5" t="inlineStr"/>
+      <c r="K425" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L425" s="5" t="inlineStr"/>
+      <c r="M425" s="5" t="inlineStr"/>
+      <c r="N425" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O425" s="5" t="inlineStr"/>
+      <c r="P425" s="5" t="inlineStr"/>
+      <c r="Q425" s="5" t="inlineStr"/>
+      <c r="R425" s="5" t="inlineStr"/>
+      <c r="S425" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="T425" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U425" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>Flex 40GB</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-40gb</t>
+        </is>
+      </c>
+      <c r="H426" s="3" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I426" s="3" t="inlineStr"/>
+      <c r="J426" s="2" t="inlineStr"/>
+      <c r="K426" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L426" s="2" t="inlineStr"/>
+      <c r="M426" s="2" t="inlineStr"/>
+      <c r="N426" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O426" s="2" t="inlineStr"/>
+      <c r="P426" s="2" t="inlineStr"/>
+      <c r="Q426" s="2" t="inlineStr"/>
+      <c r="R426" s="2" t="inlineStr"/>
+      <c r="S426" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e apps; Bônus uso livre; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="T426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U426" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B427" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C427" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D427" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E427" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F427" s="5" t="inlineStr">
+        <is>
+          <t>Pós 100GB</t>
+        </is>
+      </c>
+      <c r="G427" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-100gb</t>
+        </is>
+      </c>
+      <c r="H427" s="6" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="I427" s="6" t="inlineStr"/>
+      <c r="J427" s="5" t="inlineStr"/>
+      <c r="K427" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="L427" s="5" t="inlineStr"/>
+      <c r="M427" s="5" t="inlineStr"/>
+      <c r="N427" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O427" s="5" t="inlineStr"/>
+      <c r="P427" s="5" t="inlineStr"/>
+      <c r="Q427" s="5" t="inlineStr"/>
+      <c r="R427" s="5" t="inlineStr"/>
+      <c r="S427" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T427" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U427" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>Pós 150GB</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-150gb</t>
+        </is>
+      </c>
+      <c r="H428" s="3" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="I428" s="3" t="inlineStr"/>
+      <c r="J428" s="2" t="inlineStr"/>
+      <c r="K428" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="L428" s="2" t="inlineStr"/>
+      <c r="M428" s="2" t="inlineStr"/>
+      <c r="N428" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O428" s="2" t="inlineStr"/>
+      <c r="P428" s="2" t="inlineStr"/>
+      <c r="Q428" s="2" t="inlineStr"/>
+      <c r="R428" s="2" t="inlineStr"/>
+      <c r="S428" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas e Europa; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U428" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B429" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C429" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D429" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E429" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F429" s="5" t="inlineStr">
+        <is>
+          <t>Pós 200GB</t>
+        </is>
+      </c>
+      <c r="G429" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-200gb</t>
+        </is>
+      </c>
+      <c r="H429" s="6" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="I429" s="6" t="inlineStr"/>
+      <c r="J429" s="5" t="inlineStr"/>
+      <c r="K429" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="L429" s="5" t="inlineStr"/>
+      <c r="M429" s="5" t="inlineStr"/>
+      <c r="N429" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O429" s="5" t="inlineStr"/>
+      <c r="P429" s="5" t="inlineStr"/>
+      <c r="Q429" s="5" t="inlineStr"/>
+      <c r="R429" s="5" t="inlineStr"/>
+      <c r="S429" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T429" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U429" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>Pós 50GB com GeForce NOW</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb-geforce</t>
+        </is>
+      </c>
+      <c r="H430" s="3" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="I430" s="3" t="inlineStr"/>
+      <c r="J430" s="2" t="inlineStr"/>
+      <c r="K430" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="L430" s="2" t="inlineStr"/>
+      <c r="M430" s="2" t="inlineStr"/>
+      <c r="N430" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O430" s="2" t="inlineStr"/>
+      <c r="P430" s="2" t="inlineStr"/>
+      <c r="Q430" s="2" t="inlineStr"/>
+      <c r="R430" s="2" t="inlineStr"/>
+      <c r="S430" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado; Inclusa assinatura GeForce NOW</t>
+        </is>
+      </c>
+      <c r="T430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U430" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B431" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C431" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D431" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E431" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F431" s="5" t="inlineStr">
+        <is>
+          <t>Pós 60GB</t>
+        </is>
+      </c>
+      <c r="G431" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb</t>
+        </is>
+      </c>
+      <c r="H431" s="6" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="I431" s="6" t="inlineStr"/>
+      <c r="J431" s="5" t="inlineStr"/>
+      <c r="K431" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L431" s="5" t="inlineStr"/>
+      <c r="M431" s="5" t="inlineStr"/>
+      <c r="N431" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O431" s="5" t="inlineStr"/>
+      <c r="P431" s="5" t="inlineStr"/>
+      <c r="Q431" s="5" t="inlineStr"/>
+      <c r="R431" s="5" t="inlineStr"/>
+      <c r="S431" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T431" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U431" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 10GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-10gb</t>
+        </is>
+      </c>
+      <c r="H432" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I432" s="3" t="inlineStr"/>
+      <c r="J432" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K432" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L432" s="2" t="inlineStr"/>
+      <c r="M432" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="N432" s="2" t="inlineStr"/>
+      <c r="O432" s="2" t="inlineStr"/>
+      <c r="P432" s="2" t="inlineStr"/>
+      <c r="Q432" s="2" t="inlineStr"/>
+      <c r="R432" s="2" t="inlineStr"/>
+      <c r="S432" s="2" t="inlineStr"/>
+      <c r="T432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U432" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B433" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C433" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D433" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E433" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F433" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 12GB (30 dias)</t>
+        </is>
+      </c>
+      <c r="G433" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-30d-12gb</t>
+        </is>
+      </c>
+      <c r="H433" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I433" s="6" t="inlineStr"/>
+      <c r="J433" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$30 — validade 30 dias</t>
+        </is>
+      </c>
+      <c r="K433" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L433" s="5" t="inlineStr"/>
+      <c r="M433" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N433" s="5" t="inlineStr"/>
+      <c r="O433" s="5" t="inlineStr"/>
+      <c r="P433" s="5" t="inlineStr"/>
+      <c r="Q433" s="5" t="inlineStr"/>
+      <c r="R433" s="5" t="inlineStr"/>
+      <c r="S433" s="5" t="inlineStr"/>
+      <c r="T433" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U433" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 4GB (12 dias)</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-12d-4gb</t>
+        </is>
+      </c>
+      <c r="H434" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I434" s="3" t="inlineStr"/>
+      <c r="J434" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$15 — validade 12 dias</t>
+        </is>
+      </c>
+      <c r="K434" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L434" s="2" t="inlineStr"/>
+      <c r="M434" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N434" s="2" t="inlineStr"/>
+      <c r="O434" s="2" t="inlineStr"/>
+      <c r="P434" s="2" t="inlineStr"/>
+      <c r="Q434" s="2" t="inlineStr"/>
+      <c r="R434" s="2" t="inlineStr"/>
+      <c r="S434" s="2" t="inlineStr"/>
+      <c r="T434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U434" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B435" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C435" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D435" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E435" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F435" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 5GB (15 dias)</t>
+        </is>
+      </c>
+      <c r="G435" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-15d-5gb</t>
+        </is>
+      </c>
+      <c r="H435" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I435" s="6" t="inlineStr"/>
+      <c r="J435" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$15 — validade 15 dias</t>
+        </is>
+      </c>
+      <c r="K435" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L435" s="5" t="inlineStr"/>
+      <c r="M435" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N435" s="5" t="inlineStr"/>
+      <c r="O435" s="5" t="inlineStr"/>
+      <c r="P435" s="5" t="inlineStr"/>
+      <c r="Q435" s="5" t="inlineStr"/>
+      <c r="R435" s="5" t="inlineStr"/>
+      <c r="S435" s="5" t="inlineStr"/>
+      <c r="T435" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U435" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 6GB (20 dias)</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-20d-6gb</t>
+        </is>
+      </c>
+      <c r="H436" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I436" s="3" t="inlineStr"/>
+      <c r="J436" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$20 — validade 20 dias</t>
+        </is>
+      </c>
+      <c r="K436" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L436" s="2" t="inlineStr"/>
+      <c r="M436" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="N436" s="2" t="inlineStr"/>
+      <c r="O436" s="2" t="inlineStr"/>
+      <c r="P436" s="2" t="inlineStr"/>
+      <c r="Q436" s="2" t="inlineStr"/>
+      <c r="R436" s="2" t="inlineStr"/>
+      <c r="S436" s="2" t="inlineStr"/>
+      <c r="T436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U436" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B437" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C437" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D437" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E437" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F437" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 8GB (20 dias)</t>
+        </is>
+      </c>
+      <c r="G437" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-20d-8gb</t>
+        </is>
+      </c>
+      <c r="H437" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I437" s="6" t="inlineStr"/>
+      <c r="J437" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$20 — validade 20 dias</t>
+        </is>
+      </c>
+      <c r="K437" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L437" s="5" t="inlineStr"/>
+      <c r="M437" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="N437" s="5" t="inlineStr"/>
+      <c r="O437" s="5" t="inlineStr"/>
+      <c r="P437" s="5" t="inlineStr"/>
+      <c r="Q437" s="5" t="inlineStr"/>
+      <c r="R437" s="5" t="inlineStr"/>
+      <c r="S437" s="5" t="inlineStr"/>
+      <c r="T437" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U437" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 9GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-9gb</t>
+        </is>
+      </c>
+      <c r="H438" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I438" s="3" t="inlineStr"/>
+      <c r="J438" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K438" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L438" s="2" t="inlineStr"/>
+      <c r="M438" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="N438" s="2" t="inlineStr"/>
+      <c r="O438" s="2" t="inlineStr"/>
+      <c r="P438" s="2" t="inlineStr"/>
+      <c r="Q438" s="2" t="inlineStr"/>
+      <c r="R438" s="2" t="inlineStr"/>
+      <c r="S438" s="2" t="inlineStr"/>
+      <c r="T438" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U438" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B439" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C439" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D439" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E439" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F439" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle 41GB</t>
+        </is>
+      </c>
+      <c r="G439" s="5" t="inlineStr">
+        <is>
+          <t>tim:162901</t>
+        </is>
+      </c>
+      <c r="H439" s="6" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="I439" s="6" t="inlineStr"/>
+      <c r="J439" s="5" t="inlineStr"/>
+      <c r="K439" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="L439" s="5" t="inlineStr"/>
+      <c r="M439" s="5" t="inlineStr"/>
+      <c r="N439" s="5" t="inlineStr"/>
+      <c r="O439" s="5" t="inlineStr"/>
+      <c r="P439" s="5" t="inlineStr"/>
+      <c r="Q439" s="5" t="inlineStr"/>
+      <c r="R439" s="5" t="inlineStr"/>
+      <c r="S439" s="5" t="inlineStr"/>
+      <c r="T439" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U439" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Light Express 31GB</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>tim:143536</t>
+        </is>
+      </c>
+      <c r="H440" s="3" t="n">
+        <v>60.99</v>
+      </c>
+      <c r="I440" s="3" t="inlineStr"/>
+      <c r="J440" s="2" t="inlineStr"/>
+      <c r="K440" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="L440" s="2" t="inlineStr"/>
+      <c r="M440" s="2" t="inlineStr"/>
+      <c r="N440" s="2" t="inlineStr"/>
+      <c r="O440" s="2" t="inlineStr"/>
+      <c r="P440" s="2" t="inlineStr"/>
+      <c r="Q440" s="2" t="inlineStr"/>
+      <c r="R440" s="2" t="inlineStr"/>
+      <c r="S440" s="2" t="inlineStr"/>
+      <c r="T440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U440" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B441" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C441" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D441" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E441" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F441" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Plus 45GB</t>
+        </is>
+      </c>
+      <c r="G441" s="5" t="inlineStr">
+        <is>
+          <t>tim:155891</t>
+        </is>
+      </c>
+      <c r="H441" s="6" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I441" s="6" t="inlineStr"/>
+      <c r="J441" s="5" t="inlineStr"/>
+      <c r="K441" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="L441" s="5" t="inlineStr"/>
+      <c r="M441" s="5" t="inlineStr"/>
+      <c r="N441" s="5" t="inlineStr"/>
+      <c r="O441" s="5" t="inlineStr"/>
+      <c r="P441" s="5" t="inlineStr"/>
+      <c r="Q441" s="5" t="inlineStr"/>
+      <c r="R441" s="5" t="inlineStr"/>
+      <c r="S441" s="5" t="inlineStr"/>
+      <c r="T441" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U441" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Premium 53GB</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>tim:162896</t>
+        </is>
+      </c>
+      <c r="H442" s="3" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="I442" s="3" t="inlineStr"/>
+      <c r="J442" s="2" t="inlineStr"/>
+      <c r="K442" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="L442" s="2" t="inlineStr"/>
+      <c r="M442" s="2" t="inlineStr"/>
+      <c r="N442" s="2" t="inlineStr"/>
+      <c r="O442" s="2" t="inlineStr"/>
+      <c r="P442" s="2" t="inlineStr"/>
+      <c r="Q442" s="2" t="inlineStr"/>
+      <c r="R442" s="2" t="inlineStr"/>
+      <c r="S442" s="2" t="inlineStr"/>
+      <c r="T442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U442" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B443" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C443" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D443" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E443" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F443" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Pro Express</t>
+        </is>
+      </c>
+      <c r="G443" s="5" t="inlineStr">
+        <is>
+          <t>tim:143576</t>
+        </is>
+      </c>
+      <c r="H443" s="6" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I443" s="6" t="inlineStr"/>
+      <c r="J443" s="5" t="inlineStr"/>
+      <c r="K443" s="7" t="inlineStr"/>
+      <c r="L443" s="5" t="inlineStr"/>
+      <c r="M443" s="5" t="inlineStr"/>
+      <c r="N443" s="5" t="inlineStr"/>
+      <c r="O443" s="5" t="inlineStr"/>
+      <c r="P443" s="5" t="inlineStr"/>
+      <c r="Q443" s="5" t="inlineStr"/>
+      <c r="R443" s="5" t="inlineStr"/>
+      <c r="S443" s="5" t="inlineStr"/>
+      <c r="T443" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U443" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black 70GB</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>tim:54206</t>
+        </is>
+      </c>
+      <c r="H444" s="3" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="I444" s="3" t="inlineStr"/>
+      <c r="J444" s="2" t="inlineStr"/>
+      <c r="K444" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="L444" s="2" t="inlineStr"/>
+      <c r="M444" s="2" t="inlineStr"/>
+      <c r="N444" s="2" t="inlineStr"/>
+      <c r="O444" s="2" t="inlineStr"/>
+      <c r="P444" s="2" t="inlineStr"/>
+      <c r="Q444" s="2" t="inlineStr"/>
+      <c r="R444" s="2" t="inlineStr"/>
+      <c r="S444" s="2" t="inlineStr"/>
+      <c r="T444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U444" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B445" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C445" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D445" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E445" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F445" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black A Express 67GB</t>
+        </is>
+      </c>
+      <c r="G445" s="5" t="inlineStr">
+        <is>
+          <t>tim:55121</t>
+        </is>
+      </c>
+      <c r="H445" s="6" t="n">
+        <v>119.99</v>
+      </c>
+      <c r="I445" s="6" t="inlineStr"/>
+      <c r="J445" s="5" t="inlineStr"/>
+      <c r="K445" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="L445" s="5" t="inlineStr"/>
+      <c r="M445" s="5" t="inlineStr"/>
+      <c r="N445" s="5" t="inlineStr"/>
+      <c r="O445" s="5" t="inlineStr"/>
+      <c r="P445" s="5" t="inlineStr"/>
+      <c r="Q445" s="5" t="inlineStr"/>
+      <c r="R445" s="5" t="inlineStr"/>
+      <c r="S445" s="5" t="inlineStr"/>
+      <c r="T445" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U445" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black B Express 82GB</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>tim:52146</t>
+        </is>
+      </c>
+      <c r="H446" s="3" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="I446" s="3" t="inlineStr"/>
+      <c r="J446" s="2" t="inlineStr"/>
+      <c r="K446" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="L446" s="2" t="inlineStr"/>
+      <c r="M446" s="2" t="inlineStr"/>
+      <c r="N446" s="2" t="inlineStr"/>
+      <c r="O446" s="2" t="inlineStr"/>
+      <c r="P446" s="2" t="inlineStr"/>
+      <c r="Q446" s="2" t="inlineStr"/>
+      <c r="R446" s="2" t="inlineStr"/>
+      <c r="S446" s="2" t="inlineStr"/>
+      <c r="T446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U446" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B447" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C447" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D447" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E447" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F447" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black C Express 107GB</t>
+        </is>
+      </c>
+      <c r="G447" s="5" t="inlineStr">
+        <is>
+          <t>tim:52151</t>
+        </is>
+      </c>
+      <c r="H447" s="6" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="I447" s="6" t="inlineStr"/>
+      <c r="J447" s="5" t="inlineStr"/>
+      <c r="K447" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="L447" s="5" t="inlineStr"/>
+      <c r="M447" s="5" t="inlineStr"/>
+      <c r="N447" s="5" t="inlineStr"/>
+      <c r="O447" s="5" t="inlineStr"/>
+      <c r="P447" s="5" t="inlineStr"/>
+      <c r="Q447" s="5" t="inlineStr"/>
+      <c r="R447" s="5" t="inlineStr"/>
+      <c r="S447" s="5" t="inlineStr"/>
+      <c r="T447" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U447" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black C Ultra 95GB</t>
+        </is>
+      </c>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>tim:100581</t>
+        </is>
+      </c>
+      <c r="H448" s="3" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I448" s="3" t="inlineStr"/>
+      <c r="J448" s="2" t="inlineStr"/>
+      <c r="K448" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="L448" s="2" t="inlineStr"/>
+      <c r="M448" s="2" t="inlineStr"/>
+      <c r="N448" s="2" t="inlineStr"/>
+      <c r="O448" s="2" t="inlineStr"/>
+      <c r="P448" s="2" t="inlineStr"/>
+      <c r="Q448" s="2" t="inlineStr"/>
+      <c r="R448" s="2" t="inlineStr"/>
+      <c r="S448" s="2" t="inlineStr"/>
+      <c r="T448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U448" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B449" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C449" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D449" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E449" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F449" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black Plus 80GB</t>
+        </is>
+      </c>
+      <c r="G449" s="5" t="inlineStr">
+        <is>
+          <t>tim:54256</t>
+        </is>
+      </c>
+      <c r="H449" s="6" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="I449" s="6" t="inlineStr"/>
+      <c r="J449" s="5" t="inlineStr"/>
+      <c r="K449" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="L449" s="5" t="inlineStr"/>
+      <c r="M449" s="5" t="inlineStr"/>
+      <c r="N449" s="5" t="inlineStr"/>
+      <c r="O449" s="5" t="inlineStr"/>
+      <c r="P449" s="5" t="inlineStr"/>
+      <c r="Q449" s="5" t="inlineStr"/>
+      <c r="R449" s="5" t="inlineStr"/>
+      <c r="S449" s="5" t="inlineStr"/>
+      <c r="T449" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U449" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black Premium 110GB</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>tim:54261</t>
+        </is>
+      </c>
+      <c r="H450" s="3" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I450" s="3" t="inlineStr"/>
+      <c r="J450" s="2" t="inlineStr"/>
+      <c r="K450" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="L450" s="2" t="inlineStr"/>
+      <c r="M450" s="2" t="inlineStr"/>
+      <c r="N450" s="2" t="inlineStr"/>
+      <c r="O450" s="2" t="inlineStr"/>
+      <c r="P450" s="2" t="inlineStr"/>
+      <c r="Q450" s="2" t="inlineStr"/>
+      <c r="R450" s="2" t="inlineStr"/>
+      <c r="S450" s="2" t="inlineStr"/>
+      <c r="T450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U450" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B451" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C451" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D451" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E451" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F451" s="5" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 16GB</t>
+        </is>
+      </c>
+      <c r="G451" s="5" t="inlineStr">
+        <is>
+          <t>tim:106306</t>
+        </is>
+      </c>
+      <c r="H451" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I451" s="6" t="inlineStr"/>
+      <c r="J451" s="5" t="inlineStr"/>
+      <c r="K451" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="L451" s="5" t="inlineStr"/>
+      <c r="M451" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N451" s="5" t="inlineStr"/>
+      <c r="O451" s="5" t="inlineStr"/>
+      <c r="P451" s="5" t="inlineStr"/>
+      <c r="Q451" s="5" t="inlineStr"/>
+      <c r="R451" s="5" t="inlineStr"/>
+      <c r="S451" s="5" t="inlineStr"/>
+      <c r="T451" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U451" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 6GB</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>tim:59906</t>
+        </is>
+      </c>
+      <c r="H452" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I452" s="3" t="inlineStr"/>
+      <c r="J452" s="2" t="inlineStr"/>
+      <c r="K452" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L452" s="2" t="inlineStr"/>
+      <c r="M452" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N452" s="2" t="inlineStr"/>
+      <c r="O452" s="2" t="inlineStr"/>
+      <c r="P452" s="2" t="inlineStr"/>
+      <c r="Q452" s="2" t="inlineStr"/>
+      <c r="R452" s="2" t="inlineStr"/>
+      <c r="S452" s="2" t="inlineStr"/>
+      <c r="T452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U452" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B453" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C453" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D453" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E453" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F453" s="5" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 8GB</t>
+        </is>
+      </c>
+      <c r="G453" s="5" t="inlineStr">
+        <is>
+          <t>tim:59901</t>
+        </is>
+      </c>
+      <c r="H453" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I453" s="6" t="inlineStr"/>
+      <c r="J453" s="5" t="inlineStr"/>
+      <c r="K453" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L453" s="5" t="inlineStr"/>
+      <c r="M453" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N453" s="5" t="inlineStr"/>
+      <c r="O453" s="5" t="inlineStr"/>
+      <c r="P453" s="5" t="inlineStr"/>
+      <c r="Q453" s="5" t="inlineStr"/>
+      <c r="R453" s="5" t="inlineStr"/>
+      <c r="S453" s="5" t="inlineStr"/>
+      <c r="T453" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U453" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029270-46gb</t>
+        </is>
+      </c>
+      <c r="H454" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="I454" s="3" t="inlineStr"/>
+      <c r="J454" s="2" t="inlineStr"/>
+      <c r="K454" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="L454" s="2" t="inlineStr">
+        <is>
+          <t>15 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M454" s="2" t="inlineStr"/>
+      <c r="N454" s="2" t="inlineStr"/>
+      <c r="O454" s="2" t="inlineStr"/>
+      <c r="P454" s="2" t="inlineStr"/>
+      <c r="Q454" s="2" t="inlineStr"/>
+      <c r="R454" s="2" t="inlineStr"/>
+      <c r="S454" s="2" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="T454" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U454" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B455" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C455" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D455" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E455" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F455" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G455" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="H455" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="I455" s="6" t="inlineStr"/>
+      <c r="J455" s="5" t="inlineStr"/>
+      <c r="K455" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L455" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M455" s="5" t="inlineStr"/>
+      <c r="N455" s="5" t="inlineStr"/>
+      <c r="O455" s="5" t="inlineStr"/>
+      <c r="P455" s="5" t="inlineStr"/>
+      <c r="Q455" s="5" t="inlineStr"/>
+      <c r="R455" s="5" t="inlineStr"/>
+      <c r="S455" s="5" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="T455" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U455" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Educação</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029273-61gb</t>
+        </is>
+      </c>
+      <c r="H456" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I456" s="3" t="inlineStr"/>
+      <c r="J456" s="2" t="inlineStr"/>
+      <c r="K456" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L456" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M456" s="2" t="inlineStr"/>
+      <c r="N456" s="2" t="inlineStr"/>
+      <c r="O456" s="2" t="inlineStr"/>
+      <c r="P456" s="2" t="inlineStr"/>
+      <c r="Q456" s="2" t="inlineStr"/>
+      <c r="R456" s="2" t="inlineStr"/>
+      <c r="S456" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Vivae inclusa</t>
+        </is>
+      </c>
+      <c r="T456" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U456" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B457" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C457" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D457" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E457" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F457" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Entretenimento</t>
+        </is>
+      </c>
+      <c r="G457" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="H457" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="I457" s="6" t="inlineStr"/>
+      <c r="J457" s="5" t="inlineStr"/>
+      <c r="K457" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L457" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M457" s="5" t="inlineStr"/>
+      <c r="N457" s="5" t="inlineStr"/>
+      <c r="O457" s="5" t="inlineStr"/>
+      <c r="P457" s="5" t="inlineStr"/>
+      <c r="Q457" s="5" t="inlineStr"/>
+      <c r="R457" s="5" t="inlineStr"/>
+      <c r="S457" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vivo TV Inicial inclusa</t>
+        </is>
+      </c>
+      <c r="T457" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U457" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Música</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029313-61gb</t>
+        </is>
+      </c>
+      <c r="H458" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="I458" s="3" t="inlineStr"/>
+      <c r="J458" s="2" t="inlineStr"/>
+      <c r="K458" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L458" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M458" s="2" t="inlineStr"/>
+      <c r="N458" s="2" t="inlineStr"/>
+      <c r="O458" s="2" t="inlineStr"/>
+      <c r="P458" s="2" t="inlineStr"/>
+      <c r="Q458" s="2" t="inlineStr"/>
+      <c r="R458" s="2" t="inlineStr"/>
+      <c r="S458" s="2" t="inlineStr">
+        <is>
+          <t>Apple Music Individual</t>
+        </is>
+      </c>
+      <c r="T458" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U458" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B459" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C459" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D459" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E459" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F459" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix</t>
+        </is>
+      </c>
+      <c r="G459" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="H459" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="I459" s="6" t="inlineStr"/>
+      <c r="J459" s="5" t="inlineStr"/>
+      <c r="K459" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L459" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M459" s="5" t="inlineStr"/>
+      <c r="N459" s="5" t="inlineStr"/>
+      <c r="O459" s="5" t="inlineStr"/>
+      <c r="P459" s="5" t="inlineStr"/>
+      <c r="Q459" s="5" t="inlineStr"/>
+      <c r="R459" s="5" t="inlineStr"/>
+      <c r="S459" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão com anúncios</t>
+        </is>
+      </c>
+      <c r="T459" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U459" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Saúde</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029301-61gb</t>
+        </is>
+      </c>
+      <c r="H460" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I460" s="3" t="inlineStr"/>
+      <c r="J460" s="2" t="inlineStr"/>
+      <c r="K460" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L460" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M460" s="2" t="inlineStr"/>
+      <c r="N460" s="2" t="inlineStr"/>
+      <c r="O460" s="2" t="inlineStr"/>
+      <c r="P460" s="2" t="inlineStr"/>
+      <c r="Q460" s="2" t="inlineStr"/>
+      <c r="R460" s="2" t="inlineStr"/>
+      <c r="S460" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Vale Saúde Sempre inclusa</t>
+        </is>
+      </c>
+      <c r="T460" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U460" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B461" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C461" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D461" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E461" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F461" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G461" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025883-30gb</t>
+        </is>
+      </c>
+      <c r="H461" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I461" s="6" t="inlineStr"/>
+      <c r="J461" s="5" t="inlineStr"/>
+      <c r="K461" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L461" s="5" t="inlineStr">
+        <is>
+          <t>30 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M461" s="5" t="inlineStr"/>
+      <c r="N461" s="5" t="inlineStr"/>
+      <c r="O461" s="5" t="inlineStr"/>
+      <c r="P461" s="5" t="inlineStr"/>
+      <c r="Q461" s="5" t="inlineStr"/>
+      <c r="R461" s="5" t="inlineStr"/>
+      <c r="S461" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T461" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U461" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025885-40gb</t>
+        </is>
+      </c>
+      <c r="H462" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I462" s="3" t="inlineStr"/>
+      <c r="J462" s="2" t="inlineStr"/>
+      <c r="K462" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L462" s="2" t="inlineStr">
+        <is>
+          <t>40 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M462" s="2" t="inlineStr"/>
+      <c r="N462" s="2" t="inlineStr"/>
+      <c r="O462" s="2" t="inlineStr"/>
+      <c r="P462" s="2" t="inlineStr"/>
+      <c r="Q462" s="2" t="inlineStr"/>
+      <c r="R462" s="2" t="inlineStr"/>
+      <c r="S462" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T462" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U462" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B463" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C463" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D463" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E463" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F463" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G463" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025888-20gb</t>
+        </is>
+      </c>
+      <c r="H463" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="I463" s="6" t="inlineStr"/>
+      <c r="J463" s="5" t="inlineStr"/>
+      <c r="K463" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L463" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M463" s="5" t="inlineStr"/>
+      <c r="N463" s="5" t="inlineStr"/>
+      <c r="O463" s="5" t="inlineStr"/>
+      <c r="P463" s="5" t="inlineStr"/>
+      <c r="Q463" s="5" t="inlineStr"/>
+      <c r="R463" s="5" t="inlineStr"/>
+      <c r="S463" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T463" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U463" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Amazon</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029255-60gb</t>
+        </is>
+      </c>
+      <c r="H464" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="I464" s="3" t="inlineStr"/>
+      <c r="J464" s="2" t="inlineStr"/>
+      <c r="K464" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L464" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M464" s="2" t="inlineStr"/>
+      <c r="N464" s="2" t="inlineStr"/>
+      <c r="O464" s="2" t="inlineStr"/>
+      <c r="P464" s="2" t="inlineStr"/>
+      <c r="Q464" s="2" t="inlineStr"/>
+      <c r="R464" s="2" t="inlineStr"/>
+      <c r="S464" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Amazon Prime inclusa</t>
+        </is>
+      </c>
+      <c r="T464" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U464" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B465" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C465" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D465" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E465" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F465" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Disney+</t>
+        </is>
+      </c>
+      <c r="G465" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022115-60gb</t>
+        </is>
+      </c>
+      <c r="H465" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I465" s="6" t="inlineStr"/>
+      <c r="J465" s="5" t="inlineStr"/>
+      <c r="K465" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L465" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M465" s="5" t="inlineStr"/>
+      <c r="N465" s="5" t="inlineStr"/>
+      <c r="O465" s="5" t="inlineStr"/>
+      <c r="P465" s="5" t="inlineStr"/>
+      <c r="Q465" s="5" t="inlineStr">
+        <is>
+          <t>Disney+</t>
+        </is>
+      </c>
+      <c r="R465" s="5" t="inlineStr"/>
+      <c r="S465" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Disney+ Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="T465" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U465" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Globoplay</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029246-60gb</t>
+        </is>
+      </c>
+      <c r="H466" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="I466" s="3" t="inlineStr"/>
+      <c r="J466" s="2" t="inlineStr"/>
+      <c r="K466" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L466" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M466" s="2" t="inlineStr"/>
+      <c r="N466" s="2" t="inlineStr"/>
+      <c r="O466" s="2" t="inlineStr"/>
+      <c r="P466" s="2" t="inlineStr"/>
+      <c r="Q466" s="2" t="inlineStr">
+        <is>
+          <t>Globoplay</t>
+        </is>
+      </c>
+      <c r="R466" s="2" t="inlineStr"/>
+      <c r="S466" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Globoplay inclusa</t>
+        </is>
+      </c>
+      <c r="T466" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U466" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B467" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C467" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D467" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E467" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F467" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Netflix</t>
+        </is>
+      </c>
+      <c r="G467" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029234-60gb</t>
+        </is>
+      </c>
+      <c r="H467" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I467" s="6" t="inlineStr"/>
+      <c r="J467" s="5" t="inlineStr"/>
+      <c r="K467" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L467" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M467" s="5" t="inlineStr"/>
+      <c r="N467" s="5" t="inlineStr"/>
+      <c r="O467" s="5" t="inlineStr"/>
+      <c r="P467" s="5" t="inlineStr"/>
+      <c r="Q467" s="5" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="R467" s="5" t="inlineStr"/>
+      <c r="S467" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="T467" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U467" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Premiere</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029249-60gb</t>
+        </is>
+      </c>
+      <c r="H468" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I468" s="3" t="inlineStr"/>
+      <c r="J468" s="2" t="inlineStr"/>
+      <c r="K468" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L468" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M468" s="2" t="inlineStr"/>
+      <c r="N468" s="2" t="inlineStr"/>
+      <c r="O468" s="2" t="inlineStr"/>
+      <c r="P468" s="2" t="inlineStr"/>
+      <c r="Q468" s="2" t="inlineStr">
+        <is>
+          <t>Premiere</t>
+        </is>
+      </c>
+      <c r="R468" s="2" t="inlineStr"/>
+      <c r="S468" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Premiere inclusa</t>
+        </is>
+      </c>
+      <c r="T468" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U468" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B469" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C469" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D469" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E469" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F469" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Spotify</t>
+        </is>
+      </c>
+      <c r="G469" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029229-60gb</t>
+        </is>
+      </c>
+      <c r="H469" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="I469" s="6" t="inlineStr"/>
+      <c r="J469" s="5" t="inlineStr"/>
+      <c r="K469" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L469" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M469" s="5" t="inlineStr"/>
+      <c r="N469" s="5" t="inlineStr"/>
+      <c r="O469" s="5" t="inlineStr"/>
+      <c r="P469" s="5" t="inlineStr"/>
+      <c r="Q469" s="5" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="R469" s="5" t="inlineStr"/>
+      <c r="S469" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Spotify Premium inclusa</t>
+        </is>
+      </c>
+      <c r="T469" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U469" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Travel</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029244-70gb</t>
+        </is>
+      </c>
+      <c r="H470" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="I470" s="3" t="inlineStr"/>
+      <c r="J470" s="2" t="inlineStr"/>
+      <c r="K470" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="L470" s="2" t="inlineStr">
+        <is>
+          <t>60 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M470" s="2" t="inlineStr"/>
+      <c r="N470" s="2" t="inlineStr"/>
+      <c r="O470" s="2" t="inlineStr"/>
+      <c r="P470" s="2" t="inlineStr"/>
+      <c r="Q470" s="2" t="inlineStr"/>
+      <c r="R470" s="2" t="inlineStr"/>
+      <c r="S470" s="2" t="inlineStr">
+        <is>
+          <t>6 meses grátis de Gemini com AI Plus</t>
+        </is>
+      </c>
+      <c r="T470" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U470" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B471" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C471" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D471" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E471" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F471" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G471" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-25gb</t>
+        </is>
+      </c>
+      <c r="H471" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I471" s="6" t="inlineStr"/>
+      <c r="J471" s="5" t="inlineStr"/>
+      <c r="K471" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="L471" s="5" t="inlineStr">
+        <is>
+          <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
+        </is>
+      </c>
+      <c r="M471" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N471" s="5" t="inlineStr"/>
+      <c r="O471" s="5" t="inlineStr"/>
+      <c r="P471" s="5" t="inlineStr"/>
+      <c r="Q471" s="5" t="inlineStr"/>
+      <c r="R471" s="5" t="inlineStr"/>
+      <c r="S471" s="5" t="inlineStr"/>
+      <c r="T471" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U471" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-9gb</t>
+        </is>
+      </c>
+      <c r="H472" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I472" s="3" t="inlineStr"/>
+      <c r="J472" s="2" t="inlineStr"/>
+      <c r="K472" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L472" s="2" t="inlineStr">
+        <is>
+          <t>6 GB para navegar como quiser 3 GB para navegar no YouTube</t>
+        </is>
+      </c>
+      <c r="M472" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="N472" s="2" t="inlineStr"/>
+      <c r="O472" s="2" t="inlineStr"/>
+      <c r="P472" s="2" t="inlineStr"/>
+      <c r="Q472" s="2" t="inlineStr"/>
+      <c r="R472" s="2" t="inlineStr"/>
+      <c r="S472" s="2" t="inlineStr"/>
+      <c r="T472" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U472" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B473" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C473" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D473" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E473" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F473" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G473" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-5gb</t>
+        </is>
+      </c>
+      <c r="H473" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I473" s="6" t="inlineStr"/>
+      <c r="J473" s="5" t="inlineStr"/>
+      <c r="K473" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L473" s="5" t="inlineStr">
+        <is>
+          <t>5 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M473" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="N473" s="5" t="inlineStr"/>
+      <c r="O473" s="5" t="inlineStr"/>
+      <c r="P473" s="5" t="inlineStr"/>
+      <c r="Q473" s="5" t="inlineStr"/>
+      <c r="R473" s="5" t="inlineStr"/>
+      <c r="S473" s="5" t="inlineStr"/>
+      <c r="T473" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U473" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T22:14:27</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-4gb</t>
+        </is>
+      </c>
+      <c r="H474" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I474" s="3" t="inlineStr"/>
+      <c r="J474" s="2" t="inlineStr"/>
+      <c r="K474" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L474" s="2" t="inlineStr">
+        <is>
+          <t>4 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M474" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N474" s="2" t="inlineStr"/>
+      <c r="O474" s="2" t="inlineStr"/>
+      <c r="P474" s="2" t="inlineStr"/>
+      <c r="Q474" s="2" t="inlineStr"/>
+      <c r="R474" s="2" t="inlineStr"/>
+      <c r="S474" s="2" t="inlineStr"/>
+      <c r="T474" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U474" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U419"/>
+  <autoFilter ref="A1:U474"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -31063,12 +34856,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -31140,12 +34933,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -31211,12 +35004,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -31282,12 +35075,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -31353,12 +35146,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -31424,12 +35217,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -31495,12 +35288,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -31566,12 +35359,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -31637,12 +35430,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -31708,12 +35501,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -31779,12 +35572,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -31850,12 +35643,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -31921,12 +35714,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -31990,12 +35783,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -32059,12 +35852,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -32128,12 +35921,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -32197,12 +35990,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -32266,12 +36059,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -32335,12 +36128,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -32404,12 +36197,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -32467,12 +36260,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -32530,12 +36323,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -32593,12 +36386,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -32656,12 +36449,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -32717,12 +36510,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -32780,12 +36573,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -32843,12 +36636,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -32906,12 +36699,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -32969,12 +36762,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -33032,12 +36825,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -33095,12 +36888,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -33158,12 +36951,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -33223,12 +37016,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -33288,12 +37081,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -33353,12 +37146,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -33424,12 +37217,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -33495,12 +37288,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -33566,12 +37359,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -33637,12 +37430,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -33708,12 +37501,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -33779,12 +37572,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -33850,12 +37643,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -33921,12 +37714,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -33992,12 +37785,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -34063,12 +37856,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -34134,12 +37927,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -34209,12 +38002,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -34284,12 +38077,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -34359,12 +38152,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -34434,12 +38227,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -34509,12 +38302,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -34580,12 +38373,12 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -34649,12 +38442,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -34718,12 +38511,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -34787,12 +38580,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -34981,7 +38774,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T22:07:51</t>
+          <t>2026-06-30T22:14:27</t>
         </is>
       </c>
     </row>
@@ -34993,7 +38786,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -35014,7 +38807,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -35125,7 +38918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -35665,8 +39458,61 @@
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B11" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0)),"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0)),"")</f>
+        <v/>
+      </c>
+      <c r="M11" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Rows = day: each cell = cheapest R$ that carrier offered in the category on that snapshot_date — a live MINIFS over `history` matching the EXACT date (a locale-safe text date built from the row's date, since history stores dates as TEXT — CONTEXT §7). Pre = cheapest 30-day prepaid plan (validity_days &gt;= 28; pre-#18 dates have no validity → blank, fills from 26-Jun on). Digital = min of Vivo Lite / Claro Flex. Heatmap = per-category-block green→yellow (each cell vs all carriers in its category; subtle while prices are near-flat, differentiates as they move). Grows one row per day; charts on the `Charts` sheet.</t>
         </is>
@@ -35680,7 +39526,7 @@
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="K1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:D10">
+  <conditionalFormatting sqref="B3:D11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -35690,7 +39536,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:G10">
+  <conditionalFormatting sqref="E3:G11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -35700,7 +39546,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:J10">
+  <conditionalFormatting sqref="H3:J11">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -35710,7 +39556,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:M10">
+  <conditionalFormatting sqref="K3:M11">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -35776,15 +39622,15 @@
         </is>
       </c>
       <c r="Q38" s="10">
-        <f>IF('comparison'!B10="",NA(),'comparison'!B10)</f>
+        <f>IF('comparison'!B11="",NA(),'comparison'!B11)</f>
         <v/>
       </c>
       <c r="R38" s="10">
-        <f>IF('comparison'!C10="",NA(),'comparison'!C10)</f>
+        <f>IF('comparison'!C11="",NA(),'comparison'!C11)</f>
         <v/>
       </c>
       <c r="S38" s="10">
-        <f>IF('comparison'!D10="",NA(),'comparison'!D10)</f>
+        <f>IF('comparison'!D11="",NA(),'comparison'!D11)</f>
         <v/>
       </c>
     </row>
@@ -35795,15 +39641,15 @@
         </is>
       </c>
       <c r="Q39" s="10">
-        <f>IF('comparison'!E10="",NA(),'comparison'!E10)</f>
+        <f>IF('comparison'!E11="",NA(),'comparison'!E11)</f>
         <v/>
       </c>
       <c r="R39" s="10">
-        <f>IF('comparison'!F10="",NA(),'comparison'!F10)</f>
+        <f>IF('comparison'!F11="",NA(),'comparison'!F11)</f>
         <v/>
       </c>
       <c r="S39" s="10">
-        <f>IF('comparison'!G10="",NA(),'comparison'!G10)</f>
+        <f>IF('comparison'!G11="",NA(),'comparison'!G11)</f>
         <v/>
       </c>
     </row>
@@ -35814,15 +39660,15 @@
         </is>
       </c>
       <c r="Q40" s="10">
-        <f>IF('comparison'!H10="",NA(),'comparison'!H10)</f>
+        <f>IF('comparison'!H11="",NA(),'comparison'!H11)</f>
         <v/>
       </c>
       <c r="R40" s="10">
-        <f>IF('comparison'!I10="",NA(),'comparison'!I10)</f>
+        <f>IF('comparison'!I11="",NA(),'comparison'!I11)</f>
         <v/>
       </c>
       <c r="S40" s="10">
-        <f>IF('comparison'!J10="",NA(),'comparison'!J10)</f>
+        <f>IF('comparison'!J11="",NA(),'comparison'!J11)</f>
         <v/>
       </c>
     </row>
@@ -35833,15 +39679,15 @@
         </is>
       </c>
       <c r="Q41" s="10">
-        <f>IF('comparison'!K10="",NA(),'comparison'!K10)</f>
+        <f>IF('comparison'!K11="",NA(),'comparison'!K11)</f>
         <v/>
       </c>
       <c r="R41" s="10">
-        <f>IF('comparison'!L10="",NA(),'comparison'!L10)</f>
+        <f>IF('comparison'!L11="",NA(),'comparison'!L11)</f>
         <v/>
       </c>
       <c r="S41" s="10">
-        <f>IF('comparison'!M10="",NA(),'comparison'!M10)</f>
+        <f>IF('comparison'!M11="",NA(),'comparison'!M11)</f>
         <v/>
       </c>
     </row>

--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -19,8 +19,8 @@
     <sheet name="TIM" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$U$474</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$U$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$U$530</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$U$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -300,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$11</f>
+              <f>'comparison'!$A$3:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$B$3:$B$11</f>
+              <f>'comparison'!$B$3:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -337,12 +337,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$11</f>
+              <f>'comparison'!$A$3:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$C$3:$C$11</f>
+              <f>'comparison'!$C$3:$C$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -374,12 +374,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$11</f>
+              <f>'comparison'!$A$3:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$D$3:$D$11</f>
+              <f>'comparison'!$D$3:$D$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -497,12 +497,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$11</f>
+              <f>'comparison'!$A$3:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$E$3:$E$11</f>
+              <f>'comparison'!$E$3:$E$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -534,12 +534,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$11</f>
+              <f>'comparison'!$A$3:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$F$3:$F$11</f>
+              <f>'comparison'!$F$3:$F$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -571,12 +571,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$11</f>
+              <f>'comparison'!$A$3:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$G$3:$G$11</f>
+              <f>'comparison'!$G$3:$G$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -694,12 +694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$11</f>
+              <f>'comparison'!$A$3:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$H$3:$H$11</f>
+              <f>'comparison'!$H$3:$H$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -731,12 +731,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$11</f>
+              <f>'comparison'!$A$3:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$I$3:$I$11</f>
+              <f>'comparison'!$I$3:$I$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -768,12 +768,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$11</f>
+              <f>'comparison'!$A$3:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$J$3:$J$11</f>
+              <f>'comparison'!$J$3:$J$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -891,12 +891,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$11</f>
+              <f>'comparison'!$A$3:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$K$3:$K$11</f>
+              <f>'comparison'!$K$3:$K$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -928,12 +928,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$11</f>
+              <f>'comparison'!$A$3:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$L$3:$L$11</f>
+              <f>'comparison'!$L$3:$L$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -965,12 +965,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$11</f>
+              <f>'comparison'!$A$3:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$M$3:$M$11</f>
+              <f>'comparison'!$M$3:$M$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1602,7 +1602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U474"/>
+  <dimension ref="A1:U530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -34266,8 +34266,3888 @@
         </is>
       </c>
     </row>
+    <row r="475">
+      <c r="A475" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B475" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C475" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D475" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E475" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F475" s="5" t="inlineStr">
+        <is>
+          <t>Controle 25GB</t>
+        </is>
+      </c>
+      <c r="G475" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-25gb</t>
+        </is>
+      </c>
+      <c r="H475" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I475" s="6" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="J475" s="5" t="inlineStr">
+        <is>
+          <t>De R$ 59,90 Por:</t>
+        </is>
+      </c>
+      <c r="K475" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="L475" s="5" t="inlineStr"/>
+      <c r="M475" s="5" t="inlineStr"/>
+      <c r="N475" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O475" s="5" t="inlineStr"/>
+      <c r="P475" s="5" t="inlineStr"/>
+      <c r="Q475" s="5" t="inlineStr"/>
+      <c r="R475" s="5" t="inlineStr"/>
+      <c r="S475" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e vídeos; Bônus exclusivo; Aproveite na sua franquia; WhatsApp e ligações ilimitadas</t>
+        </is>
+      </c>
+      <c r="T475" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U475" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb</t>
+        </is>
+      </c>
+      <c r="H476" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I476" s="3" t="inlineStr"/>
+      <c r="J476" s="2" t="inlineStr"/>
+      <c r="K476" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L476" s="2" t="inlineStr"/>
+      <c r="M476" s="2" t="inlineStr"/>
+      <c r="N476" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O476" s="2" t="inlineStr"/>
+      <c r="P476" s="2" t="inlineStr"/>
+      <c r="Q476" s="2" t="inlineStr"/>
+      <c r="R476" s="2" t="inlineStr"/>
+      <c r="S476" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U476" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B477" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C477" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D477" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E477" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F477" s="5" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G477" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb-gaming</t>
+        </is>
+      </c>
+      <c r="H477" s="6" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I477" s="6" t="inlineStr"/>
+      <c r="J477" s="5" t="inlineStr"/>
+      <c r="K477" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L477" s="5" t="inlineStr"/>
+      <c r="M477" s="5" t="inlineStr"/>
+      <c r="N477" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O477" s="5" t="inlineStr"/>
+      <c r="P477" s="5" t="inlineStr"/>
+      <c r="Q477" s="5" t="inlineStr"/>
+      <c r="R477" s="5" t="inlineStr"/>
+      <c r="S477" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus para redes sociais e apps; Bônus uso livre; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T477" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="U477" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>Flex 15GB</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-15gb</t>
+        </is>
+      </c>
+      <c r="H478" s="3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I478" s="3" t="inlineStr"/>
+      <c r="J478" s="2" t="inlineStr"/>
+      <c r="K478" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L478" s="2" t="inlineStr"/>
+      <c r="M478" s="2" t="inlineStr"/>
+      <c r="N478" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O478" s="2" t="inlineStr"/>
+      <c r="P478" s="2" t="inlineStr"/>
+      <c r="Q478" s="2" t="inlineStr"/>
+      <c r="R478" s="2" t="inlineStr"/>
+      <c r="S478" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U478" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B479" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C479" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D479" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E479" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F479" s="5" t="inlineStr">
+        <is>
+          <t>Flex 20GB</t>
+        </is>
+      </c>
+      <c r="G479" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-20gb</t>
+        </is>
+      </c>
+      <c r="H479" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I479" s="6" t="inlineStr"/>
+      <c r="J479" s="5" t="inlineStr"/>
+      <c r="K479" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L479" s="5" t="inlineStr"/>
+      <c r="M479" s="5" t="inlineStr"/>
+      <c r="N479" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O479" s="5" t="inlineStr"/>
+      <c r="P479" s="5" t="inlineStr"/>
+      <c r="Q479" s="5" t="inlineStr"/>
+      <c r="R479" s="5" t="inlineStr"/>
+      <c r="S479" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="T479" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U479" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>Flex 30GB</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-30gb</t>
+        </is>
+      </c>
+      <c r="H480" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I480" s="3" t="inlineStr"/>
+      <c r="J480" s="2" t="inlineStr"/>
+      <c r="K480" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L480" s="2" t="inlineStr"/>
+      <c r="M480" s="2" t="inlineStr"/>
+      <c r="N480" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O480" s="2" t="inlineStr"/>
+      <c r="P480" s="2" t="inlineStr"/>
+      <c r="Q480" s="2" t="inlineStr"/>
+      <c r="R480" s="2" t="inlineStr"/>
+      <c r="S480" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="T480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U480" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B481" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C481" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D481" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E481" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F481" s="5" t="inlineStr">
+        <is>
+          <t>Flex 40GB</t>
+        </is>
+      </c>
+      <c r="G481" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-40gb</t>
+        </is>
+      </c>
+      <c r="H481" s="6" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I481" s="6" t="inlineStr"/>
+      <c r="J481" s="5" t="inlineStr"/>
+      <c r="K481" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L481" s="5" t="inlineStr"/>
+      <c r="M481" s="5" t="inlineStr"/>
+      <c r="N481" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O481" s="5" t="inlineStr"/>
+      <c r="P481" s="5" t="inlineStr"/>
+      <c r="Q481" s="5" t="inlineStr"/>
+      <c r="R481" s="5" t="inlineStr"/>
+      <c r="S481" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e apps; Bônus uso livre; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="T481" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="U481" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>Pós 100GB</t>
+        </is>
+      </c>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-100gb</t>
+        </is>
+      </c>
+      <c r="H482" s="3" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="I482" s="3" t="inlineStr"/>
+      <c r="J482" s="2" t="inlineStr"/>
+      <c r="K482" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L482" s="2" t="inlineStr"/>
+      <c r="M482" s="2" t="inlineStr"/>
+      <c r="N482" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O482" s="2" t="inlineStr"/>
+      <c r="P482" s="2" t="inlineStr"/>
+      <c r="Q482" s="2" t="inlineStr"/>
+      <c r="R482" s="2" t="inlineStr"/>
+      <c r="S482" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U482" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B483" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C483" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D483" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E483" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F483" s="5" t="inlineStr">
+        <is>
+          <t>Pós 150GB</t>
+        </is>
+      </c>
+      <c r="G483" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-150gb</t>
+        </is>
+      </c>
+      <c r="H483" s="6" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="I483" s="6" t="inlineStr"/>
+      <c r="J483" s="5" t="inlineStr"/>
+      <c r="K483" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="L483" s="5" t="inlineStr"/>
+      <c r="M483" s="5" t="inlineStr"/>
+      <c r="N483" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O483" s="5" t="inlineStr"/>
+      <c r="P483" s="5" t="inlineStr"/>
+      <c r="Q483" s="5" t="inlineStr"/>
+      <c r="R483" s="5" t="inlineStr"/>
+      <c r="S483" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas e Europa; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T483" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U483" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>Pós 200GB</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-200gb</t>
+        </is>
+      </c>
+      <c r="H484" s="3" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="I484" s="3" t="inlineStr"/>
+      <c r="J484" s="2" t="inlineStr"/>
+      <c r="K484" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="L484" s="2" t="inlineStr"/>
+      <c r="M484" s="2" t="inlineStr"/>
+      <c r="N484" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O484" s="2" t="inlineStr"/>
+      <c r="P484" s="2" t="inlineStr"/>
+      <c r="Q484" s="2" t="inlineStr"/>
+      <c r="R484" s="2" t="inlineStr"/>
+      <c r="S484" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T484" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U484" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B485" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C485" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D485" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E485" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F485" s="5" t="inlineStr">
+        <is>
+          <t>Pós 50GB com GeForce NOW</t>
+        </is>
+      </c>
+      <c r="G485" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb-geforce</t>
+        </is>
+      </c>
+      <c r="H485" s="6" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="I485" s="6" t="inlineStr"/>
+      <c r="J485" s="5" t="inlineStr"/>
+      <c r="K485" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="L485" s="5" t="inlineStr"/>
+      <c r="M485" s="5" t="inlineStr"/>
+      <c r="N485" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O485" s="5" t="inlineStr"/>
+      <c r="P485" s="5" t="inlineStr"/>
+      <c r="Q485" s="5" t="inlineStr"/>
+      <c r="R485" s="5" t="inlineStr"/>
+      <c r="S485" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado; Inclusa assinatura GeForce NOW</t>
+        </is>
+      </c>
+      <c r="T485" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U485" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>Pós 60GB</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb</t>
+        </is>
+      </c>
+      <c r="H486" s="3" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="I486" s="3" t="inlineStr"/>
+      <c r="J486" s="2" t="inlineStr"/>
+      <c r="K486" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L486" s="2" t="inlineStr"/>
+      <c r="M486" s="2" t="inlineStr"/>
+      <c r="N486" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="O486" s="2" t="inlineStr"/>
+      <c r="P486" s="2" t="inlineStr"/>
+      <c r="Q486" s="2" t="inlineStr"/>
+      <c r="R486" s="2" t="inlineStr"/>
+      <c r="S486" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="T486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="U486" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B487" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C487" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D487" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E487" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F487" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 10GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G487" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-10gb</t>
+        </is>
+      </c>
+      <c r="H487" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I487" s="6" t="inlineStr"/>
+      <c r="J487" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K487" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L487" s="5" t="inlineStr"/>
+      <c r="M487" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="N487" s="5" t="inlineStr"/>
+      <c r="O487" s="5" t="inlineStr"/>
+      <c r="P487" s="5" t="inlineStr"/>
+      <c r="Q487" s="5" t="inlineStr"/>
+      <c r="R487" s="5" t="inlineStr"/>
+      <c r="S487" s="5" t="inlineStr"/>
+      <c r="T487" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U487" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 12GB (30 dias)</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-30d-12gb</t>
+        </is>
+      </c>
+      <c r="H488" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I488" s="3" t="inlineStr"/>
+      <c r="J488" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$30 — validade 30 dias</t>
+        </is>
+      </c>
+      <c r="K488" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L488" s="2" t="inlineStr"/>
+      <c r="M488" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N488" s="2" t="inlineStr"/>
+      <c r="O488" s="2" t="inlineStr"/>
+      <c r="P488" s="2" t="inlineStr"/>
+      <c r="Q488" s="2" t="inlineStr"/>
+      <c r="R488" s="2" t="inlineStr"/>
+      <c r="S488" s="2" t="inlineStr"/>
+      <c r="T488" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U488" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B489" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C489" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D489" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E489" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F489" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 4GB (12 dias)</t>
+        </is>
+      </c>
+      <c r="G489" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-12d-4gb</t>
+        </is>
+      </c>
+      <c r="H489" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I489" s="6" t="inlineStr"/>
+      <c r="J489" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$15 — validade 12 dias</t>
+        </is>
+      </c>
+      <c r="K489" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L489" s="5" t="inlineStr"/>
+      <c r="M489" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N489" s="5" t="inlineStr"/>
+      <c r="O489" s="5" t="inlineStr"/>
+      <c r="P489" s="5" t="inlineStr"/>
+      <c r="Q489" s="5" t="inlineStr"/>
+      <c r="R489" s="5" t="inlineStr"/>
+      <c r="S489" s="5" t="inlineStr"/>
+      <c r="T489" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U489" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 5GB (15 dias)</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-15d-5gb</t>
+        </is>
+      </c>
+      <c r="H490" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I490" s="3" t="inlineStr"/>
+      <c r="J490" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$15 — validade 15 dias</t>
+        </is>
+      </c>
+      <c r="K490" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L490" s="2" t="inlineStr"/>
+      <c r="M490" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N490" s="2" t="inlineStr"/>
+      <c r="O490" s="2" t="inlineStr"/>
+      <c r="P490" s="2" t="inlineStr"/>
+      <c r="Q490" s="2" t="inlineStr"/>
+      <c r="R490" s="2" t="inlineStr"/>
+      <c r="S490" s="2" t="inlineStr"/>
+      <c r="T490" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U490" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B491" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C491" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D491" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E491" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F491" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 6GB (20 dias)</t>
+        </is>
+      </c>
+      <c r="G491" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-20d-6gb</t>
+        </is>
+      </c>
+      <c r="H491" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I491" s="6" t="inlineStr"/>
+      <c r="J491" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$20 — validade 20 dias</t>
+        </is>
+      </c>
+      <c r="K491" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L491" s="5" t="inlineStr"/>
+      <c r="M491" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="N491" s="5" t="inlineStr"/>
+      <c r="O491" s="5" t="inlineStr"/>
+      <c r="P491" s="5" t="inlineStr"/>
+      <c r="Q491" s="5" t="inlineStr"/>
+      <c r="R491" s="5" t="inlineStr"/>
+      <c r="S491" s="5" t="inlineStr"/>
+      <c r="T491" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U491" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 8GB (20 dias)</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-20d-8gb</t>
+        </is>
+      </c>
+      <c r="H492" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I492" s="3" t="inlineStr"/>
+      <c r="J492" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$20 — validade 20 dias</t>
+        </is>
+      </c>
+      <c r="K492" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L492" s="2" t="inlineStr"/>
+      <c r="M492" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="N492" s="2" t="inlineStr"/>
+      <c r="O492" s="2" t="inlineStr"/>
+      <c r="P492" s="2" t="inlineStr"/>
+      <c r="Q492" s="2" t="inlineStr"/>
+      <c r="R492" s="2" t="inlineStr"/>
+      <c r="S492" s="2" t="inlineStr"/>
+      <c r="T492" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U492" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B493" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C493" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D493" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E493" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F493" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 9GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G493" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-9gb</t>
+        </is>
+      </c>
+      <c r="H493" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I493" s="6" t="inlineStr"/>
+      <c r="J493" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K493" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L493" s="5" t="inlineStr"/>
+      <c r="M493" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="N493" s="5" t="inlineStr"/>
+      <c r="O493" s="5" t="inlineStr"/>
+      <c r="P493" s="5" t="inlineStr"/>
+      <c r="Q493" s="5" t="inlineStr"/>
+      <c r="R493" s="5" t="inlineStr"/>
+      <c r="S493" s="5" t="inlineStr"/>
+      <c r="T493" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="U493" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle 41GB</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>tim:162901</t>
+        </is>
+      </c>
+      <c r="H494" s="3" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="I494" s="3" t="inlineStr"/>
+      <c r="J494" s="2" t="inlineStr"/>
+      <c r="K494" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="L494" s="2" t="inlineStr"/>
+      <c r="M494" s="2" t="inlineStr"/>
+      <c r="N494" s="2" t="inlineStr"/>
+      <c r="O494" s="2" t="inlineStr"/>
+      <c r="P494" s="2" t="inlineStr"/>
+      <c r="Q494" s="2" t="inlineStr"/>
+      <c r="R494" s="2" t="inlineStr"/>
+      <c r="S494" s="2" t="inlineStr"/>
+      <c r="T494" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U494" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B495" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C495" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D495" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E495" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F495" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Light Express 31GB</t>
+        </is>
+      </c>
+      <c r="G495" s="5" t="inlineStr">
+        <is>
+          <t>tim:143536</t>
+        </is>
+      </c>
+      <c r="H495" s="6" t="n">
+        <v>60.99</v>
+      </c>
+      <c r="I495" s="6" t="inlineStr"/>
+      <c r="J495" s="5" t="inlineStr"/>
+      <c r="K495" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="L495" s="5" t="inlineStr"/>
+      <c r="M495" s="5" t="inlineStr"/>
+      <c r="N495" s="5" t="inlineStr"/>
+      <c r="O495" s="5" t="inlineStr"/>
+      <c r="P495" s="5" t="inlineStr"/>
+      <c r="Q495" s="5" t="inlineStr"/>
+      <c r="R495" s="5" t="inlineStr"/>
+      <c r="S495" s="5" t="inlineStr"/>
+      <c r="T495" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U495" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F496" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Plus 45GB</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>tim:155891</t>
+        </is>
+      </c>
+      <c r="H496" s="3" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I496" s="3" t="inlineStr"/>
+      <c r="J496" s="2" t="inlineStr"/>
+      <c r="K496" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="L496" s="2" t="inlineStr"/>
+      <c r="M496" s="2" t="inlineStr"/>
+      <c r="N496" s="2" t="inlineStr"/>
+      <c r="O496" s="2" t="inlineStr"/>
+      <c r="P496" s="2" t="inlineStr"/>
+      <c r="Q496" s="2" t="inlineStr"/>
+      <c r="R496" s="2" t="inlineStr"/>
+      <c r="S496" s="2" t="inlineStr"/>
+      <c r="T496" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U496" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B497" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C497" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D497" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E497" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F497" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Premium 53GB</t>
+        </is>
+      </c>
+      <c r="G497" s="5" t="inlineStr">
+        <is>
+          <t>tim:162896</t>
+        </is>
+      </c>
+      <c r="H497" s="6" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="I497" s="6" t="inlineStr"/>
+      <c r="J497" s="5" t="inlineStr"/>
+      <c r="K497" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="L497" s="5" t="inlineStr"/>
+      <c r="M497" s="5" t="inlineStr"/>
+      <c r="N497" s="5" t="inlineStr"/>
+      <c r="O497" s="5" t="inlineStr"/>
+      <c r="P497" s="5" t="inlineStr"/>
+      <c r="Q497" s="5" t="inlineStr"/>
+      <c r="R497" s="5" t="inlineStr"/>
+      <c r="S497" s="5" t="inlineStr"/>
+      <c r="T497" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U497" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F498" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Pro Express</t>
+        </is>
+      </c>
+      <c r="G498" s="2" t="inlineStr">
+        <is>
+          <t>tim:143576</t>
+        </is>
+      </c>
+      <c r="H498" s="3" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I498" s="3" t="inlineStr"/>
+      <c r="J498" s="2" t="inlineStr"/>
+      <c r="K498" s="4" t="inlineStr"/>
+      <c r="L498" s="2" t="inlineStr"/>
+      <c r="M498" s="2" t="inlineStr"/>
+      <c r="N498" s="2" t="inlineStr"/>
+      <c r="O498" s="2" t="inlineStr"/>
+      <c r="P498" s="2" t="inlineStr"/>
+      <c r="Q498" s="2" t="inlineStr"/>
+      <c r="R498" s="2" t="inlineStr"/>
+      <c r="S498" s="2" t="inlineStr"/>
+      <c r="T498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="U498" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B499" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C499" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D499" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E499" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F499" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black 70GB</t>
+        </is>
+      </c>
+      <c r="G499" s="5" t="inlineStr">
+        <is>
+          <t>tim:54206</t>
+        </is>
+      </c>
+      <c r="H499" s="6" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="I499" s="6" t="inlineStr"/>
+      <c r="J499" s="5" t="inlineStr"/>
+      <c r="K499" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="L499" s="5" t="inlineStr"/>
+      <c r="M499" s="5" t="inlineStr"/>
+      <c r="N499" s="5" t="inlineStr"/>
+      <c r="O499" s="5" t="inlineStr"/>
+      <c r="P499" s="5" t="inlineStr"/>
+      <c r="Q499" s="5" t="inlineStr"/>
+      <c r="R499" s="5" t="inlineStr"/>
+      <c r="S499" s="5" t="inlineStr"/>
+      <c r="T499" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U499" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F500" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black A Express 67GB</t>
+        </is>
+      </c>
+      <c r="G500" s="2" t="inlineStr">
+        <is>
+          <t>tim:55121</t>
+        </is>
+      </c>
+      <c r="H500" s="3" t="n">
+        <v>119.99</v>
+      </c>
+      <c r="I500" s="3" t="inlineStr"/>
+      <c r="J500" s="2" t="inlineStr"/>
+      <c r="K500" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="L500" s="2" t="inlineStr"/>
+      <c r="M500" s="2" t="inlineStr"/>
+      <c r="N500" s="2" t="inlineStr"/>
+      <c r="O500" s="2" t="inlineStr"/>
+      <c r="P500" s="2" t="inlineStr"/>
+      <c r="Q500" s="2" t="inlineStr"/>
+      <c r="R500" s="2" t="inlineStr"/>
+      <c r="S500" s="2" t="inlineStr"/>
+      <c r="T500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U500" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B501" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C501" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D501" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E501" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F501" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black B Express 82GB</t>
+        </is>
+      </c>
+      <c r="G501" s="5" t="inlineStr">
+        <is>
+          <t>tim:52146</t>
+        </is>
+      </c>
+      <c r="H501" s="6" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="I501" s="6" t="inlineStr"/>
+      <c r="J501" s="5" t="inlineStr"/>
+      <c r="K501" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="L501" s="5" t="inlineStr"/>
+      <c r="M501" s="5" t="inlineStr"/>
+      <c r="N501" s="5" t="inlineStr"/>
+      <c r="O501" s="5" t="inlineStr"/>
+      <c r="P501" s="5" t="inlineStr"/>
+      <c r="Q501" s="5" t="inlineStr"/>
+      <c r="R501" s="5" t="inlineStr"/>
+      <c r="S501" s="5" t="inlineStr"/>
+      <c r="T501" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U501" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F502" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black C Express 107GB</t>
+        </is>
+      </c>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>tim:52151</t>
+        </is>
+      </c>
+      <c r="H502" s="3" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="I502" s="3" t="inlineStr"/>
+      <c r="J502" s="2" t="inlineStr"/>
+      <c r="K502" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="L502" s="2" t="inlineStr"/>
+      <c r="M502" s="2" t="inlineStr"/>
+      <c r="N502" s="2" t="inlineStr"/>
+      <c r="O502" s="2" t="inlineStr"/>
+      <c r="P502" s="2" t="inlineStr"/>
+      <c r="Q502" s="2" t="inlineStr"/>
+      <c r="R502" s="2" t="inlineStr"/>
+      <c r="S502" s="2" t="inlineStr"/>
+      <c r="T502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U502" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B503" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C503" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D503" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E503" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F503" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black C Ultra 95GB</t>
+        </is>
+      </c>
+      <c r="G503" s="5" t="inlineStr">
+        <is>
+          <t>tim:100581</t>
+        </is>
+      </c>
+      <c r="H503" s="6" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I503" s="6" t="inlineStr"/>
+      <c r="J503" s="5" t="inlineStr"/>
+      <c r="K503" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="L503" s="5" t="inlineStr"/>
+      <c r="M503" s="5" t="inlineStr"/>
+      <c r="N503" s="5" t="inlineStr"/>
+      <c r="O503" s="5" t="inlineStr"/>
+      <c r="P503" s="5" t="inlineStr"/>
+      <c r="Q503" s="5" t="inlineStr"/>
+      <c r="R503" s="5" t="inlineStr"/>
+      <c r="S503" s="5" t="inlineStr"/>
+      <c r="T503" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U503" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D504" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black Plus 80GB</t>
+        </is>
+      </c>
+      <c r="G504" s="2" t="inlineStr">
+        <is>
+          <t>tim:54256</t>
+        </is>
+      </c>
+      <c r="H504" s="3" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="I504" s="3" t="inlineStr"/>
+      <c r="J504" s="2" t="inlineStr"/>
+      <c r="K504" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="L504" s="2" t="inlineStr"/>
+      <c r="M504" s="2" t="inlineStr"/>
+      <c r="N504" s="2" t="inlineStr"/>
+      <c r="O504" s="2" t="inlineStr"/>
+      <c r="P504" s="2" t="inlineStr"/>
+      <c r="Q504" s="2" t="inlineStr"/>
+      <c r="R504" s="2" t="inlineStr"/>
+      <c r="S504" s="2" t="inlineStr"/>
+      <c r="T504" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U504" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B505" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C505" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D505" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E505" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F505" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black Premium 110GB</t>
+        </is>
+      </c>
+      <c r="G505" s="5" t="inlineStr">
+        <is>
+          <t>tim:54261</t>
+        </is>
+      </c>
+      <c r="H505" s="6" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I505" s="6" t="inlineStr"/>
+      <c r="J505" s="5" t="inlineStr"/>
+      <c r="K505" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="L505" s="5" t="inlineStr"/>
+      <c r="M505" s="5" t="inlineStr"/>
+      <c r="N505" s="5" t="inlineStr"/>
+      <c r="O505" s="5" t="inlineStr"/>
+      <c r="P505" s="5" t="inlineStr"/>
+      <c r="Q505" s="5" t="inlineStr"/>
+      <c r="R505" s="5" t="inlineStr"/>
+      <c r="S505" s="5" t="inlineStr"/>
+      <c r="T505" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="U505" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 16GB</t>
+        </is>
+      </c>
+      <c r="G506" s="2" t="inlineStr">
+        <is>
+          <t>tim:106306</t>
+        </is>
+      </c>
+      <c r="H506" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I506" s="3" t="inlineStr"/>
+      <c r="J506" s="2" t="inlineStr"/>
+      <c r="K506" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="L506" s="2" t="inlineStr"/>
+      <c r="M506" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N506" s="2" t="inlineStr"/>
+      <c r="O506" s="2" t="inlineStr"/>
+      <c r="P506" s="2" t="inlineStr"/>
+      <c r="Q506" s="2" t="inlineStr"/>
+      <c r="R506" s="2" t="inlineStr"/>
+      <c r="S506" s="2" t="inlineStr"/>
+      <c r="T506" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U506" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B507" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C507" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D507" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E507" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F507" s="5" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 6GB</t>
+        </is>
+      </c>
+      <c r="G507" s="5" t="inlineStr">
+        <is>
+          <t>tim:59906</t>
+        </is>
+      </c>
+      <c r="H507" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I507" s="6" t="inlineStr"/>
+      <c r="J507" s="5" t="inlineStr"/>
+      <c r="K507" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L507" s="5" t="inlineStr"/>
+      <c r="M507" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="N507" s="5" t="inlineStr"/>
+      <c r="O507" s="5" t="inlineStr"/>
+      <c r="P507" s="5" t="inlineStr"/>
+      <c r="Q507" s="5" t="inlineStr"/>
+      <c r="R507" s="5" t="inlineStr"/>
+      <c r="S507" s="5" t="inlineStr"/>
+      <c r="T507" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U507" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 8GB</t>
+        </is>
+      </c>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>tim:59901</t>
+        </is>
+      </c>
+      <c r="H508" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I508" s="3" t="inlineStr"/>
+      <c r="J508" s="2" t="inlineStr"/>
+      <c r="K508" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L508" s="2" t="inlineStr"/>
+      <c r="M508" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="N508" s="2" t="inlineStr"/>
+      <c r="O508" s="2" t="inlineStr"/>
+      <c r="P508" s="2" t="inlineStr"/>
+      <c r="Q508" s="2" t="inlineStr"/>
+      <c r="R508" s="2" t="inlineStr"/>
+      <c r="S508" s="2" t="inlineStr"/>
+      <c r="T508" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="U508" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B509" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C509" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D509" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E509" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F509" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G509" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029270-46gb</t>
+        </is>
+      </c>
+      <c r="H509" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I509" s="6" t="inlineStr"/>
+      <c r="J509" s="5" t="inlineStr"/>
+      <c r="K509" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="L509" s="5" t="inlineStr">
+        <is>
+          <t>15 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M509" s="5" t="inlineStr"/>
+      <c r="N509" s="5" t="inlineStr"/>
+      <c r="O509" s="5" t="inlineStr"/>
+      <c r="P509" s="5" t="inlineStr"/>
+      <c r="Q509" s="5" t="inlineStr"/>
+      <c r="R509" s="5" t="inlineStr"/>
+      <c r="S509" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T509" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U509" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F510" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G510" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="H510" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I510" s="3" t="inlineStr"/>
+      <c r="J510" s="2" t="inlineStr"/>
+      <c r="K510" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L510" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M510" s="2" t="inlineStr"/>
+      <c r="N510" s="2" t="inlineStr"/>
+      <c r="O510" s="2" t="inlineStr"/>
+      <c r="P510" s="2" t="inlineStr"/>
+      <c r="Q510" s="2" t="inlineStr"/>
+      <c r="R510" s="2" t="inlineStr"/>
+      <c r="S510" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T510" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U510" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B511" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C511" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D511" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E511" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F511" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Educação</t>
+        </is>
+      </c>
+      <c r="G511" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029273-61gb</t>
+        </is>
+      </c>
+      <c r="H511" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I511" s="6" t="inlineStr"/>
+      <c r="J511" s="5" t="inlineStr"/>
+      <c r="K511" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L511" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M511" s="5" t="inlineStr"/>
+      <c r="N511" s="5" t="inlineStr"/>
+      <c r="O511" s="5" t="inlineStr"/>
+      <c r="P511" s="5" t="inlineStr"/>
+      <c r="Q511" s="5" t="inlineStr"/>
+      <c r="R511" s="5" t="inlineStr"/>
+      <c r="S511" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vivae inclusa</t>
+        </is>
+      </c>
+      <c r="T511" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U511" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D512" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F512" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Entretenimento</t>
+        </is>
+      </c>
+      <c r="G512" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="H512" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="I512" s="3" t="inlineStr"/>
+      <c r="J512" s="2" t="inlineStr"/>
+      <c r="K512" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L512" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M512" s="2" t="inlineStr"/>
+      <c r="N512" s="2" t="inlineStr"/>
+      <c r="O512" s="2" t="inlineStr"/>
+      <c r="P512" s="2" t="inlineStr"/>
+      <c r="Q512" s="2" t="inlineStr"/>
+      <c r="R512" s="2" t="inlineStr"/>
+      <c r="S512" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Vivo TV Inicial inclusa</t>
+        </is>
+      </c>
+      <c r="T512" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U512" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B513" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C513" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D513" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E513" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F513" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Música</t>
+        </is>
+      </c>
+      <c r="G513" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029313-61gb</t>
+        </is>
+      </c>
+      <c r="H513" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="I513" s="6" t="inlineStr"/>
+      <c r="J513" s="5" t="inlineStr"/>
+      <c r="K513" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L513" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M513" s="5" t="inlineStr"/>
+      <c r="N513" s="5" t="inlineStr"/>
+      <c r="O513" s="5" t="inlineStr"/>
+      <c r="P513" s="5" t="inlineStr"/>
+      <c r="Q513" s="5" t="inlineStr"/>
+      <c r="R513" s="5" t="inlineStr"/>
+      <c r="S513" s="5" t="inlineStr">
+        <is>
+          <t>Apple Music Individual</t>
+        </is>
+      </c>
+      <c r="T513" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U513" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix</t>
+        </is>
+      </c>
+      <c r="G514" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="H514" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="I514" s="3" t="inlineStr"/>
+      <c r="J514" s="2" t="inlineStr"/>
+      <c r="K514" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L514" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M514" s="2" t="inlineStr"/>
+      <c r="N514" s="2" t="inlineStr"/>
+      <c r="O514" s="2" t="inlineStr"/>
+      <c r="P514" s="2" t="inlineStr"/>
+      <c r="Q514" s="2" t="inlineStr"/>
+      <c r="R514" s="2" t="inlineStr"/>
+      <c r="S514" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão com anúncios</t>
+        </is>
+      </c>
+      <c r="T514" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U514" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B515" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C515" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D515" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E515" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F515" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Saúde</t>
+        </is>
+      </c>
+      <c r="G515" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029301-61gb</t>
+        </is>
+      </c>
+      <c r="H515" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I515" s="6" t="inlineStr"/>
+      <c r="J515" s="5" t="inlineStr"/>
+      <c r="K515" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L515" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M515" s="5" t="inlineStr"/>
+      <c r="N515" s="5" t="inlineStr"/>
+      <c r="O515" s="5" t="inlineStr"/>
+      <c r="P515" s="5" t="inlineStr"/>
+      <c r="Q515" s="5" t="inlineStr"/>
+      <c r="R515" s="5" t="inlineStr"/>
+      <c r="S515" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vale Saúde Sempre inclusa</t>
+        </is>
+      </c>
+      <c r="T515" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U515" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Segurança</t>
+        </is>
+      </c>
+      <c r="G516" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029274-61gb</t>
+        </is>
+      </c>
+      <c r="H516" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I516" s="3" t="inlineStr"/>
+      <c r="J516" s="2" t="inlineStr"/>
+      <c r="K516" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="L516" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M516" s="2" t="inlineStr"/>
+      <c r="N516" s="2" t="inlineStr"/>
+      <c r="O516" s="2" t="inlineStr"/>
+      <c r="P516" s="2" t="inlineStr"/>
+      <c r="Q516" s="2" t="inlineStr"/>
+      <c r="R516" s="2" t="inlineStr"/>
+      <c r="S516" s="2" t="inlineStr">
+        <is>
+          <t>Incluso Proteção Rua e Seguro de Bens</t>
+        </is>
+      </c>
+      <c r="T516" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="U516" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B517" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C517" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D517" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E517" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F517" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G517" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025883-30gb</t>
+        </is>
+      </c>
+      <c r="H517" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="I517" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J517" s="5" t="inlineStr">
+        <is>
+          <t>preço sem fidelidade; fidelidade 12m no promo</t>
+        </is>
+      </c>
+      <c r="K517" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L517" s="5" t="inlineStr">
+        <is>
+          <t>30 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M517" s="5" t="inlineStr"/>
+      <c r="N517" s="5" t="inlineStr"/>
+      <c r="O517" s="5" t="inlineStr"/>
+      <c r="P517" s="5" t="inlineStr"/>
+      <c r="Q517" s="5" t="inlineStr"/>
+      <c r="R517" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="S517" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T517" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U517" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G518" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025885-40gb</t>
+        </is>
+      </c>
+      <c r="H518" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="I518" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J518" s="2" t="inlineStr">
+        <is>
+          <t>preço sem fidelidade; fidelidade 12m no promo</t>
+        </is>
+      </c>
+      <c r="K518" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L518" s="2" t="inlineStr">
+        <is>
+          <t>40 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M518" s="2" t="inlineStr"/>
+      <c r="N518" s="2" t="inlineStr"/>
+      <c r="O518" s="2" t="inlineStr"/>
+      <c r="P518" s="2" t="inlineStr"/>
+      <c r="Q518" s="2" t="inlineStr"/>
+      <c r="R518" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S518" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T518" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U518" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B519" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C519" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D519" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E519" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F519" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G519" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025888-20gb</t>
+        </is>
+      </c>
+      <c r="H519" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="I519" s="6" t="inlineStr"/>
+      <c r="J519" s="5" t="inlineStr"/>
+      <c r="K519" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L519" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia</t>
+        </is>
+      </c>
+      <c r="M519" s="5" t="inlineStr"/>
+      <c r="N519" s="5" t="inlineStr"/>
+      <c r="O519" s="5" t="inlineStr"/>
+      <c r="P519" s="5" t="inlineStr"/>
+      <c r="Q519" s="5" t="inlineStr"/>
+      <c r="R519" s="5" t="inlineStr"/>
+      <c r="S519" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T519" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="U519" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D520" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F520" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Amazon</t>
+        </is>
+      </c>
+      <c r="G520" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029255-60gb</t>
+        </is>
+      </c>
+      <c r="H520" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="I520" s="3" t="inlineStr"/>
+      <c r="J520" s="2" t="inlineStr"/>
+      <c r="K520" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L520" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M520" s="2" t="inlineStr"/>
+      <c r="N520" s="2" t="inlineStr"/>
+      <c r="O520" s="2" t="inlineStr"/>
+      <c r="P520" s="2" t="inlineStr"/>
+      <c r="Q520" s="2" t="inlineStr"/>
+      <c r="R520" s="2" t="inlineStr"/>
+      <c r="S520" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Amazon Prime inclusa</t>
+        </is>
+      </c>
+      <c r="T520" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U520" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B521" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C521" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D521" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E521" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F521" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Disney+</t>
+        </is>
+      </c>
+      <c r="G521" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022115-60gb</t>
+        </is>
+      </c>
+      <c r="H521" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I521" s="6" t="inlineStr"/>
+      <c r="J521" s="5" t="inlineStr"/>
+      <c r="K521" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L521" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M521" s="5" t="inlineStr"/>
+      <c r="N521" s="5" t="inlineStr"/>
+      <c r="O521" s="5" t="inlineStr"/>
+      <c r="P521" s="5" t="inlineStr"/>
+      <c r="Q521" s="5" t="inlineStr">
+        <is>
+          <t>Disney+</t>
+        </is>
+      </c>
+      <c r="R521" s="5" t="inlineStr"/>
+      <c r="S521" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Disney+ Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="T521" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U521" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F522" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Globoplay</t>
+        </is>
+      </c>
+      <c r="G522" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029246-60gb</t>
+        </is>
+      </c>
+      <c r="H522" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="I522" s="3" t="inlineStr"/>
+      <c r="J522" s="2" t="inlineStr"/>
+      <c r="K522" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L522" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M522" s="2" t="inlineStr"/>
+      <c r="N522" s="2" t="inlineStr"/>
+      <c r="O522" s="2" t="inlineStr"/>
+      <c r="P522" s="2" t="inlineStr"/>
+      <c r="Q522" s="2" t="inlineStr">
+        <is>
+          <t>Globoplay</t>
+        </is>
+      </c>
+      <c r="R522" s="2" t="inlineStr"/>
+      <c r="S522" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Globoplay inclusa</t>
+        </is>
+      </c>
+      <c r="T522" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U522" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B523" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C523" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D523" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E523" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F523" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Netflix</t>
+        </is>
+      </c>
+      <c r="G523" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029234-60gb</t>
+        </is>
+      </c>
+      <c r="H523" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I523" s="6" t="inlineStr"/>
+      <c r="J523" s="5" t="inlineStr"/>
+      <c r="K523" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L523" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M523" s="5" t="inlineStr"/>
+      <c r="N523" s="5" t="inlineStr"/>
+      <c r="O523" s="5" t="inlineStr"/>
+      <c r="P523" s="5" t="inlineStr"/>
+      <c r="Q523" s="5" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="R523" s="5" t="inlineStr"/>
+      <c r="S523" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="T523" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U523" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D524" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F524" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Premiere</t>
+        </is>
+      </c>
+      <c r="G524" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029249-60gb</t>
+        </is>
+      </c>
+      <c r="H524" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I524" s="3" t="inlineStr"/>
+      <c r="J524" s="2" t="inlineStr"/>
+      <c r="K524" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L524" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M524" s="2" t="inlineStr"/>
+      <c r="N524" s="2" t="inlineStr"/>
+      <c r="O524" s="2" t="inlineStr"/>
+      <c r="P524" s="2" t="inlineStr"/>
+      <c r="Q524" s="2" t="inlineStr">
+        <is>
+          <t>Premiere</t>
+        </is>
+      </c>
+      <c r="R524" s="2" t="inlineStr"/>
+      <c r="S524" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Premiere inclusa</t>
+        </is>
+      </c>
+      <c r="T524" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U524" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B525" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C525" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D525" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E525" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F525" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Spotify</t>
+        </is>
+      </c>
+      <c r="G525" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029229-60gb</t>
+        </is>
+      </c>
+      <c r="H525" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="I525" s="6" t="inlineStr"/>
+      <c r="J525" s="5" t="inlineStr"/>
+      <c r="K525" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L525" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M525" s="5" t="inlineStr"/>
+      <c r="N525" s="5" t="inlineStr"/>
+      <c r="O525" s="5" t="inlineStr"/>
+      <c r="P525" s="5" t="inlineStr"/>
+      <c r="Q525" s="5" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="R525" s="5" t="inlineStr"/>
+      <c r="S525" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Spotify Premium inclusa</t>
+        </is>
+      </c>
+      <c r="T525" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U525" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D526" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F526" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Travel</t>
+        </is>
+      </c>
+      <c r="G526" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029244-70gb</t>
+        </is>
+      </c>
+      <c r="H526" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="I526" s="3" t="inlineStr"/>
+      <c r="J526" s="2" t="inlineStr"/>
+      <c r="K526" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="L526" s="2" t="inlineStr">
+        <is>
+          <t>60 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M526" s="2" t="inlineStr"/>
+      <c r="N526" s="2" t="inlineStr"/>
+      <c r="O526" s="2" t="inlineStr"/>
+      <c r="P526" s="2" t="inlineStr"/>
+      <c r="Q526" s="2" t="inlineStr"/>
+      <c r="R526" s="2" t="inlineStr"/>
+      <c r="S526" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="T526" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="U526" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B527" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C527" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D527" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E527" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F527" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G527" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-25gb</t>
+        </is>
+      </c>
+      <c r="H527" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I527" s="6" t="inlineStr"/>
+      <c r="J527" s="5" t="inlineStr"/>
+      <c r="K527" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="L527" s="5" t="inlineStr">
+        <is>
+          <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
+        </is>
+      </c>
+      <c r="M527" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N527" s="5" t="inlineStr"/>
+      <c r="O527" s="5" t="inlineStr"/>
+      <c r="P527" s="5" t="inlineStr"/>
+      <c r="Q527" s="5" t="inlineStr"/>
+      <c r="R527" s="5" t="inlineStr"/>
+      <c r="S527" s="5" t="inlineStr"/>
+      <c r="T527" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U527" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F528" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G528" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-9gb</t>
+        </is>
+      </c>
+      <c r="H528" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I528" s="3" t="inlineStr"/>
+      <c r="J528" s="2" t="inlineStr"/>
+      <c r="K528" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L528" s="2" t="inlineStr">
+        <is>
+          <t>6 GB para navegar como quiser 3 GB para navegar no YouTube</t>
+        </is>
+      </c>
+      <c r="M528" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="N528" s="2" t="inlineStr"/>
+      <c r="O528" s="2" t="inlineStr"/>
+      <c r="P528" s="2" t="inlineStr"/>
+      <c r="Q528" s="2" t="inlineStr"/>
+      <c r="R528" s="2" t="inlineStr"/>
+      <c r="S528" s="2" t="inlineStr"/>
+      <c r="T528" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U528" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B529" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C529" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D529" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E529" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F529" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G529" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-5gb</t>
+        </is>
+      </c>
+      <c r="H529" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I529" s="6" t="inlineStr"/>
+      <c r="J529" s="5" t="inlineStr"/>
+      <c r="K529" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L529" s="5" t="inlineStr">
+        <is>
+          <t>5 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M529" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="N529" s="5" t="inlineStr"/>
+      <c r="O529" s="5" t="inlineStr"/>
+      <c r="P529" s="5" t="inlineStr"/>
+      <c r="Q529" s="5" t="inlineStr"/>
+      <c r="R529" s="5" t="inlineStr"/>
+      <c r="S529" s="5" t="inlineStr"/>
+      <c r="T529" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U529" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D530" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F530" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G530" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-4gb</t>
+        </is>
+      </c>
+      <c r="H530" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I530" s="3" t="inlineStr"/>
+      <c r="J530" s="2" t="inlineStr"/>
+      <c r="K530" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L530" s="2" t="inlineStr">
+        <is>
+          <t>4 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M530" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N530" s="2" t="inlineStr"/>
+      <c r="O530" s="2" t="inlineStr"/>
+      <c r="P530" s="2" t="inlineStr"/>
+      <c r="Q530" s="2" t="inlineStr"/>
+      <c r="R530" s="2" t="inlineStr"/>
+      <c r="S530" s="2" t="inlineStr"/>
+      <c r="T530" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U530" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U474"/>
+  <autoFilter ref="A1:U530"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34624,7 +38504,7 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6 GB · 30d</t>
+          <t>6 GB · 17d</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
@@ -34644,7 +38524,7 @@
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>8 GB · 30d</t>
+          <t>8 GB · 22d</t>
         </is>
       </c>
       <c r="E18" s="5" t="n"/>
@@ -34720,7 +38600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U56"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -34856,12 +38736,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -34933,12 +38813,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -35004,12 +38884,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -35075,12 +38955,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -35146,12 +39026,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -35217,12 +39097,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -35288,12 +39168,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -35359,12 +39239,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -35430,12 +39310,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -35501,12 +39381,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -35572,12 +39452,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -35643,12 +39523,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -35714,12 +39594,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -35783,12 +39663,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -35852,12 +39732,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -35921,12 +39801,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -35990,12 +39870,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -36059,12 +39939,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -36128,12 +40008,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -36197,12 +40077,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -36260,12 +40140,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -36323,12 +40203,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -36386,12 +40266,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -36449,12 +40329,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -36510,12 +40390,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -36573,12 +40453,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -36636,12 +40516,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -36699,12 +40579,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -36762,12 +40642,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -36825,12 +40705,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -36888,12 +40768,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -36951,12 +40831,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -37016,12 +40896,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -37059,7 +40939,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
@@ -37081,12 +40961,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -37124,7 +41004,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N35" s="5" t="inlineStr"/>
       <c r="O35" s="5" t="inlineStr"/>
@@ -37146,12 +41026,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -37200,7 +41080,7 @@
       <c r="R36" s="2" t="inlineStr"/>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6 meses grátis de Gemini com AI Plus</t>
+          <t>2 meses de YouTube sem consumo no plano</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -37217,12 +41097,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -37271,7 +41151,7 @@
       <c r="R37" s="5" t="inlineStr"/>
       <c r="S37" s="5" t="inlineStr">
         <is>
-          <t>6 meses grátis de Gemini com AI Plus</t>
+          <t>2 meses de YouTube sem consumo no plano</t>
         </is>
       </c>
       <c r="T37" s="5" t="inlineStr">
@@ -37288,12 +41168,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -37359,12 +41239,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -37430,12 +41310,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -37501,12 +41381,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -37572,12 +41452,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -37643,12 +41523,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -37658,7 +41538,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>lite</t>
+          <t>control</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -37668,25 +41548,25 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Easy Lite</t>
+          <t>Vivo Controle Segurança</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600025883-30gb</t>
+          <t>vivo:VIV202600029274-61gb</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I43" s="6" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="7" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>30 GB de franquia</t>
+          <t>20 GB de franquia 31 GB de bônus</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr"/>
@@ -37697,29 +41577,29 @@
       <c r="R43" s="5" t="inlineStr"/>
       <c r="S43" s="5" t="inlineStr">
         <is>
-          <t>2 meses de YouTube sem consumo no plano</t>
+          <t>Incluso Proteção Rua e Seguro de Bens</t>
         </is>
       </c>
       <c r="T43" s="5" t="inlineStr">
         <is>
-          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
         </is>
       </c>
       <c r="U43" s="5" t="inlineStr">
         <is>
-          <t>data/raw/vivo_lite_SP.html</t>
+          <t>data/raw/vivo_control_SP.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -37744,20 +41624,26 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600025885-40gb</t>
+          <t>vivo:VIV202600025883-30gb</t>
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>preço sem fidelidade; fidelidade 12m no promo</t>
+        </is>
+      </c>
       <c r="K44" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>40 GB de franquia</t>
+          <t>30 GB de franquia</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
@@ -37765,7 +41651,9 @@
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr"/>
-      <c r="R44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
           <t>2 meses de YouTube sem consumo no plano</t>
@@ -37785,12 +41673,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -37815,20 +41703,26 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600025888-20gb</t>
+          <t>vivo:VIV202600025885-40gb</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>preço sem fidelidade; fidelidade 12m no promo</t>
+        </is>
+      </c>
       <c r="K45" s="7" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>20 GB de franquia</t>
+          <t>40 GB de franquia</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr"/>
@@ -37836,7 +41730,9 @@
       <c r="O45" s="5" t="inlineStr"/>
       <c r="P45" s="5" t="inlineStr"/>
       <c r="Q45" s="5" t="inlineStr"/>
-      <c r="R45" s="5" t="inlineStr"/>
+      <c r="R45" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="S45" s="5" t="inlineStr">
         <is>
           <t>2 meses de YouTube sem consumo no plano</t>
@@ -37856,12 +41752,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -37871,7 +41767,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>postpaid</t>
+          <t>lite</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -37881,25 +41777,25 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Vivo Pós com Amazon</t>
+          <t>Easy Lite</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029255-60gb</t>
+          <t>vivo:VIV202600025888-20gb</t>
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="I46" s="3" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="4" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>50 GB de franquia 10 GB de bônus</t>
+          <t>20 GB de franquia</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
@@ -37910,29 +41806,29 @@
       <c r="R46" s="2" t="inlineStr"/>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>Assinatura Amazon Prime inclusa</t>
+          <t>2 meses de YouTube sem consumo no plano</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>data/raw/vivo_postpaid_SP.html</t>
+          <t>data/raw/vivo_lite_SP.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -37952,16 +41848,16 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Vivo Pós com Disney+</t>
+          <t>Vivo Pós com Amazon</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600022115-60gb</t>
+          <t>vivo:VIV202600029255-60gb</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I47" s="6" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
@@ -37977,15 +41873,11 @@
       <c r="N47" s="5" t="inlineStr"/>
       <c r="O47" s="5" t="inlineStr"/>
       <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr">
-        <is>
-          <t>Disney+</t>
-        </is>
-      </c>
+      <c r="Q47" s="5" t="inlineStr"/>
       <c r="R47" s="5" t="inlineStr"/>
       <c r="S47" s="5" t="inlineStr">
         <is>
-          <t>Assinatura Disney+ Padrão inclusa</t>
+          <t>Assinatura Amazon Prime inclusa</t>
         </is>
       </c>
       <c r="T47" s="5" t="inlineStr">
@@ -38002,12 +41894,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -38027,16 +41919,16 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Vivo Pós com Globoplay</t>
+          <t>Vivo Pós com Disney+</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029246-60gb</t>
+          <t>vivo:VIV202600022115-60gb</t>
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="I48" s="3" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
@@ -38054,13 +41946,13 @@
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>Globoplay</t>
+          <t>Disney+</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr"/>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Assinatura Globoplay inclusa</t>
+          <t>Assinatura Disney+ Padrão inclusa</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
@@ -38077,12 +41969,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -38102,16 +41994,16 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Vivo Pós com Netflix</t>
+          <t>Vivo Pós com Globoplay</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029234-60gb</t>
+          <t>vivo:VIV202600029246-60gb</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I49" s="6" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr"/>
@@ -38129,13 +42021,13 @@
       <c r="P49" s="5" t="inlineStr"/>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Globoplay</t>
         </is>
       </c>
       <c r="R49" s="5" t="inlineStr"/>
       <c r="S49" s="5" t="inlineStr">
         <is>
-          <t>Assinatura Netflix Padrão inclusa</t>
+          <t>Assinatura Globoplay inclusa</t>
         </is>
       </c>
       <c r="T49" s="5" t="inlineStr">
@@ -38152,12 +42044,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -38177,12 +42069,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Vivo Pós com Premiere</t>
+          <t>Vivo Pós com Netflix</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029249-60gb</t>
+          <t>vivo:VIV202600029234-60gb</t>
         </is>
       </c>
       <c r="H50" s="3" t="n">
@@ -38204,13 +42096,13 @@
       <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Premiere</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr"/>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>Assinatura Premiere inclusa</t>
+          <t>Assinatura Netflix Padrão inclusa</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
@@ -38227,12 +42119,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -38252,16 +42144,16 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Vivo Pós com Spotify</t>
+          <t>Vivo Pós com Premiere</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029229-60gb</t>
+          <t>vivo:VIV202600029249-60gb</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="I51" s="6" t="inlineStr"/>
       <c r="J51" s="5" t="inlineStr"/>
@@ -38279,13 +42171,13 @@
       <c r="P51" s="5" t="inlineStr"/>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Premiere</t>
         </is>
       </c>
       <c r="R51" s="5" t="inlineStr"/>
       <c r="S51" s="5" t="inlineStr">
         <is>
-          <t>Assinatura Spotify Premium inclusa</t>
+          <t>Assinatura Premiere inclusa</t>
         </is>
       </c>
       <c r="T51" s="5" t="inlineStr">
@@ -38302,12 +42194,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -38327,36 +42219,40 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Vivo Pós com Travel</t>
+          <t>Vivo Pós com Spotify</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029244-70gb</t>
+          <t>vivo:VIV202600029229-60gb</t>
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="I52" s="3" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>60 GB de franquia 10 GB de bônus</t>
+          <t>50 GB de franquia 10 GB de bônus</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr"/>
-      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
       <c r="R52" s="2" t="inlineStr"/>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>6 meses grátis de Gemini com AI Plus</t>
+          <t>Assinatura Spotify Premium inclusa</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
@@ -38373,12 +42269,12 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -38388,7 +42284,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>prepaid</t>
+          <t>postpaid</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -38398,56 +42294,58 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Vivo Pré</t>
+          <t>Vivo Pós com Travel</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029370-25gb</t>
+          <t>vivo:VIV202600029244-70gb</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>30</v>
+        <v>215</v>
       </c>
       <c r="I53" s="6" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr"/>
       <c r="K53" s="7" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
-        </is>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v>30</v>
-      </c>
+          <t>60 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr"/>
       <c r="N53" s="5" t="inlineStr"/>
       <c r="O53" s="5" t="inlineStr"/>
       <c r="P53" s="5" t="inlineStr"/>
       <c r="Q53" s="5" t="inlineStr"/>
       <c r="R53" s="5" t="inlineStr"/>
-      <c r="S53" s="5" t="inlineStr"/>
+      <c r="S53" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
       <c r="T53" s="5" t="inlineStr">
         <is>
-          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
       <c r="U53" s="5" t="inlineStr">
         <is>
-          <t>data/raw/vivo_prepaid_SP.html</t>
+          <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -38472,24 +42370,24 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029370-9gb</t>
+          <t>vivo:VIV202600029370-25gb</t>
         </is>
       </c>
       <c r="H54" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I54" s="3" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>6 GB para navegar como quiser 3 GB para navegar no YouTube</t>
+          <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr"/>
@@ -38511,12 +42409,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -38541,24 +42439,24 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029370-5gb</t>
+          <t>vivo:VIV202600029370-9gb</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I55" s="6" t="inlineStr"/>
       <c r="J55" s="5" t="inlineStr"/>
       <c r="K55" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>5 GB para navegar como quiser</t>
+          <t>6 GB para navegar como quiser 3 GB para navegar no YouTube</t>
         </is>
       </c>
       <c r="M55" s="5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N55" s="5" t="inlineStr"/>
       <c r="O55" s="5" t="inlineStr"/>
@@ -38580,12 +42478,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -38610,24 +42508,24 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029370-4gb</t>
+          <t>vivo:VIV202600029370-5gb</t>
         </is>
       </c>
       <c r="H56" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I56" s="3" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>4 GB para navegar como quiser</t>
+          <t>5 GB para navegar como quiser</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr"/>
@@ -38646,9 +42544,78 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-01T18:01:33</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-4gb</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr"/>
+      <c r="K57" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>4 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N57" s="5" t="inlineStr"/>
+      <c r="O57" s="5" t="inlineStr"/>
+      <c r="P57" s="5" t="inlineStr"/>
+      <c r="Q57" s="5" t="inlineStr"/>
+      <c r="R57" s="5" t="inlineStr"/>
+      <c r="S57" s="5" t="inlineStr"/>
+      <c r="T57" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="U57" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U56"/>
-  <conditionalFormatting sqref="H2:H56">
+  <autoFilter ref="A1:U57"/>
+  <conditionalFormatting sqref="H2:H57">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -38660,7 +42627,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I56">
+  <conditionalFormatting sqref="I2:I57">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>NOT(ISBLANK(I2))</formula>
     </cfRule>
@@ -38676,7 +42643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -38735,6 +42702,125 @@
         <is>
           <t>delta_brl</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029274-61gb</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Segurança</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>price_change</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025883-30gb</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>price_change</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600025885-40gb</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -38774,7 +42860,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T22:14:27</t>
+          <t>2026-07-01T18:01:33</t>
         </is>
       </c>
     </row>
@@ -38786,7 +42872,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -38797,7 +42883,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -38807,7 +42893,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -38845,19 +42931,19 @@
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(latest!$C$2:$C$2000,$A$9)</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="C9" s="10">
         <f>IFERROR(_xlfn.MINIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="D9" s="10">
         <f>IFERROR(AVERAGEIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
-        <v/>
+        <v>98.68</v>
       </c>
       <c r="E9" s="10">
         <f>IFERROR(_xlfn.MAXIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
-        <v/>
+        <v>215</v>
       </c>
     </row>
     <row r="10">
@@ -38868,19 +42954,19 @@
       </c>
       <c r="B10" s="2">
         <f>COUNTIF(latest!$C$2:$C$2000,$A$10)</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="C10" s="10">
         <f>IFERROR(_xlfn.MINIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$10),"-")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="D10" s="10">
         <f>IFERROR(AVERAGEIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$10),"-")</f>
-        <v/>
+        <v>90.73</v>
       </c>
       <c r="E10" s="10">
         <f>IFERROR(_xlfn.MAXIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$10),"-")</f>
-        <v/>
+        <v>339.9</v>
       </c>
     </row>
     <row r="11">
@@ -38891,19 +42977,19 @@
       </c>
       <c r="B11" s="2">
         <f>COUNTIF(latest!$C$2:$C$2000,$A$11)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C11" s="10">
         <f>IFERROR(_xlfn.MINIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$11),"-")</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="D11" s="10">
         <f>IFERROR(AVERAGEIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$11),"-")</f>
-        <v/>
+        <v>95.99</v>
       </c>
       <c r="E11" s="10">
         <f>IFERROR(_xlfn.MAXIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$11),"-")</f>
-        <v/>
+        <v>164.99</v>
       </c>
     </row>
   </sheetData>
@@ -38918,7 +43004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -39040,27 +43126,27 @@
       </c>
       <c r="B3" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))),"")</f>
-        <v/>
+        <v>58.99</v>
       </c>
       <c r="C3" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))),"")</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="D3" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))),"")</f>
-        <v/>
+        <v>59.9</v>
       </c>
       <c r="E3" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))),"")</f>
-        <v/>
+        <v>119.99</v>
       </c>
       <c r="F3" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))),"")</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="G3" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))),"")</f>
-        <v/>
+        <v>124.9</v>
       </c>
       <c r="H3" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"),history!$M:$M,"&gt;=28")),"")</f>
@@ -39080,11 +43166,11 @@
       </c>
       <c r="L3" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00")),0)),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="M3" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00")),0)),"")</f>
-        <v/>
+        <v>44.9</v>
       </c>
     </row>
     <row r="4">
@@ -39093,27 +43179,27 @@
       </c>
       <c r="B4" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))),"")</f>
-        <v/>
+        <v>58.99</v>
       </c>
       <c r="C4" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))),"")</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="D4" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))),"")</f>
-        <v/>
+        <v>59.9</v>
       </c>
       <c r="E4" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))),"")</f>
-        <v/>
+        <v>119.99</v>
       </c>
       <c r="F4" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))),"")</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="G4" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))),"")</f>
-        <v/>
+        <v>124.9</v>
       </c>
       <c r="H4" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"),history!$M:$M,"&gt;=28")),"")</f>
@@ -39133,11 +43219,11 @@
       </c>
       <c r="L4" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00")),0)),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="M4" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00")),0)),"")</f>
-        <v/>
+        <v>44.9</v>
       </c>
     </row>
     <row r="5">
@@ -39146,27 +43232,27 @@
       </c>
       <c r="B5" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))),"")</f>
-        <v/>
+        <v>58.99</v>
       </c>
       <c r="C5" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))),"")</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="D5" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))),"")</f>
-        <v/>
+        <v>59.9</v>
       </c>
       <c r="E5" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))),"")</f>
-        <v/>
+        <v>119.99</v>
       </c>
       <c r="F5" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))),"")</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="G5" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))),"")</f>
-        <v/>
+        <v>124.9</v>
       </c>
       <c r="H5" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"),history!$M:$M,"&gt;=28")),"")</f>
@@ -39186,11 +43272,11 @@
       </c>
       <c r="L5" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00")),0)),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="M5" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00")),0)),"")</f>
-        <v/>
+        <v>44.9</v>
       </c>
     </row>
     <row r="6">
@@ -39199,27 +43285,27 @@
       </c>
       <c r="B6" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))),"")</f>
-        <v/>
+        <v>58.99</v>
       </c>
       <c r="C6" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))),"")</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="D6" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))),"")</f>
-        <v/>
+        <v>59.9</v>
       </c>
       <c r="E6" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))),"")</f>
-        <v/>
+        <v>119.99</v>
       </c>
       <c r="F6" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))),"")</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="G6" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))),"")</f>
-        <v/>
+        <v>124.9</v>
       </c>
       <c r="H6" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"),history!$M:$M,"&gt;=28")),"")</f>
@@ -39239,11 +43325,11 @@
       </c>
       <c r="L6" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00")),0)),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="M6" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00")),0)),"")</f>
-        <v/>
+        <v>44.9</v>
       </c>
     </row>
     <row r="7">
@@ -39252,39 +43338,39 @@
       </c>
       <c r="B7" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))),"")</f>
-        <v/>
+        <v>58.99</v>
       </c>
       <c r="C7" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))),"")</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="D7" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))),"")</f>
-        <v/>
+        <v>59.9</v>
       </c>
       <c r="E7" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))),"")</f>
-        <v/>
+        <v>119.99</v>
       </c>
       <c r="F7" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))),"")</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="G7" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))),"")</f>
-        <v/>
+        <v>124.9</v>
       </c>
       <c r="H7" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="I7" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="J7" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="K7" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0)),"")</f>
@@ -39292,11 +43378,11 @@
       </c>
       <c r="L7" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0)),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="M7" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0)),"")</f>
-        <v/>
+        <v>44.9</v>
       </c>
     </row>
     <row r="8">
@@ -39305,39 +43391,39 @@
       </c>
       <c r="B8" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
-        <v/>
+        <v>58.99</v>
       </c>
       <c r="C8" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="D8" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
-        <v/>
+        <v>59.9</v>
       </c>
       <c r="E8" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
-        <v/>
+        <v>119.99</v>
       </c>
       <c r="F8" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="G8" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
-        <v/>
+        <v>124.9</v>
       </c>
       <c r="H8" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="I8" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="J8" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="K8" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0)),"")</f>
@@ -39345,11 +43431,11 @@
       </c>
       <c r="L8" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0)),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="M8" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0)),"")</f>
-        <v/>
+        <v>44.9</v>
       </c>
     </row>
     <row r="9">
@@ -39358,39 +43444,39 @@
       </c>
       <c r="B9" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
-        <v/>
+        <v>58.99</v>
       </c>
       <c r="C9" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="D9" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
-        <v/>
+        <v>59.9</v>
       </c>
       <c r="E9" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
-        <v/>
+        <v>119.99</v>
       </c>
       <c r="F9" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="G9" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
-        <v/>
+        <v>124.9</v>
       </c>
       <c r="H9" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="I9" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="J9" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="K9" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0)),"")</f>
@@ -39398,11 +43484,11 @@
       </c>
       <c r="L9" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0)),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="M9" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0)),"")</f>
-        <v/>
+        <v>44.9</v>
       </c>
     </row>
     <row r="10">
@@ -39411,39 +43497,39 @@
       </c>
       <c r="B10" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
-        <v/>
+        <v>58.99</v>
       </c>
       <c r="C10" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="D10" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
-        <v/>
+        <v>59.9</v>
       </c>
       <c r="E10" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
-        <v/>
+        <v>119.99</v>
       </c>
       <c r="F10" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="G10" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
-        <v/>
+        <v>124.9</v>
       </c>
       <c r="H10" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="I10" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="J10" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="K10" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0)),"")</f>
@@ -39451,11 +43537,11 @@
       </c>
       <c r="L10" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0)),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="M10" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0)),"")</f>
-        <v/>
+        <v>44.9</v>
       </c>
     </row>
     <row r="11">
@@ -39464,39 +43550,39 @@
       </c>
       <c r="B11" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
-        <v/>
+        <v>58.99</v>
       </c>
       <c r="C11" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
-        <v/>
+        <v>59</v>
       </c>
       <c r="D11" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
-        <v/>
+        <v>59.9</v>
       </c>
       <c r="E11" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
-        <v/>
+        <v>119.99</v>
       </c>
       <c r="F11" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="G11" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
-        <v/>
+        <v>124.9</v>
       </c>
       <c r="H11" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="I11" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="J11" s="3">
         <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$M:$M,"&gt;=28")),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="K11" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0)),"")</f>
@@ -39504,15 +43590,68 @@
       </c>
       <c r="L11" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0)),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="M11" s="3">
         <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0)),"")</f>
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B12" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))),"")</f>
+        <v>58.99</v>
+      </c>
+      <c r="C12" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))),"")</f>
+        <v>59</v>
+      </c>
+      <c r="D12" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))),"")</f>
+        <v>59.9</v>
+      </c>
+      <c r="E12" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))),"")</f>
+        <v>119.99</v>
+      </c>
+      <c r="F12" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))),"")</f>
+        <v>150</v>
+      </c>
+      <c r="G12" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))),"")</f>
+        <v>124.9</v>
+      </c>
+      <c r="H12" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v>30</v>
+      </c>
+      <c r="I12" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v>30</v>
+      </c>
+      <c r="J12" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$M:$M,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$M:$M,"&gt;=28")),"")</f>
+        <v>30</v>
+      </c>
+      <c r="K12" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="L12" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0)),"")</f>
+        <v>35</v>
+      </c>
+      <c r="M12" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0)),"")</f>
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Rows = day: each cell = cheapest R$ that carrier offered in the category on that snapshot_date — a live MINIFS over `history` matching the EXACT date (a locale-safe text date built from the row's date, since history stores dates as TEXT — CONTEXT §7). Pre = cheapest 30-day prepaid plan (validity_days &gt;= 28; pre-#18 dates have no validity → blank, fills from 26-Jun on). Digital = min of Vivo Lite / Claro Flex. Heatmap = per-category-block green→yellow (each cell vs all carriers in its category; subtle while prices are near-flat, differentiates as they move). Grows one row per day; charts on the `Charts` sheet.</t>
         </is>
@@ -39526,7 +43665,7 @@
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="K1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:D11">
+  <conditionalFormatting sqref="B3:D12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -39536,7 +43675,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:G11">
+  <conditionalFormatting sqref="E3:G12">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -39546,7 +43685,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:J11">
+  <conditionalFormatting sqref="H3:J12">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -39556,7 +43695,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:M11">
+  <conditionalFormatting sqref="K3:M12">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -39622,15 +43761,15 @@
         </is>
       </c>
       <c r="Q38" s="10">
-        <f>IF('comparison'!B11="",NA(),'comparison'!B11)</f>
+        <f>IF('comparison'!B12="",NA(),'comparison'!B12)</f>
         <v/>
       </c>
       <c r="R38" s="10">
-        <f>IF('comparison'!C11="",NA(),'comparison'!C11)</f>
+        <f>IF('comparison'!C12="",NA(),'comparison'!C12)</f>
         <v/>
       </c>
       <c r="S38" s="10">
-        <f>IF('comparison'!D11="",NA(),'comparison'!D11)</f>
+        <f>IF('comparison'!D12="",NA(),'comparison'!D12)</f>
         <v/>
       </c>
     </row>
@@ -39641,15 +43780,15 @@
         </is>
       </c>
       <c r="Q39" s="10">
-        <f>IF('comparison'!E11="",NA(),'comparison'!E11)</f>
+        <f>IF('comparison'!E12="",NA(),'comparison'!E12)</f>
         <v/>
       </c>
       <c r="R39" s="10">
-        <f>IF('comparison'!F11="",NA(),'comparison'!F11)</f>
+        <f>IF('comparison'!F12="",NA(),'comparison'!F12)</f>
         <v/>
       </c>
       <c r="S39" s="10">
-        <f>IF('comparison'!G11="",NA(),'comparison'!G11)</f>
+        <f>IF('comparison'!G12="",NA(),'comparison'!G12)</f>
         <v/>
       </c>
     </row>
@@ -39660,15 +43799,15 @@
         </is>
       </c>
       <c r="Q40" s="10">
-        <f>IF('comparison'!H11="",NA(),'comparison'!H11)</f>
+        <f>IF('comparison'!H12="",NA(),'comparison'!H12)</f>
         <v/>
       </c>
       <c r="R40" s="10">
-        <f>IF('comparison'!I11="",NA(),'comparison'!I11)</f>
+        <f>IF('comparison'!I12="",NA(),'comparison'!I12)</f>
         <v/>
       </c>
       <c r="S40" s="10">
-        <f>IF('comparison'!J11="",NA(),'comparison'!J11)</f>
+        <f>IF('comparison'!J12="",NA(),'comparison'!J12)</f>
         <v/>
       </c>
     </row>
@@ -39679,15 +43818,15 @@
         </is>
       </c>
       <c r="Q41" s="10">
-        <f>IF('comparison'!K11="",NA(),'comparison'!K11)</f>
+        <f>IF('comparison'!K12="",NA(),'comparison'!K12)</f>
         <v/>
       </c>
       <c r="R41" s="10">
-        <f>IF('comparison'!L11="",NA(),'comparison'!L11)</f>
+        <f>IF('comparison'!L12="",NA(),'comparison'!L12)</f>
         <v/>
       </c>
       <c r="S41" s="10">
-        <f>IF('comparison'!M11="",NA(),'comparison'!M11)</f>
+        <f>IF('comparison'!M12="",NA(),'comparison'!M12)</f>
         <v/>
       </c>
     </row>
@@ -39704,7 +43843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -40115,14 +44254,14 @@
         <v>5</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>84.98999999999999</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Música (61GB)</t>
+          <t>Vivo Controle Segurança (61GB)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -40142,7 +44281,7 @@
       <c r="D20" s="15" t="n"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Netflix (61GB)</t>
+          <t>Vivo Controle Música (61GB)</t>
         </is>
       </c>
       <c r="F20" s="15" t="n"/>
@@ -40153,350 +44292,367 @@
         <v>7</v>
       </c>
       <c r="B21" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix (61GB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" s="6" t="n">
         <v>110</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle Entretenimento (61GB)</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Note: prepaid is not a clean unit — Claro Prezão is a daily fee (R$1/dia) vs Vivo/TIM recharge amounts.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>Vivo R$</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>Claro R$</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D26" s="1" t="inlineStr">
         <is>
           <t>TIM R$</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
+      <c r="E26" s="1" t="inlineStr">
         <is>
           <t>Vivo plan</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F26" s="1" t="inlineStr">
         <is>
           <t>Claro plan</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>TIM plan</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+    <row r="27">
+      <c r="A27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B27" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C27" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Vivo Pré (4GB)</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Prezão 4GB (12 dias) (4GB)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 6GB (6GB)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="n">
+    <row r="28">
+      <c r="A28" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B28" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C28" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D28" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré (5GB)</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Prezão 5GB (15 dias) (5GB)</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 8GB (8GB)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+    <row r="29">
+      <c r="A29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B29" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C29" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Vivo Pré (9GB)</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Prezão 6GB (20 dias) (6GB)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 16GB (16GB)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
+    <row r="30">
+      <c r="A30" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B30" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C30" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré (25GB)</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Prezão 8GB (20 dias) (8GB)</t>
         </is>
       </c>
-      <c r="G29" s="15" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="G30" s="15" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C31" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Prezão 10GB (25 dias) (10GB)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="n">
+    <row r="32">
+      <c r="A32" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="6" t="n">
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="15" t="n"/>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Prezão 9GB (25 dias) (9GB)</t>
         </is>
       </c>
-      <c r="G31" s="15" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="G32" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C33" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Prezão 12GB (30 dias) (12GB)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Digital</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Digital = Vivo Lite + Claro Flex (TIM has no digital line).</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
+      <c r="B37" s="1" t="inlineStr">
         <is>
           <t>Vivo R$</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>Claro R$</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr">
+      <c r="D37" s="1" t="inlineStr">
         <is>
           <t>TIM R$</t>
         </is>
       </c>
-      <c r="E36" s="1" t="inlineStr">
+      <c r="E37" s="1" t="inlineStr">
         <is>
           <t>Vivo plan</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="F37" s="1" t="inlineStr">
         <is>
           <t>Claro plan</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>TIM plan</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
+    <row r="38">
+      <c r="A38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B37" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="C37" s="3" t="n">
+      <c r="B38" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>44.9</v>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Easy Lite (30GB)</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite (20GB)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Flex 15GB (15GB)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="n">
+    <row r="39">
+      <c r="A39" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B38" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="C38" s="6" t="n">
+      <c r="B39" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="C39" s="6" t="n">
         <v>59.9</v>
       </c>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Easy Lite (20GB)</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite (30GB) · promo R$30</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Flex 20GB (20GB)</t>
         </is>
       </c>
-      <c r="G38" s="15" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="G39" s="15" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B39" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C39" s="3" t="n">
+      <c r="B40" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Easy Lite (40GB)</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite (40GB) · promo R$40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Flex 30GB (30GB)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="n">
+    <row r="41">
+      <c r="A41" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B40" s="15" t="n"/>
-      <c r="C40" s="6" t="n">
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="6" t="n">
         <v>119.9</v>
       </c>
-      <c r="D40" s="15" t="n"/>
-      <c r="E40" s="15" t="n"/>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Flex 40GB (40GB)</t>
         </is>
       </c>
-      <c r="G40" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:D11">
@@ -40514,7 +44670,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B15:D21">
+  <conditionalFormatting sqref="B15:D22">
     <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
       <formula>AND(B15&lt;&gt;"",B15=MIN($B15:$D15))</formula>
     </cfRule>
@@ -40529,9 +44685,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26:D32">
+  <conditionalFormatting sqref="B27:D33">
     <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
-      <formula>AND(B26&lt;&gt;"",B26=MIN($B26:$D26))</formula>
+      <formula>AND(B27&lt;&gt;"",B27=MIN($B27:$D27))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -40544,9 +44700,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B37:D40">
+  <conditionalFormatting sqref="B38:D41">
     <cfRule type="expression" priority="7" dxfId="1" stopIfTrue="1">
-      <formula>AND(B37&lt;&gt;"",B37=MIN($B37:$D37))</formula>
+      <formula>AND(B38&lt;&gt;"",B38=MIN($B38:$D38))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
       <colorScale>
@@ -40570,7 +44726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -40823,7 +44979,7 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6 meses grátis de Gemini com AI Plus</t>
+          <t>2 meses de YouTube sem consumo no plano</t>
         </is>
       </c>
     </row>
@@ -40861,7 +45017,7 @@
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6 meses grátis de Gemini com AI Plus</t>
+          <t>2 meses de YouTube sem consumo no plano</t>
         </is>
       </c>
     </row>
@@ -40885,7 +45041,7 @@
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>6 meses grátis de Gemini com AI Plus</t>
+          <t>2 meses de YouTube sem consumo no plano</t>
         </is>
       </c>
     </row>
@@ -40940,11 +45096,11 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Música</t>
+          <t>Vivo Controle Segurança</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="2" t="inlineStr">
@@ -40957,14 +45113,14 @@
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Apple Music Individual</t>
+          <t>Incluso Proteção Rua e Seguro de Bens</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Netflix</t>
+          <t>Vivo Controle Música</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
@@ -40981,18 +45137,18 @@
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Assinatura Netflix Padrão com anúncios</t>
+          <t>Apple Music Individual</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Entretenimento</t>
+          <t>Vivo Controle Netflix</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="2" t="inlineStr">
@@ -41005,189 +45161,217 @@
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>Assinatura Netflix Padrão com anúncios</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Entretenimento</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
           <t>Assinatura Vivo TV Inicial inclusa</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Digital</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
-      <c r="F18" s="17" t="n"/>
-      <c r="G18" s="17" t="n"/>
-      <c r="H18" s="17" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="17" t="n"/>
+      <c r="H19" s="17" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B20" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>20 GB (20 GB de franquia)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="C21" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>30 GB (30 GB de franquia)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2 meses de YouTube sem consumo no plano</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano · preço sem fidelidade; fidelidade 12m no promo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>20 GB (20 GB de franquia)</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>2 meses de YouTube sem consumo no plano</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Easy Lite</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
+      <c r="B22" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C22" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>40 GB (40 GB de franquia)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2 meses de YouTube sem consumo no plano</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano · preço sem fidelidade; fidelidade 12m no promo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="17" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="17" t="n"/>
+      <c r="H23" s="17" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B24" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>4 GB (4 GB para navegar como quiser) · 15d</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B25" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>5 GB (5 GB para navegar como quiser) · 17d</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>9 GB (6 GB para navegar como quiser 3 GB para navegar no YouTube) · 22d</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B27" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>25 GB (15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube) · 30d</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3:B9">
@@ -41202,7 +45386,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B17">
+  <conditionalFormatting sqref="B11:B18">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -41214,7 +45398,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B21">
+  <conditionalFormatting sqref="B20:B22">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -41226,7 +45410,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23:B26">
+  <conditionalFormatting sqref="B24:B27">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -34753,7 +34753,7 @@
       </c>
       <c r="B475" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C475" s="5" t="inlineStr">
@@ -34831,7 +34831,7 @@
       </c>
       <c r="B476" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C476" s="2" t="inlineStr">
@@ -34903,7 +34903,7 @@
       </c>
       <c r="B477" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C477" s="5" t="inlineStr">
@@ -34975,7 +34975,7 @@
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
@@ -35047,7 +35047,7 @@
       </c>
       <c r="B479" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C479" s="5" t="inlineStr">
@@ -35119,7 +35119,7 @@
       </c>
       <c r="B480" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C480" s="2" t="inlineStr">
@@ -35191,7 +35191,7 @@
       </c>
       <c r="B481" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C481" s="5" t="inlineStr">
@@ -35263,7 +35263,7 @@
       </c>
       <c r="B482" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C482" s="2" t="inlineStr">
@@ -35335,7 +35335,7 @@
       </c>
       <c r="B483" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C483" s="5" t="inlineStr">
@@ -35407,7 +35407,7 @@
       </c>
       <c r="B484" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C484" s="2" t="inlineStr">
@@ -35479,7 +35479,7 @@
       </c>
       <c r="B485" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C485" s="5" t="inlineStr">
@@ -35551,7 +35551,7 @@
       </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C486" s="2" t="inlineStr">
@@ -35623,7 +35623,7 @@
       </c>
       <c r="B487" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C487" s="5" t="inlineStr">
@@ -35693,7 +35693,7 @@
       </c>
       <c r="B488" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C488" s="2" t="inlineStr">
@@ -35763,7 +35763,7 @@
       </c>
       <c r="B489" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C489" s="5" t="inlineStr">
@@ -35833,7 +35833,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -35903,7 +35903,7 @@
       </c>
       <c r="B491" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C491" s="5" t="inlineStr">
@@ -35973,7 +35973,7 @@
       </c>
       <c r="B492" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C492" s="2" t="inlineStr">
@@ -36043,7 +36043,7 @@
       </c>
       <c r="B493" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C493" s="5" t="inlineStr">
@@ -36113,7 +36113,7 @@
       </c>
       <c r="B494" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C494" s="2" t="inlineStr">
@@ -36177,7 +36177,7 @@
       </c>
       <c r="B495" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C495" s="5" t="inlineStr">
@@ -36241,7 +36241,7 @@
       </c>
       <c r="B496" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C496" s="2" t="inlineStr">
@@ -36305,7 +36305,7 @@
       </c>
       <c r="B497" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C497" s="5" t="inlineStr">
@@ -36369,7 +36369,7 @@
       </c>
       <c r="B498" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C498" s="2" t="inlineStr">
@@ -36431,7 +36431,7 @@
       </c>
       <c r="B499" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C499" s="5" t="inlineStr">
@@ -36499,7 +36499,7 @@
       </c>
       <c r="B500" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C500" s="2" t="inlineStr">
@@ -36567,7 +36567,7 @@
       </c>
       <c r="B501" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C501" s="5" t="inlineStr">
@@ -36635,7 +36635,7 @@
       </c>
       <c r="B502" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C502" s="2" t="inlineStr">
@@ -36703,7 +36703,7 @@
       </c>
       <c r="B503" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C503" s="5" t="inlineStr">
@@ -36771,7 +36771,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -36839,7 +36839,7 @@
       </c>
       <c r="B505" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C505" s="5" t="inlineStr">
@@ -36907,7 +36907,7 @@
       </c>
       <c r="B506" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C506" s="2" t="inlineStr">
@@ -36973,7 +36973,7 @@
       </c>
       <c r="B507" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C507" s="5" t="inlineStr">
@@ -37039,7 +37039,7 @@
       </c>
       <c r="B508" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C508" s="2" t="inlineStr">
@@ -37105,7 +37105,7 @@
       </c>
       <c r="B509" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C509" s="5" t="inlineStr">
@@ -37177,7 +37177,7 @@
       </c>
       <c r="B510" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C510" s="2" t="inlineStr">
@@ -37202,17 +37202,17 @@
       </c>
       <c r="G510" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029300-51gb</t>
+          <t>vivo:VIV202600029300-61gb</t>
         </is>
       </c>
       <c r="H510" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I510" s="3" t="inlineStr"/>
       <c r="J510" s="2" t="inlineStr"/>
       <c r="K510" s="2" t="inlineStr"/>
       <c r="L510" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M510" s="2" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
       </c>
       <c r="B511" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C511" s="5" t="inlineStr">
@@ -37274,17 +37274,17 @@
       </c>
       <c r="G511" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029273-51gb</t>
+          <t>vivo:VIV202600029273-61gb</t>
         </is>
       </c>
       <c r="H511" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I511" s="6" t="inlineStr"/>
       <c r="J511" s="5" t="inlineStr"/>
       <c r="K511" s="5" t="inlineStr"/>
       <c r="L511" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M511" s="5" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
       </c>
       <c r="B512" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C512" s="2" t="inlineStr">
@@ -37346,17 +37346,17 @@
       </c>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029307-51gb</t>
+          <t>vivo:VIV202600029307-61gb</t>
         </is>
       </c>
       <c r="H512" s="3" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I512" s="3" t="inlineStr"/>
       <c r="J512" s="2" t="inlineStr"/>
       <c r="K512" s="2" t="inlineStr"/>
       <c r="L512" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M512" s="2" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
       </c>
       <c r="B513" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C513" s="5" t="inlineStr">
@@ -37418,17 +37418,17 @@
       </c>
       <c r="G513" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029313-51gb</t>
+          <t>vivo:VIV202600029313-61gb</t>
         </is>
       </c>
       <c r="H513" s="6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I513" s="6" t="inlineStr"/>
       <c r="J513" s="5" t="inlineStr"/>
       <c r="K513" s="5" t="inlineStr"/>
       <c r="L513" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M513" s="5" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
       </c>
       <c r="B514" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C514" s="2" t="inlineStr">
@@ -37490,17 +37490,17 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029308-51gb</t>
+          <t>vivo:VIV202600029308-61gb</t>
         </is>
       </c>
       <c r="H514" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I514" s="3" t="inlineStr"/>
       <c r="J514" s="2" t="inlineStr"/>
       <c r="K514" s="2" t="inlineStr"/>
       <c r="L514" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M514" s="2" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
       </c>
       <c r="B515" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C515" s="5" t="inlineStr">
@@ -37562,17 +37562,17 @@
       </c>
       <c r="G515" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029301-51gb</t>
+          <t>vivo:VIV202600029301-61gb</t>
         </is>
       </c>
       <c r="H515" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I515" s="6" t="inlineStr"/>
       <c r="J515" s="5" t="inlineStr"/>
       <c r="K515" s="5" t="inlineStr"/>
       <c r="L515" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M515" s="5" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
       </c>
       <c r="B516" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C516" s="2" t="inlineStr">
@@ -37634,17 +37634,17 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029274-51gb</t>
+          <t>vivo:VIV202600029274-61gb</t>
         </is>
       </c>
       <c r="H516" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I516" s="3" t="inlineStr"/>
       <c r="J516" s="2" t="inlineStr"/>
       <c r="K516" s="2" t="inlineStr"/>
       <c r="L516" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M516" s="2" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
       </c>
       <c r="B517" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C517" s="5" t="inlineStr">
@@ -37706,7 +37706,7 @@
       </c>
       <c r="G517" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600025883-30gb</t>
+          <t>vivo:VIV202600032594-30gb</t>
         </is>
       </c>
       <c r="H517" s="6" t="n">
@@ -37761,7 +37761,7 @@
       </c>
       <c r="B518" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C518" s="2" t="inlineStr">
@@ -37786,7 +37786,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600025885-40gb</t>
+          <t>vivo:VIV202600032596-40gb</t>
         </is>
       </c>
       <c r="H518" s="3" t="n">
@@ -37841,7 +37841,7 @@
       </c>
       <c r="B519" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C519" s="5" t="inlineStr">
@@ -37866,7 +37866,7 @@
       </c>
       <c r="G519" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600025888-20gb</t>
+          <t>vivo:VIV202600032599-20gb</t>
         </is>
       </c>
       <c r="H519" s="6" t="n">
@@ -37913,7 +37913,7 @@
       </c>
       <c r="B520" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C520" s="2" t="inlineStr">
@@ -37985,7 +37985,7 @@
       </c>
       <c r="B521" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C521" s="5" t="inlineStr">
@@ -38061,7 +38061,7 @@
       </c>
       <c r="B522" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C522" s="2" t="inlineStr">
@@ -38137,7 +38137,7 @@
       </c>
       <c r="B523" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C523" s="5" t="inlineStr">
@@ -38213,7 +38213,7 @@
       </c>
       <c r="B524" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C524" s="2" t="inlineStr">
@@ -38289,7 +38289,7 @@
       </c>
       <c r="B525" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C525" s="5" t="inlineStr">
@@ -38365,7 +38365,7 @@
       </c>
       <c r="B526" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C526" s="2" t="inlineStr">
@@ -38437,7 +38437,7 @@
       </c>
       <c r="B527" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C527" s="5" t="inlineStr">
@@ -38507,7 +38507,7 @@
       </c>
       <c r="B528" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C528" s="2" t="inlineStr">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="B529" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C529" s="5" t="inlineStr">
@@ -38647,7 +38647,7 @@
       </c>
       <c r="B530" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C530" s="2" t="inlineStr">
@@ -39310,7 +39310,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -39388,7 +39388,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -39460,7 +39460,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -39532,7 +39532,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -39604,7 +39604,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -39676,7 +39676,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -39748,7 +39748,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -39820,7 +39820,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -39892,7 +39892,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -39964,7 +39964,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -40036,7 +40036,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -40108,7 +40108,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -40180,7 +40180,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -40250,7 +40250,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -40320,7 +40320,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -40390,7 +40390,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -40460,7 +40460,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -40530,7 +40530,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -40600,7 +40600,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -40670,7 +40670,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -40734,7 +40734,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -40798,7 +40798,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -40862,7 +40862,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -40926,7 +40926,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -40988,7 +40988,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -41056,7 +41056,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -41124,7 +41124,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -41192,7 +41192,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -41260,7 +41260,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -41328,7 +41328,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -41396,7 +41396,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -41464,7 +41464,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -41530,7 +41530,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -41596,7 +41596,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -41662,7 +41662,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -41734,7 +41734,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -41759,17 +41759,17 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029300-51gb</t>
+          <t>vivo:VIV202600029300-61gb</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I37" s="6" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr"/>
       <c r="K37" s="5" t="inlineStr"/>
       <c r="L37" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -41831,17 +41831,17 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029273-51gb</t>
+          <t>vivo:VIV202600029273-61gb</t>
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -41878,7 +41878,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -41903,17 +41903,17 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029307-51gb</t>
+          <t>vivo:VIV202600029307-61gb</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I39" s="6" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
       <c r="K39" s="5" t="inlineStr"/>
       <c r="L39" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -41975,17 +41975,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029313-51gb</t>
+          <t>vivo:VIV202600029313-61gb</t>
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I40" s="3" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -42047,17 +42047,17 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029308-51gb</t>
+          <t>vivo:VIV202600029308-61gb</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I41" s="6" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
       <c r="K41" s="5" t="inlineStr"/>
       <c r="L41" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -42119,17 +42119,17 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029301-51gb</t>
+          <t>vivo:VIV202600029301-61gb</t>
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -42191,17 +42191,17 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029274-51gb</t>
+          <t>vivo:VIV202600029274-61gb</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I43" s="6" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="5" t="inlineStr"/>
       <c r="L43" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -42263,7 +42263,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600025883-30gb</t>
+          <t>vivo:VIV202600032594-30gb</t>
         </is>
       </c>
       <c r="H44" s="3" t="n">
@@ -42318,7 +42318,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -42343,7 +42343,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600025885-40gb</t>
+          <t>vivo:VIV202600032596-40gb</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
@@ -42398,7 +42398,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -42423,7 +42423,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600025888-20gb</t>
+          <t>vivo:VIV202600032599-20gb</t>
         </is>
       </c>
       <c r="H46" s="3" t="n">
@@ -42470,7 +42470,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -42542,7 +42542,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -42618,7 +42618,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -42694,7 +42694,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -42770,7 +42770,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -42846,7 +42846,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -42922,7 +42922,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -42994,7 +42994,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -43064,7 +43064,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -43134,7 +43134,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -43204,7 +43204,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -43296,7 +43296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -43380,17 +43380,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029273-51gb</t>
+          <t>vivo:VIV202600029274-61gb</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Educação</t>
+          <t>Vivo Controle Segurança</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I2" s="3" t="inlineStr"/>
     </row>
@@ -43407,7 +43407,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>lite</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -43417,17 +43417,17 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029274-51gb</t>
+          <t>vivo:VIV202600032594-30gb</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Segurança</t>
+          <t>Easy Lite</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr"/>
       <c r="H3" s="6" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="I3" s="6" t="inlineStr"/>
     </row>
@@ -43444,7 +43444,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>lite</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -43454,17 +43454,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029300-51gb</t>
+          <t>vivo:VIV202600032596-40gb</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle</t>
+          <t>Easy Lite</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
@@ -43481,7 +43481,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>lite</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -43491,24 +43491,24 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029301-51gb</t>
+          <t>vivo:VIV202600032599-20gb</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Saúde</t>
+          <t>Easy Lite</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr"/>
       <c r="H5" s="6" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -43518,7 +43518,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>lite</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -43528,24 +43528,24 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029307-51gb</t>
+          <t>vivo:VIV202600025883-30gb</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Entretenimento</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="n">
-        <v>105</v>
-      </c>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -43555,7 +43555,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>lite</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -43565,24 +43565,24 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029308-51gb</t>
+          <t>vivo:VIV202600025885-40gb</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Netflix</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="n">
-        <v>90</v>
-      </c>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -43592,7 +43592,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>lite</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -43602,323 +43602,19 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029313-51gb</t>
+          <t>vivo:VIV202600025888-20gb</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Música</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="n">
-        <v>90</v>
-      </c>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029273-61gb</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Vivo Controle Educação</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029300-61gb</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029301-61gb</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Vivo Controle Saúde</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029307-61gb</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Entretenimento</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029308-61gb</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Vivo Controle Netflix</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029313-61gb</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Música</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>price_change</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>lite</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600025883-30gb</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Easy Lite</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>price_change</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>lite</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600025885-40gb</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Easy Lite</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>15</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -43957,7 +43653,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T20:29:30</t>
+          <t>2026-07-01T22:16:09</t>
         </is>
       </c>
     </row>
@@ -44036,7 +43732,7 @@
       </c>
       <c r="D9" s="10">
         <f>IFERROR(AVERAGEIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
-        <v>97.09</v>
+        <v>98.68</v>
       </c>
       <c r="E9" s="10">
         <f>IFERROR(_xlfn.MAXIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
@@ -45270,7 +44966,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>69.90000000000001</v>
@@ -45280,7 +44976,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle (51GB)</t>
+          <t>Vivo Controle (61GB)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -45299,7 +44995,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>99.90000000000001</v>
@@ -45309,7 +45005,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Educação (51GB)</t>
+          <t>Vivo Controle Educação (61GB)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -45328,7 +45024,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C18" s="15" t="n"/>
       <c r="D18" s="6" t="n">
@@ -45336,7 +45032,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Saúde (51GB)</t>
+          <t>Vivo Controle Saúde (61GB)</t>
         </is>
       </c>
       <c r="F18" s="15" t="n"/>
@@ -45351,14 +45047,14 @@
         <v>5</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>84.98999999999999</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Segurança (51GB)</t>
+          <t>Vivo Controle Segurança (61GB)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -45372,13 +45068,13 @@
         <v>6</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C20" s="15" t="n"/>
       <c r="D20" s="15" t="n"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Música (51GB)</t>
+          <t>Vivo Controle Música (61GB)</t>
         </is>
       </c>
       <c r="F20" s="15" t="n"/>
@@ -45389,11 +45085,11 @@
         <v>7</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Netflix (51GB)</t>
+          <t>Vivo Controle Netflix (61GB)</t>
         </is>
       </c>
     </row>
@@ -45402,13 +45098,13 @@
         <v>8</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C22" s="15" t="n"/>
       <c r="D22" s="15" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Entretenimento (51GB)</t>
+          <t>Vivo Controle Entretenimento (61GB)</t>
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
@@ -46125,12 +45821,12 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E12" s="5" t="n"/>
@@ -46149,12 +45845,12 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -46173,12 +45869,12 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E14" s="5" t="n"/>
@@ -46197,12 +45893,12 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -46221,12 +45917,12 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E16" s="5" t="n"/>
@@ -46245,12 +45941,12 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
@@ -46269,12 +45965,12 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E18" s="5" t="n"/>

--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -19,7 +19,7 @@
     <sheet name="TIM" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$V$530</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$V$586</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$V$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -264,7 +264,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Control — cheapest R$ over time</a:t>
+              <a:t>Control – Monthly Prices</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -300,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$12</f>
+              <f>'comparison'!$A$3:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$B$3:$B$12</f>
+              <f>'comparison'!$B$3:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -337,12 +337,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$12</f>
+              <f>'comparison'!$A$3:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$C$3:$C$12</f>
+              <f>'comparison'!$C$3:$C$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -374,12 +374,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$12</f>
+              <f>'comparison'!$A$3:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$D$3:$D$12</f>
+              <f>'comparison'!$D$3:$D$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -417,9 +417,20 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="70"/>
+          <min val="40"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="ECECEC"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -461,7 +472,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Post — cheapest R$ over time</a:t>
+              <a:t>Post – Monthly Prices</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -497,12 +508,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$12</f>
+              <f>'comparison'!$A$3:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$E$3:$E$12</f>
+              <f>'comparison'!$E$3:$E$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -534,12 +545,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$12</f>
+              <f>'comparison'!$A$3:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$F$3:$F$12</f>
+              <f>'comparison'!$F$3:$F$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -571,12 +582,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$12</f>
+              <f>'comparison'!$A$3:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$G$3:$G$12</f>
+              <f>'comparison'!$G$3:$G$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -614,9 +625,20 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="170"/>
+          <min val="90"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="ECECEC"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -658,7 +680,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Pre — cheapest R$ over time</a:t>
+              <a:t>Pre – Monthly Prices</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -694,12 +716,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$12</f>
+              <f>'comparison'!$A$3:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$H$3:$H$12</f>
+              <f>'comparison'!$H$3:$H$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -731,12 +753,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$12</f>
+              <f>'comparison'!$A$3:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$I$3:$I$12</f>
+              <f>'comparison'!$I$3:$I$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -768,12 +790,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$12</f>
+              <f>'comparison'!$A$3:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$J$3:$J$12</f>
+              <f>'comparison'!$J$3:$J$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -811,9 +833,20 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="40"/>
+          <min val="20"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="ECECEC"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -855,7 +888,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Digital — cheapest R$ over time</a:t>
+              <a:t>Digital – Monthly Prices</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -891,12 +924,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$12</f>
+              <f>'comparison'!$A$3:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$K$3:$K$12</f>
+              <f>'comparison'!$K$3:$K$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -928,12 +961,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$12</f>
+              <f>'comparison'!$A$3:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$L$3:$L$12</f>
+              <f>'comparison'!$L$3:$L$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -965,12 +998,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$12</f>
+              <f>'comparison'!$A$3:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$M$3:$M$12</f>
+              <f>'comparison'!$M$3:$M$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1008,9 +1041,20 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="65"/>
+          <min val="25"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="ECECEC"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -1167,7 +1211,16 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="ECECEC"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -1602,7 +1655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V530"/>
+  <dimension ref="A1:V586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -38709,8 +38762,3972 @@
         </is>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B531" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C531" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D531" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E531" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F531" s="5" t="inlineStr">
+        <is>
+          <t>Controle 25GB</t>
+        </is>
+      </c>
+      <c r="G531" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-25gb</t>
+        </is>
+      </c>
+      <c r="H531" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I531" s="6" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="J531" s="5" t="inlineStr">
+        <is>
+          <t>De R$ 59,90 Por:</t>
+        </is>
+      </c>
+      <c r="K531" s="5" t="inlineStr"/>
+      <c r="L531" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="M531" s="5" t="inlineStr"/>
+      <c r="N531" s="5" t="inlineStr"/>
+      <c r="O531" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P531" s="5" t="inlineStr"/>
+      <c r="Q531" s="5" t="inlineStr"/>
+      <c r="R531" s="5" t="inlineStr"/>
+      <c r="S531" s="5" t="inlineStr"/>
+      <c r="T531" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e vídeos; Bônus exclusivo; Aproveite na sua franquia; WhatsApp e ligações ilimitadas</t>
+        </is>
+      </c>
+      <c r="U531" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="V531" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D532" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F532" s="2" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G532" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb</t>
+        </is>
+      </c>
+      <c r="H532" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I532" s="3" t="inlineStr"/>
+      <c r="J532" s="2" t="inlineStr"/>
+      <c r="K532" s="2" t="inlineStr"/>
+      <c r="L532" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="M532" s="2" t="inlineStr"/>
+      <c r="N532" s="2" t="inlineStr"/>
+      <c r="O532" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P532" s="2" t="inlineStr"/>
+      <c r="Q532" s="2" t="inlineStr"/>
+      <c r="R532" s="2" t="inlineStr"/>
+      <c r="S532" s="2" t="inlineStr"/>
+      <c r="T532" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="U532" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="V532" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B533" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C533" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D533" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E533" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F533" s="5" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G533" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb-gaming</t>
+        </is>
+      </c>
+      <c r="H533" s="6" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I533" s="6" t="inlineStr"/>
+      <c r="J533" s="5" t="inlineStr"/>
+      <c r="K533" s="5" t="inlineStr"/>
+      <c r="L533" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="M533" s="5" t="inlineStr"/>
+      <c r="N533" s="5" t="inlineStr"/>
+      <c r="O533" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P533" s="5" t="inlineStr"/>
+      <c r="Q533" s="5" t="inlineStr"/>
+      <c r="R533" s="5" t="inlineStr"/>
+      <c r="S533" s="5" t="inlineStr"/>
+      <c r="T533" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus para redes sociais e apps; Bônus uso livre; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="U533" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="V533" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F534" s="2" t="inlineStr">
+        <is>
+          <t>Flex 15GB</t>
+        </is>
+      </c>
+      <c r="G534" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-15gb</t>
+        </is>
+      </c>
+      <c r="H534" s="3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I534" s="3" t="inlineStr"/>
+      <c r="J534" s="2" t="inlineStr"/>
+      <c r="K534" s="2" t="inlineStr"/>
+      <c r="L534" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M534" s="2" t="inlineStr"/>
+      <c r="N534" s="2" t="inlineStr"/>
+      <c r="O534" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P534" s="2" t="inlineStr"/>
+      <c r="Q534" s="2" t="inlineStr"/>
+      <c r="R534" s="2" t="inlineStr"/>
+      <c r="S534" s="2" t="inlineStr"/>
+      <c r="T534" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="U534" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="V534" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B535" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C535" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D535" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E535" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F535" s="5" t="inlineStr">
+        <is>
+          <t>Flex 20GB</t>
+        </is>
+      </c>
+      <c r="G535" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-20gb</t>
+        </is>
+      </c>
+      <c r="H535" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I535" s="6" t="inlineStr"/>
+      <c r="J535" s="5" t="inlineStr"/>
+      <c r="K535" s="5" t="inlineStr"/>
+      <c r="L535" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="M535" s="5" t="inlineStr"/>
+      <c r="N535" s="5" t="inlineStr"/>
+      <c r="O535" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P535" s="5" t="inlineStr"/>
+      <c r="Q535" s="5" t="inlineStr"/>
+      <c r="R535" s="5" t="inlineStr"/>
+      <c r="S535" s="5" t="inlineStr"/>
+      <c r="T535" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="U535" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="V535" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F536" s="2" t="inlineStr">
+        <is>
+          <t>Flex 30GB</t>
+        </is>
+      </c>
+      <c r="G536" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-30gb</t>
+        </is>
+      </c>
+      <c r="H536" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I536" s="3" t="inlineStr"/>
+      <c r="J536" s="2" t="inlineStr"/>
+      <c r="K536" s="2" t="inlineStr"/>
+      <c r="L536" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="M536" s="2" t="inlineStr"/>
+      <c r="N536" s="2" t="inlineStr"/>
+      <c r="O536" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P536" s="2" t="inlineStr"/>
+      <c r="Q536" s="2" t="inlineStr"/>
+      <c r="R536" s="2" t="inlineStr"/>
+      <c r="S536" s="2" t="inlineStr"/>
+      <c r="T536" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="U536" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="V536" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B537" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C537" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D537" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E537" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F537" s="5" t="inlineStr">
+        <is>
+          <t>Flex 40GB</t>
+        </is>
+      </c>
+      <c r="G537" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-40gb</t>
+        </is>
+      </c>
+      <c r="H537" s="6" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I537" s="6" t="inlineStr"/>
+      <c r="J537" s="5" t="inlineStr"/>
+      <c r="K537" s="5" t="inlineStr"/>
+      <c r="L537" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="M537" s="5" t="inlineStr"/>
+      <c r="N537" s="5" t="inlineStr"/>
+      <c r="O537" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P537" s="5" t="inlineStr"/>
+      <c r="Q537" s="5" t="inlineStr"/>
+      <c r="R537" s="5" t="inlineStr"/>
+      <c r="S537" s="5" t="inlineStr"/>
+      <c r="T537" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e apps; Bônus uso livre; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="U537" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="V537" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>Pós 100GB</t>
+        </is>
+      </c>
+      <c r="G538" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-100gb</t>
+        </is>
+      </c>
+      <c r="H538" s="3" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="I538" s="3" t="inlineStr"/>
+      <c r="J538" s="2" t="inlineStr"/>
+      <c r="K538" s="2" t="inlineStr"/>
+      <c r="L538" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M538" s="2" t="inlineStr"/>
+      <c r="N538" s="2" t="inlineStr"/>
+      <c r="O538" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P538" s="2" t="inlineStr"/>
+      <c r="Q538" s="2" t="inlineStr"/>
+      <c r="R538" s="2" t="inlineStr"/>
+      <c r="S538" s="2" t="inlineStr"/>
+      <c r="T538" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="U538" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V538" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B539" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C539" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D539" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E539" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F539" s="5" t="inlineStr">
+        <is>
+          <t>Pós 150GB</t>
+        </is>
+      </c>
+      <c r="G539" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-150gb</t>
+        </is>
+      </c>
+      <c r="H539" s="6" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="I539" s="6" t="inlineStr"/>
+      <c r="J539" s="5" t="inlineStr"/>
+      <c r="K539" s="5" t="inlineStr"/>
+      <c r="L539" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="M539" s="5" t="inlineStr"/>
+      <c r="N539" s="5" t="inlineStr"/>
+      <c r="O539" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P539" s="5" t="inlineStr"/>
+      <c r="Q539" s="5" t="inlineStr"/>
+      <c r="R539" s="5" t="inlineStr"/>
+      <c r="S539" s="5" t="inlineStr"/>
+      <c r="T539" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas e Europa; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="U539" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V539" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>Pós 200GB</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-200gb</t>
+        </is>
+      </c>
+      <c r="H540" s="3" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="I540" s="3" t="inlineStr"/>
+      <c r="J540" s="2" t="inlineStr"/>
+      <c r="K540" s="2" t="inlineStr"/>
+      <c r="L540" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="M540" s="2" t="inlineStr"/>
+      <c r="N540" s="2" t="inlineStr"/>
+      <c r="O540" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P540" s="2" t="inlineStr"/>
+      <c r="Q540" s="2" t="inlineStr"/>
+      <c r="R540" s="2" t="inlineStr"/>
+      <c r="S540" s="2" t="inlineStr"/>
+      <c r="T540" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="U540" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V540" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B541" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C541" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D541" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E541" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F541" s="5" t="inlineStr">
+        <is>
+          <t>Pós 50GB com GeForce NOW</t>
+        </is>
+      </c>
+      <c r="G541" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb-geforce</t>
+        </is>
+      </c>
+      <c r="H541" s="6" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="I541" s="6" t="inlineStr"/>
+      <c r="J541" s="5" t="inlineStr"/>
+      <c r="K541" s="5" t="inlineStr"/>
+      <c r="L541" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="M541" s="5" t="inlineStr"/>
+      <c r="N541" s="5" t="inlineStr"/>
+      <c r="O541" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P541" s="5" t="inlineStr"/>
+      <c r="Q541" s="5" t="inlineStr"/>
+      <c r="R541" s="5" t="inlineStr"/>
+      <c r="S541" s="5" t="inlineStr"/>
+      <c r="T541" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado; Inclusa assinatura GeForce NOW</t>
+        </is>
+      </c>
+      <c r="U541" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V541" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>Pós 60GB</t>
+        </is>
+      </c>
+      <c r="G542" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb</t>
+        </is>
+      </c>
+      <c r="H542" s="3" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="I542" s="3" t="inlineStr"/>
+      <c r="J542" s="2" t="inlineStr"/>
+      <c r="K542" s="2" t="inlineStr"/>
+      <c r="L542" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M542" s="2" t="inlineStr"/>
+      <c r="N542" s="2" t="inlineStr"/>
+      <c r="O542" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P542" s="2" t="inlineStr"/>
+      <c r="Q542" s="2" t="inlineStr"/>
+      <c r="R542" s="2" t="inlineStr"/>
+      <c r="S542" s="2" t="inlineStr"/>
+      <c r="T542" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="U542" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V542" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B543" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C543" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D543" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E543" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F543" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 10GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G543" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-10gb</t>
+        </is>
+      </c>
+      <c r="H543" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I543" s="6" t="inlineStr"/>
+      <c r="J543" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K543" s="5" t="inlineStr"/>
+      <c r="L543" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M543" s="5" t="inlineStr"/>
+      <c r="N543" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="O543" s="5" t="inlineStr"/>
+      <c r="P543" s="5" t="inlineStr"/>
+      <c r="Q543" s="5" t="inlineStr"/>
+      <c r="R543" s="5" t="inlineStr"/>
+      <c r="S543" s="5" t="inlineStr"/>
+      <c r="T543" s="5" t="inlineStr"/>
+      <c r="U543" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V543" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 12GB (30 dias)</t>
+        </is>
+      </c>
+      <c r="G544" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-30d-12gb</t>
+        </is>
+      </c>
+      <c r="H544" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I544" s="3" t="inlineStr"/>
+      <c r="J544" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$30 — validade 30 dias</t>
+        </is>
+      </c>
+      <c r="K544" s="2" t="inlineStr"/>
+      <c r="L544" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M544" s="2" t="inlineStr"/>
+      <c r="N544" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O544" s="2" t="inlineStr"/>
+      <c r="P544" s="2" t="inlineStr"/>
+      <c r="Q544" s="2" t="inlineStr"/>
+      <c r="R544" s="2" t="inlineStr"/>
+      <c r="S544" s="2" t="inlineStr"/>
+      <c r="T544" s="2" t="inlineStr"/>
+      <c r="U544" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V544" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B545" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C545" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D545" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E545" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F545" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 4GB (12 dias)</t>
+        </is>
+      </c>
+      <c r="G545" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-12d-4gb</t>
+        </is>
+      </c>
+      <c r="H545" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I545" s="6" t="inlineStr"/>
+      <c r="J545" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$15 — validade 12 dias</t>
+        </is>
+      </c>
+      <c r="K545" s="5" t="inlineStr"/>
+      <c r="L545" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M545" s="5" t="inlineStr"/>
+      <c r="N545" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="O545" s="5" t="inlineStr"/>
+      <c r="P545" s="5" t="inlineStr"/>
+      <c r="Q545" s="5" t="inlineStr"/>
+      <c r="R545" s="5" t="inlineStr"/>
+      <c r="S545" s="5" t="inlineStr"/>
+      <c r="T545" s="5" t="inlineStr"/>
+      <c r="U545" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V545" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 5GB (15 dias)</t>
+        </is>
+      </c>
+      <c r="G546" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-15d-5gb</t>
+        </is>
+      </c>
+      <c r="H546" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I546" s="3" t="inlineStr"/>
+      <c r="J546" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$15 — validade 15 dias</t>
+        </is>
+      </c>
+      <c r="K546" s="2" t="inlineStr"/>
+      <c r="L546" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M546" s="2" t="inlineStr"/>
+      <c r="N546" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O546" s="2" t="inlineStr"/>
+      <c r="P546" s="2" t="inlineStr"/>
+      <c r="Q546" s="2" t="inlineStr"/>
+      <c r="R546" s="2" t="inlineStr"/>
+      <c r="S546" s="2" t="inlineStr"/>
+      <c r="T546" s="2" t="inlineStr"/>
+      <c r="U546" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V546" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B547" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C547" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D547" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E547" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F547" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 6GB (20 dias)</t>
+        </is>
+      </c>
+      <c r="G547" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-20d-6gb</t>
+        </is>
+      </c>
+      <c r="H547" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I547" s="6" t="inlineStr"/>
+      <c r="J547" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$20 — validade 20 dias</t>
+        </is>
+      </c>
+      <c r="K547" s="5" t="inlineStr"/>
+      <c r="L547" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M547" s="5" t="inlineStr"/>
+      <c r="N547" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O547" s="5" t="inlineStr"/>
+      <c r="P547" s="5" t="inlineStr"/>
+      <c r="Q547" s="5" t="inlineStr"/>
+      <c r="R547" s="5" t="inlineStr"/>
+      <c r="S547" s="5" t="inlineStr"/>
+      <c r="T547" s="5" t="inlineStr"/>
+      <c r="U547" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V547" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 8GB (20 dias)</t>
+        </is>
+      </c>
+      <c r="G548" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-20d-8gb</t>
+        </is>
+      </c>
+      <c r="H548" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I548" s="3" t="inlineStr"/>
+      <c r="J548" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$20 — validade 20 dias</t>
+        </is>
+      </c>
+      <c r="K548" s="2" t="inlineStr"/>
+      <c r="L548" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M548" s="2" t="inlineStr"/>
+      <c r="N548" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O548" s="2" t="inlineStr"/>
+      <c r="P548" s="2" t="inlineStr"/>
+      <c r="Q548" s="2" t="inlineStr"/>
+      <c r="R548" s="2" t="inlineStr"/>
+      <c r="S548" s="2" t="inlineStr"/>
+      <c r="T548" s="2" t="inlineStr"/>
+      <c r="U548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V548" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B549" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C549" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D549" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E549" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F549" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 9GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G549" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-9gb</t>
+        </is>
+      </c>
+      <c r="H549" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I549" s="6" t="inlineStr"/>
+      <c r="J549" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K549" s="5" t="inlineStr"/>
+      <c r="L549" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="M549" s="5" t="inlineStr"/>
+      <c r="N549" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="O549" s="5" t="inlineStr"/>
+      <c r="P549" s="5" t="inlineStr"/>
+      <c r="Q549" s="5" t="inlineStr"/>
+      <c r="R549" s="5" t="inlineStr"/>
+      <c r="S549" s="5" t="inlineStr"/>
+      <c r="T549" s="5" t="inlineStr"/>
+      <c r="U549" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V549" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle 41GB</t>
+        </is>
+      </c>
+      <c r="G550" s="2" t="inlineStr">
+        <is>
+          <t>tim:162901</t>
+        </is>
+      </c>
+      <c r="H550" s="3" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="I550" s="3" t="inlineStr"/>
+      <c r="J550" s="2" t="inlineStr"/>
+      <c r="K550" s="2" t="inlineStr"/>
+      <c r="L550" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="M550" s="2" t="inlineStr"/>
+      <c r="N550" s="2" t="inlineStr"/>
+      <c r="O550" s="2" t="inlineStr"/>
+      <c r="P550" s="2" t="inlineStr"/>
+      <c r="Q550" s="2" t="inlineStr"/>
+      <c r="R550" s="2" t="inlineStr"/>
+      <c r="S550" s="2" t="inlineStr"/>
+      <c r="T550" s="2" t="inlineStr"/>
+      <c r="U550" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="V550" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B551" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C551" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D551" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E551" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F551" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Light Express 31GB</t>
+        </is>
+      </c>
+      <c r="G551" s="5" t="inlineStr">
+        <is>
+          <t>tim:143536</t>
+        </is>
+      </c>
+      <c r="H551" s="6" t="n">
+        <v>60.99</v>
+      </c>
+      <c r="I551" s="6" t="inlineStr"/>
+      <c r="J551" s="5" t="inlineStr"/>
+      <c r="K551" s="5" t="inlineStr"/>
+      <c r="L551" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="M551" s="5" t="inlineStr"/>
+      <c r="N551" s="5" t="inlineStr"/>
+      <c r="O551" s="5" t="inlineStr"/>
+      <c r="P551" s="5" t="inlineStr"/>
+      <c r="Q551" s="5" t="inlineStr"/>
+      <c r="R551" s="5" t="inlineStr"/>
+      <c r="S551" s="5" t="inlineStr"/>
+      <c r="T551" s="5" t="inlineStr"/>
+      <c r="U551" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="V551" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Plus 45GB</t>
+        </is>
+      </c>
+      <c r="G552" s="2" t="inlineStr">
+        <is>
+          <t>tim:155891</t>
+        </is>
+      </c>
+      <c r="H552" s="3" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I552" s="3" t="inlineStr"/>
+      <c r="J552" s="2" t="inlineStr"/>
+      <c r="K552" s="2" t="inlineStr"/>
+      <c r="L552" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="M552" s="2" t="inlineStr"/>
+      <c r="N552" s="2" t="inlineStr"/>
+      <c r="O552" s="2" t="inlineStr"/>
+      <c r="P552" s="2" t="inlineStr"/>
+      <c r="Q552" s="2" t="inlineStr"/>
+      <c r="R552" s="2" t="inlineStr"/>
+      <c r="S552" s="2" t="inlineStr"/>
+      <c r="T552" s="2" t="inlineStr"/>
+      <c r="U552" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="V552" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B553" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C553" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D553" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E553" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F553" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Premium 53GB</t>
+        </is>
+      </c>
+      <c r="G553" s="5" t="inlineStr">
+        <is>
+          <t>tim:162896</t>
+        </is>
+      </c>
+      <c r="H553" s="6" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="I553" s="6" t="inlineStr"/>
+      <c r="J553" s="5" t="inlineStr"/>
+      <c r="K553" s="5" t="inlineStr"/>
+      <c r="L553" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="M553" s="5" t="inlineStr"/>
+      <c r="N553" s="5" t="inlineStr"/>
+      <c r="O553" s="5" t="inlineStr"/>
+      <c r="P553" s="5" t="inlineStr"/>
+      <c r="Q553" s="5" t="inlineStr"/>
+      <c r="R553" s="5" t="inlineStr"/>
+      <c r="S553" s="5" t="inlineStr"/>
+      <c r="T553" s="5" t="inlineStr"/>
+      <c r="U553" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="V553" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Pro Express</t>
+        </is>
+      </c>
+      <c r="G554" s="2" t="inlineStr">
+        <is>
+          <t>tim:143576</t>
+        </is>
+      </c>
+      <c r="H554" s="3" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I554" s="3" t="inlineStr"/>
+      <c r="J554" s="2" t="inlineStr"/>
+      <c r="K554" s="2" t="inlineStr"/>
+      <c r="L554" s="4" t="inlineStr"/>
+      <c r="M554" s="2" t="inlineStr"/>
+      <c r="N554" s="2" t="inlineStr"/>
+      <c r="O554" s="2" t="inlineStr"/>
+      <c r="P554" s="2" t="inlineStr"/>
+      <c r="Q554" s="2" t="inlineStr"/>
+      <c r="R554" s="2" t="inlineStr"/>
+      <c r="S554" s="2" t="inlineStr"/>
+      <c r="T554" s="2" t="inlineStr"/>
+      <c r="U554" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="V554" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B555" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C555" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D555" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E555" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F555" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black 70GB</t>
+        </is>
+      </c>
+      <c r="G555" s="5" t="inlineStr">
+        <is>
+          <t>tim:54206</t>
+        </is>
+      </c>
+      <c r="H555" s="6" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="I555" s="6" t="inlineStr"/>
+      <c r="J555" s="5" t="inlineStr"/>
+      <c r="K555" s="5" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="L555" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="M555" s="5" t="inlineStr"/>
+      <c r="N555" s="5" t="inlineStr"/>
+      <c r="O555" s="5" t="inlineStr"/>
+      <c r="P555" s="5" t="inlineStr"/>
+      <c r="Q555" s="5" t="inlineStr"/>
+      <c r="R555" s="5" t="inlineStr"/>
+      <c r="S555" s="5" t="inlineStr"/>
+      <c r="T555" s="5" t="inlineStr"/>
+      <c r="U555" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="V555" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black A Express 67GB</t>
+        </is>
+      </c>
+      <c r="G556" s="2" t="inlineStr">
+        <is>
+          <t>tim:55121</t>
+        </is>
+      </c>
+      <c r="H556" s="3" t="n">
+        <v>119.99</v>
+      </c>
+      <c r="I556" s="3" t="inlineStr"/>
+      <c r="J556" s="2" t="inlineStr"/>
+      <c r="K556" s="2" t="inlineStr">
+        <is>
+          <t>credit_card</t>
+        </is>
+      </c>
+      <c r="L556" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="M556" s="2" t="inlineStr"/>
+      <c r="N556" s="2" t="inlineStr"/>
+      <c r="O556" s="2" t="inlineStr"/>
+      <c r="P556" s="2" t="inlineStr"/>
+      <c r="Q556" s="2" t="inlineStr"/>
+      <c r="R556" s="2" t="inlineStr"/>
+      <c r="S556" s="2" t="inlineStr"/>
+      <c r="T556" s="2" t="inlineStr"/>
+      <c r="U556" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="V556" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B557" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C557" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D557" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E557" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F557" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black B Express 82GB</t>
+        </is>
+      </c>
+      <c r="G557" s="5" t="inlineStr">
+        <is>
+          <t>tim:52146</t>
+        </is>
+      </c>
+      <c r="H557" s="6" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="I557" s="6" t="inlineStr"/>
+      <c r="J557" s="5" t="inlineStr"/>
+      <c r="K557" s="5" t="inlineStr">
+        <is>
+          <t>credit_card</t>
+        </is>
+      </c>
+      <c r="L557" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="M557" s="5" t="inlineStr"/>
+      <c r="N557" s="5" t="inlineStr"/>
+      <c r="O557" s="5" t="inlineStr"/>
+      <c r="P557" s="5" t="inlineStr"/>
+      <c r="Q557" s="5" t="inlineStr"/>
+      <c r="R557" s="5" t="inlineStr"/>
+      <c r="S557" s="5" t="inlineStr"/>
+      <c r="T557" s="5" t="inlineStr"/>
+      <c r="U557" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="V557" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black C Express 107GB</t>
+        </is>
+      </c>
+      <c r="G558" s="2" t="inlineStr">
+        <is>
+          <t>tim:52151</t>
+        </is>
+      </c>
+      <c r="H558" s="3" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="I558" s="3" t="inlineStr"/>
+      <c r="J558" s="2" t="inlineStr"/>
+      <c r="K558" s="2" t="inlineStr">
+        <is>
+          <t>credit_card</t>
+        </is>
+      </c>
+      <c r="L558" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="M558" s="2" t="inlineStr"/>
+      <c r="N558" s="2" t="inlineStr"/>
+      <c r="O558" s="2" t="inlineStr"/>
+      <c r="P558" s="2" t="inlineStr"/>
+      <c r="Q558" s="2" t="inlineStr"/>
+      <c r="R558" s="2" t="inlineStr"/>
+      <c r="S558" s="2" t="inlineStr"/>
+      <c r="T558" s="2" t="inlineStr"/>
+      <c r="U558" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="V558" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B559" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C559" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D559" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E559" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F559" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black C Ultra 95GB</t>
+        </is>
+      </c>
+      <c r="G559" s="5" t="inlineStr">
+        <is>
+          <t>tim:100581</t>
+        </is>
+      </c>
+      <c r="H559" s="6" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I559" s="6" t="inlineStr"/>
+      <c r="J559" s="5" t="inlineStr"/>
+      <c r="K559" s="5" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="L559" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="M559" s="5" t="inlineStr"/>
+      <c r="N559" s="5" t="inlineStr"/>
+      <c r="O559" s="5" t="inlineStr"/>
+      <c r="P559" s="5" t="inlineStr"/>
+      <c r="Q559" s="5" t="inlineStr"/>
+      <c r="R559" s="5" t="inlineStr"/>
+      <c r="S559" s="5" t="inlineStr"/>
+      <c r="T559" s="5" t="inlineStr"/>
+      <c r="U559" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="V559" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black Plus 80GB</t>
+        </is>
+      </c>
+      <c r="G560" s="2" t="inlineStr">
+        <is>
+          <t>tim:54256</t>
+        </is>
+      </c>
+      <c r="H560" s="3" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="I560" s="3" t="inlineStr"/>
+      <c r="J560" s="2" t="inlineStr"/>
+      <c r="K560" s="2" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="L560" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="M560" s="2" t="inlineStr"/>
+      <c r="N560" s="2" t="inlineStr"/>
+      <c r="O560" s="2" t="inlineStr"/>
+      <c r="P560" s="2" t="inlineStr"/>
+      <c r="Q560" s="2" t="inlineStr"/>
+      <c r="R560" s="2" t="inlineStr"/>
+      <c r="S560" s="2" t="inlineStr"/>
+      <c r="T560" s="2" t="inlineStr"/>
+      <c r="U560" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="V560" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B561" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C561" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D561" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E561" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F561" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black Premium 110GB</t>
+        </is>
+      </c>
+      <c r="G561" s="5" t="inlineStr">
+        <is>
+          <t>tim:54261</t>
+        </is>
+      </c>
+      <c r="H561" s="6" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I561" s="6" t="inlineStr"/>
+      <c r="J561" s="5" t="inlineStr"/>
+      <c r="K561" s="5" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="L561" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="M561" s="5" t="inlineStr"/>
+      <c r="N561" s="5" t="inlineStr"/>
+      <c r="O561" s="5" t="inlineStr"/>
+      <c r="P561" s="5" t="inlineStr"/>
+      <c r="Q561" s="5" t="inlineStr"/>
+      <c r="R561" s="5" t="inlineStr"/>
+      <c r="S561" s="5" t="inlineStr"/>
+      <c r="T561" s="5" t="inlineStr"/>
+      <c r="U561" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="V561" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F562" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 16GB</t>
+        </is>
+      </c>
+      <c r="G562" s="2" t="inlineStr">
+        <is>
+          <t>tim:106306</t>
+        </is>
+      </c>
+      <c r="H562" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I562" s="3" t="inlineStr"/>
+      <c r="J562" s="2" t="inlineStr"/>
+      <c r="K562" s="2" t="inlineStr"/>
+      <c r="L562" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M562" s="2" t="inlineStr"/>
+      <c r="N562" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O562" s="2" t="inlineStr"/>
+      <c r="P562" s="2" t="inlineStr"/>
+      <c r="Q562" s="2" t="inlineStr"/>
+      <c r="R562" s="2" t="inlineStr"/>
+      <c r="S562" s="2" t="inlineStr"/>
+      <c r="T562" s="2" t="inlineStr"/>
+      <c r="U562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="V562" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B563" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C563" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D563" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E563" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F563" s="5" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 6GB</t>
+        </is>
+      </c>
+      <c r="G563" s="5" t="inlineStr">
+        <is>
+          <t>tim:59906</t>
+        </is>
+      </c>
+      <c r="H563" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I563" s="6" t="inlineStr"/>
+      <c r="J563" s="5" t="inlineStr"/>
+      <c r="K563" s="5" t="inlineStr"/>
+      <c r="L563" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M563" s="5" t="inlineStr"/>
+      <c r="N563" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="O563" s="5" t="inlineStr"/>
+      <c r="P563" s="5" t="inlineStr"/>
+      <c r="Q563" s="5" t="inlineStr"/>
+      <c r="R563" s="5" t="inlineStr"/>
+      <c r="S563" s="5" t="inlineStr"/>
+      <c r="T563" s="5" t="inlineStr"/>
+      <c r="U563" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="V563" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 8GB</t>
+        </is>
+      </c>
+      <c r="G564" s="2" t="inlineStr">
+        <is>
+          <t>tim:59901</t>
+        </is>
+      </c>
+      <c r="H564" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I564" s="3" t="inlineStr"/>
+      <c r="J564" s="2" t="inlineStr"/>
+      <c r="K564" s="2" t="inlineStr"/>
+      <c r="L564" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M564" s="2" t="inlineStr"/>
+      <c r="N564" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="O564" s="2" t="inlineStr"/>
+      <c r="P564" s="2" t="inlineStr"/>
+      <c r="Q564" s="2" t="inlineStr"/>
+      <c r="R564" s="2" t="inlineStr"/>
+      <c r="S564" s="2" t="inlineStr"/>
+      <c r="T564" s="2" t="inlineStr"/>
+      <c r="U564" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="V564" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B565" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C565" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D565" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E565" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F565" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G565" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029270-46gb</t>
+        </is>
+      </c>
+      <c r="H565" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I565" s="6" t="inlineStr"/>
+      <c r="J565" s="5" t="inlineStr"/>
+      <c r="K565" s="5" t="inlineStr"/>
+      <c r="L565" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="M565" s="5" t="inlineStr">
+        <is>
+          <t>15 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N565" s="5" t="inlineStr"/>
+      <c r="O565" s="5" t="inlineStr"/>
+      <c r="P565" s="5" t="inlineStr"/>
+      <c r="Q565" s="5" t="inlineStr"/>
+      <c r="R565" s="5" t="inlineStr"/>
+      <c r="S565" s="5" t="inlineStr"/>
+      <c r="T565" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="U565" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V565" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F566" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G566" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="H566" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I566" s="3" t="inlineStr"/>
+      <c r="J566" s="2" t="inlineStr"/>
+      <c r="K566" s="2" t="inlineStr"/>
+      <c r="L566" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="M566" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N566" s="2" t="inlineStr"/>
+      <c r="O566" s="2" t="inlineStr"/>
+      <c r="P566" s="2" t="inlineStr"/>
+      <c r="Q566" s="2" t="inlineStr"/>
+      <c r="R566" s="2" t="inlineStr"/>
+      <c r="S566" s="2" t="inlineStr"/>
+      <c r="T566" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="U566" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V566" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B567" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C567" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D567" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E567" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F567" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Educação</t>
+        </is>
+      </c>
+      <c r="G567" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029273-61gb</t>
+        </is>
+      </c>
+      <c r="H567" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I567" s="6" t="inlineStr"/>
+      <c r="J567" s="5" t="inlineStr"/>
+      <c r="K567" s="5" t="inlineStr"/>
+      <c r="L567" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="M567" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N567" s="5" t="inlineStr"/>
+      <c r="O567" s="5" t="inlineStr"/>
+      <c r="P567" s="5" t="inlineStr"/>
+      <c r="Q567" s="5" t="inlineStr"/>
+      <c r="R567" s="5" t="inlineStr"/>
+      <c r="S567" s="5" t="inlineStr"/>
+      <c r="T567" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vivae inclusa</t>
+        </is>
+      </c>
+      <c r="U567" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V567" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F568" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Entretenimento</t>
+        </is>
+      </c>
+      <c r="G568" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="H568" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="I568" s="3" t="inlineStr"/>
+      <c r="J568" s="2" t="inlineStr"/>
+      <c r="K568" s="2" t="inlineStr"/>
+      <c r="L568" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="M568" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N568" s="2" t="inlineStr"/>
+      <c r="O568" s="2" t="inlineStr"/>
+      <c r="P568" s="2" t="inlineStr"/>
+      <c r="Q568" s="2" t="inlineStr"/>
+      <c r="R568" s="2" t="inlineStr"/>
+      <c r="S568" s="2" t="inlineStr"/>
+      <c r="T568" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Vivo TV Inicial inclusa</t>
+        </is>
+      </c>
+      <c r="U568" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V568" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B569" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C569" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D569" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E569" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F569" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Música</t>
+        </is>
+      </c>
+      <c r="G569" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029313-61gb</t>
+        </is>
+      </c>
+      <c r="H569" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="I569" s="6" t="inlineStr"/>
+      <c r="J569" s="5" t="inlineStr"/>
+      <c r="K569" s="5" t="inlineStr"/>
+      <c r="L569" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="M569" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N569" s="5" t="inlineStr"/>
+      <c r="O569" s="5" t="inlineStr"/>
+      <c r="P569" s="5" t="inlineStr"/>
+      <c r="Q569" s="5" t="inlineStr"/>
+      <c r="R569" s="5" t="inlineStr"/>
+      <c r="S569" s="5" t="inlineStr"/>
+      <c r="T569" s="5" t="inlineStr">
+        <is>
+          <t>Apple Music Individual</t>
+        </is>
+      </c>
+      <c r="U569" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V569" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F570" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix</t>
+        </is>
+      </c>
+      <c r="G570" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="H570" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="I570" s="3" t="inlineStr"/>
+      <c r="J570" s="2" t="inlineStr"/>
+      <c r="K570" s="2" t="inlineStr"/>
+      <c r="L570" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="M570" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N570" s="2" t="inlineStr"/>
+      <c r="O570" s="2" t="inlineStr"/>
+      <c r="P570" s="2" t="inlineStr"/>
+      <c r="Q570" s="2" t="inlineStr"/>
+      <c r="R570" s="2" t="inlineStr"/>
+      <c r="S570" s="2" t="inlineStr"/>
+      <c r="T570" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão com anúncios</t>
+        </is>
+      </c>
+      <c r="U570" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V570" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B571" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C571" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D571" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E571" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F571" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Saúde</t>
+        </is>
+      </c>
+      <c r="G571" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029301-61gb</t>
+        </is>
+      </c>
+      <c r="H571" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I571" s="6" t="inlineStr"/>
+      <c r="J571" s="5" t="inlineStr"/>
+      <c r="K571" s="5" t="inlineStr"/>
+      <c r="L571" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="M571" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N571" s="5" t="inlineStr"/>
+      <c r="O571" s="5" t="inlineStr"/>
+      <c r="P571" s="5" t="inlineStr"/>
+      <c r="Q571" s="5" t="inlineStr"/>
+      <c r="R571" s="5" t="inlineStr"/>
+      <c r="S571" s="5" t="inlineStr"/>
+      <c r="T571" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vale Saúde Sempre inclusa</t>
+        </is>
+      </c>
+      <c r="U571" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V571" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F572" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Segurança</t>
+        </is>
+      </c>
+      <c r="G572" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029274-61gb</t>
+        </is>
+      </c>
+      <c r="H572" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I572" s="3" t="inlineStr"/>
+      <c r="J572" s="2" t="inlineStr"/>
+      <c r="K572" s="2" t="inlineStr"/>
+      <c r="L572" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="M572" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N572" s="2" t="inlineStr"/>
+      <c r="O572" s="2" t="inlineStr"/>
+      <c r="P572" s="2" t="inlineStr"/>
+      <c r="Q572" s="2" t="inlineStr"/>
+      <c r="R572" s="2" t="inlineStr"/>
+      <c r="S572" s="2" t="inlineStr"/>
+      <c r="T572" s="2" t="inlineStr">
+        <is>
+          <t>Incluso Proteção Rua e Seguro de Bens</t>
+        </is>
+      </c>
+      <c r="U572" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V572" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B573" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C573" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D573" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E573" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F573" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G573" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600032594-30gb</t>
+        </is>
+      </c>
+      <c r="H573" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="I573" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J573" s="5" t="inlineStr">
+        <is>
+          <t>preço sem fidelidade; fidelidade 12m no promo</t>
+        </is>
+      </c>
+      <c r="K573" s="5" t="inlineStr"/>
+      <c r="L573" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="M573" s="5" t="inlineStr">
+        <is>
+          <t>30 GB de franquia</t>
+        </is>
+      </c>
+      <c r="N573" s="5" t="inlineStr"/>
+      <c r="O573" s="5" t="inlineStr"/>
+      <c r="P573" s="5" t="inlineStr"/>
+      <c r="Q573" s="5" t="inlineStr"/>
+      <c r="R573" s="5" t="inlineStr"/>
+      <c r="S573" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="T573" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="U573" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="V573" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G574" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600032596-40gb</t>
+        </is>
+      </c>
+      <c r="H574" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="I574" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J574" s="2" t="inlineStr">
+        <is>
+          <t>preço sem fidelidade; fidelidade 12m no promo</t>
+        </is>
+      </c>
+      <c r="K574" s="2" t="inlineStr"/>
+      <c r="L574" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="M574" s="2" t="inlineStr">
+        <is>
+          <t>40 GB de franquia</t>
+        </is>
+      </c>
+      <c r="N574" s="2" t="inlineStr"/>
+      <c r="O574" s="2" t="inlineStr"/>
+      <c r="P574" s="2" t="inlineStr"/>
+      <c r="Q574" s="2" t="inlineStr"/>
+      <c r="R574" s="2" t="inlineStr"/>
+      <c r="S574" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="T574" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="U574" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="V574" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B575" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C575" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D575" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E575" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F575" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G575" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600032599-20gb</t>
+        </is>
+      </c>
+      <c r="H575" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="I575" s="6" t="inlineStr"/>
+      <c r="J575" s="5" t="inlineStr"/>
+      <c r="K575" s="5" t="inlineStr"/>
+      <c r="L575" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="M575" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia</t>
+        </is>
+      </c>
+      <c r="N575" s="5" t="inlineStr"/>
+      <c r="O575" s="5" t="inlineStr"/>
+      <c r="P575" s="5" t="inlineStr"/>
+      <c r="Q575" s="5" t="inlineStr"/>
+      <c r="R575" s="5" t="inlineStr"/>
+      <c r="S575" s="5" t="inlineStr"/>
+      <c r="T575" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="U575" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="V575" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F576" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Amazon</t>
+        </is>
+      </c>
+      <c r="G576" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029255-60gb</t>
+        </is>
+      </c>
+      <c r="H576" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="I576" s="3" t="inlineStr"/>
+      <c r="J576" s="2" t="inlineStr"/>
+      <c r="K576" s="2" t="inlineStr"/>
+      <c r="L576" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M576" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N576" s="2" t="inlineStr"/>
+      <c r="O576" s="2" t="inlineStr"/>
+      <c r="P576" s="2" t="inlineStr"/>
+      <c r="Q576" s="2" t="inlineStr"/>
+      <c r="R576" s="2" t="inlineStr"/>
+      <c r="S576" s="2" t="inlineStr"/>
+      <c r="T576" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Amazon Prime inclusa</t>
+        </is>
+      </c>
+      <c r="U576" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="V576" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B577" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C577" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D577" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E577" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F577" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Disney+</t>
+        </is>
+      </c>
+      <c r="G577" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022115-60gb</t>
+        </is>
+      </c>
+      <c r="H577" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I577" s="6" t="inlineStr"/>
+      <c r="J577" s="5" t="inlineStr"/>
+      <c r="K577" s="5" t="inlineStr"/>
+      <c r="L577" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="M577" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N577" s="5" t="inlineStr"/>
+      <c r="O577" s="5" t="inlineStr"/>
+      <c r="P577" s="5" t="inlineStr"/>
+      <c r="Q577" s="5" t="inlineStr"/>
+      <c r="R577" s="5" t="inlineStr">
+        <is>
+          <t>Disney+</t>
+        </is>
+      </c>
+      <c r="S577" s="5" t="inlineStr"/>
+      <c r="T577" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Disney+ Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="U577" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="V577" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Globoplay</t>
+        </is>
+      </c>
+      <c r="G578" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029246-60gb</t>
+        </is>
+      </c>
+      <c r="H578" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="I578" s="3" t="inlineStr"/>
+      <c r="J578" s="2" t="inlineStr"/>
+      <c r="K578" s="2" t="inlineStr"/>
+      <c r="L578" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M578" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N578" s="2" t="inlineStr"/>
+      <c r="O578" s="2" t="inlineStr"/>
+      <c r="P578" s="2" t="inlineStr"/>
+      <c r="Q578" s="2" t="inlineStr"/>
+      <c r="R578" s="2" t="inlineStr">
+        <is>
+          <t>Globoplay</t>
+        </is>
+      </c>
+      <c r="S578" s="2" t="inlineStr"/>
+      <c r="T578" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Globoplay inclusa</t>
+        </is>
+      </c>
+      <c r="U578" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="V578" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B579" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C579" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D579" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E579" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F579" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Netflix</t>
+        </is>
+      </c>
+      <c r="G579" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029234-60gb</t>
+        </is>
+      </c>
+      <c r="H579" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I579" s="6" t="inlineStr"/>
+      <c r="J579" s="5" t="inlineStr"/>
+      <c r="K579" s="5" t="inlineStr"/>
+      <c r="L579" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="M579" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N579" s="5" t="inlineStr"/>
+      <c r="O579" s="5" t="inlineStr"/>
+      <c r="P579" s="5" t="inlineStr"/>
+      <c r="Q579" s="5" t="inlineStr"/>
+      <c r="R579" s="5" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="S579" s="5" t="inlineStr"/>
+      <c r="T579" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="U579" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="V579" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Premiere</t>
+        </is>
+      </c>
+      <c r="G580" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029249-60gb</t>
+        </is>
+      </c>
+      <c r="H580" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I580" s="3" t="inlineStr"/>
+      <c r="J580" s="2" t="inlineStr"/>
+      <c r="K580" s="2" t="inlineStr"/>
+      <c r="L580" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M580" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N580" s="2" t="inlineStr"/>
+      <c r="O580" s="2" t="inlineStr"/>
+      <c r="P580" s="2" t="inlineStr"/>
+      <c r="Q580" s="2" t="inlineStr"/>
+      <c r="R580" s="2" t="inlineStr">
+        <is>
+          <t>Premiere</t>
+        </is>
+      </c>
+      <c r="S580" s="2" t="inlineStr"/>
+      <c r="T580" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Premiere inclusa</t>
+        </is>
+      </c>
+      <c r="U580" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="V580" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B581" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C581" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D581" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E581" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F581" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Spotify</t>
+        </is>
+      </c>
+      <c r="G581" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029229-60gb</t>
+        </is>
+      </c>
+      <c r="H581" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="I581" s="6" t="inlineStr"/>
+      <c r="J581" s="5" t="inlineStr"/>
+      <c r="K581" s="5" t="inlineStr"/>
+      <c r="L581" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="M581" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N581" s="5" t="inlineStr"/>
+      <c r="O581" s="5" t="inlineStr"/>
+      <c r="P581" s="5" t="inlineStr"/>
+      <c r="Q581" s="5" t="inlineStr"/>
+      <c r="R581" s="5" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="S581" s="5" t="inlineStr"/>
+      <c r="T581" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Spotify Premium inclusa</t>
+        </is>
+      </c>
+      <c r="U581" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="V581" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Travel</t>
+        </is>
+      </c>
+      <c r="G582" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029244-70gb</t>
+        </is>
+      </c>
+      <c r="H582" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="I582" s="3" t="inlineStr"/>
+      <c r="J582" s="2" t="inlineStr"/>
+      <c r="K582" s="2" t="inlineStr"/>
+      <c r="L582" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="M582" s="2" t="inlineStr">
+        <is>
+          <t>60 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N582" s="2" t="inlineStr"/>
+      <c r="O582" s="2" t="inlineStr"/>
+      <c r="P582" s="2" t="inlineStr"/>
+      <c r="Q582" s="2" t="inlineStr"/>
+      <c r="R582" s="2" t="inlineStr"/>
+      <c r="S582" s="2" t="inlineStr"/>
+      <c r="T582" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="U582" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="V582" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B583" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C583" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D583" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E583" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F583" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G583" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-25gb</t>
+        </is>
+      </c>
+      <c r="H583" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I583" s="6" t="inlineStr"/>
+      <c r="J583" s="5" t="inlineStr"/>
+      <c r="K583" s="5" t="inlineStr"/>
+      <c r="L583" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="M583" s="5" t="inlineStr">
+        <is>
+          <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
+        </is>
+      </c>
+      <c r="N583" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="O583" s="5" t="inlineStr"/>
+      <c r="P583" s="5" t="inlineStr"/>
+      <c r="Q583" s="5" t="inlineStr"/>
+      <c r="R583" s="5" t="inlineStr"/>
+      <c r="S583" s="5" t="inlineStr"/>
+      <c r="T583" s="5" t="inlineStr"/>
+      <c r="U583" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="V583" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F584" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G584" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-9gb</t>
+        </is>
+      </c>
+      <c r="H584" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I584" s="3" t="inlineStr"/>
+      <c r="J584" s="2" t="inlineStr"/>
+      <c r="K584" s="2" t="inlineStr"/>
+      <c r="L584" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M584" s="2" t="inlineStr">
+        <is>
+          <t>6 GB para navegar como quiser 3 GB para navegar no YouTube</t>
+        </is>
+      </c>
+      <c r="N584" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="O584" s="2" t="inlineStr"/>
+      <c r="P584" s="2" t="inlineStr"/>
+      <c r="Q584" s="2" t="inlineStr"/>
+      <c r="R584" s="2" t="inlineStr"/>
+      <c r="S584" s="2" t="inlineStr"/>
+      <c r="T584" s="2" t="inlineStr"/>
+      <c r="U584" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="V584" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B585" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C585" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D585" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E585" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F585" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G585" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-5gb</t>
+        </is>
+      </c>
+      <c r="H585" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I585" s="6" t="inlineStr"/>
+      <c r="J585" s="5" t="inlineStr"/>
+      <c r="K585" s="5" t="inlineStr"/>
+      <c r="L585" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M585" s="5" t="inlineStr">
+        <is>
+          <t>5 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="N585" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="O585" s="5" t="inlineStr"/>
+      <c r="P585" s="5" t="inlineStr"/>
+      <c r="Q585" s="5" t="inlineStr"/>
+      <c r="R585" s="5" t="inlineStr"/>
+      <c r="S585" s="5" t="inlineStr"/>
+      <c r="T585" s="5" t="inlineStr"/>
+      <c r="U585" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="V585" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:51:26</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F586" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G586" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-4gb</t>
+        </is>
+      </c>
+      <c r="H586" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I586" s="3" t="inlineStr"/>
+      <c r="J586" s="2" t="inlineStr"/>
+      <c r="K586" s="2" t="inlineStr"/>
+      <c r="L586" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M586" s="2" t="inlineStr">
+        <is>
+          <t>4 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="N586" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O586" s="2" t="inlineStr"/>
+      <c r="P586" s="2" t="inlineStr"/>
+      <c r="Q586" s="2" t="inlineStr"/>
+      <c r="R586" s="2" t="inlineStr"/>
+      <c r="S586" s="2" t="inlineStr"/>
+      <c r="T586" s="2" t="inlineStr"/>
+      <c r="U586" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="V586" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V530"/>
+  <autoFilter ref="A1:V586"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39305,12 +43322,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -39383,12 +43400,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -39455,12 +43472,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -39527,12 +43544,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -39599,12 +43616,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -39671,12 +43688,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -39743,12 +43760,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -39815,12 +43832,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -39887,12 +43904,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -39959,12 +43976,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -40031,12 +44048,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -40103,12 +44120,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -40175,12 +44192,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -40245,12 +44262,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -40315,12 +44332,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -40385,12 +44402,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -40455,12 +44472,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -40525,12 +44542,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -40595,12 +44612,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -40665,12 +44682,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -40729,12 +44746,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -40793,12 +44810,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -40857,12 +44874,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -40921,12 +44938,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -40983,12 +45000,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -41051,12 +45068,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -41119,12 +45136,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -41187,12 +45204,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -41255,12 +45272,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -41323,12 +45340,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -41391,12 +45408,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -41459,12 +45476,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -41525,12 +45542,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -41591,12 +45608,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -41657,12 +45674,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -41729,12 +45746,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -41801,12 +45818,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -41873,12 +45890,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -41945,12 +45962,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -42017,12 +46034,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -42089,12 +46106,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -42161,12 +46178,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -42233,12 +46250,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -42313,12 +46330,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -42393,12 +46410,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -42465,12 +46482,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -42537,12 +46554,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -42613,12 +46630,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -42689,12 +46706,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -42765,12 +46782,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -42841,12 +46858,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -42917,12 +46934,12 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -42989,12 +47006,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -43059,12 +47076,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -43129,12 +47146,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -43199,12 +47216,12 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -43296,7 +47313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -43356,265 +47373,6 @@
           <t>delta_brl</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029274-61gb</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Segurança</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>lite</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600032594-30gb</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Easy Lite</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>lite</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600032596-40gb</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Easy Lite</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>lite</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600032599-20gb</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Easy Lite</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>lite</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600025883-30gb</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Easy Lite</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>lite</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600025885-40gb</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Easy Lite</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>vivo</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>lite</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600025888-20gb</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Easy Lite</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -43653,7 +47411,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T22:16:09</t>
+          <t>2026-07-02T17:51:26</t>
         </is>
       </c>
     </row>
@@ -43665,7 +47423,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -43686,7 +47444,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -43797,7 +47555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -43954,15 +47712,15 @@
         <v/>
       </c>
       <c r="K3" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00")),0)),"")</f>
         <v/>
       </c>
       <c r="L3" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00")),0)),"")</f>
-        <v>30</v>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00")),0)),"")</f>
+        <v/>
       </c>
       <c r="M3" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00")),0)),"")</f>
         <v>44.9</v>
       </c>
     </row>
@@ -44007,15 +47765,15 @@
         <v/>
       </c>
       <c r="K4" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00")),0)),"")</f>
         <v/>
       </c>
       <c r="L4" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00")),0)),"")</f>
-        <v>30</v>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00")),0)),"")</f>
+        <v/>
       </c>
       <c r="M4" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00")),0)),"")</f>
         <v>44.9</v>
       </c>
     </row>
@@ -44060,15 +47818,15 @@
         <v/>
       </c>
       <c r="K5" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00")),0)),"")</f>
         <v/>
       </c>
       <c r="L5" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00")),0)),"")</f>
-        <v>30</v>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00")),0)),"")</f>
+        <v/>
       </c>
       <c r="M5" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00")),0)),"")</f>
         <v>44.9</v>
       </c>
     </row>
@@ -44113,15 +47871,15 @@
         <v/>
       </c>
       <c r="K6" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00")),0)),"")</f>
         <v/>
       </c>
       <c r="L6" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00")),0)),"")</f>
-        <v>30</v>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00")),0)),"")</f>
+        <v/>
       </c>
       <c r="M6" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00")),0)),"")</f>
         <v>44.9</v>
       </c>
     </row>
@@ -44166,15 +47924,15 @@
         <v>30</v>
       </c>
       <c r="K7" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0)),"")</f>
         <v/>
       </c>
       <c r="L7" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0)),"")</f>
-        <v>30</v>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0)),"")</f>
+        <v/>
       </c>
       <c r="M7" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00")),0)),"")</f>
         <v>44.9</v>
       </c>
     </row>
@@ -44219,15 +47977,15 @@
         <v>30</v>
       </c>
       <c r="K8" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0)),"")</f>
         <v/>
       </c>
       <c r="L8" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0)),"")</f>
-        <v>30</v>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0)),"")</f>
+        <v/>
       </c>
       <c r="M8" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00")),0)),"")</f>
         <v>44.9</v>
       </c>
     </row>
@@ -44272,15 +48030,15 @@
         <v>30</v>
       </c>
       <c r="K9" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0)),"")</f>
         <v/>
       </c>
       <c r="L9" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0)),"")</f>
-        <v>30</v>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0)),"")</f>
+        <v/>
       </c>
       <c r="M9" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00")),0)),"")</f>
         <v>44.9</v>
       </c>
     </row>
@@ -44325,15 +48083,15 @@
         <v>30</v>
       </c>
       <c r="K10" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0)),"")</f>
         <v/>
       </c>
       <c r="L10" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0)),"")</f>
-        <v>30</v>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0)),"")</f>
+        <v/>
       </c>
       <c r="M10" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00")),0)),"")</f>
         <v>44.9</v>
       </c>
     </row>
@@ -44378,15 +48136,15 @@
         <v>30</v>
       </c>
       <c r="K11" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0)),"")</f>
         <v/>
       </c>
       <c r="L11" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0)),"")</f>
-        <v>30</v>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0)),"")</f>
+        <v/>
       </c>
       <c r="M11" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00")),0)),"")</f>
         <v>44.9</v>
       </c>
     </row>
@@ -44431,22 +48189,82 @@
         <v>30</v>
       </c>
       <c r="K12" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0)),"")</f>
         <v/>
       </c>
       <c r="L12" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0)),"")</f>
-        <v>35</v>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0)),"")</f>
+        <v>45</v>
       </c>
       <c r="M12" s="3">
-        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0)),"")</f>
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00")),0)),"")</f>
         <v>44.9</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B13" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"))),"")</f>
+        <v>58.99</v>
+      </c>
+      <c r="C13" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"))),"")</f>
+        <v>59</v>
+      </c>
+      <c r="D13" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"))),"")</f>
+        <v>59.9</v>
+      </c>
+      <c r="E13" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <v>129.99</v>
+      </c>
+      <c r="F13" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <v>150</v>
+      </c>
+      <c r="G13" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <v>124.9</v>
+      </c>
+      <c r="H13" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$N:$N,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$N:$N,"&gt;=28")),"")</f>
+        <v>30</v>
+      </c>
+      <c r="I13" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$N:$N,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$N:$N,"&gt;=28")),"")</f>
+        <v>30</v>
+      </c>
+      <c r="J13" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$N:$N,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$N:$N,"&gt;=28")),"")</f>
+        <v>30</v>
+      </c>
+      <c r="K13" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00")),0)),"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00")),0)),"")</f>
+        <v>45</v>
+      </c>
+      <c r="M13" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00")),0)),"")</f>
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Rows = day: each cell = cheapest R$ that carrier offered in the category on that snapshot_date — a live MINIFS over `history` matching the EXACT date (a locale-safe text date built from the row's date, since history stores dates as TEXT — CONTEXT §7). Pre = cheapest 30-day prepaid plan (validity_days &gt;= 28; pre-#18 dates have no validity → blank, fills from 26-Jun on). Digital = min of Vivo Lite / Claro Flex. Heatmap = per-category-block green→yellow (each cell vs all carriers in its category; subtle while prices are near-flat, differentiates as they move). Grows one row per day; charts on the `Charts` sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Post — TIM: the entry-level price is the cheapest BILL-payment plan (R$129,99), not the R$119,99 credit-card-only plan — credit-card-only plans have low adoption, so they are excluded from the entry-level comparison (JPMorgan methodology). All TIM plans still appear in `history` + the TIM sheet.</t>
         </is>
       </c>
     </row>
@@ -44458,7 +48276,7 @@
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="K1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:D12">
+  <conditionalFormatting sqref="B3:D13">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -44468,7 +48286,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:G12">
+  <conditionalFormatting sqref="E3:G13">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -44478,7 +48296,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:J12">
+  <conditionalFormatting sqref="H3:J13">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -44488,7 +48306,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:M12">
+  <conditionalFormatting sqref="K3:M13">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -44554,15 +48372,15 @@
         </is>
       </c>
       <c r="Q38" s="10">
-        <f>IF('comparison'!B12="",NA(),'comparison'!B12)</f>
+        <f>IF('comparison'!B13="",NA(),'comparison'!B13)</f>
         <v/>
       </c>
       <c r="R38" s="10">
-        <f>IF('comparison'!C12="",NA(),'comparison'!C12)</f>
+        <f>IF('comparison'!C13="",NA(),'comparison'!C13)</f>
         <v/>
       </c>
       <c r="S38" s="10">
-        <f>IF('comparison'!D12="",NA(),'comparison'!D12)</f>
+        <f>IF('comparison'!D13="",NA(),'comparison'!D13)</f>
         <v/>
       </c>
     </row>
@@ -44573,15 +48391,15 @@
         </is>
       </c>
       <c r="Q39" s="10">
-        <f>IF('comparison'!E12="",NA(),'comparison'!E12)</f>
+        <f>IF('comparison'!E13="",NA(),'comparison'!E13)</f>
         <v/>
       </c>
       <c r="R39" s="10">
-        <f>IF('comparison'!F12="",NA(),'comparison'!F12)</f>
+        <f>IF('comparison'!F13="",NA(),'comparison'!F13)</f>
         <v/>
       </c>
       <c r="S39" s="10">
-        <f>IF('comparison'!G12="",NA(),'comparison'!G12)</f>
+        <f>IF('comparison'!G13="",NA(),'comparison'!G13)</f>
         <v/>
       </c>
     </row>
@@ -44592,15 +48410,15 @@
         </is>
       </c>
       <c r="Q40" s="10">
-        <f>IF('comparison'!H12="",NA(),'comparison'!H12)</f>
+        <f>IF('comparison'!H13="",NA(),'comparison'!H13)</f>
         <v/>
       </c>
       <c r="R40" s="10">
-        <f>IF('comparison'!I12="",NA(),'comparison'!I12)</f>
+        <f>IF('comparison'!I13="",NA(),'comparison'!I13)</f>
         <v/>
       </c>
       <c r="S40" s="10">
-        <f>IF('comparison'!J12="",NA(),'comparison'!J12)</f>
+        <f>IF('comparison'!J13="",NA(),'comparison'!J13)</f>
         <v/>
       </c>
     </row>
@@ -44611,15 +48429,15 @@
         </is>
       </c>
       <c r="Q41" s="10">
-        <f>IF('comparison'!K12="",NA(),'comparison'!K12)</f>
+        <f>IF('comparison'!K13="",NA(),'comparison'!K13)</f>
         <v/>
       </c>
       <c r="R41" s="10">
-        <f>IF('comparison'!L12="",NA(),'comparison'!L12)</f>
+        <f>IF('comparison'!L13="",NA(),'comparison'!L13)</f>
         <v/>
       </c>
       <c r="S41" s="10">
-        <f>IF('comparison'!M12="",NA(),'comparison'!M12)</f>
+        <f>IF('comparison'!M13="",NA(),'comparison'!M13)</f>
         <v/>
       </c>
     </row>

--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -38770,7 +38770,7 @@
       </c>
       <c r="B531" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C531" s="5" t="inlineStr">
@@ -38848,7 +38848,7 @@
       </c>
       <c r="B532" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C532" s="2" t="inlineStr">
@@ -38920,7 +38920,7 @@
       </c>
       <c r="B533" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C533" s="5" t="inlineStr">
@@ -38992,7 +38992,7 @@
       </c>
       <c r="B534" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C534" s="2" t="inlineStr">
@@ -39064,7 +39064,7 @@
       </c>
       <c r="B535" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C535" s="5" t="inlineStr">
@@ -39136,7 +39136,7 @@
       </c>
       <c r="B536" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C536" s="2" t="inlineStr">
@@ -39208,7 +39208,7 @@
       </c>
       <c r="B537" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C537" s="5" t="inlineStr">
@@ -39280,7 +39280,7 @@
       </c>
       <c r="B538" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C538" s="2" t="inlineStr">
@@ -39352,7 +39352,7 @@
       </c>
       <c r="B539" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C539" s="5" t="inlineStr">
@@ -39424,7 +39424,7 @@
       </c>
       <c r="B540" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C540" s="2" t="inlineStr">
@@ -39496,7 +39496,7 @@
       </c>
       <c r="B541" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C541" s="5" t="inlineStr">
@@ -39568,7 +39568,7 @@
       </c>
       <c r="B542" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C542" s="2" t="inlineStr">
@@ -39640,7 +39640,7 @@
       </c>
       <c r="B543" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C543" s="5" t="inlineStr">
@@ -39710,7 +39710,7 @@
       </c>
       <c r="B544" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C544" s="2" t="inlineStr">
@@ -39780,7 +39780,7 @@
       </c>
       <c r="B545" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C545" s="5" t="inlineStr">
@@ -39850,7 +39850,7 @@
       </c>
       <c r="B546" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C546" s="2" t="inlineStr">
@@ -39920,7 +39920,7 @@
       </c>
       <c r="B547" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C547" s="5" t="inlineStr">
@@ -39990,7 +39990,7 @@
       </c>
       <c r="B548" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C548" s="2" t="inlineStr">
@@ -40060,7 +40060,7 @@
       </c>
       <c r="B549" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C549" s="5" t="inlineStr">
@@ -40130,7 +40130,7 @@
       </c>
       <c r="B550" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C550" s="2" t="inlineStr">
@@ -40194,7 +40194,7 @@
       </c>
       <c r="B551" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C551" s="5" t="inlineStr">
@@ -40258,7 +40258,7 @@
       </c>
       <c r="B552" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C552" s="2" t="inlineStr">
@@ -40322,7 +40322,7 @@
       </c>
       <c r="B553" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C553" s="5" t="inlineStr">
@@ -40386,7 +40386,7 @@
       </c>
       <c r="B554" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C554" s="2" t="inlineStr">
@@ -40448,7 +40448,7 @@
       </c>
       <c r="B555" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C555" s="5" t="inlineStr">
@@ -40516,7 +40516,7 @@
       </c>
       <c r="B556" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C556" s="2" t="inlineStr">
@@ -40584,7 +40584,7 @@
       </c>
       <c r="B557" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C557" s="5" t="inlineStr">
@@ -40652,7 +40652,7 @@
       </c>
       <c r="B558" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C558" s="2" t="inlineStr">
@@ -40720,7 +40720,7 @@
       </c>
       <c r="B559" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C559" s="5" t="inlineStr">
@@ -40788,7 +40788,7 @@
       </c>
       <c r="B560" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C560" s="2" t="inlineStr">
@@ -40856,7 +40856,7 @@
       </c>
       <c r="B561" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C561" s="5" t="inlineStr">
@@ -40924,7 +40924,7 @@
       </c>
       <c r="B562" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C562" s="2" t="inlineStr">
@@ -40990,7 +40990,7 @@
       </c>
       <c r="B563" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C563" s="5" t="inlineStr">
@@ -41056,7 +41056,7 @@
       </c>
       <c r="B564" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C564" s="2" t="inlineStr">
@@ -41122,7 +41122,7 @@
       </c>
       <c r="B565" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C565" s="5" t="inlineStr">
@@ -41194,7 +41194,7 @@
       </c>
       <c r="B566" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C566" s="2" t="inlineStr">
@@ -41219,17 +41219,17 @@
       </c>
       <c r="G566" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029300-61gb</t>
+          <t>vivo:VIV202600029300-51gb</t>
         </is>
       </c>
       <c r="H566" s="3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I566" s="3" t="inlineStr"/>
       <c r="J566" s="2" t="inlineStr"/>
       <c r="K566" s="2" t="inlineStr"/>
       <c r="L566" s="4" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M566" s="2" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
       </c>
       <c r="B567" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C567" s="5" t="inlineStr">
@@ -41291,17 +41291,17 @@
       </c>
       <c r="G567" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029273-61gb</t>
+          <t>vivo:VIV202600029273-51gb</t>
         </is>
       </c>
       <c r="H567" s="6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I567" s="6" t="inlineStr"/>
       <c r="J567" s="5" t="inlineStr"/>
       <c r="K567" s="5" t="inlineStr"/>
       <c r="L567" s="7" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M567" s="5" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
       </c>
       <c r="B568" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C568" s="2" t="inlineStr">
@@ -41363,17 +41363,17 @@
       </c>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029307-61gb</t>
+          <t>vivo:VIV202600029307-51gb</t>
         </is>
       </c>
       <c r="H568" s="3" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I568" s="3" t="inlineStr"/>
       <c r="J568" s="2" t="inlineStr"/>
       <c r="K568" s="2" t="inlineStr"/>
       <c r="L568" s="4" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M568" s="2" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
       </c>
       <c r="B569" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C569" s="5" t="inlineStr">
@@ -41435,17 +41435,17 @@
       </c>
       <c r="G569" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029313-61gb</t>
+          <t>vivo:VIV202600029313-51gb</t>
         </is>
       </c>
       <c r="H569" s="6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I569" s="6" t="inlineStr"/>
       <c r="J569" s="5" t="inlineStr"/>
       <c r="K569" s="5" t="inlineStr"/>
       <c r="L569" s="7" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M569" s="5" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
       </c>
       <c r="B570" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C570" s="2" t="inlineStr">
@@ -41507,17 +41507,17 @@
       </c>
       <c r="G570" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029308-61gb</t>
+          <t>vivo:VIV202600029308-51gb</t>
         </is>
       </c>
       <c r="H570" s="3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I570" s="3" t="inlineStr"/>
       <c r="J570" s="2" t="inlineStr"/>
       <c r="K570" s="2" t="inlineStr"/>
       <c r="L570" s="4" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M570" s="2" t="inlineStr">
         <is>
@@ -41554,7 +41554,7 @@
       </c>
       <c r="B571" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C571" s="5" t="inlineStr">
@@ -41579,17 +41579,17 @@
       </c>
       <c r="G571" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029301-61gb</t>
+          <t>vivo:VIV202600029301-51gb</t>
         </is>
       </c>
       <c r="H571" s="6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I571" s="6" t="inlineStr"/>
       <c r="J571" s="5" t="inlineStr"/>
       <c r="K571" s="5" t="inlineStr"/>
       <c r="L571" s="7" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M571" s="5" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
       </c>
       <c r="B572" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C572" s="2" t="inlineStr">
@@ -41651,17 +41651,17 @@
       </c>
       <c r="G572" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029274-61gb</t>
+          <t>vivo:VIV202600029274-51gb</t>
         </is>
       </c>
       <c r="H572" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I572" s="3" t="inlineStr"/>
       <c r="J572" s="2" t="inlineStr"/>
       <c r="K572" s="2" t="inlineStr"/>
       <c r="L572" s="4" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M572" s="2" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
       </c>
       <c r="B573" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C573" s="5" t="inlineStr">
@@ -41778,7 +41778,7 @@
       </c>
       <c r="B574" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C574" s="2" t="inlineStr">
@@ -41858,7 +41858,7 @@
       </c>
       <c r="B575" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C575" s="5" t="inlineStr">
@@ -41930,7 +41930,7 @@
       </c>
       <c r="B576" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C576" s="2" t="inlineStr">
@@ -42002,7 +42002,7 @@
       </c>
       <c r="B577" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C577" s="5" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="B578" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C578" s="2" t="inlineStr">
@@ -42154,7 +42154,7 @@
       </c>
       <c r="B579" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C579" s="5" t="inlineStr">
@@ -42230,7 +42230,7 @@
       </c>
       <c r="B580" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C580" s="2" t="inlineStr">
@@ -42306,7 +42306,7 @@
       </c>
       <c r="B581" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C581" s="5" t="inlineStr">
@@ -42382,7 +42382,7 @@
       </c>
       <c r="B582" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C582" s="2" t="inlineStr">
@@ -42454,7 +42454,7 @@
       </c>
       <c r="B583" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C583" s="5" t="inlineStr">
@@ -42524,7 +42524,7 @@
       </c>
       <c r="B584" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C584" s="2" t="inlineStr">
@@ -42594,7 +42594,7 @@
       </c>
       <c r="B585" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C585" s="5" t="inlineStr">
@@ -42664,7 +42664,7 @@
       </c>
       <c r="B586" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C586" s="2" t="inlineStr">
@@ -43327,7 +43327,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -43405,7 +43405,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -43477,7 +43477,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -43549,7 +43549,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -43621,7 +43621,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -43693,7 +43693,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -43765,7 +43765,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -43837,7 +43837,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -43909,7 +43909,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -43981,7 +43981,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -44053,7 +44053,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -44125,7 +44125,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -44197,7 +44197,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -44267,7 +44267,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -44337,7 +44337,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -44477,7 +44477,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -44547,7 +44547,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -44617,7 +44617,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -44687,7 +44687,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -44751,7 +44751,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -44815,7 +44815,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -44879,7 +44879,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -44943,7 +44943,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -45005,7 +45005,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -45073,7 +45073,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -45141,7 +45141,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -45209,7 +45209,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -45277,7 +45277,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -45345,7 +45345,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -45413,7 +45413,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -45481,7 +45481,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -45547,7 +45547,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -45613,7 +45613,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -45679,7 +45679,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -45751,7 +45751,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -45776,17 +45776,17 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029300-61gb</t>
+          <t>vivo:VIV202600029300-51gb</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I37" s="6" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr"/>
       <c r="K37" s="5" t="inlineStr"/>
       <c r="L37" s="7" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -45848,17 +45848,17 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029273-61gb</t>
+          <t>vivo:VIV202600029273-51gb</t>
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="4" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -45920,17 +45920,17 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029307-61gb</t>
+          <t>vivo:VIV202600029307-51gb</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I39" s="6" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
       <c r="K39" s="5" t="inlineStr"/>
       <c r="L39" s="7" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -45992,17 +45992,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029313-61gb</t>
+          <t>vivo:VIV202600029313-51gb</t>
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I40" s="3" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="4" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -46039,7 +46039,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -46064,17 +46064,17 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029308-61gb</t>
+          <t>vivo:VIV202600029308-51gb</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I41" s="6" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
       <c r="K41" s="5" t="inlineStr"/>
       <c r="L41" s="7" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
@@ -46111,7 +46111,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -46136,17 +46136,17 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029301-61gb</t>
+          <t>vivo:VIV202600029301-51gb</t>
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="4" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -46208,17 +46208,17 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029274-61gb</t>
+          <t>vivo:VIV202600029274-51gb</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I43" s="6" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="5" t="inlineStr"/>
       <c r="L43" s="7" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -46335,7 +46335,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -46415,7 +46415,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -46487,7 +46487,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -46559,7 +46559,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -46635,7 +46635,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -46711,7 +46711,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -46787,7 +46787,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -46863,7 +46863,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -46939,7 +46939,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -47011,7 +47011,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -47081,7 +47081,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -47151,7 +47151,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -47221,7 +47221,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -47313,7 +47313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -47373,6 +47373,524 @@
           <t>delta_brl</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029273-51gb</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Educação</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029274-51gb</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Segurança</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-51gb</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029301-51gb</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Saúde</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-51gb</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Entretenimento</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-51gb</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029313-51gb</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Música</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029273-61gb</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Educação</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029274-61gb</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Segurança</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029301-61gb</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Saúde</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Entretenimento</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029313-61gb</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Música</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -47411,7 +47929,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:51:26</t>
+          <t>2026-07-02T22:04:41</t>
         </is>
       </c>
     </row>
@@ -47490,7 +48008,7 @@
       </c>
       <c r="D9" s="10">
         <f>IFERROR(AVERAGEIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
-        <v>98.68</v>
+        <v>97.09</v>
       </c>
       <c r="E9" s="10">
         <f>IFERROR(_xlfn.MAXIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
@@ -48784,7 +49302,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>69.90000000000001</v>
@@ -48794,7 +49312,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle (61GB)</t>
+          <t>Vivo Controle (51GB)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -48813,7 +49331,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>99.90000000000001</v>
@@ -48823,7 +49341,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Educação (61GB)</t>
+          <t>Vivo Controle Educação (51GB)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -48842,7 +49360,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C18" s="15" t="n"/>
       <c r="D18" s="6" t="n">
@@ -48850,7 +49368,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Saúde (61GB)</t>
+          <t>Vivo Controle Saúde (51GB)</t>
         </is>
       </c>
       <c r="F18" s="15" t="n"/>
@@ -48865,14 +49383,14 @@
         <v>5</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>84.98999999999999</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Segurança (61GB)</t>
+          <t>Vivo Controle Segurança (51GB)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -48886,13 +49404,13 @@
         <v>6</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C20" s="15" t="n"/>
       <c r="D20" s="15" t="n"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Música (61GB)</t>
+          <t>Vivo Controle Música (51GB)</t>
         </is>
       </c>
       <c r="F20" s="15" t="n"/>
@@ -48903,11 +49421,11 @@
         <v>7</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Netflix (61GB)</t>
+          <t>Vivo Controle Netflix (51GB)</t>
         </is>
       </c>
     </row>
@@ -48916,13 +49434,13 @@
         <v>8</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C22" s="15" t="n"/>
       <c r="D22" s="15" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Entretenimento (61GB)</t>
+          <t>Vivo Controle Entretenimento (51GB)</t>
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
@@ -49639,12 +50157,12 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E12" s="5" t="n"/>
@@ -49663,12 +50181,12 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -49687,12 +50205,12 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E14" s="5" t="n"/>
@@ -49711,12 +50229,12 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -49735,12 +50253,12 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E16" s="5" t="n"/>
@@ -49759,12 +50277,12 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
@@ -49783,12 +50301,12 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E18" s="5" t="n"/>

--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -19,7 +19,7 @@
     <sheet name="TIM" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$V$586</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$V$642</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$V$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -300,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$13</f>
+              <f>'comparison'!$A$3:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$B$3:$B$13</f>
+              <f>'comparison'!$B$3:$B$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -337,12 +337,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$13</f>
+              <f>'comparison'!$A$3:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$C$3:$C$13</f>
+              <f>'comparison'!$C$3:$C$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -374,12 +374,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$13</f>
+              <f>'comparison'!$A$3:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$D$3:$D$13</f>
+              <f>'comparison'!$D$3:$D$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -508,12 +508,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$13</f>
+              <f>'comparison'!$A$3:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$E$3:$E$13</f>
+              <f>'comparison'!$E$3:$E$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -545,12 +545,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$13</f>
+              <f>'comparison'!$A$3:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$F$3:$F$13</f>
+              <f>'comparison'!$F$3:$F$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -582,12 +582,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$13</f>
+              <f>'comparison'!$A$3:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$G$3:$G$13</f>
+              <f>'comparison'!$G$3:$G$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$13</f>
+              <f>'comparison'!$A$3:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$H$3:$H$13</f>
+              <f>'comparison'!$H$3:$H$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -753,12 +753,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$13</f>
+              <f>'comparison'!$A$3:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$I$3:$I$13</f>
+              <f>'comparison'!$I$3:$I$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -790,12 +790,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$13</f>
+              <f>'comparison'!$A$3:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$J$3:$J$13</f>
+              <f>'comparison'!$J$3:$J$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -924,12 +924,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$13</f>
+              <f>'comparison'!$A$3:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$K$3:$K$13</f>
+              <f>'comparison'!$K$3:$K$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -961,12 +961,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$13</f>
+              <f>'comparison'!$A$3:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$L$3:$L$13</f>
+              <f>'comparison'!$L$3:$L$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -998,12 +998,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$13</f>
+              <f>'comparison'!$A$3:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$M$3:$M$13</f>
+              <f>'comparison'!$M$3:$M$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1655,7 +1655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V586"/>
+  <dimension ref="A1:V642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -42726,8 +42726,3972 @@
         </is>
       </c>
     </row>
+    <row r="587">
+      <c r="A587" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B587" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C587" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D587" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E587" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F587" s="5" t="inlineStr">
+        <is>
+          <t>Controle 25GB</t>
+        </is>
+      </c>
+      <c r="G587" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-25gb</t>
+        </is>
+      </c>
+      <c r="H587" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I587" s="6" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="J587" s="5" t="inlineStr">
+        <is>
+          <t>De R$ 59,90 Por:</t>
+        </is>
+      </c>
+      <c r="K587" s="5" t="inlineStr"/>
+      <c r="L587" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="M587" s="5" t="inlineStr"/>
+      <c r="N587" s="5" t="inlineStr"/>
+      <c r="O587" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P587" s="5" t="inlineStr"/>
+      <c r="Q587" s="5" t="inlineStr"/>
+      <c r="R587" s="5" t="inlineStr"/>
+      <c r="S587" s="5" t="inlineStr"/>
+      <c r="T587" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e vídeos; Bônus exclusivo; Aproveite na sua franquia; WhatsApp e ligações ilimitadas</t>
+        </is>
+      </c>
+      <c r="U587" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="V587" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F588" s="2" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G588" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb</t>
+        </is>
+      </c>
+      <c r="H588" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I588" s="3" t="inlineStr"/>
+      <c r="J588" s="2" t="inlineStr"/>
+      <c r="K588" s="2" t="inlineStr"/>
+      <c r="L588" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="M588" s="2" t="inlineStr"/>
+      <c r="N588" s="2" t="inlineStr"/>
+      <c r="O588" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P588" s="2" t="inlineStr"/>
+      <c r="Q588" s="2" t="inlineStr"/>
+      <c r="R588" s="2" t="inlineStr"/>
+      <c r="S588" s="2" t="inlineStr"/>
+      <c r="T588" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="U588" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="V588" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B589" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C589" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D589" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E589" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F589" s="5" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G589" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb-gaming</t>
+        </is>
+      </c>
+      <c r="H589" s="6" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I589" s="6" t="inlineStr"/>
+      <c r="J589" s="5" t="inlineStr"/>
+      <c r="K589" s="5" t="inlineStr"/>
+      <c r="L589" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="M589" s="5" t="inlineStr"/>
+      <c r="N589" s="5" t="inlineStr"/>
+      <c r="O589" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P589" s="5" t="inlineStr"/>
+      <c r="Q589" s="5" t="inlineStr"/>
+      <c r="R589" s="5" t="inlineStr"/>
+      <c r="S589" s="5" t="inlineStr"/>
+      <c r="T589" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus para redes sociais e apps; Bônus uso livre; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="U589" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="V589" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B590" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D590" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F590" s="2" t="inlineStr">
+        <is>
+          <t>Flex 15GB</t>
+        </is>
+      </c>
+      <c r="G590" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-15gb</t>
+        </is>
+      </c>
+      <c r="H590" s="3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I590" s="3" t="inlineStr"/>
+      <c r="J590" s="2" t="inlineStr"/>
+      <c r="K590" s="2" t="inlineStr"/>
+      <c r="L590" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M590" s="2" t="inlineStr"/>
+      <c r="N590" s="2" t="inlineStr"/>
+      <c r="O590" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P590" s="2" t="inlineStr"/>
+      <c r="Q590" s="2" t="inlineStr"/>
+      <c r="R590" s="2" t="inlineStr"/>
+      <c r="S590" s="2" t="inlineStr"/>
+      <c r="T590" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="U590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="V590" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B591" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C591" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D591" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E591" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F591" s="5" t="inlineStr">
+        <is>
+          <t>Flex 20GB</t>
+        </is>
+      </c>
+      <c r="G591" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-20gb</t>
+        </is>
+      </c>
+      <c r="H591" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I591" s="6" t="inlineStr"/>
+      <c r="J591" s="5" t="inlineStr"/>
+      <c r="K591" s="5" t="inlineStr"/>
+      <c r="L591" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="M591" s="5" t="inlineStr"/>
+      <c r="N591" s="5" t="inlineStr"/>
+      <c r="O591" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P591" s="5" t="inlineStr"/>
+      <c r="Q591" s="5" t="inlineStr"/>
+      <c r="R591" s="5" t="inlineStr"/>
+      <c r="S591" s="5" t="inlineStr"/>
+      <c r="T591" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="U591" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="V591" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F592" s="2" t="inlineStr">
+        <is>
+          <t>Flex 30GB</t>
+        </is>
+      </c>
+      <c r="G592" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-30gb</t>
+        </is>
+      </c>
+      <c r="H592" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I592" s="3" t="inlineStr"/>
+      <c r="J592" s="2" t="inlineStr"/>
+      <c r="K592" s="2" t="inlineStr"/>
+      <c r="L592" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="M592" s="2" t="inlineStr"/>
+      <c r="N592" s="2" t="inlineStr"/>
+      <c r="O592" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P592" s="2" t="inlineStr"/>
+      <c r="Q592" s="2" t="inlineStr"/>
+      <c r="R592" s="2" t="inlineStr"/>
+      <c r="S592" s="2" t="inlineStr"/>
+      <c r="T592" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="U592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="V592" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B593" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C593" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D593" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E593" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F593" s="5" t="inlineStr">
+        <is>
+          <t>Flex 40GB</t>
+        </is>
+      </c>
+      <c r="G593" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-40gb</t>
+        </is>
+      </c>
+      <c r="H593" s="6" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I593" s="6" t="inlineStr"/>
+      <c r="J593" s="5" t="inlineStr"/>
+      <c r="K593" s="5" t="inlineStr"/>
+      <c r="L593" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="M593" s="5" t="inlineStr"/>
+      <c r="N593" s="5" t="inlineStr"/>
+      <c r="O593" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P593" s="5" t="inlineStr"/>
+      <c r="Q593" s="5" t="inlineStr"/>
+      <c r="R593" s="5" t="inlineStr"/>
+      <c r="S593" s="5" t="inlineStr"/>
+      <c r="T593" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e apps; Bônus uso livre; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="U593" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="V593" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F594" s="2" t="inlineStr">
+        <is>
+          <t>Pós 100GB</t>
+        </is>
+      </c>
+      <c r="G594" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-100gb</t>
+        </is>
+      </c>
+      <c r="H594" s="3" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="I594" s="3" t="inlineStr"/>
+      <c r="J594" s="2" t="inlineStr"/>
+      <c r="K594" s="2" t="inlineStr"/>
+      <c r="L594" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M594" s="2" t="inlineStr"/>
+      <c r="N594" s="2" t="inlineStr"/>
+      <c r="O594" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P594" s="2" t="inlineStr"/>
+      <c r="Q594" s="2" t="inlineStr"/>
+      <c r="R594" s="2" t="inlineStr"/>
+      <c r="S594" s="2" t="inlineStr"/>
+      <c r="T594" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="U594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V594" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B595" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C595" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D595" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E595" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F595" s="5" t="inlineStr">
+        <is>
+          <t>Pós 150GB</t>
+        </is>
+      </c>
+      <c r="G595" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-150gb</t>
+        </is>
+      </c>
+      <c r="H595" s="6" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="I595" s="6" t="inlineStr"/>
+      <c r="J595" s="5" t="inlineStr"/>
+      <c r="K595" s="5" t="inlineStr"/>
+      <c r="L595" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="M595" s="5" t="inlineStr"/>
+      <c r="N595" s="5" t="inlineStr"/>
+      <c r="O595" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P595" s="5" t="inlineStr"/>
+      <c r="Q595" s="5" t="inlineStr"/>
+      <c r="R595" s="5" t="inlineStr"/>
+      <c r="S595" s="5" t="inlineStr"/>
+      <c r="T595" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas e Europa; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="U595" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V595" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D596" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F596" s="2" t="inlineStr">
+        <is>
+          <t>Pós 200GB</t>
+        </is>
+      </c>
+      <c r="G596" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-200gb</t>
+        </is>
+      </c>
+      <c r="H596" s="3" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="I596" s="3" t="inlineStr"/>
+      <c r="J596" s="2" t="inlineStr"/>
+      <c r="K596" s="2" t="inlineStr"/>
+      <c r="L596" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="M596" s="2" t="inlineStr"/>
+      <c r="N596" s="2" t="inlineStr"/>
+      <c r="O596" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P596" s="2" t="inlineStr"/>
+      <c r="Q596" s="2" t="inlineStr"/>
+      <c r="R596" s="2" t="inlineStr"/>
+      <c r="S596" s="2" t="inlineStr"/>
+      <c r="T596" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="U596" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V596" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B597" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C597" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D597" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E597" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F597" s="5" t="inlineStr">
+        <is>
+          <t>Pós 50GB com GeForce NOW</t>
+        </is>
+      </c>
+      <c r="G597" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb-geforce</t>
+        </is>
+      </c>
+      <c r="H597" s="6" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="I597" s="6" t="inlineStr"/>
+      <c r="J597" s="5" t="inlineStr"/>
+      <c r="K597" s="5" t="inlineStr"/>
+      <c r="L597" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="M597" s="5" t="inlineStr"/>
+      <c r="N597" s="5" t="inlineStr"/>
+      <c r="O597" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P597" s="5" t="inlineStr"/>
+      <c r="Q597" s="5" t="inlineStr"/>
+      <c r="R597" s="5" t="inlineStr"/>
+      <c r="S597" s="5" t="inlineStr"/>
+      <c r="T597" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado; Inclusa assinatura GeForce NOW</t>
+        </is>
+      </c>
+      <c r="U597" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V597" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D598" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F598" s="2" t="inlineStr">
+        <is>
+          <t>Pós 60GB</t>
+        </is>
+      </c>
+      <c r="G598" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb</t>
+        </is>
+      </c>
+      <c r="H598" s="3" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="I598" s="3" t="inlineStr"/>
+      <c r="J598" s="2" t="inlineStr"/>
+      <c r="K598" s="2" t="inlineStr"/>
+      <c r="L598" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M598" s="2" t="inlineStr"/>
+      <c r="N598" s="2" t="inlineStr"/>
+      <c r="O598" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P598" s="2" t="inlineStr"/>
+      <c r="Q598" s="2" t="inlineStr"/>
+      <c r="R598" s="2" t="inlineStr"/>
+      <c r="S598" s="2" t="inlineStr"/>
+      <c r="T598" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="U598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V598" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B599" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C599" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D599" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E599" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F599" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 10GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G599" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-10gb</t>
+        </is>
+      </c>
+      <c r="H599" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I599" s="6" t="inlineStr"/>
+      <c r="J599" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K599" s="5" t="inlineStr"/>
+      <c r="L599" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M599" s="5" t="inlineStr"/>
+      <c r="N599" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="O599" s="5" t="inlineStr"/>
+      <c r="P599" s="5" t="inlineStr"/>
+      <c r="Q599" s="5" t="inlineStr"/>
+      <c r="R599" s="5" t="inlineStr"/>
+      <c r="S599" s="5" t="inlineStr"/>
+      <c r="T599" s="5" t="inlineStr"/>
+      <c r="U599" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V599" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D600" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F600" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 12GB (30 dias)</t>
+        </is>
+      </c>
+      <c r="G600" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-30d-12gb</t>
+        </is>
+      </c>
+      <c r="H600" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I600" s="3" t="inlineStr"/>
+      <c r="J600" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$30 — validade 30 dias</t>
+        </is>
+      </c>
+      <c r="K600" s="2" t="inlineStr"/>
+      <c r="L600" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M600" s="2" t="inlineStr"/>
+      <c r="N600" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O600" s="2" t="inlineStr"/>
+      <c r="P600" s="2" t="inlineStr"/>
+      <c r="Q600" s="2" t="inlineStr"/>
+      <c r="R600" s="2" t="inlineStr"/>
+      <c r="S600" s="2" t="inlineStr"/>
+      <c r="T600" s="2" t="inlineStr"/>
+      <c r="U600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V600" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B601" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C601" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D601" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E601" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F601" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 4GB (12 dias)</t>
+        </is>
+      </c>
+      <c r="G601" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-12d-4gb</t>
+        </is>
+      </c>
+      <c r="H601" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I601" s="6" t="inlineStr"/>
+      <c r="J601" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$15 — validade 12 dias</t>
+        </is>
+      </c>
+      <c r="K601" s="5" t="inlineStr"/>
+      <c r="L601" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M601" s="5" t="inlineStr"/>
+      <c r="N601" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="O601" s="5" t="inlineStr"/>
+      <c r="P601" s="5" t="inlineStr"/>
+      <c r="Q601" s="5" t="inlineStr"/>
+      <c r="R601" s="5" t="inlineStr"/>
+      <c r="S601" s="5" t="inlineStr"/>
+      <c r="T601" s="5" t="inlineStr"/>
+      <c r="U601" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V601" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F602" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 5GB (15 dias)</t>
+        </is>
+      </c>
+      <c r="G602" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-15d-5gb</t>
+        </is>
+      </c>
+      <c r="H602" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I602" s="3" t="inlineStr"/>
+      <c r="J602" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$15 — validade 15 dias</t>
+        </is>
+      </c>
+      <c r="K602" s="2" t="inlineStr"/>
+      <c r="L602" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M602" s="2" t="inlineStr"/>
+      <c r="N602" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O602" s="2" t="inlineStr"/>
+      <c r="P602" s="2" t="inlineStr"/>
+      <c r="Q602" s="2" t="inlineStr"/>
+      <c r="R602" s="2" t="inlineStr"/>
+      <c r="S602" s="2" t="inlineStr"/>
+      <c r="T602" s="2" t="inlineStr"/>
+      <c r="U602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V602" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B603" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C603" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D603" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E603" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F603" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 6GB (20 dias)</t>
+        </is>
+      </c>
+      <c r="G603" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-20d-6gb</t>
+        </is>
+      </c>
+      <c r="H603" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I603" s="6" t="inlineStr"/>
+      <c r="J603" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$20 — validade 20 dias</t>
+        </is>
+      </c>
+      <c r="K603" s="5" t="inlineStr"/>
+      <c r="L603" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M603" s="5" t="inlineStr"/>
+      <c r="N603" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O603" s="5" t="inlineStr"/>
+      <c r="P603" s="5" t="inlineStr"/>
+      <c r="Q603" s="5" t="inlineStr"/>
+      <c r="R603" s="5" t="inlineStr"/>
+      <c r="S603" s="5" t="inlineStr"/>
+      <c r="T603" s="5" t="inlineStr"/>
+      <c r="U603" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V603" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D604" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F604" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 8GB (20 dias)</t>
+        </is>
+      </c>
+      <c r="G604" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-20d-8gb</t>
+        </is>
+      </c>
+      <c r="H604" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I604" s="3" t="inlineStr"/>
+      <c r="J604" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$20 — validade 20 dias</t>
+        </is>
+      </c>
+      <c r="K604" s="2" t="inlineStr"/>
+      <c r="L604" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M604" s="2" t="inlineStr"/>
+      <c r="N604" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O604" s="2" t="inlineStr"/>
+      <c r="P604" s="2" t="inlineStr"/>
+      <c r="Q604" s="2" t="inlineStr"/>
+      <c r="R604" s="2" t="inlineStr"/>
+      <c r="S604" s="2" t="inlineStr"/>
+      <c r="T604" s="2" t="inlineStr"/>
+      <c r="U604" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V604" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B605" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C605" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D605" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E605" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F605" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 9GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G605" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-9gb</t>
+        </is>
+      </c>
+      <c r="H605" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I605" s="6" t="inlineStr"/>
+      <c r="J605" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K605" s="5" t="inlineStr"/>
+      <c r="L605" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="M605" s="5" t="inlineStr"/>
+      <c r="N605" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="O605" s="5" t="inlineStr"/>
+      <c r="P605" s="5" t="inlineStr"/>
+      <c r="Q605" s="5" t="inlineStr"/>
+      <c r="R605" s="5" t="inlineStr"/>
+      <c r="S605" s="5" t="inlineStr"/>
+      <c r="T605" s="5" t="inlineStr"/>
+      <c r="U605" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V605" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B606" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C606" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D606" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F606" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle 41GB</t>
+        </is>
+      </c>
+      <c r="G606" s="2" t="inlineStr">
+        <is>
+          <t>tim:162901</t>
+        </is>
+      </c>
+      <c r="H606" s="3" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="I606" s="3" t="inlineStr"/>
+      <c r="J606" s="2" t="inlineStr"/>
+      <c r="K606" s="2" t="inlineStr"/>
+      <c r="L606" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="M606" s="2" t="inlineStr"/>
+      <c r="N606" s="2" t="inlineStr"/>
+      <c r="O606" s="2" t="inlineStr"/>
+      <c r="P606" s="2" t="inlineStr"/>
+      <c r="Q606" s="2" t="inlineStr"/>
+      <c r="R606" s="2" t="inlineStr"/>
+      <c r="S606" s="2" t="inlineStr"/>
+      <c r="T606" s="2" t="inlineStr"/>
+      <c r="U606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="V606" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B607" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C607" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D607" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E607" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F607" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Light Express 31GB</t>
+        </is>
+      </c>
+      <c r="G607" s="5" t="inlineStr">
+        <is>
+          <t>tim:143536</t>
+        </is>
+      </c>
+      <c r="H607" s="6" t="n">
+        <v>60.99</v>
+      </c>
+      <c r="I607" s="6" t="inlineStr"/>
+      <c r="J607" s="5" t="inlineStr"/>
+      <c r="K607" s="5" t="inlineStr"/>
+      <c r="L607" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="M607" s="5" t="inlineStr"/>
+      <c r="N607" s="5" t="inlineStr"/>
+      <c r="O607" s="5" t="inlineStr"/>
+      <c r="P607" s="5" t="inlineStr"/>
+      <c r="Q607" s="5" t="inlineStr"/>
+      <c r="R607" s="5" t="inlineStr"/>
+      <c r="S607" s="5" t="inlineStr"/>
+      <c r="T607" s="5" t="inlineStr"/>
+      <c r="U607" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="V607" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B608" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C608" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D608" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E608" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F608" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Plus 45GB</t>
+        </is>
+      </c>
+      <c r="G608" s="2" t="inlineStr">
+        <is>
+          <t>tim:155891</t>
+        </is>
+      </c>
+      <c r="H608" s="3" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I608" s="3" t="inlineStr"/>
+      <c r="J608" s="2" t="inlineStr"/>
+      <c r="K608" s="2" t="inlineStr"/>
+      <c r="L608" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="M608" s="2" t="inlineStr"/>
+      <c r="N608" s="2" t="inlineStr"/>
+      <c r="O608" s="2" t="inlineStr"/>
+      <c r="P608" s="2" t="inlineStr"/>
+      <c r="Q608" s="2" t="inlineStr"/>
+      <c r="R608" s="2" t="inlineStr"/>
+      <c r="S608" s="2" t="inlineStr"/>
+      <c r="T608" s="2" t="inlineStr"/>
+      <c r="U608" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="V608" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B609" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C609" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D609" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E609" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F609" s="5" t="inlineStr">
+        <is>
+          <t>TIM Controle Premium 53GB</t>
+        </is>
+      </c>
+      <c r="G609" s="5" t="inlineStr">
+        <is>
+          <t>tim:162896</t>
+        </is>
+      </c>
+      <c r="H609" s="6" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="I609" s="6" t="inlineStr"/>
+      <c r="J609" s="5" t="inlineStr"/>
+      <c r="K609" s="5" t="inlineStr"/>
+      <c r="L609" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="M609" s="5" t="inlineStr"/>
+      <c r="N609" s="5" t="inlineStr"/>
+      <c r="O609" s="5" t="inlineStr"/>
+      <c r="P609" s="5" t="inlineStr"/>
+      <c r="Q609" s="5" t="inlineStr"/>
+      <c r="R609" s="5" t="inlineStr"/>
+      <c r="S609" s="5" t="inlineStr"/>
+      <c r="T609" s="5" t="inlineStr"/>
+      <c r="U609" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="V609" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B610" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C610" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D610" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F610" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle Pro Express</t>
+        </is>
+      </c>
+      <c r="G610" s="2" t="inlineStr">
+        <is>
+          <t>tim:143576</t>
+        </is>
+      </c>
+      <c r="H610" s="3" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I610" s="3" t="inlineStr"/>
+      <c r="J610" s="2" t="inlineStr"/>
+      <c r="K610" s="2" t="inlineStr"/>
+      <c r="L610" s="4" t="inlineStr"/>
+      <c r="M610" s="2" t="inlineStr"/>
+      <c r="N610" s="2" t="inlineStr"/>
+      <c r="O610" s="2" t="inlineStr"/>
+      <c r="P610" s="2" t="inlineStr"/>
+      <c r="Q610" s="2" t="inlineStr"/>
+      <c r="R610" s="2" t="inlineStr"/>
+      <c r="S610" s="2" t="inlineStr"/>
+      <c r="T610" s="2" t="inlineStr"/>
+      <c r="U610" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
+        </is>
+      </c>
+      <c r="V610" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B611" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C611" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D611" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E611" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F611" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black 70GB</t>
+        </is>
+      </c>
+      <c r="G611" s="5" t="inlineStr">
+        <is>
+          <t>tim:54206</t>
+        </is>
+      </c>
+      <c r="H611" s="6" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="I611" s="6" t="inlineStr"/>
+      <c r="J611" s="5" t="inlineStr"/>
+      <c r="K611" s="5" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="L611" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="M611" s="5" t="inlineStr"/>
+      <c r="N611" s="5" t="inlineStr"/>
+      <c r="O611" s="5" t="inlineStr"/>
+      <c r="P611" s="5" t="inlineStr"/>
+      <c r="Q611" s="5" t="inlineStr"/>
+      <c r="R611" s="5" t="inlineStr"/>
+      <c r="S611" s="5" t="inlineStr"/>
+      <c r="T611" s="5" t="inlineStr"/>
+      <c r="U611" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="V611" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D612" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F612" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black A Express 67GB</t>
+        </is>
+      </c>
+      <c r="G612" s="2" t="inlineStr">
+        <is>
+          <t>tim:55121</t>
+        </is>
+      </c>
+      <c r="H612" s="3" t="n">
+        <v>119.99</v>
+      </c>
+      <c r="I612" s="3" t="inlineStr"/>
+      <c r="J612" s="2" t="inlineStr"/>
+      <c r="K612" s="2" t="inlineStr">
+        <is>
+          <t>credit_card</t>
+        </is>
+      </c>
+      <c r="L612" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="M612" s="2" t="inlineStr"/>
+      <c r="N612" s="2" t="inlineStr"/>
+      <c r="O612" s="2" t="inlineStr"/>
+      <c r="P612" s="2" t="inlineStr"/>
+      <c r="Q612" s="2" t="inlineStr"/>
+      <c r="R612" s="2" t="inlineStr"/>
+      <c r="S612" s="2" t="inlineStr"/>
+      <c r="T612" s="2" t="inlineStr"/>
+      <c r="U612" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="V612" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B613" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C613" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D613" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E613" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F613" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black B Express 82GB</t>
+        </is>
+      </c>
+      <c r="G613" s="5" t="inlineStr">
+        <is>
+          <t>tim:52146</t>
+        </is>
+      </c>
+      <c r="H613" s="6" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="I613" s="6" t="inlineStr"/>
+      <c r="J613" s="5" t="inlineStr"/>
+      <c r="K613" s="5" t="inlineStr">
+        <is>
+          <t>credit_card</t>
+        </is>
+      </c>
+      <c r="L613" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="M613" s="5" t="inlineStr"/>
+      <c r="N613" s="5" t="inlineStr"/>
+      <c r="O613" s="5" t="inlineStr"/>
+      <c r="P613" s="5" t="inlineStr"/>
+      <c r="Q613" s="5" t="inlineStr"/>
+      <c r="R613" s="5" t="inlineStr"/>
+      <c r="S613" s="5" t="inlineStr"/>
+      <c r="T613" s="5" t="inlineStr"/>
+      <c r="U613" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="V613" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C614" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D614" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F614" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black C Express 107GB</t>
+        </is>
+      </c>
+      <c r="G614" s="2" t="inlineStr">
+        <is>
+          <t>tim:52151</t>
+        </is>
+      </c>
+      <c r="H614" s="3" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="I614" s="3" t="inlineStr"/>
+      <c r="J614" s="2" t="inlineStr"/>
+      <c r="K614" s="2" t="inlineStr">
+        <is>
+          <t>credit_card</t>
+        </is>
+      </c>
+      <c r="L614" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="M614" s="2" t="inlineStr"/>
+      <c r="N614" s="2" t="inlineStr"/>
+      <c r="O614" s="2" t="inlineStr"/>
+      <c r="P614" s="2" t="inlineStr"/>
+      <c r="Q614" s="2" t="inlineStr"/>
+      <c r="R614" s="2" t="inlineStr"/>
+      <c r="S614" s="2" t="inlineStr"/>
+      <c r="T614" s="2" t="inlineStr"/>
+      <c r="U614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="V614" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B615" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C615" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D615" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E615" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F615" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black C Ultra 95GB</t>
+        </is>
+      </c>
+      <c r="G615" s="5" t="inlineStr">
+        <is>
+          <t>tim:100581</t>
+        </is>
+      </c>
+      <c r="H615" s="6" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I615" s="6" t="inlineStr"/>
+      <c r="J615" s="5" t="inlineStr"/>
+      <c r="K615" s="5" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="L615" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="M615" s="5" t="inlineStr"/>
+      <c r="N615" s="5" t="inlineStr"/>
+      <c r="O615" s="5" t="inlineStr"/>
+      <c r="P615" s="5" t="inlineStr"/>
+      <c r="Q615" s="5" t="inlineStr"/>
+      <c r="R615" s="5" t="inlineStr"/>
+      <c r="S615" s="5" t="inlineStr"/>
+      <c r="T615" s="5" t="inlineStr"/>
+      <c r="U615" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="V615" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B616" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C616" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D616" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F616" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black Plus 80GB</t>
+        </is>
+      </c>
+      <c r="G616" s="2" t="inlineStr">
+        <is>
+          <t>tim:54256</t>
+        </is>
+      </c>
+      <c r="H616" s="3" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="I616" s="3" t="inlineStr"/>
+      <c r="J616" s="2" t="inlineStr"/>
+      <c r="K616" s="2" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="L616" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="M616" s="2" t="inlineStr"/>
+      <c r="N616" s="2" t="inlineStr"/>
+      <c r="O616" s="2" t="inlineStr"/>
+      <c r="P616" s="2" t="inlineStr"/>
+      <c r="Q616" s="2" t="inlineStr"/>
+      <c r="R616" s="2" t="inlineStr"/>
+      <c r="S616" s="2" t="inlineStr"/>
+      <c r="T616" s="2" t="inlineStr"/>
+      <c r="U616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="V616" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B617" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C617" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D617" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E617" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F617" s="5" t="inlineStr">
+        <is>
+          <t>TIM Black Premium 110GB</t>
+        </is>
+      </c>
+      <c r="G617" s="5" t="inlineStr">
+        <is>
+          <t>tim:54261</t>
+        </is>
+      </c>
+      <c r="H617" s="6" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="I617" s="6" t="inlineStr"/>
+      <c r="J617" s="5" t="inlineStr"/>
+      <c r="K617" s="5" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="L617" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="M617" s="5" t="inlineStr"/>
+      <c r="N617" s="5" t="inlineStr"/>
+      <c r="O617" s="5" t="inlineStr"/>
+      <c r="P617" s="5" t="inlineStr"/>
+      <c r="Q617" s="5" t="inlineStr"/>
+      <c r="R617" s="5" t="inlineStr"/>
+      <c r="S617" s="5" t="inlineStr"/>
+      <c r="T617" s="5" t="inlineStr"/>
+      <c r="U617" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
+        </is>
+      </c>
+      <c r="V617" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C618" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D618" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E618" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F618" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 16GB</t>
+        </is>
+      </c>
+      <c r="G618" s="2" t="inlineStr">
+        <is>
+          <t>tim:106306</t>
+        </is>
+      </c>
+      <c r="H618" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I618" s="3" t="inlineStr"/>
+      <c r="J618" s="2" t="inlineStr"/>
+      <c r="K618" s="2" t="inlineStr"/>
+      <c r="L618" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M618" s="2" t="inlineStr"/>
+      <c r="N618" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O618" s="2" t="inlineStr"/>
+      <c r="P618" s="2" t="inlineStr"/>
+      <c r="Q618" s="2" t="inlineStr"/>
+      <c r="R618" s="2" t="inlineStr"/>
+      <c r="S618" s="2" t="inlineStr"/>
+      <c r="T618" s="2" t="inlineStr"/>
+      <c r="U618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="V618" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B619" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C619" s="5" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D619" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E619" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F619" s="5" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 6GB</t>
+        </is>
+      </c>
+      <c r="G619" s="5" t="inlineStr">
+        <is>
+          <t>tim:59906</t>
+        </is>
+      </c>
+      <c r="H619" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I619" s="6" t="inlineStr"/>
+      <c r="J619" s="5" t="inlineStr"/>
+      <c r="K619" s="5" t="inlineStr"/>
+      <c r="L619" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M619" s="5" t="inlineStr"/>
+      <c r="N619" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="O619" s="5" t="inlineStr"/>
+      <c r="P619" s="5" t="inlineStr"/>
+      <c r="Q619" s="5" t="inlineStr"/>
+      <c r="R619" s="5" t="inlineStr"/>
+      <c r="S619" s="5" t="inlineStr"/>
+      <c r="T619" s="5" t="inlineStr"/>
+      <c r="U619" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="V619" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C620" s="2" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="D620" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F620" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus 8GB</t>
+        </is>
+      </c>
+      <c r="G620" s="2" t="inlineStr">
+        <is>
+          <t>tim:59901</t>
+        </is>
+      </c>
+      <c r="H620" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I620" s="3" t="inlineStr"/>
+      <c r="J620" s="2" t="inlineStr"/>
+      <c r="K620" s="2" t="inlineStr"/>
+      <c r="L620" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M620" s="2" t="inlineStr"/>
+      <c r="N620" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="O620" s="2" t="inlineStr"/>
+      <c r="P620" s="2" t="inlineStr"/>
+      <c r="Q620" s="2" t="inlineStr"/>
+      <c r="R620" s="2" t="inlineStr"/>
+      <c r="S620" s="2" t="inlineStr"/>
+      <c r="T620" s="2" t="inlineStr"/>
+      <c r="U620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
+        </is>
+      </c>
+      <c r="V620" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/tim_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B621" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C621" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D621" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E621" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F621" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G621" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029270-46gb</t>
+        </is>
+      </c>
+      <c r="H621" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I621" s="6" t="inlineStr"/>
+      <c r="J621" s="5" t="inlineStr"/>
+      <c r="K621" s="5" t="inlineStr"/>
+      <c r="L621" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="M621" s="5" t="inlineStr">
+        <is>
+          <t>15 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N621" s="5" t="inlineStr"/>
+      <c r="O621" s="5" t="inlineStr"/>
+      <c r="P621" s="5" t="inlineStr"/>
+      <c r="Q621" s="5" t="inlineStr"/>
+      <c r="R621" s="5" t="inlineStr"/>
+      <c r="S621" s="5" t="inlineStr"/>
+      <c r="T621" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="U621" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V621" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D622" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F622" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle</t>
+        </is>
+      </c>
+      <c r="G622" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="H622" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I622" s="3" t="inlineStr"/>
+      <c r="J622" s="2" t="inlineStr"/>
+      <c r="K622" s="2" t="inlineStr"/>
+      <c r="L622" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="M622" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N622" s="2" t="inlineStr"/>
+      <c r="O622" s="2" t="inlineStr"/>
+      <c r="P622" s="2" t="inlineStr"/>
+      <c r="Q622" s="2" t="inlineStr"/>
+      <c r="R622" s="2" t="inlineStr"/>
+      <c r="S622" s="2" t="inlineStr"/>
+      <c r="T622" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="U622" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V622" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B623" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C623" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D623" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E623" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F623" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Educação</t>
+        </is>
+      </c>
+      <c r="G623" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029273-61gb</t>
+        </is>
+      </c>
+      <c r="H623" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I623" s="6" t="inlineStr"/>
+      <c r="J623" s="5" t="inlineStr"/>
+      <c r="K623" s="5" t="inlineStr"/>
+      <c r="L623" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="M623" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N623" s="5" t="inlineStr"/>
+      <c r="O623" s="5" t="inlineStr"/>
+      <c r="P623" s="5" t="inlineStr"/>
+      <c r="Q623" s="5" t="inlineStr"/>
+      <c r="R623" s="5" t="inlineStr"/>
+      <c r="S623" s="5" t="inlineStr"/>
+      <c r="T623" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vivae inclusa</t>
+        </is>
+      </c>
+      <c r="U623" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V623" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B624" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C624" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D624" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F624" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Entretenimento</t>
+        </is>
+      </c>
+      <c r="G624" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="H624" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="I624" s="3" t="inlineStr"/>
+      <c r="J624" s="2" t="inlineStr"/>
+      <c r="K624" s="2" t="inlineStr"/>
+      <c r="L624" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="M624" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N624" s="2" t="inlineStr"/>
+      <c r="O624" s="2" t="inlineStr"/>
+      <c r="P624" s="2" t="inlineStr"/>
+      <c r="Q624" s="2" t="inlineStr"/>
+      <c r="R624" s="2" t="inlineStr"/>
+      <c r="S624" s="2" t="inlineStr"/>
+      <c r="T624" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Vivo TV Inicial inclusa</t>
+        </is>
+      </c>
+      <c r="U624" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V624" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B625" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C625" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D625" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E625" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F625" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Música</t>
+        </is>
+      </c>
+      <c r="G625" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029313-61gb</t>
+        </is>
+      </c>
+      <c r="H625" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="I625" s="6" t="inlineStr"/>
+      <c r="J625" s="5" t="inlineStr"/>
+      <c r="K625" s="5" t="inlineStr"/>
+      <c r="L625" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="M625" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N625" s="5" t="inlineStr"/>
+      <c r="O625" s="5" t="inlineStr"/>
+      <c r="P625" s="5" t="inlineStr"/>
+      <c r="Q625" s="5" t="inlineStr"/>
+      <c r="R625" s="5" t="inlineStr"/>
+      <c r="S625" s="5" t="inlineStr"/>
+      <c r="T625" s="5" t="inlineStr">
+        <is>
+          <t>Apple Music Individual</t>
+        </is>
+      </c>
+      <c r="U625" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V625" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B626" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C626" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D626" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E626" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F626" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix</t>
+        </is>
+      </c>
+      <c r="G626" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="H626" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="I626" s="3" t="inlineStr"/>
+      <c r="J626" s="2" t="inlineStr"/>
+      <c r="K626" s="2" t="inlineStr"/>
+      <c r="L626" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="M626" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N626" s="2" t="inlineStr"/>
+      <c r="O626" s="2" t="inlineStr"/>
+      <c r="P626" s="2" t="inlineStr"/>
+      <c r="Q626" s="2" t="inlineStr"/>
+      <c r="R626" s="2" t="inlineStr"/>
+      <c r="S626" s="2" t="inlineStr"/>
+      <c r="T626" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão com anúncios</t>
+        </is>
+      </c>
+      <c r="U626" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V626" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B627" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C627" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D627" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E627" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F627" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Saúde</t>
+        </is>
+      </c>
+      <c r="G627" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029301-61gb</t>
+        </is>
+      </c>
+      <c r="H627" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I627" s="6" t="inlineStr"/>
+      <c r="J627" s="5" t="inlineStr"/>
+      <c r="K627" s="5" t="inlineStr"/>
+      <c r="L627" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="M627" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N627" s="5" t="inlineStr"/>
+      <c r="O627" s="5" t="inlineStr"/>
+      <c r="P627" s="5" t="inlineStr"/>
+      <c r="Q627" s="5" t="inlineStr"/>
+      <c r="R627" s="5" t="inlineStr"/>
+      <c r="S627" s="5" t="inlineStr"/>
+      <c r="T627" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Vale Saúde Sempre inclusa</t>
+        </is>
+      </c>
+      <c r="U627" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V627" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B628" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C628" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D628" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E628" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F628" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle Segurança</t>
+        </is>
+      </c>
+      <c r="G628" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029274-61gb</t>
+        </is>
+      </c>
+      <c r="H628" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I628" s="3" t="inlineStr"/>
+      <c r="J628" s="2" t="inlineStr"/>
+      <c r="K628" s="2" t="inlineStr"/>
+      <c r="L628" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="M628" s="2" t="inlineStr">
+        <is>
+          <t>20 GB de franquia 31 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N628" s="2" t="inlineStr"/>
+      <c r="O628" s="2" t="inlineStr"/>
+      <c r="P628" s="2" t="inlineStr"/>
+      <c r="Q628" s="2" t="inlineStr"/>
+      <c r="R628" s="2" t="inlineStr"/>
+      <c r="S628" s="2" t="inlineStr"/>
+      <c r="T628" s="2" t="inlineStr">
+        <is>
+          <t>Incluso Proteção Rua e Seguro de Bens</t>
+        </is>
+      </c>
+      <c r="U628" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
+        </is>
+      </c>
+      <c r="V628" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_control_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B629" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C629" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D629" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E629" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F629" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G629" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600032594-30gb</t>
+        </is>
+      </c>
+      <c r="H629" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="I629" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J629" s="5" t="inlineStr">
+        <is>
+          <t>preço sem fidelidade; fidelidade 12m no promo</t>
+        </is>
+      </c>
+      <c r="K629" s="5" t="inlineStr"/>
+      <c r="L629" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="M629" s="5" t="inlineStr">
+        <is>
+          <t>30 GB de franquia</t>
+        </is>
+      </c>
+      <c r="N629" s="5" t="inlineStr"/>
+      <c r="O629" s="5" t="inlineStr"/>
+      <c r="P629" s="5" t="inlineStr"/>
+      <c r="Q629" s="5" t="inlineStr"/>
+      <c r="R629" s="5" t="inlineStr"/>
+      <c r="S629" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="T629" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="U629" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="V629" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B630" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C630" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D630" s="2" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E630" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F630" s="2" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G630" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600032596-40gb</t>
+        </is>
+      </c>
+      <c r="H630" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="I630" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J630" s="2" t="inlineStr">
+        <is>
+          <t>preço sem fidelidade; fidelidade 12m no promo</t>
+        </is>
+      </c>
+      <c r="K630" s="2" t="inlineStr"/>
+      <c r="L630" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="M630" s="2" t="inlineStr">
+        <is>
+          <t>40 GB de franquia</t>
+        </is>
+      </c>
+      <c r="N630" s="2" t="inlineStr"/>
+      <c r="O630" s="2" t="inlineStr"/>
+      <c r="P630" s="2" t="inlineStr"/>
+      <c r="Q630" s="2" t="inlineStr"/>
+      <c r="R630" s="2" t="inlineStr"/>
+      <c r="S630" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="T630" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="U630" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="V630" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B631" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C631" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D631" s="5" t="inlineStr">
+        <is>
+          <t>lite</t>
+        </is>
+      </c>
+      <c r="E631" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F631" s="5" t="inlineStr">
+        <is>
+          <t>Easy Lite</t>
+        </is>
+      </c>
+      <c r="G631" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600032599-20gb</t>
+        </is>
+      </c>
+      <c r="H631" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="I631" s="6" t="inlineStr"/>
+      <c r="J631" s="5" t="inlineStr"/>
+      <c r="K631" s="5" t="inlineStr"/>
+      <c r="L631" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="M631" s="5" t="inlineStr">
+        <is>
+          <t>20 GB de franquia</t>
+        </is>
+      </c>
+      <c r="N631" s="5" t="inlineStr"/>
+      <c r="O631" s="5" t="inlineStr"/>
+      <c r="P631" s="5" t="inlineStr"/>
+      <c r="Q631" s="5" t="inlineStr"/>
+      <c r="R631" s="5" t="inlineStr"/>
+      <c r="S631" s="5" t="inlineStr"/>
+      <c r="T631" s="5" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="U631" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
+        </is>
+      </c>
+      <c r="V631" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_lite_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B632" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C632" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D632" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F632" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Amazon</t>
+        </is>
+      </c>
+      <c r="G632" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029255-60gb</t>
+        </is>
+      </c>
+      <c r="H632" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="I632" s="3" t="inlineStr"/>
+      <c r="J632" s="2" t="inlineStr"/>
+      <c r="K632" s="2" t="inlineStr"/>
+      <c r="L632" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M632" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N632" s="2" t="inlineStr"/>
+      <c r="O632" s="2" t="inlineStr"/>
+      <c r="P632" s="2" t="inlineStr"/>
+      <c r="Q632" s="2" t="inlineStr"/>
+      <c r="R632" s="2" t="inlineStr"/>
+      <c r="S632" s="2" t="inlineStr"/>
+      <c r="T632" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Amazon Prime inclusa</t>
+        </is>
+      </c>
+      <c r="U632" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="V632" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B633" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C633" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D633" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E633" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F633" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Disney+</t>
+        </is>
+      </c>
+      <c r="G633" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600022115-60gb</t>
+        </is>
+      </c>
+      <c r="H633" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I633" s="6" t="inlineStr"/>
+      <c r="J633" s="5" t="inlineStr"/>
+      <c r="K633" s="5" t="inlineStr"/>
+      <c r="L633" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="M633" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N633" s="5" t="inlineStr"/>
+      <c r="O633" s="5" t="inlineStr"/>
+      <c r="P633" s="5" t="inlineStr"/>
+      <c r="Q633" s="5" t="inlineStr"/>
+      <c r="R633" s="5" t="inlineStr">
+        <is>
+          <t>Disney+</t>
+        </is>
+      </c>
+      <c r="S633" s="5" t="inlineStr"/>
+      <c r="T633" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Disney+ Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="U633" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="V633" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B634" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C634" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D634" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E634" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F634" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Globoplay</t>
+        </is>
+      </c>
+      <c r="G634" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029246-60gb</t>
+        </is>
+      </c>
+      <c r="H634" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="I634" s="3" t="inlineStr"/>
+      <c r="J634" s="2" t="inlineStr"/>
+      <c r="K634" s="2" t="inlineStr"/>
+      <c r="L634" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M634" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N634" s="2" t="inlineStr"/>
+      <c r="O634" s="2" t="inlineStr"/>
+      <c r="P634" s="2" t="inlineStr"/>
+      <c r="Q634" s="2" t="inlineStr"/>
+      <c r="R634" s="2" t="inlineStr">
+        <is>
+          <t>Globoplay</t>
+        </is>
+      </c>
+      <c r="S634" s="2" t="inlineStr"/>
+      <c r="T634" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Globoplay inclusa</t>
+        </is>
+      </c>
+      <c r="U634" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="V634" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B635" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C635" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D635" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E635" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F635" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Netflix</t>
+        </is>
+      </c>
+      <c r="G635" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029234-60gb</t>
+        </is>
+      </c>
+      <c r="H635" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="I635" s="6" t="inlineStr"/>
+      <c r="J635" s="5" t="inlineStr"/>
+      <c r="K635" s="5" t="inlineStr"/>
+      <c r="L635" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="M635" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N635" s="5" t="inlineStr"/>
+      <c r="O635" s="5" t="inlineStr"/>
+      <c r="P635" s="5" t="inlineStr"/>
+      <c r="Q635" s="5" t="inlineStr"/>
+      <c r="R635" s="5" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="S635" s="5" t="inlineStr"/>
+      <c r="T635" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Netflix Padrão inclusa</t>
+        </is>
+      </c>
+      <c r="U635" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="V635" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B636" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C636" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D636" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E636" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F636" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Premiere</t>
+        </is>
+      </c>
+      <c r="G636" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029249-60gb</t>
+        </is>
+      </c>
+      <c r="H636" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I636" s="3" t="inlineStr"/>
+      <c r="J636" s="2" t="inlineStr"/>
+      <c r="K636" s="2" t="inlineStr"/>
+      <c r="L636" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M636" s="2" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N636" s="2" t="inlineStr"/>
+      <c r="O636" s="2" t="inlineStr"/>
+      <c r="P636" s="2" t="inlineStr"/>
+      <c r="Q636" s="2" t="inlineStr"/>
+      <c r="R636" s="2" t="inlineStr">
+        <is>
+          <t>Premiere</t>
+        </is>
+      </c>
+      <c r="S636" s="2" t="inlineStr"/>
+      <c r="T636" s="2" t="inlineStr">
+        <is>
+          <t>Assinatura Premiere inclusa</t>
+        </is>
+      </c>
+      <c r="U636" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="V636" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B637" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C637" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D637" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E637" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F637" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Spotify</t>
+        </is>
+      </c>
+      <c r="G637" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029229-60gb</t>
+        </is>
+      </c>
+      <c r="H637" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="I637" s="6" t="inlineStr"/>
+      <c r="J637" s="5" t="inlineStr"/>
+      <c r="K637" s="5" t="inlineStr"/>
+      <c r="L637" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="M637" s="5" t="inlineStr">
+        <is>
+          <t>50 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N637" s="5" t="inlineStr"/>
+      <c r="O637" s="5" t="inlineStr"/>
+      <c r="P637" s="5" t="inlineStr"/>
+      <c r="Q637" s="5" t="inlineStr"/>
+      <c r="R637" s="5" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="S637" s="5" t="inlineStr"/>
+      <c r="T637" s="5" t="inlineStr">
+        <is>
+          <t>Assinatura Spotify Premium inclusa</t>
+        </is>
+      </c>
+      <c r="U637" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="V637" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B638" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C638" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D638" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E638" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F638" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós com Travel</t>
+        </is>
+      </c>
+      <c r="G638" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029244-70gb</t>
+        </is>
+      </c>
+      <c r="H638" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="I638" s="3" t="inlineStr"/>
+      <c r="J638" s="2" t="inlineStr"/>
+      <c r="K638" s="2" t="inlineStr"/>
+      <c r="L638" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="M638" s="2" t="inlineStr">
+        <is>
+          <t>60 GB de franquia 10 GB de bônus</t>
+        </is>
+      </c>
+      <c r="N638" s="2" t="inlineStr"/>
+      <c r="O638" s="2" t="inlineStr"/>
+      <c r="P638" s="2" t="inlineStr"/>
+      <c r="Q638" s="2" t="inlineStr"/>
+      <c r="R638" s="2" t="inlineStr"/>
+      <c r="S638" s="2" t="inlineStr"/>
+      <c r="T638" s="2" t="inlineStr">
+        <is>
+          <t>2 meses de YouTube sem consumo no plano</t>
+        </is>
+      </c>
+      <c r="U638" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
+        </is>
+      </c>
+      <c r="V638" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_postpaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B639" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C639" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D639" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E639" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F639" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G639" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-25gb</t>
+        </is>
+      </c>
+      <c r="H639" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I639" s="6" t="inlineStr"/>
+      <c r="J639" s="5" t="inlineStr"/>
+      <c r="K639" s="5" t="inlineStr"/>
+      <c r="L639" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="M639" s="5" t="inlineStr">
+        <is>
+          <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
+        </is>
+      </c>
+      <c r="N639" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="O639" s="5" t="inlineStr"/>
+      <c r="P639" s="5" t="inlineStr"/>
+      <c r="Q639" s="5" t="inlineStr"/>
+      <c r="R639" s="5" t="inlineStr"/>
+      <c r="S639" s="5" t="inlineStr"/>
+      <c r="T639" s="5" t="inlineStr"/>
+      <c r="U639" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="V639" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C640" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D640" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E640" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F640" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G640" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-9gb</t>
+        </is>
+      </c>
+      <c r="H640" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I640" s="3" t="inlineStr"/>
+      <c r="J640" s="2" t="inlineStr"/>
+      <c r="K640" s="2" t="inlineStr"/>
+      <c r="L640" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M640" s="2" t="inlineStr">
+        <is>
+          <t>6 GB para navegar como quiser 3 GB para navegar no YouTube</t>
+        </is>
+      </c>
+      <c r="N640" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="O640" s="2" t="inlineStr"/>
+      <c r="P640" s="2" t="inlineStr"/>
+      <c r="Q640" s="2" t="inlineStr"/>
+      <c r="R640" s="2" t="inlineStr"/>
+      <c r="S640" s="2" t="inlineStr"/>
+      <c r="T640" s="2" t="inlineStr"/>
+      <c r="U640" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="V640" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B641" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C641" s="5" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D641" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E641" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F641" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G641" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-5gb</t>
+        </is>
+      </c>
+      <c r="H641" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I641" s="6" t="inlineStr"/>
+      <c r="J641" s="5" t="inlineStr"/>
+      <c r="K641" s="5" t="inlineStr"/>
+      <c r="L641" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M641" s="5" t="inlineStr">
+        <is>
+          <t>5 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="N641" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="O641" s="5" t="inlineStr"/>
+      <c r="P641" s="5" t="inlineStr"/>
+      <c r="Q641" s="5" t="inlineStr"/>
+      <c r="R641" s="5" t="inlineStr"/>
+      <c r="S641" s="5" t="inlineStr"/>
+      <c r="T641" s="5" t="inlineStr"/>
+      <c r="U641" s="5" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="V641" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B642" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T17:00:50</t>
+        </is>
+      </c>
+      <c r="C642" s="2" t="inlineStr">
+        <is>
+          <t>vivo</t>
+        </is>
+      </c>
+      <c r="D642" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E642" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F642" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pré</t>
+        </is>
+      </c>
+      <c r="G642" s="2" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029370-4gb</t>
+        </is>
+      </c>
+      <c r="H642" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I642" s="3" t="inlineStr"/>
+      <c r="J642" s="2" t="inlineStr"/>
+      <c r="K642" s="2" t="inlineStr"/>
+      <c r="L642" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M642" s="2" t="inlineStr">
+        <is>
+          <t>4 GB para navegar como quiser</t>
+        </is>
+      </c>
+      <c r="N642" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O642" s="2" t="inlineStr"/>
+      <c r="P642" s="2" t="inlineStr"/>
+      <c r="Q642" s="2" t="inlineStr"/>
+      <c r="R642" s="2" t="inlineStr"/>
+      <c r="S642" s="2" t="inlineStr"/>
+      <c r="T642" s="2" t="inlineStr"/>
+      <c r="U642" s="2" t="inlineStr">
+        <is>
+          <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
+        </is>
+      </c>
+      <c r="V642" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/vivo_prepaid_SP.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V586"/>
+  <autoFilter ref="A1:V642"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43322,12 +47286,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -43400,12 +47364,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -43472,12 +47436,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -43544,12 +47508,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -43616,12 +47580,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -43688,12 +47652,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -43760,12 +47724,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -43832,12 +47796,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -43904,12 +47868,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -43976,12 +47940,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -44048,12 +48012,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -44120,12 +48084,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -44192,12 +48156,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -44262,12 +48226,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -44332,12 +48296,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -44402,12 +48366,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -44472,12 +48436,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -44542,12 +48506,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -44612,12 +48576,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -44682,12 +48646,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -44746,12 +48710,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -44810,12 +48774,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -44874,12 +48838,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -44938,12 +48902,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -45000,12 +48964,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -45068,12 +49032,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -45136,12 +49100,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -45204,12 +49168,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -45272,12 +49236,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -45340,12 +49304,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -45408,12 +49372,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -45476,12 +49440,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -45542,12 +49506,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -45608,12 +49572,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -45674,12 +49638,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -45746,12 +49710,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -45776,17 +49740,17 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029300-51gb</t>
+          <t>vivo:VIV202600029300-61gb</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I37" s="6" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr"/>
       <c r="K37" s="5" t="inlineStr"/>
       <c r="L37" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
@@ -45818,12 +49782,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -45848,17 +49812,17 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029273-51gb</t>
+          <t>vivo:VIV202600029273-61gb</t>
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -45890,12 +49854,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -45920,17 +49884,17 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029307-51gb</t>
+          <t>vivo:VIV202600029307-61gb</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I39" s="6" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
       <c r="K39" s="5" t="inlineStr"/>
       <c r="L39" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
@@ -45962,12 +49926,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -45992,17 +49956,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029313-51gb</t>
+          <t>vivo:VIV202600029313-61gb</t>
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I40" s="3" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -46034,12 +49998,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -46064,17 +50028,17 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029308-51gb</t>
+          <t>vivo:VIV202600029308-61gb</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I41" s="6" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
       <c r="K41" s="5" t="inlineStr"/>
       <c r="L41" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
@@ -46106,12 +50070,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -46136,17 +50100,17 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029301-51gb</t>
+          <t>vivo:VIV202600029301-61gb</t>
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -46178,12 +50142,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -46208,17 +50172,17 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029274-51gb</t>
+          <t>vivo:VIV202600029274-61gb</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I43" s="6" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="5" t="inlineStr"/>
       <c r="L43" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
@@ -46250,12 +50214,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -46330,12 +50294,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -46410,12 +50374,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -46482,12 +50446,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -46554,12 +50518,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -46630,12 +50594,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -46706,12 +50670,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -46782,12 +50746,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -46858,12 +50822,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -46934,12 +50898,12 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -47006,12 +50970,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -47076,12 +51040,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -47146,12 +51110,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -47216,12 +51180,12 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -47397,7 +51361,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029273-51gb</t>
+          <t>vivo:VIV202600029273-61gb</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -47407,7 +51371,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I2" s="3" t="inlineStr"/>
     </row>
@@ -47434,7 +51398,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029274-51gb</t>
+          <t>vivo:VIV202600029274-61gb</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -47444,7 +51408,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr"/>
       <c r="H3" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I3" s="6" t="inlineStr"/>
     </row>
@@ -47471,7 +51435,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029300-51gb</t>
+          <t>vivo:VIV202600029300-61gb</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -47481,7 +51445,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
@@ -47508,7 +51472,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029301-51gb</t>
+          <t>vivo:VIV202600029301-61gb</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -47518,7 +51482,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr"/>
       <c r="H5" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I5" s="6" t="inlineStr"/>
     </row>
@@ -47545,7 +51509,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029307-51gb</t>
+          <t>vivo:VIV202600029307-61gb</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -47555,7 +51519,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
@@ -47582,7 +51546,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029308-51gb</t>
+          <t>vivo:VIV202600029308-61gb</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -47592,7 +51556,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I7" s="6" t="inlineStr"/>
     </row>
@@ -47619,7 +51583,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029313-51gb</t>
+          <t>vivo:VIV202600029313-61gb</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -47629,7 +51593,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
@@ -47656,7 +51620,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029273-61gb</t>
+          <t>vivo:VIV202600029273-51gb</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -47665,7 +51629,7 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" s="6" t="inlineStr"/>
@@ -47693,7 +51657,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029274-61gb</t>
+          <t>vivo:VIV202600029274-51gb</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -47702,7 +51666,7 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr"/>
@@ -47730,7 +51694,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029300-61gb</t>
+          <t>vivo:VIV202600029300-51gb</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -47739,7 +51703,7 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H11" s="6" t="inlineStr"/>
       <c r="I11" s="6" t="inlineStr"/>
@@ -47767,7 +51731,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029301-61gb</t>
+          <t>vivo:VIV202600029301-51gb</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -47776,7 +51740,7 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="3" t="inlineStr"/>
@@ -47804,7 +51768,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029307-61gb</t>
+          <t>vivo:VIV202600029307-51gb</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -47813,7 +51777,7 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" s="6" t="inlineStr"/>
@@ -47841,7 +51805,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029308-61gb</t>
+          <t>vivo:VIV202600029308-51gb</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -47850,7 +51814,7 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr"/>
@@ -47878,7 +51842,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029313-61gb</t>
+          <t>vivo:VIV202600029313-51gb</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -47887,7 +51851,7 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H15" s="6" t="inlineStr"/>
       <c r="I15" s="6" t="inlineStr"/>
@@ -47929,7 +51893,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T22:04:41</t>
+          <t>2026-07-03T17:00:50</t>
         </is>
       </c>
     </row>
@@ -47941,7 +51905,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -47962,7 +51926,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -48008,7 +51972,7 @@
       </c>
       <c r="D9" s="10">
         <f>IFERROR(AVERAGEIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
-        <v>97.09</v>
+        <v>98.68</v>
       </c>
       <c r="E9" s="10">
         <f>IFERROR(_xlfn.MAXIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
@@ -48073,7 +52037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -48206,15 +52170,15 @@
         <v>59.9</v>
       </c>
       <c r="E3" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))),"")</f>
         <v>119.99</v>
       </c>
       <c r="F3" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))),"")</f>
         <v>150</v>
       </c>
       <c r="G3" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A3)&amp;"-"&amp;TEXT(MONTH($A3),"00")&amp;"-"&amp;TEXT(DAY($A3),"00"))),"")</f>
         <v>124.9</v>
       </c>
       <c r="H3" s="3">
@@ -48259,15 +52223,15 @@
         <v>59.9</v>
       </c>
       <c r="E4" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))),"")</f>
         <v>119.99</v>
       </c>
       <c r="F4" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))),"")</f>
         <v>150</v>
       </c>
       <c r="G4" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A4)&amp;"-"&amp;TEXT(MONTH($A4),"00")&amp;"-"&amp;TEXT(DAY($A4),"00"))),"")</f>
         <v>124.9</v>
       </c>
       <c r="H4" s="3">
@@ -48312,15 +52276,15 @@
         <v>59.9</v>
       </c>
       <c r="E5" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))),"")</f>
         <v>119.99</v>
       </c>
       <c r="F5" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))),"")</f>
         <v>150</v>
       </c>
       <c r="G5" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A5)&amp;"-"&amp;TEXT(MONTH($A5),"00")&amp;"-"&amp;TEXT(DAY($A5),"00"))),"")</f>
         <v>124.9</v>
       </c>
       <c r="H5" s="3">
@@ -48365,15 +52329,15 @@
         <v>59.9</v>
       </c>
       <c r="E6" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))),"")</f>
         <v>119.99</v>
       </c>
       <c r="F6" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))),"")</f>
         <v>150</v>
       </c>
       <c r="G6" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A6)&amp;"-"&amp;TEXT(MONTH($A6),"00")&amp;"-"&amp;TEXT(DAY($A6),"00"))),"")</f>
         <v>124.9</v>
       </c>
       <c r="H6" s="3">
@@ -48418,15 +52382,15 @@
         <v>59.9</v>
       </c>
       <c r="E7" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))),"")</f>
         <v>119.99</v>
       </c>
       <c r="F7" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))),"")</f>
         <v>150</v>
       </c>
       <c r="G7" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A7)&amp;"-"&amp;TEXT(MONTH($A7),"00")&amp;"-"&amp;TEXT(DAY($A7),"00"))),"")</f>
         <v>124.9</v>
       </c>
       <c r="H7" s="3">
@@ -48471,15 +52435,15 @@
         <v>59.9</v>
       </c>
       <c r="E8" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
         <v>119.99</v>
       </c>
       <c r="F8" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
         <v>150</v>
       </c>
       <c r="G8" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A8)&amp;"-"&amp;TEXT(MONTH($A8),"00")&amp;"-"&amp;TEXT(DAY($A8),"00"))),"")</f>
         <v>124.9</v>
       </c>
       <c r="H8" s="3">
@@ -48524,15 +52488,15 @@
         <v>59.9</v>
       </c>
       <c r="E9" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
         <v>119.99</v>
       </c>
       <c r="F9" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
         <v>150</v>
       </c>
       <c r="G9" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A9)&amp;"-"&amp;TEXT(MONTH($A9),"00")&amp;"-"&amp;TEXT(DAY($A9),"00"))),"")</f>
         <v>124.9</v>
       </c>
       <c r="H9" s="3">
@@ -48577,15 +52541,15 @@
         <v>59.9</v>
       </c>
       <c r="E10" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
         <v>119.99</v>
       </c>
       <c r="F10" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
         <v>150</v>
       </c>
       <c r="G10" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A10)&amp;"-"&amp;TEXT(MONTH($A10),"00")&amp;"-"&amp;TEXT(DAY($A10),"00"))),"")</f>
         <v>124.9</v>
       </c>
       <c r="H10" s="3">
@@ -48630,15 +52594,15 @@
         <v>59.9</v>
       </c>
       <c r="E11" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
         <v>119.99</v>
       </c>
       <c r="F11" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
         <v>150</v>
       </c>
       <c r="G11" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A11)&amp;"-"&amp;TEXT(MONTH($A11),"00")&amp;"-"&amp;TEXT(DAY($A11),"00"))),"")</f>
         <v>124.9</v>
       </c>
       <c r="H11" s="3">
@@ -48683,15 +52647,15 @@
         <v>59.9</v>
       </c>
       <c r="E12" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
-        <v>129.99</v>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))),"")</f>
+        <v>119.99</v>
       </c>
       <c r="F12" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))),"")</f>
         <v>150</v>
       </c>
       <c r="G12" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A12)&amp;"-"&amp;TEXT(MONTH($A12),"00")&amp;"-"&amp;TEXT(DAY($A12),"00"))),"")</f>
         <v>124.9</v>
       </c>
       <c r="H12" s="3">
@@ -48736,15 +52700,15 @@
         <v>59.9</v>
       </c>
       <c r="E13" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
-        <v>129.99</v>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"))),"")</f>
+        <v>119.99</v>
       </c>
       <c r="F13" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"))),"")</f>
         <v>150</v>
       </c>
       <c r="G13" s="3">
-        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$K:$K,"&lt;&gt;credit_card")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"),history!$K:$K,"&lt;&gt;credit_card")),"")</f>
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A13)&amp;"-"&amp;TEXT(MONTH($A13),"00")&amp;"-"&amp;TEXT(DAY($A13),"00"))),"")</f>
         <v>124.9</v>
       </c>
       <c r="H13" s="3">
@@ -48772,17 +52736,70 @@
         <v>44.9</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Rows = day: each cell = cheapest R$ that carrier offered in the category on that snapshot_date — a live MINIFS over `history` matching the EXACT date (a locale-safe text date built from the row's date, since history stores dates as TEXT — CONTEXT §7). Pre = cheapest 30-day prepaid plan (validity_days &gt;= 28; pre-#18 dates have no validity → blank, fills from 26-Jun on). Digital = min of Vivo Lite / Claro Flex. Heatmap = per-category-block green→yellow (each cell vs all carriers in its category; subtle while prices are near-flat, differentiates as they move). Grows one row per day; charts on the `Charts` sheet.</t>
-        </is>
+    <row r="14">
+      <c r="A14" s="12" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B14" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"))),"")</f>
+        <v>58.99</v>
+      </c>
+      <c r="C14" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"))),"")</f>
+        <v>59</v>
+      </c>
+      <c r="D14" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"))),"")</f>
+        <v>59.9</v>
+      </c>
+      <c r="E14" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"))),"")</f>
+        <v>119.99</v>
+      </c>
+      <c r="F14" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"))),"")</f>
+        <v>150</v>
+      </c>
+      <c r="G14" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"))=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"))),"")</f>
+        <v>124.9</v>
+      </c>
+      <c r="H14" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"),history!$N:$N,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"),history!$N:$N,"&gt;=28")),"")</f>
+        <v>30</v>
+      </c>
+      <c r="I14" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"),history!$N:$N,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"),history!$N:$N,"&gt;=28")),"")</f>
+        <v>30</v>
+      </c>
+      <c r="J14" s="3">
+        <f>IFERROR(IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"),history!$N:$N,"&gt;=28")=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"),history!$N:$N,"&gt;=28")),"")</f>
+        <v>30</v>
+      </c>
+      <c r="K14" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00")),0)),"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00")),0)),"")</f>
+        <v>45</v>
+      </c>
+      <c r="M14" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00"),history!$S:$S,"&gt;0"),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,YEAR($A14)&amp;"-"&amp;TEXT(MONTH($A14),"00")&amp;"-"&amp;TEXT(DAY($A14),"00")),0)),"")</f>
+        <v>44.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Post — TIM: the entry-level price is the cheapest BILL-payment plan (R$129,99), not the R$119,99 credit-card-only plan — credit-card-only plans have low adoption, so they are excluded from the entry-level comparison (JPMorgan methodology). All TIM plans still appear in `history` + the TIM sheet.</t>
+          <t>Rows = day: each cell = cheapest R$ that carrier offered in the category on that snapshot_date — a live MINIFS over `history` matching the EXACT date (a locale-safe text date built from the row's date, since history stores dates as TEXT — CONTEXT §7). Pre = cheapest 30-day prepaid plan (validity_days &gt;= 28; pre-#18 dates have no validity → blank, fills from 26-Jun on). Digital = min of Vivo Lite / Claro Flex. Heatmap = per-category-block green→yellow (each cell vs all carriers in its category; subtle while prices are near-flat, differentiates as they move). Grows one row per day; charts on the `Charts` sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Post — TIM: the entry-level tracked is the cheapest postpaid plan, R$119,99 — note it is CREDIT-CARD-only ("no cartão"; TIM's Express line); the cheapest bill-payment ("na fatura") plan is R$129,99. Both are in `history` + the TIM sheet, with the billing type in `payment_method` — a price change on the tracked plan shows in `changes` and the daily alert.</t>
         </is>
       </c>
     </row>
@@ -48794,7 +52811,7 @@
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="K1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:D13">
+  <conditionalFormatting sqref="B3:D14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -48804,7 +52821,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:G13">
+  <conditionalFormatting sqref="E3:G14">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -48814,7 +52831,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:J13">
+  <conditionalFormatting sqref="H3:J14">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -48824,7 +52841,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:M13">
+  <conditionalFormatting sqref="K3:M14">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -48890,15 +52907,15 @@
         </is>
       </c>
       <c r="Q38" s="10">
-        <f>IF('comparison'!B13="",NA(),'comparison'!B13)</f>
+        <f>IF('comparison'!B14="",NA(),'comparison'!B14)</f>
         <v/>
       </c>
       <c r="R38" s="10">
-        <f>IF('comparison'!C13="",NA(),'comparison'!C13)</f>
+        <f>IF('comparison'!C14="",NA(),'comparison'!C14)</f>
         <v/>
       </c>
       <c r="S38" s="10">
-        <f>IF('comparison'!D13="",NA(),'comparison'!D13)</f>
+        <f>IF('comparison'!D14="",NA(),'comparison'!D14)</f>
         <v/>
       </c>
     </row>
@@ -48909,15 +52926,15 @@
         </is>
       </c>
       <c r="Q39" s="10">
-        <f>IF('comparison'!E13="",NA(),'comparison'!E13)</f>
+        <f>IF('comparison'!E14="",NA(),'comparison'!E14)</f>
         <v/>
       </c>
       <c r="R39" s="10">
-        <f>IF('comparison'!F13="",NA(),'comparison'!F13)</f>
+        <f>IF('comparison'!F14="",NA(),'comparison'!F14)</f>
         <v/>
       </c>
       <c r="S39" s="10">
-        <f>IF('comparison'!G13="",NA(),'comparison'!G13)</f>
+        <f>IF('comparison'!G14="",NA(),'comparison'!G14)</f>
         <v/>
       </c>
     </row>
@@ -48928,15 +52945,15 @@
         </is>
       </c>
       <c r="Q40" s="10">
-        <f>IF('comparison'!H13="",NA(),'comparison'!H13)</f>
+        <f>IF('comparison'!H14="",NA(),'comparison'!H14)</f>
         <v/>
       </c>
       <c r="R40" s="10">
-        <f>IF('comparison'!I13="",NA(),'comparison'!I13)</f>
+        <f>IF('comparison'!I14="",NA(),'comparison'!I14)</f>
         <v/>
       </c>
       <c r="S40" s="10">
-        <f>IF('comparison'!J13="",NA(),'comparison'!J13)</f>
+        <f>IF('comparison'!J14="",NA(),'comparison'!J14)</f>
         <v/>
       </c>
     </row>
@@ -48947,15 +52964,15 @@
         </is>
       </c>
       <c r="Q41" s="10">
-        <f>IF('comparison'!K13="",NA(),'comparison'!K13)</f>
+        <f>IF('comparison'!K14="",NA(),'comparison'!K14)</f>
         <v/>
       </c>
       <c r="R41" s="10">
-        <f>IF('comparison'!L13="",NA(),'comparison'!L13)</f>
+        <f>IF('comparison'!L14="",NA(),'comparison'!L14)</f>
         <v/>
       </c>
       <c r="S41" s="10">
-        <f>IF('comparison'!M13="",NA(),'comparison'!M13)</f>
+        <f>IF('comparison'!M14="",NA(),'comparison'!M14)</f>
         <v/>
       </c>
     </row>
@@ -49302,7 +53319,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>69.90000000000001</v>
@@ -49312,7 +53329,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle (51GB)</t>
+          <t>Vivo Controle (61GB)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -49331,7 +53348,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>99.90000000000001</v>
@@ -49341,7 +53358,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Educação (51GB)</t>
+          <t>Vivo Controle Educação (61GB)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -49360,7 +53377,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C18" s="15" t="n"/>
       <c r="D18" s="6" t="n">
@@ -49368,7 +53385,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Saúde (51GB)</t>
+          <t>Vivo Controle Saúde (61GB)</t>
         </is>
       </c>
       <c r="F18" s="15" t="n"/>
@@ -49383,14 +53400,14 @@
         <v>5</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>84.98999999999999</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Segurança (51GB)</t>
+          <t>Vivo Controle Segurança (61GB)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -49404,13 +53421,13 @@
         <v>6</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C20" s="15" t="n"/>
       <c r="D20" s="15" t="n"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Música (51GB)</t>
+          <t>Vivo Controle Música (61GB)</t>
         </is>
       </c>
       <c r="F20" s="15" t="n"/>
@@ -49421,11 +53438,11 @@
         <v>7</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Netflix (51GB)</t>
+          <t>Vivo Controle Netflix (61GB)</t>
         </is>
       </c>
     </row>
@@ -49434,13 +53451,13 @@
         <v>8</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C22" s="15" t="n"/>
       <c r="D22" s="15" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Vivo Controle Entretenimento (51GB)</t>
+          <t>Vivo Controle Entretenimento (61GB)</t>
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
@@ -50157,12 +54174,12 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E12" s="5" t="n"/>
@@ -50181,12 +54198,12 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -50205,12 +54222,12 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E14" s="5" t="n"/>
@@ -50229,12 +54246,12 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -50253,12 +54270,12 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E16" s="5" t="n"/>
@@ -50277,12 +54294,12 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
@@ -50301,12 +54318,12 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E18" s="5" t="n"/>

--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -42734,7 +42734,7 @@
       </c>
       <c r="B587" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C587" s="5" t="inlineStr">
@@ -42812,7 +42812,7 @@
       </c>
       <c r="B588" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C588" s="2" t="inlineStr">
@@ -42884,7 +42884,7 @@
       </c>
       <c r="B589" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C589" s="5" t="inlineStr">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="B590" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C590" s="2" t="inlineStr">
@@ -43028,7 +43028,7 @@
       </c>
       <c r="B591" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C591" s="5" t="inlineStr">
@@ -43100,7 +43100,7 @@
       </c>
       <c r="B592" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C592" s="2" t="inlineStr">
@@ -43172,7 +43172,7 @@
       </c>
       <c r="B593" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C593" s="5" t="inlineStr">
@@ -43244,7 +43244,7 @@
       </c>
       <c r="B594" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C594" s="2" t="inlineStr">
@@ -43316,7 +43316,7 @@
       </c>
       <c r="B595" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C595" s="5" t="inlineStr">
@@ -43388,7 +43388,7 @@
       </c>
       <c r="B596" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C596" s="2" t="inlineStr">
@@ -43460,7 +43460,7 @@
       </c>
       <c r="B597" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C597" s="5" t="inlineStr">
@@ -43532,7 +43532,7 @@
       </c>
       <c r="B598" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C598" s="2" t="inlineStr">
@@ -43604,7 +43604,7 @@
       </c>
       <c r="B599" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C599" s="5" t="inlineStr">
@@ -43674,7 +43674,7 @@
       </c>
       <c r="B600" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C600" s="2" t="inlineStr">
@@ -43744,7 +43744,7 @@
       </c>
       <c r="B601" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C601" s="5" t="inlineStr">
@@ -43814,7 +43814,7 @@
       </c>
       <c r="B602" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C602" s="2" t="inlineStr">
@@ -43884,7 +43884,7 @@
       </c>
       <c r="B603" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C603" s="5" t="inlineStr">
@@ -43954,7 +43954,7 @@
       </c>
       <c r="B604" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C604" s="2" t="inlineStr">
@@ -44024,7 +44024,7 @@
       </c>
       <c r="B605" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C605" s="5" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="B606" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C606" s="2" t="inlineStr">
@@ -44158,7 +44158,7 @@
       </c>
       <c r="B607" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C607" s="5" t="inlineStr">
@@ -44222,7 +44222,7 @@
       </c>
       <c r="B608" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C608" s="2" t="inlineStr">
@@ -44286,7 +44286,7 @@
       </c>
       <c r="B609" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C609" s="5" t="inlineStr">
@@ -44350,7 +44350,7 @@
       </c>
       <c r="B610" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C610" s="2" t="inlineStr">
@@ -44412,7 +44412,7 @@
       </c>
       <c r="B611" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C611" s="5" t="inlineStr">
@@ -44480,7 +44480,7 @@
       </c>
       <c r="B612" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C612" s="2" t="inlineStr">
@@ -44548,7 +44548,7 @@
       </c>
       <c r="B613" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C613" s="5" t="inlineStr">
@@ -44616,7 +44616,7 @@
       </c>
       <c r="B614" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C614" s="2" t="inlineStr">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="B615" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C615" s="5" t="inlineStr">
@@ -44752,7 +44752,7 @@
       </c>
       <c r="B616" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C616" s="2" t="inlineStr">
@@ -44820,7 +44820,7 @@
       </c>
       <c r="B617" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C617" s="5" t="inlineStr">
@@ -44888,7 +44888,7 @@
       </c>
       <c r="B618" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C618" s="2" t="inlineStr">
@@ -44954,7 +44954,7 @@
       </c>
       <c r="B619" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C619" s="5" t="inlineStr">
@@ -45020,7 +45020,7 @@
       </c>
       <c r="B620" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C620" s="2" t="inlineStr">
@@ -45086,7 +45086,7 @@
       </c>
       <c r="B621" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C621" s="5" t="inlineStr">
@@ -45158,7 +45158,7 @@
       </c>
       <c r="B622" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C622" s="2" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="B623" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C623" s="5" t="inlineStr">
@@ -45302,7 +45302,7 @@
       </c>
       <c r="B624" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C624" s="2" t="inlineStr">
@@ -45374,7 +45374,7 @@
       </c>
       <c r="B625" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C625" s="5" t="inlineStr">
@@ -45446,7 +45446,7 @@
       </c>
       <c r="B626" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C626" s="2" t="inlineStr">
@@ -45518,7 +45518,7 @@
       </c>
       <c r="B627" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C627" s="5" t="inlineStr">
@@ -45590,7 +45590,7 @@
       </c>
       <c r="B628" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C628" s="2" t="inlineStr">
@@ -45662,7 +45662,7 @@
       </c>
       <c r="B629" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C629" s="5" t="inlineStr">
@@ -45742,7 +45742,7 @@
       </c>
       <c r="B630" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C630" s="2" t="inlineStr">
@@ -45822,7 +45822,7 @@
       </c>
       <c r="B631" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C631" s="5" t="inlineStr">
@@ -45894,7 +45894,7 @@
       </c>
       <c r="B632" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C632" s="2" t="inlineStr">
@@ -45966,7 +45966,7 @@
       </c>
       <c r="B633" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C633" s="5" t="inlineStr">
@@ -46042,7 +46042,7 @@
       </c>
       <c r="B634" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C634" s="2" t="inlineStr">
@@ -46118,7 +46118,7 @@
       </c>
       <c r="B635" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C635" s="5" t="inlineStr">
@@ -46194,7 +46194,7 @@
       </c>
       <c r="B636" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C636" s="2" t="inlineStr">
@@ -46270,7 +46270,7 @@
       </c>
       <c r="B637" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C637" s="5" t="inlineStr">
@@ -46346,7 +46346,7 @@
       </c>
       <c r="B638" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C638" s="2" t="inlineStr">
@@ -46418,7 +46418,7 @@
       </c>
       <c r="B639" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C639" s="5" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="B640" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C640" s="2" t="inlineStr">
@@ -46558,7 +46558,7 @@
       </c>
       <c r="B641" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C641" s="5" t="inlineStr">
@@ -46628,7 +46628,7 @@
       </c>
       <c r="B642" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C642" s="2" t="inlineStr">
@@ -47291,7 +47291,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -47369,7 +47369,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -47441,7 +47441,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -47513,7 +47513,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -47585,7 +47585,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -47657,7 +47657,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -47729,7 +47729,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -47801,7 +47801,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -47873,7 +47873,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -47945,7 +47945,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -48017,7 +48017,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -48089,7 +48089,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -48161,7 +48161,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -48231,7 +48231,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -48301,7 +48301,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -48371,7 +48371,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -48511,7 +48511,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -48581,7 +48581,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -48651,7 +48651,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -48715,7 +48715,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -48779,7 +48779,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -48843,7 +48843,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -48907,7 +48907,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -48969,7 +48969,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -49037,7 +49037,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -49105,7 +49105,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -49173,7 +49173,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -49241,7 +49241,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -49309,7 +49309,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -49377,7 +49377,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -49445,7 +49445,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -49511,7 +49511,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -49577,7 +49577,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -49643,7 +49643,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -49715,7 +49715,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -49787,7 +49787,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -49859,7 +49859,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -49931,7 +49931,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -50075,7 +50075,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -50147,7 +50147,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -50219,7 +50219,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -50299,7 +50299,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -50379,7 +50379,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -50451,7 +50451,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -50523,7 +50523,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -50599,7 +50599,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -50675,7 +50675,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -50751,7 +50751,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -50827,7 +50827,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -50903,7 +50903,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -50975,7 +50975,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -51045,7 +51045,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -51115,7 +51115,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -51893,7 +51893,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T17:00:50</t>
+          <t>2026-07-03T22:03:07</t>
         </is>
       </c>
     </row>

--- a/projects/mobile-price-tracker/data/mobile_plans.xlsx
+++ b/projects/mobile-price-tracker/data/mobile_plans.xlsx
@@ -19,7 +19,7 @@
     <sheet name="TIM" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$V$642</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$V$698</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$V$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -300,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$14</f>
+              <f>'comparison'!$A$3:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$B$3:$B$14</f>
+              <f>'comparison'!$B$3:$B$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -337,12 +337,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$14</f>
+              <f>'comparison'!$A$3:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$C$3:$C$14</f>
+              <f>'comparison'!$C$3:$C$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -374,12 +374,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$14</f>
+              <f>'comparison'!$A$3:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$D$3:$D$14</f>
+              <f>'comparison'!$D$3:$D$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -508,12 +508,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$14</f>
+              <f>'comparison'!$A$3:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$E$3:$E$14</f>
+              <f>'comparison'!$E$3:$E$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -545,12 +545,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$14</f>
+              <f>'comparison'!$A$3:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$F$3:$F$14</f>
+              <f>'comparison'!$F$3:$F$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -582,12 +582,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$14</f>
+              <f>'comparison'!$A$3:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$G$3:$G$14</f>
+              <f>'comparison'!$G$3:$G$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$14</f>
+              <f>'comparison'!$A$3:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$H$3:$H$14</f>
+              <f>'comparison'!$H$3:$H$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -753,12 +753,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$14</f>
+              <f>'comparison'!$A$3:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$I$3:$I$14</f>
+              <f>'comparison'!$I$3:$I$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -790,12 +790,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$14</f>
+              <f>'comparison'!$A$3:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$J$3:$J$14</f>
+              <f>'comparison'!$J$3:$J$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -924,12 +924,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$14</f>
+              <f>'comparison'!$A$3:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$K$3:$K$14</f>
+              <f>'comparison'!$K$3:$K$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -961,12 +961,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$14</f>
+              <f>'comparison'!$A$3:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$L$3:$L$14</f>
+              <f>'comparison'!$L$3:$L$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -998,12 +998,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'comparison'!$A$3:$A$14</f>
+              <f>'comparison'!$A$3:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'comparison'!$M$3:$M$14</f>
+              <f>'comparison'!$M$3:$M$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1655,7 +1655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V642"/>
+  <dimension ref="A1:V698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -46690,8 +46690,3972 @@
         </is>
       </c>
     </row>
+    <row r="643">
+      <c r="A643" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B643" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C643" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D643" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E643" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F643" s="5" t="inlineStr">
+        <is>
+          <t>Controle 25GB</t>
+        </is>
+      </c>
+      <c r="G643" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-25gb</t>
+        </is>
+      </c>
+      <c r="H643" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I643" s="6" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="J643" s="5" t="inlineStr">
+        <is>
+          <t>De R$ 59,90 Por:</t>
+        </is>
+      </c>
+      <c r="K643" s="5" t="inlineStr"/>
+      <c r="L643" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="M643" s="5" t="inlineStr"/>
+      <c r="N643" s="5" t="inlineStr"/>
+      <c r="O643" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P643" s="5" t="inlineStr"/>
+      <c r="Q643" s="5" t="inlineStr"/>
+      <c r="R643" s="5" t="inlineStr"/>
+      <c r="S643" s="5" t="inlineStr"/>
+      <c r="T643" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e vídeos; Bônus exclusivo; Aproveite na sua franquia; WhatsApp e ligações ilimitadas</t>
+        </is>
+      </c>
+      <c r="U643" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="V643" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B644" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C644" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D644" s="2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E644" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F644" s="2" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G644" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb</t>
+        </is>
+      </c>
+      <c r="H644" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I644" s="3" t="inlineStr"/>
+      <c r="J644" s="2" t="inlineStr"/>
+      <c r="K644" s="2" t="inlineStr"/>
+      <c r="L644" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="M644" s="2" t="inlineStr"/>
+      <c r="N644" s="2" t="inlineStr"/>
+      <c r="O644" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P644" s="2" t="inlineStr"/>
+      <c r="Q644" s="2" t="inlineStr"/>
+      <c r="R644" s="2" t="inlineStr"/>
+      <c r="S644" s="2" t="inlineStr"/>
+      <c r="T644" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="U644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="V644" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B645" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C645" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D645" s="5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E645" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F645" s="5" t="inlineStr">
+        <is>
+          <t>Controle 30GB</t>
+        </is>
+      </c>
+      <c r="G645" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-controle-30gb-gaming</t>
+        </is>
+      </c>
+      <c r="H645" s="6" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I645" s="6" t="inlineStr"/>
+      <c r="J645" s="5" t="inlineStr"/>
+      <c r="K645" s="5" t="inlineStr"/>
+      <c r="L645" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="M645" s="5" t="inlineStr"/>
+      <c r="N645" s="5" t="inlineStr"/>
+      <c r="O645" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P645" s="5" t="inlineStr"/>
+      <c r="Q645" s="5" t="inlineStr"/>
+      <c r="R645" s="5" t="inlineStr"/>
+      <c r="S645" s="5" t="inlineStr"/>
+      <c r="T645" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus para redes sociais e apps; Bônus uso livre; Redes sociais e apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="U645" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/controle</t>
+        </is>
+      </c>
+      <c r="V645" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_control_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B646" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C646" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D646" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E646" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F646" s="2" t="inlineStr">
+        <is>
+          <t>Flex 15GB</t>
+        </is>
+      </c>
+      <c r="G646" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-15gb</t>
+        </is>
+      </c>
+      <c r="H646" s="3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I646" s="3" t="inlineStr"/>
+      <c r="J646" s="2" t="inlineStr"/>
+      <c r="K646" s="2" t="inlineStr"/>
+      <c r="L646" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M646" s="2" t="inlineStr"/>
+      <c r="N646" s="2" t="inlineStr"/>
+      <c r="O646" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P646" s="2" t="inlineStr"/>
+      <c r="Q646" s="2" t="inlineStr"/>
+      <c r="R646" s="2" t="inlineStr"/>
+      <c r="S646" s="2" t="inlineStr"/>
+      <c r="T646" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="U646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="V646" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B647" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C647" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D647" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E647" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F647" s="5" t="inlineStr">
+        <is>
+          <t>Flex 20GB</t>
+        </is>
+      </c>
+      <c r="G647" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-20gb</t>
+        </is>
+      </c>
+      <c r="H647" s="6" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I647" s="6" t="inlineStr"/>
+      <c r="J647" s="5" t="inlineStr"/>
+      <c r="K647" s="5" t="inlineStr"/>
+      <c r="L647" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="M647" s="5" t="inlineStr"/>
+      <c r="N647" s="5" t="inlineStr"/>
+      <c r="O647" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P647" s="5" t="inlineStr"/>
+      <c r="Q647" s="5" t="inlineStr"/>
+      <c r="R647" s="5" t="inlineStr"/>
+      <c r="S647" s="5" t="inlineStr"/>
+      <c r="T647" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
+        </is>
+      </c>
+      <c r="U647" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="V647" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B648" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C648" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D648" s="2" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E648" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F648" s="2" t="inlineStr">
+        <is>
+          <t>Flex 30GB</t>
+        </is>
+      </c>
+      <c r="G648" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-30gb</t>
+        </is>
+      </c>
+      <c r="H648" s="3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I648" s="3" t="inlineStr"/>
+      <c r="J648" s="2" t="inlineStr"/>
+      <c r="K648" s="2" t="inlineStr"/>
+      <c r="L648" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="M648" s="2" t="inlineStr"/>
+      <c r="N648" s="2" t="inlineStr"/>
+      <c r="O648" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P648" s="2" t="inlineStr"/>
+      <c r="Q648" s="2" t="inlineStr"/>
+      <c r="R648" s="2" t="inlineStr"/>
+      <c r="S648" s="2" t="inlineStr"/>
+      <c r="T648" s="2" t="inlineStr">
+        <is>
+          <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="U648" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="V648" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B649" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C649" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D649" s="5" t="inlineStr">
+        <is>
+          <t>flex</t>
+        </is>
+      </c>
+      <c r="E649" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F649" s="5" t="inlineStr">
+        <is>
+          <t>Flex 40GB</t>
+        </is>
+      </c>
+      <c r="G649" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-flex-40gb</t>
+        </is>
+      </c>
+      <c r="H649" s="6" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="I649" s="6" t="inlineStr"/>
+      <c r="J649" s="5" t="inlineStr"/>
+      <c r="K649" s="5" t="inlineStr"/>
+      <c r="L649" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="M649" s="5" t="inlineStr"/>
+      <c r="N649" s="5" t="inlineStr"/>
+      <c r="O649" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P649" s="5" t="inlineStr"/>
+      <c r="Q649" s="5" t="inlineStr"/>
+      <c r="R649" s="5" t="inlineStr"/>
+      <c r="S649" s="5" t="inlineStr"/>
+      <c r="T649" s="5" t="inlineStr">
+        <is>
+          <t>Para uso livre; Para redes sociais e apps; Bônus uso livre; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
+        </is>
+      </c>
+      <c r="U649" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/flex</t>
+        </is>
+      </c>
+      <c r="V649" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_flex_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B650" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C650" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D650" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E650" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F650" s="2" t="inlineStr">
+        <is>
+          <t>Pós 100GB</t>
+        </is>
+      </c>
+      <c r="G650" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-100gb</t>
+        </is>
+      </c>
+      <c r="H650" s="3" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="I650" s="3" t="inlineStr"/>
+      <c r="J650" s="2" t="inlineStr"/>
+      <c r="K650" s="2" t="inlineStr"/>
+      <c r="L650" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M650" s="2" t="inlineStr"/>
+      <c r="N650" s="2" t="inlineStr"/>
+      <c r="O650" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P650" s="2" t="inlineStr"/>
+      <c r="Q650" s="2" t="inlineStr"/>
+      <c r="R650" s="2" t="inlineStr"/>
+      <c r="S650" s="2" t="inlineStr"/>
+      <c r="T650" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="U650" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V650" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B651" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C651" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D651" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E651" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F651" s="5" t="inlineStr">
+        <is>
+          <t>Pós 150GB</t>
+        </is>
+      </c>
+      <c r="G651" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-150gb</t>
+        </is>
+      </c>
+      <c r="H651" s="6" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="I651" s="6" t="inlineStr"/>
+      <c r="J651" s="5" t="inlineStr"/>
+      <c r="K651" s="5" t="inlineStr"/>
+      <c r="L651" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="M651" s="5" t="inlineStr"/>
+      <c r="N651" s="5" t="inlineStr"/>
+      <c r="O651" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P651" s="5" t="inlineStr"/>
+      <c r="Q651" s="5" t="inlineStr"/>
+      <c r="R651" s="5" t="inlineStr"/>
+      <c r="S651" s="5" t="inlineStr"/>
+      <c r="T651" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas e Europa; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="U651" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V651" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B652" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C652" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D652" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E652" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F652" s="2" t="inlineStr">
+        <is>
+          <t>Pós 200GB</t>
+        </is>
+      </c>
+      <c r="G652" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-200gb</t>
+        </is>
+      </c>
+      <c r="H652" s="3" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="I652" s="3" t="inlineStr"/>
+      <c r="J652" s="2" t="inlineStr"/>
+      <c r="K652" s="2" t="inlineStr"/>
+      <c r="L652" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="M652" s="2" t="inlineStr"/>
+      <c r="N652" s="2" t="inlineStr"/>
+      <c r="O652" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P652" s="2" t="inlineStr"/>
+      <c r="Q652" s="2" t="inlineStr"/>
+      <c r="R652" s="2" t="inlineStr"/>
+      <c r="S652" s="2" t="inlineStr"/>
+      <c r="T652" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="U652" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V652" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B653" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C653" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D653" s="5" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E653" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F653" s="5" t="inlineStr">
+        <is>
+          <t>Pós 50GB com GeForce NOW</t>
+        </is>
+      </c>
+      <c r="G653" s="5" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb-geforce</t>
+        </is>
+      </c>
+      <c r="H653" s="6" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="I653" s="6" t="inlineStr"/>
+      <c r="J653" s="5" t="inlineStr"/>
+      <c r="K653" s="5" t="inlineStr"/>
+      <c r="L653" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="M653" s="5" t="inlineStr"/>
+      <c r="N653" s="5" t="inlineStr"/>
+      <c r="O653" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P653" s="5" t="inlineStr"/>
+      <c r="Q653" s="5" t="inlineStr"/>
+      <c r="R653" s="5" t="inlineStr"/>
+      <c r="S653" s="5" t="inlineStr"/>
+      <c r="T653" s="5" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado; Inclusa assinatura GeForce NOW</t>
+        </is>
+      </c>
+      <c r="U653" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V653" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B654" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C654" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D654" s="2" t="inlineStr">
+        <is>
+          <t>postpaid</t>
+        </is>
+      </c>
+      <c r="E654" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F654" s="2" t="inlineStr">
+        <is>
+          <t>Pós 60GB</t>
+        </is>
+      </c>
+      <c r="G654" s="2" t="inlineStr">
+        <is>
+          <t>claro:plano-pos-60gb</t>
+        </is>
+      </c>
+      <c r="H654" s="3" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="I654" s="3" t="inlineStr"/>
+      <c r="J654" s="2" t="inlineStr"/>
+      <c r="K654" s="2" t="inlineStr"/>
+      <c r="L654" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M654" s="2" t="inlineStr"/>
+      <c r="N654" s="2" t="inlineStr"/>
+      <c r="O654" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="P654" s="2" t="inlineStr"/>
+      <c r="Q654" s="2" t="inlineStr"/>
+      <c r="R654" s="2" t="inlineStr"/>
+      <c r="S654" s="2" t="inlineStr"/>
+      <c r="T654" s="2" t="inlineStr">
+        <is>
+          <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
+        </is>
+      </c>
+      <c r="U654" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/pos</t>
+        </is>
+      </c>
+      <c r="V654" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_postpaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B655" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C655" s="5" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D655" s="5" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E655" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F655" s="5" t="inlineStr">
+        <is>
+          <t>Prezão 10GB (25 dias)</t>
+        </is>
+      </c>
+      <c r="G655" s="5" t="inlineStr">
+        <is>
+          <t>claro:prezao-25d-10gb</t>
+        </is>
+      </c>
+      <c r="H655" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I655" s="6" t="inlineStr"/>
+      <c r="J655" s="5" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$25 — validade 25 dias</t>
+        </is>
+      </c>
+      <c r="K655" s="5" t="inlineStr"/>
+      <c r="L655" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M655" s="5" t="inlineStr"/>
+      <c r="N655" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="O655" s="5" t="inlineStr"/>
+      <c r="P655" s="5" t="inlineStr"/>
+      <c r="Q655" s="5" t="inlineStr"/>
+      <c r="R655" s="5" t="inlineStr"/>
+      <c r="S655" s="5" t="inlineStr"/>
+      <c r="T655" s="5" t="inlineStr"/>
+      <c r="U655" s="5" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V655" s="5" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B656" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C656" s="2" t="inlineStr">
+        <is>
+          <t>claro</t>
+        </is>
+      </c>
+      <c r="D656" s="2" t="inlineStr">
+        <is>
+          <t>prepaid</t>
+        </is>
+      </c>
+      <c r="E656" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F656" s="2" t="inlineStr">
+        <is>
+          <t>Prezão 12GB (30 dias)</t>
+        </is>
+      </c>
+      <c r="G656" s="2" t="inlineStr">
+        <is>
+          <t>claro:prezao-30d-12gb</t>
+        </is>
+      </c>
+      <c r="H656" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I656" s="3" t="inlineStr"/>
+      <c r="J656" s="2" t="inlineStr">
+        <is>
+          <t>recarga Prezão R$30 — validade 30 dias</t>
+        </is>
+      </c>
+      <c r="K656" s="2" t="inlineStr"/>
+      <c r="L656" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M656" s="2" t="inlineStr"/>
+      <c r="N656" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O656" s="2" t="inlineStr"/>
+      <c r="P656" s="2" t="inlineStr"/>
+      <c r="Q656" s="2" t="inlineStr"/>
+      <c r="R656" s="2" t="inlineStr"/>
+      <c r="S656" s="2" t="inlineStr"/>
+      <c r="T656" s="2" t="inlineStr"/>
+      <c r="U656" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claro.com.br/celular/planos-pre/prezao</t>
+        </is>
+      </c>
+      <c r="V656" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/claro_prepaid_SP.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B657" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-04T21:56:26</t>
+        </is>
+      </c>
+      <c r="C657" s="5" t="inlineStr"